--- a/data/DNR.MI.xlsx
+++ b/data/DNR.MI.xlsx
@@ -24729,6 +24729,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1060">
+      <c r="A1060" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1060" t="n">
+        <v>211005</v>
+      </c>
+      <c r="C1060" t="n">
+        <v>6.53499984741211</v>
+      </c>
+      <c r="D1060" t="n">
+        <v>6.31500005722046</v>
+      </c>
+      <c r="E1060" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F1060" t="n">
+        <v>6.42500019073486</v>
+      </c>
+      <c r="G1060" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DNR.MI.xlsx
+++ b/data/DNR.MI.xlsx
@@ -24752,6 +24752,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1061">
+      <c r="A1061" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1061" t="n">
+        <v>101951</v>
+      </c>
+      <c r="C1061" t="n">
+        <v>6.4850001335144</v>
+      </c>
+      <c r="D1061" t="n">
+        <v>6.375</v>
+      </c>
+      <c r="E1061" t="n">
+        <v>6.44999980926514</v>
+      </c>
+      <c r="F1061" t="n">
+        <v>6.46000003814697</v>
+      </c>
+      <c r="G1061" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DNR.MI.xlsx
+++ b/data/DNR.MI.xlsx
@@ -24775,6 +24775,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1062">
+      <c r="A1062" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1062" t="n">
+        <v>168137</v>
+      </c>
+      <c r="C1062" t="n">
+        <v>6.65999984741211</v>
+      </c>
+      <c r="D1062" t="n">
+        <v>6.40000009536743</v>
+      </c>
+      <c r="E1062" t="n">
+        <v>6.40000009536743</v>
+      </c>
+      <c r="F1062" t="n">
+        <v>6.67500019073486</v>
+      </c>
+      <c r="G1062" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DNR.MI.xlsx
+++ b/data/DNR.MI.xlsx
@@ -24783,7 +24783,7 @@
         <v>168137</v>
       </c>
       <c r="C1062" t="n">
-        <v>6.65999984741211</v>
+        <v>6.67500019073486</v>
       </c>
       <c r="D1062" t="n">
         <v>6.40000009536743</v>
@@ -24795,6 +24795,29 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G1062" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1063" t="n">
+        <v>298661</v>
+      </c>
+      <c r="C1063" t="n">
+        <v>7</v>
+      </c>
+      <c r="D1063" t="n">
+        <v>6.65000009536743</v>
+      </c>
+      <c r="E1063" t="n">
+        <v>6.67999982833862</v>
+      </c>
+      <c r="F1063" t="n">
+        <v>7.07000017166138</v>
+      </c>
+      <c r="G1063" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DNR.MI.xlsx
+++ b/data/DNR.MI.xlsx
@@ -24639,22 +24639,22 @@
     </row>
     <row r="1056">
       <c r="A1056" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1056" t="n">
-        <v>146447</v>
+        <v>119830</v>
       </c>
       <c r="C1056" t="n">
-        <v>6.96999979019165</v>
+        <v>6.94999980926514</v>
       </c>
       <c r="D1056" t="n">
-        <v>6.80999994277954</v>
+        <v>6.82999992370605</v>
       </c>
       <c r="E1056" t="n">
-        <v>6.94999980926514</v>
+        <v>6.90000009536743</v>
       </c>
       <c r="F1056" t="n">
-        <v>6.94500017166138</v>
+        <v>6.88000011444092</v>
       </c>
       <c r="G1056" t="s">
         <v>7</v>
@@ -24662,22 +24662,22 @@
     </row>
     <row r="1057">
       <c r="A1057" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1057" t="n">
-        <v>133432</v>
+        <v>146447</v>
       </c>
       <c r="C1057" t="n">
-        <v>6.94000005722046</v>
+        <v>6.96999979019165</v>
       </c>
       <c r="D1057" t="n">
-        <v>6.67000007629395</v>
+        <v>6.80999994277954</v>
       </c>
       <c r="E1057" t="n">
-        <v>6.92999982833862</v>
+        <v>6.94999980926514</v>
       </c>
       <c r="F1057" t="n">
-        <v>6.67500019073486</v>
+        <v>6.94500017166138</v>
       </c>
       <c r="G1057" t="s">
         <v>7</v>
@@ -24685,22 +24685,22 @@
     </row>
     <row r="1058">
       <c r="A1058" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1058" t="n">
-        <v>121563</v>
+        <v>133432</v>
       </c>
       <c r="C1058" t="n">
-        <v>6.71500015258789</v>
+        <v>6.94000005722046</v>
       </c>
       <c r="D1058" t="n">
-        <v>6.45499992370605</v>
+        <v>6.67000007629395</v>
       </c>
       <c r="E1058" t="n">
-        <v>6.71000003814697</v>
+        <v>6.92999982833862</v>
       </c>
       <c r="F1058" t="n">
-        <v>6.45499992370605</v>
+        <v>6.67500019073486</v>
       </c>
       <c r="G1058" t="s">
         <v>7</v>
@@ -24708,22 +24708,22 @@
     </row>
     <row r="1059">
       <c r="A1059" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1059" t="n">
-        <v>81715</v>
+        <v>121563</v>
       </c>
       <c r="C1059" t="n">
-        <v>6.57999992370605</v>
+        <v>6.71500015258789</v>
       </c>
       <c r="D1059" t="n">
-        <v>6.48000001907349</v>
+        <v>6.45499992370605</v>
       </c>
       <c r="E1059" t="n">
-        <v>6.5</v>
+        <v>6.71000003814697</v>
       </c>
       <c r="F1059" t="n">
-        <v>6.55000019073486</v>
+        <v>6.45499992370605</v>
       </c>
       <c r="G1059" t="s">
         <v>7</v>
@@ -24731,22 +24731,22 @@
     </row>
     <row r="1060">
       <c r="A1060" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1060" t="n">
-        <v>211005</v>
+        <v>81715</v>
       </c>
       <c r="C1060" t="n">
-        <v>6.53499984741211</v>
+        <v>6.57999992370605</v>
       </c>
       <c r="D1060" t="n">
-        <v>6.31500005722046</v>
+        <v>6.48000001907349</v>
       </c>
       <c r="E1060" t="n">
         <v>6.5</v>
       </c>
       <c r="F1060" t="n">
-        <v>6.42500019073486</v>
+        <v>6.55000019073486</v>
       </c>
       <c r="G1060" t="s">
         <v>7</v>
@@ -24754,22 +24754,22 @@
     </row>
     <row r="1061">
       <c r="A1061" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1061" t="n">
-        <v>101951</v>
+        <v>211005</v>
       </c>
       <c r="C1061" t="n">
-        <v>6.4850001335144</v>
+        <v>6.53499984741211</v>
       </c>
       <c r="D1061" t="n">
-        <v>6.375</v>
+        <v>6.31500005722046</v>
       </c>
       <c r="E1061" t="n">
-        <v>6.44999980926514</v>
+        <v>6.5</v>
       </c>
       <c r="F1061" t="n">
-        <v>6.46000003814697</v>
+        <v>6.42500019073486</v>
       </c>
       <c r="G1061" t="s">
         <v>7</v>
@@ -24777,22 +24777,22 @@
     </row>
     <row r="1062">
       <c r="A1062" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1062" t="n">
-        <v>168137</v>
+        <v>101951</v>
       </c>
       <c r="C1062" t="n">
-        <v>6.67500019073486</v>
+        <v>6.4850001335144</v>
       </c>
       <c r="D1062" t="n">
-        <v>6.40000009536743</v>
+        <v>6.375</v>
       </c>
       <c r="E1062" t="n">
-        <v>6.40000009536743</v>
+        <v>6.44999980926514</v>
       </c>
       <c r="F1062" t="n">
-        <v>6.67500019073486</v>
+        <v>6.46000003814697</v>
       </c>
       <c r="G1062" t="s">
         <v>7</v>
@@ -24800,24 +24800,47 @@
     </row>
     <row r="1063">
       <c r="A1063" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1063" t="n">
-        <v>298661</v>
+        <v>168137</v>
       </c>
       <c r="C1063" t="n">
-        <v>7</v>
+        <v>6.67500019073486</v>
       </c>
       <c r="D1063" t="n">
-        <v>6.65000009536743</v>
+        <v>6.40000009536743</v>
       </c>
       <c r="E1063" t="n">
-        <v>6.67999982833862</v>
+        <v>6.40000009536743</v>
       </c>
       <c r="F1063" t="n">
-        <v>7.07000017166138</v>
+        <v>6.67500019073486</v>
       </c>
       <c r="G1063" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1064" t="n">
+        <v>716821</v>
+      </c>
+      <c r="C1064" t="n">
+        <v>7.51999998092651</v>
+      </c>
+      <c r="D1064" t="n">
+        <v>7.08500003814697</v>
+      </c>
+      <c r="E1064" t="n">
+        <v>7.19999980926514</v>
+      </c>
+      <c r="F1064" t="n">
+        <v>7.08500003814697</v>
+      </c>
+      <c r="G1064" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DNR.MI.xlsx
+++ b/data/DNR.MI.xlsx
@@ -629,7 +629,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G10" t="n">
-        <v>12.5173177719116</v>
+        <v>12.5173168182373</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>12.5173177719116</v>
+        <v>12.5173168182373</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G12" t="n">
-        <v>12.4504299163818</v>
+        <v>12.4504308700562</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G15" t="n">
-        <v>13.0046329498291</v>
+        <v>13.0046319961548</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G20" t="n">
-        <v>13.8072690963745</v>
+        <v>13.8072700500488</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G22" t="n">
-        <v>14.065260887146</v>
+        <v>14.0652599334717</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G25" t="n">
-        <v>13.9410429000854</v>
+        <v>13.9410438537598</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G27" t="n">
-        <v>14.1990327835083</v>
+        <v>14.199031829834</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G29" t="n">
-        <v>13.826379776001</v>
+        <v>13.8263807296753</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>15.1927738189697</v>
+        <v>15.192774772644</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G44" t="n">
-        <v>16.1387386322021</v>
+        <v>16.1387405395508</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>15.5749816894531</v>
+        <v>15.5749826431274</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G46" t="n">
-        <v>15.4507646560669</v>
+        <v>15.4507656097412</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G50" t="n">
-        <v>15.2309951782227</v>
+        <v>15.2309942245483</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G54" t="n">
-        <v>14.0079288482666</v>
+        <v>14.0079278945923</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G57" t="n">
-        <v>14.7436809539795</v>
+        <v>14.7436800003052</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>15.75</v>
       </c>
       <c r="G59" t="n">
-        <v>15.049446105957</v>
+        <v>15.0494451522827</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G61" t="n">
-        <v>15.5558710098267</v>
+        <v>15.5558729171753</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G62" t="n">
-        <v>15.2309951782227</v>
+        <v>15.2309942245483</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G63" t="n">
-        <v>15.1736631393433</v>
+        <v>15.1736640930176</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G67" t="n">
-        <v>15.2309951782227</v>
+        <v>15.2309942245483</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G69" t="n">
-        <v>15.3552112579346</v>
+        <v>15.3552122116089</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G70" t="n">
-        <v>15.3360996246338</v>
+        <v>15.3361005783081</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G72" t="n">
-        <v>14.6003503799438</v>
+        <v>14.6003513336182</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G73" t="n">
-        <v>14.3519172668457</v>
+        <v>14.3519163131714</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>15.5</v>
       </c>
       <c r="G77" t="n">
-        <v>14.8105659484863</v>
+        <v>14.8105669021606</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G78" t="n">
-        <v>14.065260887146</v>
+        <v>14.0652599334717</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G85" t="n">
-        <v>12.9377450942993</v>
+        <v>12.9377460479736</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G86" t="n">
-        <v>13.0046329498291</v>
+        <v>13.0046319961548</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G87" t="n">
-        <v>13.6448307037354</v>
+        <v>13.6448316574097</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G88" t="n">
-        <v>14.6003503799438</v>
+        <v>14.6003513336182</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>15.5699996948242</v>
       </c>
       <c r="G90" t="n">
-        <v>14.8774518966675</v>
+        <v>14.8774509429932</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>15.5</v>
       </c>
       <c r="G91" t="n">
-        <v>14.8105659484863</v>
+        <v>14.8105669021606</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G93" t="n">
-        <v>14.6767921447754</v>
+        <v>14.6767930984497</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G94" t="n">
-        <v>14.6003503799438</v>
+        <v>14.6003513336182</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G95" t="n">
-        <v>14.1990327835083</v>
+        <v>14.199031829834</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>14.6194610595703</v>
+        <v>14.6194620132446</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G99" t="n">
-        <v>14.9347839355469</v>
+        <v>14.9347829818726</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G100" t="n">
-        <v>14.9347839355469</v>
+        <v>14.9347829818726</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G107" t="n">
-        <v>14.6576824188232</v>
+        <v>14.6576833724976</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G113" t="n">
-        <v>14.7914543151855</v>
+        <v>14.7914552688599</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>14.5</v>
       </c>
       <c r="G119" t="n">
-        <v>13.8550462722778</v>
+        <v>13.8550453186035</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>14.25</v>
       </c>
       <c r="G121" t="n">
-        <v>13.6161642074585</v>
+        <v>13.6161651611328</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>14.5</v>
       </c>
       <c r="G124" t="n">
-        <v>13.8550462722778</v>
+        <v>13.8550453186035</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G130" t="n">
-        <v>15.0398902893066</v>
+        <v>15.0398893356323</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G132" t="n">
-        <v>15.1258878707886</v>
+        <v>15.1258869171143</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>15.75</v>
       </c>
       <c r="G133" t="n">
-        <v>15.049446105957</v>
+        <v>15.0494451522827</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G137" t="n">
-        <v>15.1736631393433</v>
+        <v>15.1736640930176</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>16.5</v>
       </c>
       <c r="G138" t="n">
-        <v>15.7660865783691</v>
+        <v>15.7660856246948</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G139" t="n">
-        <v>16.3011779785156</v>
+        <v>16.3011798858643</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G141" t="n">
-        <v>16.2534027099609</v>
+        <v>16.2534008026123</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G146" t="n">
-        <v>16.769380569458</v>
+        <v>16.7693824768066</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>16.6100006103516</v>
       </c>
       <c r="G149" t="n">
-        <v>15.8711948394775</v>
+        <v>15.8711929321289</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G156" t="n">
-        <v>17.6962375640869</v>
+        <v>17.6962356567383</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G161" t="n">
-        <v>17.4477996826172</v>
+        <v>17.4478015899658</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G163" t="n">
-        <v>17.2089233398438</v>
+        <v>17.2089214324951</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>19.5</v>
       </c>
       <c r="G169" t="n">
-        <v>18.6326465606689</v>
+        <v>18.6326484680176</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G173" t="n">
-        <v>18.508430480957</v>
+        <v>18.5084323883057</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>18.7700004577637</v>
       </c>
       <c r="G174" t="n">
-        <v>17.935115814209</v>
+        <v>17.9351177215576</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G179" t="n">
-        <v>18.8524169921875</v>
+        <v>18.8524188995361</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G184" t="n">
-        <v>17.189811706543</v>
+        <v>17.1898097991943</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G188" t="n">
-        <v>17.658016204834</v>
+        <v>17.6580181121826</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G189" t="n">
-        <v>17.658016204834</v>
+        <v>17.6580181121826</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G192" t="n">
-        <v>16.5305023193359</v>
+        <v>16.5305004119873</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>16.3871746063232</v>
+        <v>16.3871765136719</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G195" t="n">
-        <v>16.3011779785156</v>
+        <v>16.3011798858643</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G197" t="n">
-        <v>16.3489532470703</v>
+        <v>16.3489551544189</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G198" t="n">
-        <v>16.3011779785156</v>
+        <v>16.3011798858643</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>16.6260528564453</v>
+        <v>16.6260547637939</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G203" t="n">
-        <v>16.7407188415527</v>
+        <v>16.7407169342041</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G204" t="n">
-        <v>16.7884922027588</v>
+        <v>16.7884941101074</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G212" t="n">
-        <v>17.2184772491455</v>
+        <v>17.2184791564941</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G216" t="n">
-        <v>17.6293525695801</v>
+        <v>17.6293506622314</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G222" t="n">
-        <v>18.5789909362793</v>
+        <v>18.5789890289307</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>19.1367454528809</v>
+        <v>19.1367473602295</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G240" t="n">
-        <v>19.4637031555176</v>
+        <v>19.4637050628662</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G245" t="n">
-        <v>17.6077270507812</v>
+        <v>17.6077289581299</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G246" t="n">
-        <v>17.8481407165527</v>
+        <v>17.8481388092041</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G248" t="n">
-        <v>18.5789909362793</v>
+        <v>18.5789890289307</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G249" t="n">
-        <v>18.4924430847168</v>
+        <v>18.4924411773682</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G250" t="n">
-        <v>18.4924430847168</v>
+        <v>18.4924411773682</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G251" t="n">
-        <v>18.434741973877</v>
+        <v>18.4347438812256</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>19.5</v>
       </c>
       <c r="G252" t="n">
-        <v>18.7520866394043</v>
+        <v>18.7520885467529</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G254" t="n">
-        <v>18.3866634368896</v>
+        <v>18.386661529541</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G255" t="n">
-        <v>19.4637031555176</v>
+        <v>19.4637050628662</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G256" t="n">
-        <v>19.4637031555176</v>
+        <v>19.4637050628662</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G257" t="n">
-        <v>19.6944980621338</v>
+        <v>19.6944999694824</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G258" t="n">
-        <v>20.1368579864502</v>
+        <v>20.1368560791016</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G260" t="n">
-        <v>19.5598697662354</v>
+        <v>19.5598678588867</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G262" t="n">
-        <v>19.3098392486572</v>
+        <v>19.3098411560059</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>18.7700004577637</v>
       </c>
       <c r="G271" t="n">
-        <v>18.050085067749</v>
+        <v>18.0500869750977</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G274" t="n">
-        <v>17.5115642547607</v>
+        <v>17.5115623474121</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G276" t="n">
-        <v>18.5020599365234</v>
+        <v>18.5020580291748</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G278" t="n">
-        <v>18.6270732879639</v>
+        <v>18.6270751953125</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G295" t="n">
-        <v>17.1749877929688</v>
+        <v>17.1749897003174</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G296" t="n">
-        <v>17.2807693481445</v>
+        <v>17.2807712554932</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G301" t="n">
-        <v>16.4441394805908</v>
+        <v>16.4441375732422</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>17</v>
       </c>
       <c r="G302" t="n">
-        <v>16.347972869873</v>
+        <v>16.3479747772217</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G305" t="n">
-        <v>16.3575916290283</v>
+        <v>16.3575897216797</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G314" t="n">
-        <v>15.6555881500244</v>
+        <v>15.655590057373</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>16.2700004577637</v>
       </c>
       <c r="G316" t="n">
-        <v>15.6459732055664</v>
+        <v>15.6459722518921</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G318" t="n">
-        <v>14.4150657653809</v>
+        <v>14.4150667190552</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>15.0299997329712</v>
       </c>
       <c r="G319" t="n">
-        <v>14.4535322189331</v>
+        <v>14.4535312652588</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G321" t="n">
-        <v>14.4631490707397</v>
+        <v>14.4631481170654</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G327" t="n">
-        <v>14.0881052017212</v>
+        <v>14.0881061553955</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G328" t="n">
-        <v>14.2227363586426</v>
+        <v>14.2227373123169</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G333" t="n">
-        <v>12.8571996688843</v>
+        <v>12.8572006225586</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G341" t="n">
-        <v>13.2803249359131</v>
+        <v>13.2803239822388</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>14.0100002288818</v>
       </c>
       <c r="G343" t="n">
-        <v>13.4726543426514</v>
+        <v>13.4726533889771</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G344" t="n">
-        <v>13.0399131774902</v>
+        <v>13.0399141311646</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G348" t="n">
-        <v>14.2227363586426</v>
+        <v>14.2227373123169</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G349" t="n">
-        <v>14.5785446166992</v>
+        <v>14.5785455703735</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G350" t="n">
-        <v>14.2708196640015</v>
+        <v>14.2708187103271</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G355" t="n">
-        <v>13.6842155456543</v>
+        <v>13.68421459198</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G356" t="n">
-        <v>13.7322969436646</v>
+        <v>13.7322978973389</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>14.3900003433228</v>
       </c>
       <c r="G358" t="n">
-        <v>13.8380784988403</v>
+        <v>13.8380794525146</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G359" t="n">
-        <v>13.6649827957153</v>
+        <v>13.664981842041</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G361" t="n">
-        <v>13.5399684906006</v>
+        <v>13.5399694442749</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G368" t="n">
-        <v>14.7131757736206</v>
+        <v>14.7131767272949</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G371" t="n">
-        <v>15.6844387054443</v>
+        <v>15.68443775177</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G375" t="n">
-        <v>14.8381910324097</v>
+        <v>14.8381900787354</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G376" t="n">
-        <v>15.0305194854736</v>
+        <v>15.0305185317993</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G381" t="n">
-        <v>14.8862714767456</v>
+        <v>14.8862724304199</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G385" t="n">
-        <v>14.4439163208008</v>
+        <v>14.4439153671265</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G386" t="n">
-        <v>14.0977230072021</v>
+        <v>14.0977220535278</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>14.7700004577637</v>
       </c>
       <c r="G389" t="n">
-        <v>14.2035036087036</v>
+        <v>14.2035045623779</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G390" t="n">
-        <v>14.4631490707397</v>
+        <v>14.4631481170654</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>14.2700004577637</v>
       </c>
       <c r="G391" t="n">
-        <v>13.7226810455322</v>
+        <v>13.7226819992065</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>14.5</v>
       </c>
       <c r="G392" t="n">
-        <v>13.9438600540161</v>
+        <v>13.9438591003418</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G394" t="n">
-        <v>13.7419137954712</v>
+        <v>13.7419147491455</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>14.25</v>
       </c>
       <c r="G396" t="n">
-        <v>13.7034473419189</v>
+        <v>13.7034482955933</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G397" t="n">
-        <v>13.6649827957153</v>
+        <v>13.664981842041</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G405" t="n">
-        <v>13.5880517959595</v>
+        <v>13.5880508422852</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G415" t="n">
-        <v>14.8862714767456</v>
+        <v>14.8862724304199</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G416" t="n">
-        <v>14.7516412734985</v>
+        <v>14.7516422271729</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G418" t="n">
-        <v>14.6458606719971</v>
+        <v>14.6458597183228</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G425" t="n">
-        <v>14.1554222106934</v>
+        <v>14.155421257019</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G427" t="n">
-        <v>13.6649827957153</v>
+        <v>13.664981842041</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G428" t="n">
-        <v>13.8188447952271</v>
+        <v>13.8188457489014</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>14.25</v>
       </c>
       <c r="G430" t="n">
-        <v>13.7034473419189</v>
+        <v>13.7034482955933</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G439" t="n">
-        <v>12.8571996688843</v>
+        <v>12.8572006225586</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G442" t="n">
-        <v>12.9725980758667</v>
+        <v>12.9725971221924</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G444" t="n">
-        <v>12.472541809082</v>
+        <v>12.4725427627563</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G445" t="n">
-        <v>12.7802686691284</v>
+        <v>12.7802677154541</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G449" t="n">
-        <v>12.809118270874</v>
+        <v>12.8091173171997</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G451" t="n">
-        <v>12.9629802703857</v>
+        <v>12.9629812240601</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G454" t="n">
-        <v>11.6839933395386</v>
+        <v>11.6839923858643</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G457" t="n">
-        <v>11.9724855422974</v>
+        <v>11.9724864959717</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G460" t="n">
-        <v>12.1744318008423</v>
+        <v>12.1744327545166</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G462" t="n">
-        <v>12.1455821990967</v>
+        <v>12.145583152771</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G464" t="n">
-        <v>11.9724855422974</v>
+        <v>11.9724864959717</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G465" t="n">
-        <v>12.8668165206909</v>
+        <v>12.8668174743652</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G470" t="n">
-        <v>13.3476390838623</v>
+        <v>13.3476400375366</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -28088,6 +28088,32 @@
         <v>7.39499998092651</v>
       </c>
       <c r="H1066" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1067" t="n">
+        <v>4575930</v>
+      </c>
+      <c r="C1067" t="n">
+        <v>6.82000017166138</v>
+      </c>
+      <c r="D1067" t="n">
+        <v>6.02500009536743</v>
+      </c>
+      <c r="E1067" t="n">
+        <v>6.78000020980835</v>
+      </c>
+      <c r="F1067" t="n">
+        <v>6.05999994277954</v>
+      </c>
+      <c r="G1067" t="n">
+        <v>6.05999994277954</v>
+      </c>
+      <c r="H1067" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DNR.MI.xlsx
+++ b/data/DNR.MI.xlsx
@@ -447,7 +447,7 @@
         <v>13.25</v>
       </c>
       <c r="G3" t="n">
-        <v>12.66064453125</v>
+        <v>12.6606454849243</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>12.6128692626953</v>
+        <v>12.612868309021</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G10" t="n">
-        <v>12.5173168182373</v>
+        <v>12.5173177719116</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>12.5173168182373</v>
+        <v>12.5173177719116</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G12" t="n">
-        <v>12.4504308700562</v>
+        <v>12.4504299163818</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G16" t="n">
-        <v>13.415506362915</v>
+        <v>13.4155054092407</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G18" t="n">
-        <v>13.1575155258179</v>
+        <v>13.1575164794922</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G19" t="n">
-        <v>13.5683879852295</v>
+        <v>13.5683898925781</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G21" t="n">
-        <v>14.0748138427734</v>
+        <v>14.0748147964478</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G22" t="n">
-        <v>14.0652599334717</v>
+        <v>14.065260887146</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>14.1417026519775</v>
+        <v>14.1417016983032</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G25" t="n">
-        <v>13.9410438537598</v>
+        <v>13.9410429000854</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>14.75</v>
       </c>
       <c r="G28" t="n">
-        <v>14.0939254760742</v>
+        <v>14.0939264297485</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G29" t="n">
-        <v>13.8263807296753</v>
+        <v>13.826379776001</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G32" t="n">
-        <v>13.5683879852295</v>
+        <v>13.5683898925781</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G33" t="n">
-        <v>13.7403831481934</v>
+        <v>13.740382194519</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>14.3299999237061</v>
       </c>
       <c r="G39" t="n">
-        <v>13.69260597229</v>
+        <v>13.6926069259644</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G41" t="n">
-        <v>14.8870067596436</v>
+        <v>14.8870077133179</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>15.192774772644</v>
+        <v>15.1927738189697</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>15.3838777542114</v>
+        <v>15.3838787078857</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G44" t="n">
-        <v>16.1387405395508</v>
+        <v>16.1387386322021</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>15.5749826431274</v>
+        <v>15.5749807357788</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G46" t="n">
-        <v>15.4507656097412</v>
+        <v>15.4507646560669</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G49" t="n">
-        <v>15.6418695449829</v>
+        <v>15.6418685913086</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G50" t="n">
-        <v>15.2309942245483</v>
+        <v>15.230993270874</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>15.8900003433228</v>
       </c>
       <c r="G51" t="n">
-        <v>15.183219909668</v>
+        <v>15.1832189559937</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G53" t="n">
-        <v>14.2372541427612</v>
+        <v>14.2372531890869</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G54" t="n">
-        <v>14.0079278945923</v>
+        <v>14.0079288482666</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G57" t="n">
-        <v>14.7436800003052</v>
+        <v>14.7436809539795</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G58" t="n">
-        <v>14.4092473983765</v>
+        <v>14.4092464447021</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G60" t="n">
-        <v>15.4889841079712</v>
+        <v>15.4889850616455</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G61" t="n">
-        <v>15.5558729171753</v>
+        <v>15.5558710098267</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G62" t="n">
-        <v>15.2309942245483</v>
+        <v>15.230993270874</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G63" t="n">
-        <v>15.1736640930176</v>
+        <v>15.1736631393433</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G65" t="n">
-        <v>15.7469749450684</v>
+        <v>15.7469758987427</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G67" t="n">
-        <v>15.2309942245483</v>
+        <v>15.230993270874</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G69" t="n">
-        <v>15.3552122116089</v>
+        <v>15.3552131652832</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G74" t="n">
-        <v>14.3136959075928</v>
+        <v>14.3136949539185</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G75" t="n">
-        <v>14.1894779205322</v>
+        <v>14.1894788742065</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>15.5</v>
       </c>
       <c r="G77" t="n">
-        <v>14.8105669021606</v>
+        <v>14.8105659484863</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G78" t="n">
-        <v>14.0652599334717</v>
+        <v>14.065260887146</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G79" t="n">
-        <v>13.8646001815796</v>
+        <v>13.8646011352539</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="n">
-        <v>14.3328065872192</v>
+        <v>14.3328056335449</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G84" t="n">
-        <v>13.1670703887939</v>
+        <v>13.1670713424683</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G85" t="n">
-        <v>12.9377460479736</v>
+        <v>12.9377450942993</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G89" t="n">
-        <v>15.0303354263306</v>
+        <v>15.0303363800049</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>15.5699996948242</v>
       </c>
       <c r="G90" t="n">
-        <v>14.8774509429932</v>
+        <v>14.8774518966675</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>15.5</v>
       </c>
       <c r="G91" t="n">
-        <v>14.8105669021606</v>
+        <v>14.8105659484863</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G92" t="n">
-        <v>14.5621299743652</v>
+        <v>14.5621309280396</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G93" t="n">
-        <v>14.6767930984497</v>
+        <v>14.6767921447754</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>14.6194620132446</v>
+        <v>14.6194610595703</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G101" t="n">
-        <v>15.3265476226807</v>
+        <v>15.326548576355</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G109" t="n">
-        <v>14.8487873077393</v>
+        <v>14.8487863540649</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G110" t="n">
-        <v>15.0876665115356</v>
+        <v>15.0876655578613</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G111" t="n">
-        <v>14.9443387985229</v>
+        <v>14.9443397521973</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G112" t="n">
-        <v>14.6481275558472</v>
+        <v>14.6481266021729</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G113" t="n">
-        <v>14.7914552688599</v>
+        <v>14.7914543151855</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G114" t="n">
-        <v>14.7819013595581</v>
+        <v>14.7819004058838</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G117" t="n">
-        <v>14.4474678039551</v>
+        <v>14.4474687576294</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>14.5</v>
       </c>
       <c r="G119" t="n">
-        <v>13.8550453186035</v>
+        <v>13.8550462722778</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>14.5</v>
       </c>
       <c r="G124" t="n">
-        <v>13.8550453186035</v>
+        <v>13.8550462722778</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G125" t="n">
-        <v>14.4952440261841</v>
+        <v>14.4952430725098</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G128" t="n">
-        <v>14.8870067596436</v>
+        <v>14.8870077133179</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G130" t="n">
-        <v>15.0398893356323</v>
+        <v>15.0398902893066</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G131" t="n">
-        <v>15.0876665115356</v>
+        <v>15.0876655578613</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G132" t="n">
-        <v>15.1258869171143</v>
+        <v>15.1258878707886</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>14.953893661499</v>
+        <v>14.9538946151733</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G136" t="n">
-        <v>15.2692155838013</v>
+        <v>15.269214630127</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G137" t="n">
-        <v>15.1736640930176</v>
+        <v>15.1736631393433</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G139" t="n">
-        <v>16.3011798858643</v>
+        <v>16.301176071167</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G141" t="n">
-        <v>16.2534008026123</v>
+        <v>16.2534027099609</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G145" t="n">
-        <v>16.2916221618652</v>
+        <v>16.2916202545166</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G146" t="n">
-        <v>16.7693824768066</v>
+        <v>16.769380569458</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>16.6100006103516</v>
       </c>
       <c r="G149" t="n">
-        <v>15.8711929321289</v>
+        <v>15.8711948394775</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G150" t="n">
-        <v>15.6418695449829</v>
+        <v>15.6418685913086</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G153" t="n">
-        <v>16.587833404541</v>
+        <v>16.5878314971924</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G156" t="n">
-        <v>17.6962356567383</v>
+        <v>17.6962375640869</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G158" t="n">
-        <v>17.4669132232666</v>
+        <v>17.466911315918</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G164" t="n">
-        <v>17.5529098510742</v>
+        <v>17.5529117584229</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>17.8204555511475</v>
+        <v>17.8204536437988</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>19.5</v>
       </c>
       <c r="G169" t="n">
-        <v>18.6326484680176</v>
+        <v>18.6326465606689</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>19.75</v>
       </c>
       <c r="G172" t="n">
-        <v>18.8715286254883</v>
+        <v>18.8715267181396</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G173" t="n">
-        <v>18.5084323883057</v>
+        <v>18.508430480957</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>18.7700004577637</v>
       </c>
       <c r="G174" t="n">
-        <v>17.9351177215576</v>
+        <v>17.935115814209</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>17.7726783752441</v>
+        <v>17.7726802825928</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G184" t="n">
-        <v>17.1898097991943</v>
+        <v>17.189811706543</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G186" t="n">
-        <v>16.6833839416504</v>
+        <v>16.683385848999</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G188" t="n">
-        <v>17.6580181121826</v>
+        <v>17.658016204834</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G189" t="n">
-        <v>17.6580181121826</v>
+        <v>17.658016204834</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G192" t="n">
-        <v>16.5305004119873</v>
+        <v>16.5305023193359</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G193" t="n">
-        <v>16.4540596008301</v>
+        <v>16.4540615081787</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>16.3871765136719</v>
+        <v>16.3871746063232</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G195" t="n">
-        <v>16.3011798858643</v>
+        <v>16.301176071167</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G197" t="n">
-        <v>16.3489551544189</v>
+        <v>16.3489532470703</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G198" t="n">
-        <v>16.3011798858643</v>
+        <v>16.301176071167</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G199" t="n">
-        <v>16.6069431304932</v>
+        <v>16.6069450378418</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G200" t="n">
-        <v>16.6833839416504</v>
+        <v>16.683385848999</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G202" t="n">
-        <v>16.587833404541</v>
+        <v>16.5878314971924</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G204" t="n">
-        <v>16.7884941101074</v>
+        <v>16.7884922027588</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G206" t="n">
-        <v>17.2375907897949</v>
+        <v>17.2375869750977</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G207" t="n">
-        <v>16.6547203063965</v>
+        <v>16.6547222137451</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G208" t="n">
-        <v>16.9031562805176</v>
+        <v>16.9031581878662</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G210" t="n">
-        <v>17.2375907897949</v>
+        <v>17.2375869750977</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G211" t="n">
-        <v>17.37135887146</v>
+        <v>17.3713607788086</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G212" t="n">
-        <v>17.2184791564941</v>
+        <v>17.2184772491455</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>17.2949199676514</v>
+        <v>17.2949180603027</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G215" t="n">
-        <v>17.476469039917</v>
+        <v>17.4764709472656</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G216" t="n">
-        <v>17.6293506622314</v>
+        <v>17.6293525695801</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>19.2700004577637</v>
       </c>
       <c r="G221" t="n">
-        <v>18.5309085845947</v>
+        <v>18.5309104919434</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G229" t="n">
-        <v>18.8097858428955</v>
+        <v>18.8097839355469</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>18.3674278259277</v>
+        <v>18.3674297332764</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>19.75</v>
       </c>
       <c r="G233" t="n">
-        <v>18.9925003051758</v>
+        <v>18.9924983978271</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>19.1367473602295</v>
+        <v>19.1367454528809</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>19.3290748596191</v>
+        <v>19.3290729522705</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G240" t="n">
-        <v>19.4637050628662</v>
+        <v>19.4637031555176</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>19.4252395629883</v>
+        <v>19.4252414703369</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G243" t="n">
-        <v>19.0405807495117</v>
+        <v>19.0405788421631</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G249" t="n">
-        <v>18.4924411773682</v>
+        <v>18.4924430847168</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G250" t="n">
-        <v>18.4924411773682</v>
+        <v>18.4924430847168</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>19.5</v>
       </c>
       <c r="G252" t="n">
-        <v>18.7520885467529</v>
+        <v>18.7520866394043</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G254" t="n">
-        <v>18.386661529541</v>
+        <v>18.3866634368896</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G255" t="n">
-        <v>19.4637050628662</v>
+        <v>19.4637031555176</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G256" t="n">
-        <v>19.4637050628662</v>
+        <v>19.4637031555176</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G257" t="n">
-        <v>19.6944999694824</v>
+        <v>19.6944980621338</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G260" t="n">
-        <v>19.5598678588867</v>
+        <v>19.5598697662354</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G261" t="n">
-        <v>19.2713756561279</v>
+        <v>19.2713775634766</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>19.8098983764648</v>
+        <v>19.8098964691162</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>20.1399993896484</v>
       </c>
       <c r="G270" t="n">
-        <v>19.3675384521484</v>
+        <v>19.3675403594971</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>18.7700004577637</v>
       </c>
       <c r="G271" t="n">
-        <v>18.0500869750977</v>
+        <v>18.050085067749</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G274" t="n">
-        <v>17.5115623474121</v>
+        <v>17.5115642547607</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G275" t="n">
-        <v>18.2904987335205</v>
+        <v>18.2904968261719</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G278" t="n">
-        <v>18.6270751953125</v>
+        <v>18.6270732879639</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G282" t="n">
-        <v>17.8866062164307</v>
+        <v>17.8866081237793</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G283" t="n">
-        <v>17.5981101989746</v>
+        <v>17.5981121063232</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G284" t="n">
-        <v>17.540412902832</v>
+        <v>17.5404148101807</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G289" t="n">
-        <v>16.6460819244385</v>
+        <v>16.6460838317871</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G290" t="n">
-        <v>17.194221496582</v>
+        <v>17.1942195892334</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G291" t="n">
-        <v>17.4923305511475</v>
+        <v>17.4923324584961</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G296" t="n">
-        <v>17.2807712554932</v>
+        <v>17.2807674407959</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G300" t="n">
-        <v>16.6460819244385</v>
+        <v>16.6460838317871</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>17</v>
       </c>
       <c r="G302" t="n">
-        <v>16.3479747772217</v>
+        <v>16.347972869873</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G304" t="n">
-        <v>16.7230129241943</v>
+        <v>16.723014831543</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G305" t="n">
-        <v>16.3575897216797</v>
+        <v>16.3575916290283</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>16.75</v>
       </c>
       <c r="G307" t="n">
-        <v>16.1075630187988</v>
+        <v>16.1075611114502</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G309" t="n">
-        <v>15.7132883071899</v>
+        <v>15.7132873535156</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G310" t="n">
-        <v>15.5401906967163</v>
+        <v>15.5401916503906</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>15.4824924468994</v>
+        <v>15.4824934005737</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G314" t="n">
-        <v>15.655590057373</v>
+        <v>15.6555881500244</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G315" t="n">
-        <v>15.8479166030884</v>
+        <v>15.8479175567627</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G318" t="n">
-        <v>14.4150667190552</v>
+        <v>14.4150648117065</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G322" t="n">
-        <v>14.5689287185669</v>
+        <v>14.5689296722412</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>15</v>
       </c>
       <c r="G324" t="n">
-        <v>14.4246835708618</v>
+        <v>14.4246826171875</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G327" t="n">
-        <v>14.0881061553955</v>
+        <v>14.0881052017212</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G331" t="n">
-        <v>13.1745433807373</v>
+        <v>13.174542427063</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G333" t="n">
-        <v>12.8572006225586</v>
+        <v>12.8571996688843</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G334" t="n">
-        <v>12.6744890213013</v>
+        <v>12.674488067627</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G338" t="n">
-        <v>13.9053945541382</v>
+        <v>13.9053936004639</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G339" t="n">
-        <v>13.828462600708</v>
+        <v>13.8284616470337</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G341" t="n">
-        <v>13.2803239822388</v>
+        <v>13.2803249359131</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G345" t="n">
-        <v>13.6553649902344</v>
+        <v>13.655366897583</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G346" t="n">
-        <v>14.5016145706177</v>
+        <v>14.5016136169434</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G347" t="n">
-        <v>14.6362438201904</v>
+        <v>14.6362447738647</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G351" t="n">
-        <v>14.1073389053345</v>
+        <v>14.1073398590088</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G353" t="n">
-        <v>14.3092851638794</v>
+        <v>14.3092861175537</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G354" t="n">
-        <v>14.2996683120728</v>
+        <v>14.2996673583984</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G357" t="n">
-        <v>13.7611465454102</v>
+        <v>13.7611474990845</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G359" t="n">
-        <v>13.664981842041</v>
+        <v>13.6649827957153</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G360" t="n">
-        <v>13.2707071304321</v>
+        <v>13.2707080841064</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G361" t="n">
-        <v>13.5399694442749</v>
+        <v>13.5399684906006</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G363" t="n">
-        <v>13.1841592788696</v>
+        <v>13.1841602325439</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G366" t="n">
-        <v>13.5015029907227</v>
+        <v>13.5015020370483</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G367" t="n">
-        <v>13.5495862960815</v>
+        <v>13.5495853424072</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G368" t="n">
-        <v>14.7131767272949</v>
+        <v>14.7131757736206</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G369" t="n">
-        <v>14.6747102737427</v>
+        <v>14.674711227417</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G370" t="n">
-        <v>14.9151220321655</v>
+        <v>14.9151210784912</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G373" t="n">
-        <v>14.9151220321655</v>
+        <v>14.9151210784912</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G375" t="n">
-        <v>14.8381900787354</v>
+        <v>14.8381910324097</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G379" t="n">
-        <v>14.5016145706177</v>
+        <v>14.5016136169434</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G381" t="n">
-        <v>14.8862724304199</v>
+        <v>14.8862714767456</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G386" t="n">
-        <v>14.0977220535278</v>
+        <v>14.0977230072021</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G388" t="n">
-        <v>13.982325553894</v>
+        <v>13.9823265075684</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>14.2700004577637</v>
       </c>
       <c r="G391" t="n">
-        <v>13.7226819992065</v>
+        <v>13.7226810455322</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>14.5</v>
       </c>
       <c r="G392" t="n">
-        <v>13.9438591003418</v>
+        <v>13.9438600540161</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G397" t="n">
-        <v>13.664981842041</v>
+        <v>13.6649827957153</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G398" t="n">
-        <v>13.3668718338013</v>
+        <v>13.3668727874756</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>13.6553649902344</v>
+        <v>13.655366897583</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G408" t="n">
-        <v>14.1650371551514</v>
+        <v>14.1650381088257</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G415" t="n">
-        <v>14.8862724304199</v>
+        <v>14.8862714767456</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G418" t="n">
-        <v>14.6458597183228</v>
+        <v>14.6458606719971</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G421" t="n">
-        <v>14.5016145706177</v>
+        <v>14.5016136169434</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G422" t="n">
-        <v>14.3092851638794</v>
+        <v>14.3092861175537</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G423" t="n">
-        <v>14.2323541641235</v>
+        <v>14.2323532104492</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G425" t="n">
-        <v>14.155421257019</v>
+        <v>14.1554222106934</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G427" t="n">
-        <v>13.664981842041</v>
+        <v>13.6649827957153</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>14.1899995803833</v>
       </c>
       <c r="G431" t="n">
-        <v>13.6457490921021</v>
+        <v>13.6457481384277</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G432" t="n">
-        <v>12.6937208175659</v>
+        <v>12.6937198638916</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G433" t="n">
-        <v>12.6456384658813</v>
+        <v>12.645637512207</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>13.25</v>
       </c>
       <c r="G434" t="n">
-        <v>12.7418022155762</v>
+        <v>12.7418031692505</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>13.25</v>
       </c>
       <c r="G435" t="n">
-        <v>12.7418022155762</v>
+        <v>12.7418031692505</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G438" t="n">
-        <v>12.6456384658813</v>
+        <v>12.645637512207</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G439" t="n">
-        <v>12.8572006225586</v>
+        <v>12.8571996688843</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G441" t="n">
-        <v>12.3763771057129</v>
+        <v>12.3763780593872</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G444" t="n">
-        <v>12.4725427627563</v>
+        <v>12.472541809082</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G445" t="n">
-        <v>12.7802677154541</v>
+        <v>12.7802686691284</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G452" t="n">
-        <v>12.6937208175659</v>
+        <v>12.6937198638916</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G453" t="n">
-        <v>11.9244031906128</v>
+        <v>11.9244041442871</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G454" t="n">
-        <v>11.6839923858643</v>
+        <v>11.6839933395386</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G459" t="n">
-        <v>11.8859376907349</v>
+        <v>11.8859386444092</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G460" t="n">
-        <v>12.1744327545166</v>
+        <v>12.1744318008423</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G462" t="n">
-        <v>12.145583152771</v>
+        <v>12.1455821990967</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G463" t="n">
-        <v>12.0494174957275</v>
+        <v>12.0494184494019</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G465" t="n">
-        <v>12.8668174743652</v>
+        <v>12.8668165206909</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G467" t="n">
-        <v>12.7514190673828</v>
+        <v>12.7514200210571</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G470" t="n">
-        <v>13.3476400375366</v>
+        <v>13.3476390838623</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G472" t="n">
-        <v>13.1841592788696</v>
+        <v>13.1841602325439</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G474" t="n">
-        <v>12.7782716751099</v>
+        <v>12.7782726287842</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G476" t="n">
-        <v>13.0790500640869</v>
+        <v>13.0790510177612</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G477" t="n">
-        <v>12.9141082763672</v>
+        <v>12.9141073226929</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G478" t="n">
-        <v>12.4871940612793</v>
+        <v>12.4871950149536</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G479" t="n">
-        <v>12.8461894989014</v>
+        <v>12.8461885452271</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G482" t="n">
-        <v>12.8073797225952</v>
+        <v>12.8073787689209</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G494" t="n">
-        <v>11.3519945144653</v>
+        <v>11.3519954681396</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G497" t="n">
-        <v>11.4878311157227</v>
+        <v>11.487832069397</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G501" t="n">
-        <v>11.3519945144653</v>
+        <v>11.3519954681396</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G508" t="n">
-        <v>11.0803241729736</v>
+        <v>11.0803232192993</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G512" t="n">
-        <v>11.0803241729736</v>
+        <v>11.0803232192993</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G516" t="n">
-        <v>10.9735956192017</v>
+        <v>10.973596572876</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G519" t="n">
-        <v>10.9638938903809</v>
+        <v>10.9638929367065</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G524" t="n">
-        <v>10.5854921340942</v>
+        <v>10.5854930877686</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G526" t="n">
-        <v>10.3817386627197</v>
+        <v>10.381739616394</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G542" t="n">
-        <v>9.67830467224121</v>
+        <v>9.67830371856689</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G544" t="n">
-        <v>9.51821231842041</v>
+        <v>9.51821136474609</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G545" t="n">
-        <v>9.54731845855713</v>
+        <v>9.54731941223145</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G550" t="n">
-        <v>9.24653911590576</v>
+        <v>9.24654006958008</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G551" t="n">
-        <v>9.16891860961914</v>
+        <v>9.16891956329346</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>8.91499996185303</v>
       </c>
       <c r="G554" t="n">
-        <v>8.64983177185059</v>
+        <v>8.6498327255249</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G555" t="n">
-        <v>9.08159637451172</v>
+        <v>9.0815954208374</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G556" t="n">
-        <v>9.09129810333252</v>
+        <v>9.09129905700684</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G558" t="n">
-        <v>9.08159637451172</v>
+        <v>9.0815954208374</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G560" t="n">
-        <v>9.24653911590576</v>
+        <v>9.24654006958008</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>9.55500030517578</v>
       </c>
       <c r="G561" t="n">
-        <v>9.27079677581787</v>
+        <v>9.27079582214355</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G566" t="n">
-        <v>9.15921688079834</v>
+        <v>9.15921592712402</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G572" t="n">
-        <v>8.91665172576904</v>
+        <v>8.91665267944336</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>8.90499973297119</v>
       </c>
       <c r="G574" t="n">
-        <v>8.64013004302979</v>
+        <v>8.64012908935547</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G576" t="n">
-        <v>8.66438579559326</v>
+        <v>8.66438674926758</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>8.75</v>
       </c>
       <c r="G579" t="n">
-        <v>8.4897403717041</v>
+        <v>8.48973941802979</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G580" t="n">
-        <v>8.72260093688965</v>
+        <v>8.72260189056396</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.82499980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>8.56250953674316</v>
+        <v>8.56250858306885</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G584" t="n">
-        <v>8.80022144317627</v>
+        <v>8.80022239685059</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.91499996185303</v>
       </c>
       <c r="G585" t="n">
-        <v>8.64983177185059</v>
+        <v>8.6498327255249</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G587" t="n">
-        <v>8.7614107131958</v>
+        <v>8.76141166687012</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G591" t="n">
-        <v>8.387864112854</v>
+        <v>8.38786315917969</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G593" t="n">
-        <v>8.74200630187988</v>
+        <v>8.7420072555542</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>8.56736087799072</v>
+        <v>8.56735992431641</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G598" t="n">
-        <v>8.7614107131958</v>
+        <v>8.76141166687012</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>8.47500038146973</v>
       </c>
       <c r="G601" t="n">
-        <v>8.22291946411133</v>
+        <v>8.22292041778564</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>8.28499984741211</v>
       </c>
       <c r="G602" t="n">
-        <v>8.03857040405273</v>
+        <v>8.03857135772705</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G605" t="n">
-        <v>7.67472505569458</v>
+        <v>7.67472457885742</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G606" t="n">
-        <v>7.46126842498779</v>
+        <v>7.46126890182495</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G609" t="n">
-        <v>7.73779201507568</v>
+        <v>7.73779153823853</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>8.00500011444092</v>
       </c>
       <c r="G611" t="n">
-        <v>7.76689910888672</v>
+        <v>7.76689958572388</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G614" t="n">
-        <v>7.73779201507568</v>
+        <v>7.73779153823853</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>7.9850001335144</v>
       </c>
       <c r="G615" t="n">
-        <v>7.7474946975708</v>
+        <v>7.74749422073364</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G617" t="n">
-        <v>7.95609855651855</v>
+        <v>7.95609951019287</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>8.14500045776367</v>
       </c>
       <c r="G618" t="n">
-        <v>7.90273571014404</v>
+        <v>7.90273523330688</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>8.17500019073486</v>
       </c>
       <c r="G619" t="n">
-        <v>7.93184328079224</v>
+        <v>7.93184280395508</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>7.44671535491943</v>
+        <v>7.44671487808228</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>7.64499998092651</v>
       </c>
       <c r="G624" t="n">
-        <v>7.41760730743408</v>
+        <v>7.41760683059692</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G625" t="n">
-        <v>7.41275548934937</v>
+        <v>7.41275596618652</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>7.31087875366211</v>
+        <v>7.31087923049927</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G631" t="n">
-        <v>7.53888893127441</v>
+        <v>7.53888940811157</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G632" t="n">
-        <v>7.42245817184448</v>
+        <v>7.42245864868164</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>7.77500009536743</v>
       </c>
       <c r="G633" t="n">
-        <v>7.54374074935913</v>
+        <v>7.54374027252197</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>7.875</v>
       </c>
       <c r="G634" t="n">
-        <v>7.64076614379883</v>
+        <v>7.64076566696167</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G637" t="n">
-        <v>7.05861234664917</v>
+        <v>7.05861282348633</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>6.84515619277954</v>
+        <v>6.84515571594238</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G641" t="n">
-        <v>6.98099184036255</v>
+        <v>6.98099231719971</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>7.17989492416382</v>
+        <v>7.17989444732666</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G652" t="n">
-        <v>6.96643781661987</v>
+        <v>6.96643829345703</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G653" t="n">
-        <v>6.78694105148315</v>
+        <v>6.786940574646</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G658" t="n">
-        <v>6.78694105148315</v>
+        <v>6.786940574646</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G663" t="n">
-        <v>6.67536115646362</v>
+        <v>6.67536163330078</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>8.65499973297119</v>
       </c>
       <c r="G665" t="n">
-        <v>8.39756488800049</v>
+        <v>8.3975658416748</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G666" t="n">
-        <v>8.19866371154785</v>
+        <v>8.19866275787354</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G667" t="n">
-        <v>8.52855110168457</v>
+        <v>8.52855014801025</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>9.07499980926514</v>
       </c>
       <c r="G671" t="n">
-        <v>8.80507278442383</v>
+        <v>8.80507373809814</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G673" t="n">
-        <v>8.74200630187988</v>
+        <v>8.7420072555542</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>9.04763793945312</v>
+        <v>9.04763698577881</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G678" t="n">
-        <v>9.04763793945312</v>
+        <v>9.04763698577881</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G679" t="n">
-        <v>8.94090938568115</v>
+        <v>8.94090843200684</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G686" t="n">
-        <v>6.82575130462646</v>
+        <v>6.82575082778931</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G688" t="n">
-        <v>6.44250011444092</v>
+        <v>6.44249963760376</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G689" t="n">
-        <v>6.66080760955811</v>
+        <v>6.66080713272095</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>6.64499998092651</v>
       </c>
       <c r="G690" t="n">
-        <v>6.44735097885132</v>
+        <v>6.44735145568848</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G691" t="n">
-        <v>6.46190500259399</v>
+        <v>6.46190452575684</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>6.32606935501099</v>
+        <v>6.32606887817383</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G696" t="n">
-        <v>6.09805870056152</v>
+        <v>6.09805917739868</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G697" t="n">
-        <v>5.84094095230103</v>
+        <v>5.84094142913818</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G699" t="n">
-        <v>6.0107364654541</v>
+        <v>6.01073598861694</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>6.35500001907349</v>
       </c>
       <c r="G702" t="n">
-        <v>6.16597700119019</v>
+        <v>6.16597652435303</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G703" t="n">
-        <v>6.07380294799805</v>
+        <v>6.07380247116089</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G705" t="n">
-        <v>5.97677707672119</v>
+        <v>5.97677659988403</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>6.125</v>
       </c>
       <c r="G709" t="n">
-        <v>5.94281816482544</v>
+        <v>5.94281768798828</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G715" t="n">
-        <v>6.43279790878296</v>
+        <v>6.4327974319458</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G716" t="n">
-        <v>6.27755641937256</v>
+        <v>6.2775559425354</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G719" t="n">
-        <v>6.50071477890015</v>
+        <v>6.5007152557373</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G724" t="n">
-        <v>6.67536115646362</v>
+        <v>6.67536163330078</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -28114,6 +28114,32 @@
         <v>6.05999994277954</v>
       </c>
       <c r="H1067" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1068" t="n">
+        <v>1541987</v>
+      </c>
+      <c r="C1068" t="n">
+        <v>6.16499996185303</v>
+      </c>
+      <c r="D1068" t="n">
+        <v>5.92999982833862</v>
+      </c>
+      <c r="E1068" t="n">
+        <v>6.10500001907349</v>
+      </c>
+      <c r="F1068" t="n">
+        <v>6.01000022888184</v>
+      </c>
+      <c r="G1068" t="n">
+        <v>6.01000022888184</v>
+      </c>
+      <c r="H1068" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DNR.MI.xlsx
+++ b/data/DNR.MI.xlsx
@@ -447,7 +447,7 @@
         <v>13.25</v>
       </c>
       <c r="G3" t="n">
-        <v>12.6606454849243</v>
+        <v>12.66064453125</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>12.612868309021</v>
+        <v>12.6128692626953</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G5" t="n">
-        <v>12.4886512756348</v>
+        <v>12.4886503219604</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G7" t="n">
-        <v>12.5077619552612</v>
+        <v>12.5077610015869</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G13" t="n">
-        <v>12.5459833145142</v>
+        <v>12.5459823608398</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G15" t="n">
-        <v>13.0046319961548</v>
+        <v>13.0046329498291</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G16" t="n">
-        <v>13.4155054092407</v>
+        <v>13.415506362915</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G17" t="n">
-        <v>13.7021617889404</v>
+        <v>13.7021627426147</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G19" t="n">
-        <v>13.5683898925781</v>
+        <v>13.5683879852295</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G20" t="n">
-        <v>13.8072700500488</v>
+        <v>13.8072690963745</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>14.1417016983032</v>
+        <v>14.1417026519775</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G25" t="n">
-        <v>13.9410429000854</v>
+        <v>13.9410419464111</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G27" t="n">
-        <v>14.199031829834</v>
+        <v>14.1990337371826</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>14.75</v>
       </c>
       <c r="G28" t="n">
-        <v>14.0939264297485</v>
+        <v>14.0939254760742</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G30" t="n">
-        <v>13.7021617889404</v>
+        <v>13.7021627426147</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G31" t="n">
-        <v>13.5492792129517</v>
+        <v>13.549280166626</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G32" t="n">
-        <v>13.5683898925781</v>
+        <v>13.5683879852295</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G33" t="n">
-        <v>13.740382194519</v>
+        <v>13.7403831481934</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G38" t="n">
-        <v>13.4250621795654</v>
+        <v>13.4250612258911</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>15.1927738189697</v>
+        <v>15.1927728652954</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>15.3838787078857</v>
+        <v>15.3838777542114</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>15.5749807357788</v>
+        <v>15.5749816894531</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G49" t="n">
-        <v>15.6418685913086</v>
+        <v>15.6418695449829</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G50" t="n">
-        <v>15.230993270874</v>
+        <v>15.2309951782227</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G53" t="n">
-        <v>14.2372531890869</v>
+        <v>14.2372541427612</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G57" t="n">
-        <v>14.7436809539795</v>
+        <v>14.7436800003052</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G58" t="n">
-        <v>14.4092464447021</v>
+        <v>14.4092473983765</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>15.75</v>
       </c>
       <c r="G59" t="n">
-        <v>15.0494451522827</v>
+        <v>15.049446105957</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G60" t="n">
-        <v>15.4889850616455</v>
+        <v>15.4889841079712</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G62" t="n">
-        <v>15.230993270874</v>
+        <v>15.2309951782227</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G64" t="n">
-        <v>14.9634485244751</v>
+        <v>14.9634494781494</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G65" t="n">
-        <v>15.7469758987427</v>
+        <v>15.746973991394</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G67" t="n">
-        <v>15.230993270874</v>
+        <v>15.2309951782227</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G68" t="n">
-        <v>15.517650604248</v>
+        <v>15.5176515579224</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G69" t="n">
-        <v>15.3552131652832</v>
+        <v>15.3552112579346</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G72" t="n">
-        <v>14.6003513336182</v>
+        <v>14.6003503799438</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G75" t="n">
-        <v>14.1894788742065</v>
+        <v>14.1894779205322</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>15.5</v>
       </c>
       <c r="G77" t="n">
-        <v>14.8105659484863</v>
+        <v>14.810564994812</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G79" t="n">
-        <v>13.8646011352539</v>
+        <v>13.8646001815796</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G80" t="n">
-        <v>13.9888181686401</v>
+        <v>13.9888191223145</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="n">
-        <v>14.3328056335449</v>
+        <v>14.3328065872192</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G86" t="n">
-        <v>13.0046319961548</v>
+        <v>13.0046329498291</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G87" t="n">
-        <v>13.6448316574097</v>
+        <v>13.6448307037354</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G88" t="n">
-        <v>14.6003513336182</v>
+        <v>14.6003503799438</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G89" t="n">
-        <v>15.0303363800049</v>
+        <v>15.0303354263306</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>15.5699996948242</v>
       </c>
       <c r="G90" t="n">
-        <v>14.8774518966675</v>
+        <v>14.8774528503418</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>15.5</v>
       </c>
       <c r="G91" t="n">
-        <v>14.8105659484863</v>
+        <v>14.810564994812</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G92" t="n">
-        <v>14.5621309280396</v>
+        <v>14.5621299743652</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G94" t="n">
-        <v>14.6003513336182</v>
+        <v>14.6003503799438</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G95" t="n">
-        <v>14.199031829834</v>
+        <v>14.1990337371826</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>14.6194610595703</v>
+        <v>14.6194620132446</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G97" t="n">
-        <v>14.8678979873657</v>
+        <v>14.8678970336914</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G98" t="n">
-        <v>14.8678979873657</v>
+        <v>14.8678970336914</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G99" t="n">
-        <v>14.9347829818726</v>
+        <v>14.9347848892212</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G100" t="n">
-        <v>14.9347829818726</v>
+        <v>14.9347848892212</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G102" t="n">
-        <v>15.3456563949585</v>
+        <v>15.3456573486328</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G105" t="n">
-        <v>14.5907964706421</v>
+        <v>14.5907974243164</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G106" t="n">
-        <v>14.2754745483398</v>
+        <v>14.2754735946655</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G107" t="n">
-        <v>14.6576833724976</v>
+        <v>14.6576814651489</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G110" t="n">
-        <v>15.0876655578613</v>
+        <v>15.0876665115356</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G111" t="n">
-        <v>14.9443397521973</v>
+        <v>14.9443387985229</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G114" t="n">
-        <v>14.7819004058838</v>
+        <v>14.7819013595581</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G117" t="n">
-        <v>14.4474687576294</v>
+        <v>14.4474678039551</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G118" t="n">
-        <v>14.0461492538452</v>
+        <v>14.0461502075195</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>14.25</v>
       </c>
       <c r="G121" t="n">
-        <v>13.6161651611328</v>
+        <v>13.6161642074585</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G122" t="n">
-        <v>13.9314880371094</v>
+        <v>13.9314870834351</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G123" t="n">
-        <v>13.7021617889404</v>
+        <v>13.7021627426147</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G125" t="n">
-        <v>14.4952430725098</v>
+        <v>14.4952449798584</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G127" t="n">
-        <v>14.9634485244751</v>
+        <v>14.9634494781494</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G131" t="n">
-        <v>15.0876655578613</v>
+        <v>15.0876665115356</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G132" t="n">
-        <v>15.1258878707886</v>
+        <v>15.1258888244629</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>15.75</v>
       </c>
       <c r="G133" t="n">
-        <v>15.0494451522827</v>
+        <v>15.049446105957</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>14.9538946151733</v>
+        <v>14.953893661499</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>15.6899995803833</v>
       </c>
       <c r="G135" t="n">
-        <v>14.992115020752</v>
+        <v>14.9921140670776</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G136" t="n">
-        <v>15.269214630127</v>
+        <v>15.2692155838013</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>16.5</v>
       </c>
       <c r="G138" t="n">
-        <v>15.7660856246948</v>
+        <v>15.7660865783691</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G139" t="n">
-        <v>16.301176071167</v>
+        <v>16.3011779785156</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G142" t="n">
-        <v>16.9795989990234</v>
+        <v>16.9795970916748</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>17.8700008392334</v>
       </c>
       <c r="G143" t="n">
-        <v>17.0751514434814</v>
+        <v>17.0751495361328</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G146" t="n">
-        <v>16.769380569458</v>
+        <v>16.7693824768066</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G148" t="n">
-        <v>15.8425273895264</v>
+        <v>15.842529296875</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>16.6100006103516</v>
       </c>
       <c r="G149" t="n">
-        <v>15.8711948394775</v>
+        <v>15.8711957931519</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G150" t="n">
-        <v>15.6418685913086</v>
+        <v>15.6418695449829</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G153" t="n">
-        <v>16.5878314971924</v>
+        <v>16.5878353118896</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>17.3426933288574</v>
+        <v>17.3426952362061</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>18.25</v>
       </c>
       <c r="G155" t="n">
-        <v>17.4382457733154</v>
+        <v>17.4382476806641</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G156" t="n">
-        <v>17.6962375640869</v>
+        <v>17.6962394714355</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G158" t="n">
-        <v>17.466911315918</v>
+        <v>17.4669132232666</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G159" t="n">
-        <v>17.3904705047607</v>
+        <v>17.3904724121094</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G160" t="n">
-        <v>17.3904705047607</v>
+        <v>17.3904724121094</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G161" t="n">
-        <v>17.4478015899658</v>
+        <v>17.4477996826172</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G163" t="n">
-        <v>17.2089214324951</v>
+        <v>17.2089233398438</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G165" t="n">
-        <v>17.9542293548584</v>
+        <v>17.9542274475098</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>17.8204536437988</v>
+        <v>17.8204555511475</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G170" t="n">
-        <v>18.9001941680908</v>
+        <v>18.9001922607422</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>19.75</v>
       </c>
       <c r="G172" t="n">
-        <v>18.8715267181396</v>
+        <v>18.8715286254883</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>18.7700004577637</v>
       </c>
       <c r="G174" t="n">
-        <v>17.935115814209</v>
+        <v>17.9351177215576</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>18.4415416717529</v>
+        <v>18.4415435791016</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>17.7726802825928</v>
+        <v>17.7726783752441</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G179" t="n">
-        <v>18.8524188995361</v>
+        <v>18.8524150848389</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G185" t="n">
-        <v>16.3967304229736</v>
+        <v>16.396728515625</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G192" t="n">
-        <v>16.5305023193359</v>
+        <v>16.5305042266846</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G193" t="n">
-        <v>16.4540615081787</v>
+        <v>16.4540596008301</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>16.3871746063232</v>
+        <v>16.3871726989746</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G195" t="n">
-        <v>16.301176071167</v>
+        <v>16.3011779785156</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G198" t="n">
-        <v>16.301176071167</v>
+        <v>16.3011779785156</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G202" t="n">
-        <v>16.5878314971924</v>
+        <v>16.5878353118896</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G206" t="n">
-        <v>17.2375869750977</v>
+        <v>17.2375888824463</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G207" t="n">
-        <v>16.6547222137451</v>
+        <v>16.6547203063965</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G208" t="n">
-        <v>16.9031581878662</v>
+        <v>16.9031543731689</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G210" t="n">
-        <v>17.2375869750977</v>
+        <v>17.2375888824463</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G212" t="n">
-        <v>17.2184772491455</v>
+        <v>17.2184753417969</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>17.2949180603027</v>
+        <v>17.2949199676514</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G214" t="n">
-        <v>16.6642742156982</v>
+        <v>16.6642761230469</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G215" t="n">
-        <v>17.4764709472656</v>
+        <v>17.476469039917</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G218" t="n">
-        <v>18.4415416717529</v>
+        <v>18.4415435791016</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G219" t="n">
-        <v>18.4415416717529</v>
+        <v>18.4415435791016</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>19.2700004577637</v>
       </c>
       <c r="G221" t="n">
-        <v>18.5309104919434</v>
+        <v>18.5309085845947</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G222" t="n">
-        <v>18.5789890289307</v>
+        <v>18.5789909362793</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G229" t="n">
-        <v>18.8097839355469</v>
+        <v>18.8097858428955</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>18.3674297332764</v>
+        <v>18.3674278259277</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>19.75</v>
       </c>
       <c r="G233" t="n">
-        <v>18.9924983978271</v>
+        <v>18.9925003051758</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>19.3290729522705</v>
+        <v>19.3290748596191</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>19.4252414703369</v>
+        <v>19.4252395629883</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G243" t="n">
-        <v>19.0405788421631</v>
+        <v>19.0405807495117</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G245" t="n">
-        <v>17.6077289581299</v>
+        <v>17.6077270507812</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G246" t="n">
-        <v>17.8481388092041</v>
+        <v>17.8481407165527</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G248" t="n">
-        <v>18.5789890289307</v>
+        <v>18.5789909362793</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G251" t="n">
-        <v>18.4347438812256</v>
+        <v>18.434741973877</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G258" t="n">
-        <v>20.1368560791016</v>
+        <v>20.1368579864502</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G261" t="n">
-        <v>19.2713775634766</v>
+        <v>19.2713756561279</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G262" t="n">
-        <v>19.3098411560059</v>
+        <v>19.3098392486572</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>19.8098964691162</v>
+        <v>19.8098983764648</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>20.1399993896484</v>
       </c>
       <c r="G270" t="n">
-        <v>19.3675403594971</v>
+        <v>19.3675384521484</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G275" t="n">
-        <v>18.2904968261719</v>
+        <v>18.2904987335205</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G276" t="n">
-        <v>18.5020580291748</v>
+        <v>18.5020599365234</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G282" t="n">
-        <v>17.8866081237793</v>
+        <v>17.8866062164307</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G283" t="n">
-        <v>17.5981121063232</v>
+        <v>17.5981101989746</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G284" t="n">
-        <v>17.5404148101807</v>
+        <v>17.540412902832</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G289" t="n">
-        <v>16.6460838317871</v>
+        <v>16.6460819244385</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G290" t="n">
-        <v>17.1942195892334</v>
+        <v>17.194221496582</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G291" t="n">
-        <v>17.4923324584961</v>
+        <v>17.4923305511475</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G295" t="n">
-        <v>17.1749897003174</v>
+        <v>17.1749877929688</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G296" t="n">
-        <v>17.2807674407959</v>
+        <v>17.2807693481445</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G300" t="n">
-        <v>16.6460838317871</v>
+        <v>16.6460819244385</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G301" t="n">
-        <v>16.4441375732422</v>
+        <v>16.4441394805908</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G304" t="n">
-        <v>16.723014831543</v>
+        <v>16.7230129241943</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>16.75</v>
       </c>
       <c r="G307" t="n">
-        <v>16.1075611114502</v>
+        <v>16.1075630187988</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G309" t="n">
-        <v>15.7132873535156</v>
+        <v>15.7132883071899</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G310" t="n">
-        <v>15.5401916503906</v>
+        <v>15.5401906967163</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>15.4824934005737</v>
+        <v>15.4824924468994</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G315" t="n">
-        <v>15.8479175567627</v>
+        <v>15.8479166030884</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>16.2700004577637</v>
       </c>
       <c r="G316" t="n">
-        <v>15.6459722518921</v>
+        <v>15.6459732055664</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G318" t="n">
-        <v>14.4150648117065</v>
+        <v>14.4150657653809</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>15.0299997329712</v>
       </c>
       <c r="G319" t="n">
-        <v>14.4535312652588</v>
+        <v>14.4535322189331</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G321" t="n">
-        <v>14.4631481170654</v>
+        <v>14.4631490707397</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G322" t="n">
-        <v>14.5689296722412</v>
+        <v>14.5689287185669</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>15</v>
       </c>
       <c r="G324" t="n">
-        <v>14.4246826171875</v>
+        <v>14.4246835708618</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G328" t="n">
-        <v>14.2227373123169</v>
+        <v>14.2227363586426</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G331" t="n">
-        <v>13.174542427063</v>
+        <v>13.1745433807373</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G334" t="n">
-        <v>12.674488067627</v>
+        <v>12.6744890213013</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G338" t="n">
-        <v>13.9053936004639</v>
+        <v>13.9053945541382</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G339" t="n">
-        <v>13.8284616470337</v>
+        <v>13.828462600708</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>14.0100002288818</v>
       </c>
       <c r="G343" t="n">
-        <v>13.4726533889771</v>
+        <v>13.4726543426514</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G344" t="n">
-        <v>13.0399141311646</v>
+        <v>13.0399131774902</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G345" t="n">
-        <v>13.655366897583</v>
+        <v>13.6553649902344</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G346" t="n">
-        <v>14.5016136169434</v>
+        <v>14.5016145706177</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G347" t="n">
-        <v>14.6362447738647</v>
+        <v>14.6362438201904</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G348" t="n">
-        <v>14.2227373123169</v>
+        <v>14.2227363586426</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G349" t="n">
-        <v>14.5785455703735</v>
+        <v>14.5785446166992</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G350" t="n">
-        <v>14.2708187103271</v>
+        <v>14.2708196640015</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G351" t="n">
-        <v>14.1073398590088</v>
+        <v>14.1073389053345</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G353" t="n">
-        <v>14.3092861175537</v>
+        <v>14.3092851638794</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G354" t="n">
-        <v>14.2996673583984</v>
+        <v>14.2996683120728</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G355" t="n">
-        <v>13.68421459198</v>
+        <v>13.6842155456543</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G356" t="n">
-        <v>13.7322978973389</v>
+        <v>13.7322969436646</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G357" t="n">
-        <v>13.7611474990845</v>
+        <v>13.7611465454102</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>14.3900003433228</v>
       </c>
       <c r="G358" t="n">
-        <v>13.8380794525146</v>
+        <v>13.8380784988403</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G360" t="n">
-        <v>13.2707080841064</v>
+        <v>13.2707071304321</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G363" t="n">
-        <v>13.1841602325439</v>
+        <v>13.1841592788696</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G366" t="n">
-        <v>13.5015020370483</v>
+        <v>13.5015029907227</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G367" t="n">
-        <v>13.5495853424072</v>
+        <v>13.5495862960815</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G369" t="n">
-        <v>14.674711227417</v>
+        <v>14.6747102737427</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G370" t="n">
-        <v>14.9151210784912</v>
+        <v>14.9151220321655</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G371" t="n">
-        <v>15.68443775177</v>
+        <v>15.6844387054443</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G373" t="n">
-        <v>14.9151210784912</v>
+        <v>14.9151220321655</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G376" t="n">
-        <v>15.0305185317993</v>
+        <v>15.0305194854736</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G379" t="n">
-        <v>14.5016136169434</v>
+        <v>14.5016145706177</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G385" t="n">
-        <v>14.4439153671265</v>
+        <v>14.4439163208008</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G388" t="n">
-        <v>13.9823265075684</v>
+        <v>13.982325553894</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>14.7700004577637</v>
       </c>
       <c r="G389" t="n">
-        <v>14.2035045623779</v>
+        <v>14.2035036087036</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G390" t="n">
-        <v>14.4631481170654</v>
+        <v>14.4631490707397</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G394" t="n">
-        <v>13.7419147491455</v>
+        <v>13.7419137954712</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>14.25</v>
       </c>
       <c r="G396" t="n">
-        <v>13.7034482955933</v>
+        <v>13.7034473419189</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G398" t="n">
-        <v>13.3668727874756</v>
+        <v>13.3668718338013</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G405" t="n">
-        <v>13.5880508422852</v>
+        <v>13.5880517959595</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>13.655366897583</v>
+        <v>13.6553649902344</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G408" t="n">
-        <v>14.1650381088257</v>
+        <v>14.1650371551514</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G416" t="n">
-        <v>14.7516422271729</v>
+        <v>14.7516412734985</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G421" t="n">
-        <v>14.5016136169434</v>
+        <v>14.5016145706177</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G422" t="n">
-        <v>14.3092861175537</v>
+        <v>14.3092851638794</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G423" t="n">
-        <v>14.2323532104492</v>
+        <v>14.2323541641235</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G428" t="n">
-        <v>13.8188457489014</v>
+        <v>13.8188447952271</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>14.25</v>
       </c>
       <c r="G430" t="n">
-        <v>13.7034482955933</v>
+        <v>13.7034473419189</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>14.1899995803833</v>
       </c>
       <c r="G431" t="n">
-        <v>13.6457481384277</v>
+        <v>13.6457490921021</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G432" t="n">
-        <v>12.6937198638916</v>
+        <v>12.6937208175659</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G433" t="n">
-        <v>12.645637512207</v>
+        <v>12.6456384658813</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>13.25</v>
       </c>
       <c r="G434" t="n">
-        <v>12.7418031692505</v>
+        <v>12.7418022155762</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>13.25</v>
       </c>
       <c r="G435" t="n">
-        <v>12.7418031692505</v>
+        <v>12.7418022155762</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G438" t="n">
-        <v>12.645637512207</v>
+        <v>12.6456384658813</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G441" t="n">
-        <v>12.3763780593872</v>
+        <v>12.3763771057129</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G442" t="n">
-        <v>12.9725971221924</v>
+        <v>12.9725980758667</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G449" t="n">
-        <v>12.8091173171997</v>
+        <v>12.809118270874</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G451" t="n">
-        <v>12.9629812240601</v>
+        <v>12.9629802703857</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G452" t="n">
-        <v>12.6937198638916</v>
+        <v>12.6937208175659</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G453" t="n">
-        <v>11.9244041442871</v>
+        <v>11.9244031906128</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G457" t="n">
-        <v>11.9724864959717</v>
+        <v>11.9724855422974</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G459" t="n">
-        <v>11.8859386444092</v>
+        <v>11.8859376907349</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G463" t="n">
-        <v>12.0494184494019</v>
+        <v>12.0494174957275</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G464" t="n">
-        <v>11.9724864959717</v>
+        <v>11.9724855422974</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G467" t="n">
-        <v>12.7514200210571</v>
+        <v>12.7514190673828</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G472" t="n">
-        <v>13.1841602325439</v>
+        <v>13.1841592788696</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G474" t="n">
-        <v>12.7782726287842</v>
+        <v>12.7782716751099</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G476" t="n">
-        <v>13.0790510177612</v>
+        <v>13.0790500640869</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G477" t="n">
-        <v>12.9141073226929</v>
+        <v>12.9141082763672</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G478" t="n">
-        <v>12.4871950149536</v>
+        <v>12.4871940612793</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G479" t="n">
-        <v>12.8461885452271</v>
+        <v>12.8461894989014</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G482" t="n">
-        <v>12.8073787689209</v>
+        <v>12.8073797225952</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G494" t="n">
-        <v>11.3519954681396</v>
+        <v>11.3519945144653</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G497" t="n">
-        <v>11.487832069397</v>
+        <v>11.4878311157227</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G501" t="n">
-        <v>11.3519954681396</v>
+        <v>11.3519945144653</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G508" t="n">
-        <v>11.0803232192993</v>
+        <v>11.0803241729736</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G512" t="n">
-        <v>11.0803232192993</v>
+        <v>11.0803241729736</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G516" t="n">
-        <v>10.973596572876</v>
+        <v>10.9735956192017</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G519" t="n">
-        <v>10.9638929367065</v>
+        <v>10.9638938903809</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G524" t="n">
-        <v>10.5854930877686</v>
+        <v>10.5854921340942</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G526" t="n">
-        <v>10.381739616394</v>
+        <v>10.3817386627197</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G542" t="n">
-        <v>9.67830371856689</v>
+        <v>9.67830467224121</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G544" t="n">
-        <v>9.51821136474609</v>
+        <v>9.51821231842041</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G545" t="n">
-        <v>9.54731941223145</v>
+        <v>9.54731845855713</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G550" t="n">
-        <v>9.24654006958008</v>
+        <v>9.24653911590576</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G551" t="n">
-        <v>9.16891956329346</v>
+        <v>9.16891860961914</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>8.91499996185303</v>
       </c>
       <c r="G554" t="n">
-        <v>8.6498327255249</v>
+        <v>8.64983177185059</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G555" t="n">
-        <v>9.0815954208374</v>
+        <v>9.08159637451172</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G556" t="n">
-        <v>9.09129905700684</v>
+        <v>9.09129810333252</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G558" t="n">
-        <v>9.0815954208374</v>
+        <v>9.08159637451172</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G560" t="n">
-        <v>9.24654006958008</v>
+        <v>9.24653911590576</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>9.55500030517578</v>
       </c>
       <c r="G561" t="n">
-        <v>9.27079582214355</v>
+        <v>9.27079677581787</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G566" t="n">
-        <v>9.15921592712402</v>
+        <v>9.15921688079834</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G572" t="n">
-        <v>8.91665267944336</v>
+        <v>8.91665172576904</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>8.90499973297119</v>
       </c>
       <c r="G574" t="n">
-        <v>8.64012908935547</v>
+        <v>8.64013004302979</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G576" t="n">
-        <v>8.66438674926758</v>
+        <v>8.66438579559326</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>8.75</v>
       </c>
       <c r="G579" t="n">
-        <v>8.48973941802979</v>
+        <v>8.4897403717041</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G580" t="n">
-        <v>8.72260189056396</v>
+        <v>8.72260093688965</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.82499980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>8.56250858306885</v>
+        <v>8.56250953674316</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G584" t="n">
-        <v>8.80022239685059</v>
+        <v>8.80022144317627</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.91499996185303</v>
       </c>
       <c r="G585" t="n">
-        <v>8.6498327255249</v>
+        <v>8.64983177185059</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G587" t="n">
-        <v>8.76141166687012</v>
+        <v>8.7614107131958</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G591" t="n">
-        <v>8.38786315917969</v>
+        <v>8.387864112854</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G593" t="n">
-        <v>8.7420072555542</v>
+        <v>8.74200630187988</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>8.56735992431641</v>
+        <v>8.56736087799072</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G598" t="n">
-        <v>8.76141166687012</v>
+        <v>8.7614107131958</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>8.47500038146973</v>
       </c>
       <c r="G601" t="n">
-        <v>8.22292041778564</v>
+        <v>8.22291946411133</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>8.28499984741211</v>
       </c>
       <c r="G602" t="n">
-        <v>8.03857135772705</v>
+        <v>8.03857040405273</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G605" t="n">
-        <v>7.67472457885742</v>
+        <v>7.67472505569458</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G606" t="n">
-        <v>7.46126890182495</v>
+        <v>7.46126842498779</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G609" t="n">
-        <v>7.73779153823853</v>
+        <v>7.73779201507568</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>8.00500011444092</v>
       </c>
       <c r="G611" t="n">
-        <v>7.76689958572388</v>
+        <v>7.76689910888672</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G614" t="n">
-        <v>7.73779153823853</v>
+        <v>7.73779201507568</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>7.9850001335144</v>
       </c>
       <c r="G615" t="n">
-        <v>7.74749422073364</v>
+        <v>7.7474946975708</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G617" t="n">
-        <v>7.95609951019287</v>
+        <v>7.95609855651855</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>8.14500045776367</v>
       </c>
       <c r="G618" t="n">
-        <v>7.90273523330688</v>
+        <v>7.90273571014404</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>8.17500019073486</v>
       </c>
       <c r="G619" t="n">
-        <v>7.93184280395508</v>
+        <v>7.93184328079224</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>7.44671487808228</v>
+        <v>7.44671535491943</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>7.64499998092651</v>
       </c>
       <c r="G624" t="n">
-        <v>7.41760683059692</v>
+        <v>7.41760730743408</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G625" t="n">
-        <v>7.41275596618652</v>
+        <v>7.41275548934937</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>7.31087923049927</v>
+        <v>7.31087875366211</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G631" t="n">
-        <v>7.53888940811157</v>
+        <v>7.53888893127441</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G632" t="n">
-        <v>7.42245864868164</v>
+        <v>7.42245817184448</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>7.77500009536743</v>
       </c>
       <c r="G633" t="n">
-        <v>7.54374027252197</v>
+        <v>7.54374074935913</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>7.875</v>
       </c>
       <c r="G634" t="n">
-        <v>7.64076566696167</v>
+        <v>7.64076614379883</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G637" t="n">
-        <v>7.05861282348633</v>
+        <v>7.05861234664917</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>6.84515571594238</v>
+        <v>6.84515619277954</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G641" t="n">
-        <v>6.98099231719971</v>
+        <v>6.98099184036255</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>7.17989444732666</v>
+        <v>7.17989492416382</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G652" t="n">
-        <v>6.96643829345703</v>
+        <v>6.96643781661987</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G653" t="n">
-        <v>6.786940574646</v>
+        <v>6.78694105148315</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G658" t="n">
-        <v>6.786940574646</v>
+        <v>6.78694105148315</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G663" t="n">
-        <v>6.67536163330078</v>
+        <v>6.67536115646362</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>8.65499973297119</v>
       </c>
       <c r="G665" t="n">
-        <v>8.3975658416748</v>
+        <v>8.39756488800049</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G666" t="n">
-        <v>8.19866275787354</v>
+        <v>8.19866371154785</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G667" t="n">
-        <v>8.52855014801025</v>
+        <v>8.52855110168457</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>9.07499980926514</v>
       </c>
       <c r="G671" t="n">
-        <v>8.80507373809814</v>
+        <v>8.80507278442383</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G673" t="n">
-        <v>8.7420072555542</v>
+        <v>8.74200630187988</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>9.04763698577881</v>
+        <v>9.04763793945312</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G678" t="n">
-        <v>9.04763698577881</v>
+        <v>9.04763793945312</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G679" t="n">
-        <v>8.94090843200684</v>
+        <v>8.94090938568115</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G686" t="n">
-        <v>6.82575082778931</v>
+        <v>6.82575130462646</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G688" t="n">
-        <v>6.44249963760376</v>
+        <v>6.44250011444092</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G689" t="n">
-        <v>6.66080713272095</v>
+        <v>6.66080760955811</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>6.64499998092651</v>
       </c>
       <c r="G690" t="n">
-        <v>6.44735145568848</v>
+        <v>6.44735097885132</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G691" t="n">
-        <v>6.46190452575684</v>
+        <v>6.46190500259399</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>6.32606887817383</v>
+        <v>6.32606935501099</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G696" t="n">
-        <v>6.09805917739868</v>
+        <v>6.09805870056152</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G697" t="n">
-        <v>5.84094142913818</v>
+        <v>5.84094095230103</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G699" t="n">
-        <v>6.01073598861694</v>
+        <v>6.0107364654541</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>6.35500001907349</v>
       </c>
       <c r="G702" t="n">
-        <v>6.16597652435303</v>
+        <v>6.16597700119019</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G703" t="n">
-        <v>6.07380247116089</v>
+        <v>6.07380294799805</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G705" t="n">
-        <v>5.97677659988403</v>
+        <v>5.97677707672119</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>6.125</v>
       </c>
       <c r="G709" t="n">
-        <v>5.94281768798828</v>
+        <v>5.94281816482544</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G715" t="n">
-        <v>6.4327974319458</v>
+        <v>6.43279790878296</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G716" t="n">
-        <v>6.2775559425354</v>
+        <v>6.27755641937256</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G719" t="n">
-        <v>6.5007152557373</v>
+        <v>6.50071477890015</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G724" t="n">
-        <v>6.67536163330078</v>
+        <v>6.67536115646362</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -28140,6 +28140,32 @@
         <v>6.01000022888184</v>
       </c>
       <c r="H1068" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1069" t="n">
+        <v>877202</v>
+      </c>
+      <c r="C1069" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="D1069" t="n">
+        <v>5.8600001335144</v>
+      </c>
+      <c r="E1069" t="n">
+        <v>5.94000005722046</v>
+      </c>
+      <c r="F1069" t="n">
+        <v>5.8600001335144</v>
+      </c>
+      <c r="G1069" t="n">
+        <v>5.8600001335144</v>
+      </c>
+      <c r="H1069" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DNR.MI.xlsx
+++ b/data/DNR.MI.xlsx
@@ -447,7 +447,7 @@
         <v>13.25</v>
       </c>
       <c r="G3" t="n">
-        <v>12.66064453125</v>
+        <v>12.6606464385986</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>12.6128692626953</v>
+        <v>12.612868309021</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G5" t="n">
-        <v>12.4886503219604</v>
+        <v>12.4886512756348</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G7" t="n">
-        <v>12.5077610015869</v>
+        <v>12.5077619552612</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G12" t="n">
-        <v>12.4504299163818</v>
+        <v>12.4504308700562</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G15" t="n">
-        <v>13.0046329498291</v>
+        <v>13.0046319961548</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G16" t="n">
-        <v>13.415506362915</v>
+        <v>13.4155054092407</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G19" t="n">
-        <v>13.5683879852295</v>
+        <v>13.5683889389038</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G25" t="n">
-        <v>13.9410419464111</v>
+        <v>13.9410429000854</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G27" t="n">
-        <v>14.1990337371826</v>
+        <v>14.1990327835083</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>14.75</v>
       </c>
       <c r="G28" t="n">
-        <v>14.0939254760742</v>
+        <v>14.0939264297485</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G31" t="n">
-        <v>13.549280166626</v>
+        <v>13.5492792129517</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G32" t="n">
-        <v>13.5683879852295</v>
+        <v>13.5683889389038</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G34" t="n">
-        <v>13.3486204147339</v>
+        <v>13.3486194610596</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G35" t="n">
-        <v>13.5397243499756</v>
+        <v>13.5397233963013</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G36" t="n">
-        <v>13.3486204147339</v>
+        <v>13.3486194610596</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G38" t="n">
-        <v>13.4250612258911</v>
+        <v>13.4250621795654</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G40" t="n">
-        <v>13.8454904556274</v>
+        <v>13.8454895019531</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>15.1927728652954</v>
+        <v>15.1927738189697</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>15.3838777542114</v>
+        <v>15.3838787078857</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>15.5749816894531</v>
+        <v>15.5749826431274</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G48" t="n">
-        <v>16.0909633636475</v>
+        <v>16.0909614562988</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G53" t="n">
-        <v>14.2372541427612</v>
+        <v>14.2372531890869</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G57" t="n">
-        <v>14.7436800003052</v>
+        <v>14.7436809539795</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G58" t="n">
-        <v>14.4092473983765</v>
+        <v>14.4092483520508</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>15.75</v>
       </c>
       <c r="G59" t="n">
-        <v>15.049446105957</v>
+        <v>15.0494470596313</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G60" t="n">
-        <v>15.4889841079712</v>
+        <v>15.4889850616455</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G65" t="n">
-        <v>15.746973991394</v>
+        <v>15.7469778060913</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G68" t="n">
-        <v>15.5176515579224</v>
+        <v>15.5176496505737</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G69" t="n">
-        <v>15.3552112579346</v>
+        <v>15.3552122116089</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G70" t="n">
-        <v>15.3361005783081</v>
+        <v>15.3361015319824</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G71" t="n">
-        <v>15.097222328186</v>
+        <v>15.0972232818604</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G72" t="n">
-        <v>14.6003503799438</v>
+        <v>14.6003513336182</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G73" t="n">
-        <v>14.3519163131714</v>
+        <v>14.3519172668457</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G75" t="n">
-        <v>14.1894779205322</v>
+        <v>14.1894788742065</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G80" t="n">
-        <v>13.9888191223145</v>
+        <v>13.9888181686401</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G83" t="n">
-        <v>13.9505977630615</v>
+        <v>13.9505968093872</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G84" t="n">
-        <v>13.1670713424683</v>
+        <v>13.1670703887939</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G85" t="n">
-        <v>12.9377450942993</v>
+        <v>12.9377460479736</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G86" t="n">
-        <v>13.0046329498291</v>
+        <v>13.0046319961548</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G88" t="n">
-        <v>14.6003503799438</v>
+        <v>14.6003513336182</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G89" t="n">
-        <v>15.0303354263306</v>
+        <v>15.0303344726562</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>15.5699996948242</v>
       </c>
       <c r="G90" t="n">
-        <v>14.8774528503418</v>
+        <v>14.8774518966675</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G92" t="n">
-        <v>14.5621299743652</v>
+        <v>14.5621309280396</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G94" t="n">
-        <v>14.6003503799438</v>
+        <v>14.6003513336182</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G95" t="n">
-        <v>14.1990337371826</v>
+        <v>14.1990327835083</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G97" t="n">
-        <v>14.8678970336914</v>
+        <v>14.8678979873657</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G98" t="n">
-        <v>14.8678970336914</v>
+        <v>14.8678979873657</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G99" t="n">
-        <v>14.9347848892212</v>
+        <v>14.9347829818726</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G100" t="n">
-        <v>14.9347848892212</v>
+        <v>14.9347829818726</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G101" t="n">
-        <v>15.326548576355</v>
+        <v>15.3265476226807</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G102" t="n">
-        <v>15.3456573486328</v>
+        <v>15.3456563949585</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G105" t="n">
-        <v>14.5907974243164</v>
+        <v>14.5907964706421</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G106" t="n">
-        <v>14.2754735946655</v>
+        <v>14.2754745483398</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G107" t="n">
-        <v>14.6576814651489</v>
+        <v>14.6576833724976</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G113" t="n">
-        <v>14.7914543151855</v>
+        <v>14.7914552688599</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G114" t="n">
-        <v>14.7819013595581</v>
+        <v>14.7819004058838</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G116" t="n">
-        <v>14.4570226669312</v>
+        <v>14.4570245742798</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G118" t="n">
-        <v>14.0461502075195</v>
+        <v>14.0461492538452</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>14.5</v>
       </c>
       <c r="G119" t="n">
-        <v>13.8550462722778</v>
+        <v>13.8550453186035</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>14.25</v>
       </c>
       <c r="G121" t="n">
-        <v>13.6161642074585</v>
+        <v>13.6161651611328</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>14.5</v>
       </c>
       <c r="G124" t="n">
-        <v>13.8550462722778</v>
+        <v>13.8550453186035</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G125" t="n">
-        <v>14.4952449798584</v>
+        <v>14.4952440261841</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G129" t="n">
-        <v>15.1641092300415</v>
+        <v>15.1641073226929</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G130" t="n">
-        <v>15.0398902893066</v>
+        <v>15.0398893356323</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G132" t="n">
-        <v>15.1258888244629</v>
+        <v>15.1258869171143</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>15.75</v>
       </c>
       <c r="G133" t="n">
-        <v>15.049446105957</v>
+        <v>15.0494470596313</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>16.5</v>
       </c>
       <c r="G138" t="n">
-        <v>15.7660865783691</v>
+        <v>15.7660856246948</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G140" t="n">
-        <v>16.1865158081055</v>
+        <v>16.1865139007568</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G141" t="n">
-        <v>16.2534027099609</v>
+        <v>16.2534008026123</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G142" t="n">
-        <v>16.9795970916748</v>
+        <v>16.9795989990234</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G144" t="n">
-        <v>16.5687236785889</v>
+        <v>16.5687255859375</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G145" t="n">
-        <v>16.2916202545166</v>
+        <v>16.2916221618652</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G146" t="n">
-        <v>16.7693824768066</v>
+        <v>16.769380569458</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G148" t="n">
-        <v>15.842529296875</v>
+        <v>15.8425283432007</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>16.6100006103516</v>
       </c>
       <c r="G149" t="n">
-        <v>15.8711957931519</v>
+        <v>15.8711948394775</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G152" t="n">
-        <v>16.5687236785889</v>
+        <v>16.5687255859375</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G153" t="n">
-        <v>16.5878353118896</v>
+        <v>16.587833404541</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G156" t="n">
-        <v>17.6962394714355</v>
+        <v>17.6962375640869</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G161" t="n">
-        <v>17.4477996826172</v>
+        <v>17.4478015899658</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G162" t="n">
-        <v>17.5815753936768</v>
+        <v>17.5815734863281</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G163" t="n">
-        <v>17.2089233398438</v>
+        <v>17.2089214324951</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G164" t="n">
-        <v>17.5529117584229</v>
+        <v>17.5529098510742</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G165" t="n">
-        <v>17.9542274475098</v>
+        <v>17.9542293548584</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>17.8204555511475</v>
+        <v>17.8204536437988</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G167" t="n">
-        <v>18.2313289642334</v>
+        <v>18.2313270568848</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G168" t="n">
-        <v>18.5562057495117</v>
+        <v>18.5562076568604</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>19.5</v>
       </c>
       <c r="G169" t="n">
-        <v>18.6326465606689</v>
+        <v>18.6326503753662</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G170" t="n">
-        <v>18.9001922607422</v>
+        <v>18.9001941680908</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G171" t="n">
-        <v>18.7664203643799</v>
+        <v>18.7664184570312</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>19.75</v>
       </c>
       <c r="G172" t="n">
-        <v>18.8715286254883</v>
+        <v>18.8715267181396</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G173" t="n">
-        <v>18.508430480957</v>
+        <v>18.5084323883057</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>18.7700004577637</v>
       </c>
       <c r="G174" t="n">
-        <v>17.9351177215576</v>
+        <v>17.9351196289062</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>18.4415435791016</v>
+        <v>18.4415397644043</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G177" t="n">
-        <v>18.3077697753906</v>
+        <v>18.3077716827393</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>18.75</v>
       </c>
       <c r="G178" t="n">
-        <v>17.9160079956055</v>
+        <v>17.9160060882568</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G179" t="n">
-        <v>18.8524150848389</v>
+        <v>18.8524169921875</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G180" t="n">
-        <v>18.7664203643799</v>
+        <v>18.7664184570312</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>18.75</v>
       </c>
       <c r="G182" t="n">
-        <v>17.9160079956055</v>
+        <v>17.9160060882568</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G185" t="n">
-        <v>16.396728515625</v>
+        <v>16.3967304229736</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G192" t="n">
-        <v>16.5305042266846</v>
+        <v>16.5305023193359</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G193" t="n">
-        <v>16.4540596008301</v>
+        <v>16.4540576934814</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>16.3871726989746</v>
+        <v>16.3871746063232</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G197" t="n">
-        <v>16.3489532470703</v>
+        <v>16.3489551544189</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G199" t="n">
-        <v>16.6069450378418</v>
+        <v>16.6069431304932</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>16.6260547637939</v>
+        <v>16.6260528564453</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G202" t="n">
-        <v>16.5878353118896</v>
+        <v>16.587833404541</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G205" t="n">
-        <v>17.0369281768799</v>
+        <v>17.0369262695312</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G206" t="n">
-        <v>17.2375888824463</v>
+        <v>17.2375869750977</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G207" t="n">
-        <v>16.6547203063965</v>
+        <v>16.6547222137451</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G208" t="n">
-        <v>16.9031543731689</v>
+        <v>16.9031581878662</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G210" t="n">
-        <v>17.2375888824463</v>
+        <v>17.2375869750977</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G212" t="n">
-        <v>17.2184753417969</v>
+        <v>17.2184772491455</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G217" t="n">
-        <v>18.2313289642334</v>
+        <v>18.2313270568848</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G218" t="n">
-        <v>18.4415435791016</v>
+        <v>18.4415397644043</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G219" t="n">
-        <v>18.4415435791016</v>
+        <v>18.4415397644043</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G220" t="n">
-        <v>18.0020065307617</v>
+        <v>18.0020046234131</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G222" t="n">
-        <v>18.5789909362793</v>
+        <v>18.5789890289307</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>19.25</v>
       </c>
       <c r="G224" t="n">
-        <v>18.5116748809814</v>
+        <v>18.5116767883301</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>18.3674278259277</v>
+        <v>18.3674297332764</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G236" t="n">
-        <v>20.1753215789795</v>
+        <v>20.1753234863281</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>20.5</v>
       </c>
       <c r="G237" t="n">
-        <v>19.7137336730957</v>
+        <v>19.7137317657471</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>19.3290748596191</v>
+        <v>19.3290729522705</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G240" t="n">
-        <v>19.4637031555176</v>
+        <v>19.4637050628662</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>19.4252395629883</v>
+        <v>19.4252414703369</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G245" t="n">
-        <v>17.6077270507812</v>
+        <v>17.6077289581299</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G246" t="n">
-        <v>17.8481407165527</v>
+        <v>17.8481388092041</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G248" t="n">
-        <v>18.5789909362793</v>
+        <v>18.5789890289307</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G251" t="n">
-        <v>18.434741973877</v>
+        <v>18.4347438812256</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>19.4099998474121</v>
       </c>
       <c r="G253" t="n">
-        <v>18.6655387878418</v>
+        <v>18.6655406951904</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G255" t="n">
-        <v>19.4637031555176</v>
+        <v>19.4637050628662</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G256" t="n">
-        <v>19.4637031555176</v>
+        <v>19.4637050628662</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G257" t="n">
-        <v>19.6944980621338</v>
+        <v>19.6944999694824</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G260" t="n">
-        <v>19.5598697662354</v>
+        <v>19.5598678588867</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G262" t="n">
-        <v>19.3098392486572</v>
+        <v>19.3098411560059</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>20.5</v>
       </c>
       <c r="G263" t="n">
-        <v>19.7137336730957</v>
+        <v>19.7137317657471</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>20.5</v>
       </c>
       <c r="G266" t="n">
-        <v>19.7137336730957</v>
+        <v>19.7137317657471</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>20.5</v>
       </c>
       <c r="G267" t="n">
-        <v>19.7137336730957</v>
+        <v>19.7137317657471</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>20.1399993896484</v>
       </c>
       <c r="G270" t="n">
-        <v>19.3675384521484</v>
+        <v>19.3675403594971</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G273" t="n">
-        <v>17.569263458252</v>
+        <v>17.5692653656006</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G276" t="n">
-        <v>18.5020599365234</v>
+        <v>18.5020580291748</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>19.4099998474121</v>
       </c>
       <c r="G279" t="n">
-        <v>18.6655387878418</v>
+        <v>18.6655406951904</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G290" t="n">
-        <v>17.194221496582</v>
+        <v>17.1942195892334</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G291" t="n">
-        <v>17.4923305511475</v>
+        <v>17.4923324584961</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G292" t="n">
-        <v>17.569263458252</v>
+        <v>17.5692653656006</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G301" t="n">
-        <v>16.4441394805908</v>
+        <v>16.4441375732422</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G304" t="n">
-        <v>16.7230129241943</v>
+        <v>16.723014831543</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G305" t="n">
-        <v>16.3575916290283</v>
+        <v>16.3575897216797</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G310" t="n">
-        <v>15.5401906967163</v>
+        <v>15.5401916503906</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G314" t="n">
-        <v>15.6555881500244</v>
+        <v>15.6555891036987</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G315" t="n">
-        <v>15.8479166030884</v>
+        <v>15.8479175567627</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>16.2700004577637</v>
       </c>
       <c r="G316" t="n">
-        <v>15.6459732055664</v>
+        <v>15.6459722518921</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>15.0299997329712</v>
       </c>
       <c r="G319" t="n">
-        <v>14.4535322189331</v>
+        <v>14.4535312652588</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G321" t="n">
-        <v>14.4631490707397</v>
+        <v>14.4631471633911</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>15</v>
       </c>
       <c r="G324" t="n">
-        <v>14.4246835708618</v>
+        <v>14.4246826171875</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>14.1361885070801</v>
+        <v>14.1361875534058</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G327" t="n">
-        <v>14.0881052017212</v>
+        <v>14.0881061553955</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G328" t="n">
-        <v>14.2227363586426</v>
+        <v>14.2227373123169</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G333" t="n">
-        <v>12.8571996688843</v>
+        <v>12.8572006225586</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G334" t="n">
-        <v>12.6744890213013</v>
+        <v>12.674488067627</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>14.0100002288818</v>
       </c>
       <c r="G343" t="n">
-        <v>13.4726543426514</v>
+        <v>13.4726533889771</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G344" t="n">
-        <v>13.0399131774902</v>
+        <v>13.0399141311646</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G345" t="n">
-        <v>13.6553649902344</v>
+        <v>13.6553659439087</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G346" t="n">
-        <v>14.5016145706177</v>
+        <v>14.5016136169434</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G347" t="n">
-        <v>14.6362438201904</v>
+        <v>14.6362447738647</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G348" t="n">
-        <v>14.2227363586426</v>
+        <v>14.2227373123169</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G349" t="n">
-        <v>14.5785446166992</v>
+        <v>14.5785455703735</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G350" t="n">
-        <v>14.2708196640015</v>
+        <v>14.2708187103271</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G351" t="n">
-        <v>14.1073389053345</v>
+        <v>14.1073398590088</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G354" t="n">
-        <v>14.2996683120728</v>
+        <v>14.2996673583984</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G355" t="n">
-        <v>13.6842155456543</v>
+        <v>13.68421459198</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G356" t="n">
-        <v>13.7322969436646</v>
+        <v>13.7322978973389</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G363" t="n">
-        <v>13.1841592788696</v>
+        <v>13.1841602325439</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G364" t="n">
-        <v>13.4341878890991</v>
+        <v>13.4341869354248</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G367" t="n">
-        <v>13.5495862960815</v>
+        <v>13.5495853424072</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G369" t="n">
-        <v>14.6747102737427</v>
+        <v>14.674711227417</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G371" t="n">
-        <v>15.6844387054443</v>
+        <v>15.6844367980957</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G376" t="n">
-        <v>15.0305194854736</v>
+        <v>15.0305185317993</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G379" t="n">
-        <v>14.5016145706177</v>
+        <v>14.5016136169434</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G381" t="n">
-        <v>14.8862714767456</v>
+        <v>14.8862724304199</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G382" t="n">
-        <v>14.8958892822266</v>
+        <v>14.8958883285522</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G383" t="n">
-        <v>14.867039680481</v>
+        <v>14.8670387268066</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G385" t="n">
-        <v>14.4439163208008</v>
+        <v>14.4439153671265</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G386" t="n">
-        <v>14.0977230072021</v>
+        <v>14.0977220535278</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G387" t="n">
-        <v>14.1361885070801</v>
+        <v>14.1361875534058</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>14.7700004577637</v>
       </c>
       <c r="G389" t="n">
-        <v>14.2035036087036</v>
+        <v>14.2035045623779</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G390" t="n">
-        <v>14.4631490707397</v>
+        <v>14.4631471633911</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>14.2700004577637</v>
       </c>
       <c r="G391" t="n">
-        <v>13.7226810455322</v>
+        <v>13.7226819992065</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G394" t="n">
-        <v>13.7419137954712</v>
+        <v>13.7419147491455</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>14.25</v>
       </c>
       <c r="G396" t="n">
-        <v>13.7034473419189</v>
+        <v>13.7034482955933</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G398" t="n">
-        <v>13.3668718338013</v>
+        <v>13.3668727874756</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G400" t="n">
-        <v>14.0784902572632</v>
+        <v>14.0784912109375</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G405" t="n">
-        <v>13.5880517959595</v>
+        <v>13.5880508422852</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>13.6553649902344</v>
+        <v>13.6553659439087</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G410" t="n">
-        <v>14.7901077270508</v>
+        <v>14.7901067733765</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G415" t="n">
-        <v>14.8862714767456</v>
+        <v>14.8862724304199</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G416" t="n">
-        <v>14.7516412734985</v>
+        <v>14.7516422271729</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G421" t="n">
-        <v>14.5016145706177</v>
+        <v>14.5016136169434</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G428" t="n">
-        <v>13.8188447952271</v>
+        <v>13.8188457489014</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>14.25</v>
       </c>
       <c r="G430" t="n">
-        <v>13.7034473419189</v>
+        <v>13.7034482955933</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G433" t="n">
-        <v>12.6456384658813</v>
+        <v>12.645637512207</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G438" t="n">
-        <v>12.6456384658813</v>
+        <v>12.645637512207</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G439" t="n">
-        <v>12.8571996688843</v>
+        <v>12.8572006225586</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G442" t="n">
-        <v>12.9725980758667</v>
+        <v>12.9725971221924</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G444" t="n">
-        <v>12.472541809082</v>
+        <v>12.4725427627563</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G445" t="n">
-        <v>12.7802686691284</v>
+        <v>12.7802677154541</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G449" t="n">
-        <v>12.809118270874</v>
+        <v>12.8091173171997</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G451" t="n">
-        <v>12.9629802703857</v>
+        <v>12.9629812240601</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G453" t="n">
-        <v>11.9244031906128</v>
+        <v>11.9244041442871</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G454" t="n">
-        <v>11.6839933395386</v>
+        <v>11.6839923858643</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G455" t="n">
-        <v>11.7513084411621</v>
+        <v>11.7513074874878</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G457" t="n">
-        <v>11.9724855422974</v>
+        <v>11.9724864959717</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G460" t="n">
-        <v>12.1744318008423</v>
+        <v>12.1744327545166</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G462" t="n">
-        <v>12.1455821990967</v>
+        <v>12.145583152771</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G464" t="n">
-        <v>11.9724855422974</v>
+        <v>11.9724864959717</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G467" t="n">
-        <v>12.7514190673828</v>
+        <v>12.7514200210571</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G470" t="n">
-        <v>13.3476390838623</v>
+        <v>13.3476400375366</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G472" t="n">
-        <v>13.1841592788696</v>
+        <v>13.1841602325439</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G474" t="n">
-        <v>12.7782716751099</v>
+        <v>12.7782726287842</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G476" t="n">
-        <v>13.0790500640869</v>
+        <v>13.0790510177612</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G477" t="n">
-        <v>12.9141082763672</v>
+        <v>12.9141073226929</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G478" t="n">
-        <v>12.4871940612793</v>
+        <v>12.4871950149536</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G479" t="n">
-        <v>12.8461894989014</v>
+        <v>12.8461885452271</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G482" t="n">
-        <v>12.8073797225952</v>
+        <v>12.8073787689209</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G494" t="n">
-        <v>11.3519945144653</v>
+        <v>11.3519954681396</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G497" t="n">
-        <v>11.4878311157227</v>
+        <v>11.487832069397</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G501" t="n">
-        <v>11.3519945144653</v>
+        <v>11.3519954681396</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G508" t="n">
-        <v>11.0803241729736</v>
+        <v>11.0803232192993</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G512" t="n">
-        <v>11.0803241729736</v>
+        <v>11.0803232192993</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G516" t="n">
-        <v>10.9735956192017</v>
+        <v>10.973596572876</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G519" t="n">
-        <v>10.9638938903809</v>
+        <v>10.9638929367065</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G524" t="n">
-        <v>10.5854921340942</v>
+        <v>10.5854930877686</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G526" t="n">
-        <v>10.3817386627197</v>
+        <v>10.381739616394</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G542" t="n">
-        <v>9.67830467224121</v>
+        <v>9.67830371856689</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G544" t="n">
-        <v>9.51821231842041</v>
+        <v>9.51821136474609</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G545" t="n">
-        <v>9.54731845855713</v>
+        <v>9.54731941223145</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G550" t="n">
-        <v>9.24653911590576</v>
+        <v>9.24654006958008</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G551" t="n">
-        <v>9.16891860961914</v>
+        <v>9.16891956329346</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>8.91499996185303</v>
       </c>
       <c r="G554" t="n">
-        <v>8.64983177185059</v>
+        <v>8.6498327255249</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G555" t="n">
-        <v>9.08159637451172</v>
+        <v>9.0815954208374</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G556" t="n">
-        <v>9.09129810333252</v>
+        <v>9.09129905700684</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G558" t="n">
-        <v>9.08159637451172</v>
+        <v>9.0815954208374</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G560" t="n">
-        <v>9.24653911590576</v>
+        <v>9.24654006958008</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>9.55500030517578</v>
       </c>
       <c r="G561" t="n">
-        <v>9.27079677581787</v>
+        <v>9.27079582214355</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G566" t="n">
-        <v>9.15921688079834</v>
+        <v>9.15921592712402</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G572" t="n">
-        <v>8.91665172576904</v>
+        <v>8.91665267944336</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>8.90499973297119</v>
       </c>
       <c r="G574" t="n">
-        <v>8.64013004302979</v>
+        <v>8.64012908935547</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G576" t="n">
-        <v>8.66438579559326</v>
+        <v>8.66438674926758</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>8.75</v>
       </c>
       <c r="G579" t="n">
-        <v>8.4897403717041</v>
+        <v>8.48973941802979</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G580" t="n">
-        <v>8.72260093688965</v>
+        <v>8.72260189056396</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.82499980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>8.56250953674316</v>
+        <v>8.56250858306885</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G584" t="n">
-        <v>8.80022144317627</v>
+        <v>8.80022239685059</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.91499996185303</v>
       </c>
       <c r="G585" t="n">
-        <v>8.64983177185059</v>
+        <v>8.6498327255249</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G587" t="n">
-        <v>8.7614107131958</v>
+        <v>8.76141166687012</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G591" t="n">
-        <v>8.387864112854</v>
+        <v>8.38786315917969</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G593" t="n">
-        <v>8.74200630187988</v>
+        <v>8.7420072555542</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>8.56736087799072</v>
+        <v>8.56735992431641</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G598" t="n">
-        <v>8.7614107131958</v>
+        <v>8.76141166687012</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>8.47500038146973</v>
       </c>
       <c r="G601" t="n">
-        <v>8.22291946411133</v>
+        <v>8.22292041778564</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>8.28499984741211</v>
       </c>
       <c r="G602" t="n">
-        <v>8.03857040405273</v>
+        <v>8.03857135772705</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G605" t="n">
-        <v>7.67472505569458</v>
+        <v>7.67472457885742</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G606" t="n">
-        <v>7.46126842498779</v>
+        <v>7.46126890182495</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G609" t="n">
-        <v>7.73779201507568</v>
+        <v>7.73779153823853</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>8.00500011444092</v>
       </c>
       <c r="G611" t="n">
-        <v>7.76689910888672</v>
+        <v>7.76689958572388</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G614" t="n">
-        <v>7.73779201507568</v>
+        <v>7.73779153823853</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>7.9850001335144</v>
       </c>
       <c r="G615" t="n">
-        <v>7.7474946975708</v>
+        <v>7.74749422073364</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G617" t="n">
-        <v>7.95609855651855</v>
+        <v>7.95609951019287</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>8.14500045776367</v>
       </c>
       <c r="G618" t="n">
-        <v>7.90273571014404</v>
+        <v>7.90273523330688</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>8.17500019073486</v>
       </c>
       <c r="G619" t="n">
-        <v>7.93184328079224</v>
+        <v>7.93184280395508</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>7.44671535491943</v>
+        <v>7.44671487808228</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>7.64499998092651</v>
       </c>
       <c r="G624" t="n">
-        <v>7.41760730743408</v>
+        <v>7.41760683059692</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G625" t="n">
-        <v>7.41275548934937</v>
+        <v>7.41275596618652</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>7.31087875366211</v>
+        <v>7.31087923049927</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G631" t="n">
-        <v>7.53888893127441</v>
+        <v>7.53888940811157</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G632" t="n">
-        <v>7.42245817184448</v>
+        <v>7.42245864868164</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>7.77500009536743</v>
       </c>
       <c r="G633" t="n">
-        <v>7.54374074935913</v>
+        <v>7.54374027252197</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>7.875</v>
       </c>
       <c r="G634" t="n">
-        <v>7.64076614379883</v>
+        <v>7.64076566696167</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G637" t="n">
-        <v>7.05861234664917</v>
+        <v>7.05861282348633</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>6.84515619277954</v>
+        <v>6.84515571594238</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G641" t="n">
-        <v>6.98099184036255</v>
+        <v>6.98099231719971</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>7.17989492416382</v>
+        <v>7.17989444732666</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G652" t="n">
-        <v>6.96643781661987</v>
+        <v>6.96643829345703</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G653" t="n">
-        <v>6.78694105148315</v>
+        <v>6.786940574646</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G658" t="n">
-        <v>6.78694105148315</v>
+        <v>6.786940574646</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G663" t="n">
-        <v>6.67536115646362</v>
+        <v>6.67536163330078</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>8.65499973297119</v>
       </c>
       <c r="G665" t="n">
-        <v>8.39756488800049</v>
+        <v>8.3975658416748</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G666" t="n">
-        <v>8.19866371154785</v>
+        <v>8.19866275787354</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G667" t="n">
-        <v>8.52855110168457</v>
+        <v>8.52855014801025</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>9.07499980926514</v>
       </c>
       <c r="G671" t="n">
-        <v>8.80507278442383</v>
+        <v>8.80507373809814</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G673" t="n">
-        <v>8.74200630187988</v>
+        <v>8.7420072555542</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>9.04763793945312</v>
+        <v>9.04763698577881</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G678" t="n">
-        <v>9.04763793945312</v>
+        <v>9.04763698577881</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G679" t="n">
-        <v>8.94090938568115</v>
+        <v>8.94090843200684</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G686" t="n">
-        <v>6.82575130462646</v>
+        <v>6.82575082778931</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G688" t="n">
-        <v>6.44250011444092</v>
+        <v>6.44249963760376</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G689" t="n">
-        <v>6.66080760955811</v>
+        <v>6.66080713272095</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>6.64499998092651</v>
       </c>
       <c r="G690" t="n">
-        <v>6.44735097885132</v>
+        <v>6.44735145568848</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G691" t="n">
-        <v>6.46190500259399</v>
+        <v>6.46190452575684</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>6.32606935501099</v>
+        <v>6.32606887817383</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G696" t="n">
-        <v>6.09805870056152</v>
+        <v>6.09805917739868</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G697" t="n">
-        <v>5.84094095230103</v>
+        <v>5.84094142913818</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G699" t="n">
-        <v>6.0107364654541</v>
+        <v>6.01073598861694</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>6.35500001907349</v>
       </c>
       <c r="G702" t="n">
-        <v>6.16597700119019</v>
+        <v>6.16597652435303</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G703" t="n">
-        <v>6.07380294799805</v>
+        <v>6.07380247116089</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G705" t="n">
-        <v>5.97677707672119</v>
+        <v>5.97677659988403</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>6.125</v>
       </c>
       <c r="G709" t="n">
-        <v>5.94281816482544</v>
+        <v>5.94281768798828</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G715" t="n">
-        <v>6.43279790878296</v>
+        <v>6.4327974319458</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G716" t="n">
-        <v>6.27755641937256</v>
+        <v>6.2775559425354</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G719" t="n">
-        <v>6.50071477890015</v>
+        <v>6.5007152557373</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G724" t="n">
-        <v>6.67536115646362</v>
+        <v>6.67536163330078</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -28166,6 +28166,32 @@
         <v>5.8600001335144</v>
       </c>
       <c r="H1069" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1070" t="n">
+        <v>619264</v>
+      </c>
+      <c r="C1070" t="n">
+        <v>6.01000022888184</v>
+      </c>
+      <c r="D1070" t="n">
+        <v>5.86999988555908</v>
+      </c>
+      <c r="E1070" t="n">
+        <v>5.95499992370605</v>
+      </c>
+      <c r="F1070" t="n">
+        <v>5.8600001335144</v>
+      </c>
+      <c r="G1070" t="n">
+        <v>5.8600001335144</v>
+      </c>
+      <c r="H1070" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DNR.MI.xlsx
+++ b/data/DNR.MI.xlsx
@@ -421,7 +421,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G2" t="n">
-        <v>12.5555381774902</v>
+        <v>12.5555391311646</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>13.25</v>
       </c>
       <c r="G3" t="n">
-        <v>12.6606464385986</v>
+        <v>12.6606454849243</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>12.612868309021</v>
+        <v>12.6128692626953</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G5" t="n">
-        <v>12.4886522293091</v>
+        <v>12.4886512756348</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G7" t="n">
-        <v>12.5077610015869</v>
+        <v>12.5077619552612</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G9" t="n">
-        <v>12.3548793792725</v>
+        <v>12.3548784255981</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>12.851749420166</v>
+        <v>12.8517484664917</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G16" t="n">
-        <v>13.4155054092407</v>
+        <v>13.415506362915</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G21" t="n">
-        <v>14.0748147964478</v>
+        <v>14.0748138427734</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>14.1417016983032</v>
+        <v>14.1417026519775</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G26" t="n">
-        <v>14.1608114242554</v>
+        <v>14.1608123779297</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G31" t="n">
-        <v>13.5492792129517</v>
+        <v>13.5492782592773</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G33" t="n">
-        <v>13.740382194519</v>
+        <v>13.7403831481934</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G37" t="n">
-        <v>13.2912883758545</v>
+        <v>13.2912893295288</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>15.1927738189697</v>
+        <v>15.1927728652954</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>14.7627897262573</v>
+        <v>14.7627906799316</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G53" t="n">
-        <v>14.2372531890869</v>
+        <v>14.2372541427612</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G54" t="n">
-        <v>14.0079298019409</v>
+        <v>14.0079288482666</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G56" t="n">
-        <v>15.1163311004639</v>
+        <v>15.1163330078125</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G57" t="n">
-        <v>14.7436800003052</v>
+        <v>14.7436790466309</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G61" t="n">
-        <v>15.5558710098267</v>
+        <v>15.555871963501</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G65" t="n">
-        <v>15.7469758987427</v>
+        <v>15.746973991394</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>16.2900009155273</v>
       </c>
       <c r="G66" t="n">
-        <v>15.5654268264771</v>
+        <v>15.5654277801514</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G68" t="n">
-        <v>15.5176496505737</v>
+        <v>15.517650604248</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G69" t="n">
-        <v>15.3552131652832</v>
+        <v>15.3552122116089</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G71" t="n">
-        <v>15.0972232818604</v>
+        <v>15.097222328186</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G72" t="n">
-        <v>14.6003513336182</v>
+        <v>14.6003503799438</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G73" t="n">
-        <v>14.3519163131714</v>
+        <v>14.3519172668457</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G80" t="n">
-        <v>13.9888181686401</v>
+        <v>13.9888191223145</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G87" t="n">
-        <v>13.6448307037354</v>
+        <v>13.644829750061</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G88" t="n">
-        <v>14.6003513336182</v>
+        <v>14.6003503799438</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>15.5699996948242</v>
       </c>
       <c r="G90" t="n">
-        <v>14.8774528503418</v>
+        <v>14.8774518966675</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G92" t="n">
-        <v>14.5621309280396</v>
+        <v>14.5621299743652</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G94" t="n">
-        <v>14.6003513336182</v>
+        <v>14.6003503799438</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G99" t="n">
-        <v>14.9347829818726</v>
+        <v>14.9347839355469</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G100" t="n">
-        <v>14.9347829818726</v>
+        <v>14.9347839355469</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G101" t="n">
-        <v>15.326548576355</v>
+        <v>15.3265476226807</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G103" t="n">
-        <v>15.3074378967285</v>
+        <v>15.3074369430542</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G105" t="n">
-        <v>14.5907964706421</v>
+        <v>14.5907974243164</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G106" t="n">
-        <v>14.2754745483398</v>
+        <v>14.2754735946655</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G107" t="n">
-        <v>14.6576833724976</v>
+        <v>14.6576824188232</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G108" t="n">
-        <v>14.7627897262573</v>
+        <v>14.7627906799316</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G109" t="n">
-        <v>14.8487863540649</v>
+        <v>14.8487854003906</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G110" t="n">
-        <v>15.0876655578613</v>
+        <v>15.08766746521</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G111" t="n">
-        <v>14.9443397521973</v>
+        <v>14.9443378448486</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G113" t="n">
-        <v>14.7914543151855</v>
+        <v>14.7914552688599</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G117" t="n">
-        <v>14.4474687576294</v>
+        <v>14.4474668502808</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>14.5</v>
       </c>
       <c r="G119" t="n">
-        <v>13.8550453186035</v>
+        <v>13.8550462722778</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>13.7594928741455</v>
+        <v>13.7594938278198</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>14.25</v>
       </c>
       <c r="G121" t="n">
-        <v>13.6161661148071</v>
+        <v>13.6161651611328</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G122" t="n">
-        <v>13.9314880371094</v>
+        <v>13.9314870834351</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>14.5</v>
       </c>
       <c r="G124" t="n">
-        <v>13.8550453186035</v>
+        <v>13.8550462722778</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G129" t="n">
-        <v>15.1641082763672</v>
+        <v>15.1641092300415</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G131" t="n">
-        <v>15.0876655578613</v>
+        <v>15.08766746521</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>14.953893661499</v>
+        <v>14.9538946151733</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>15.6899995803833</v>
       </c>
       <c r="G135" t="n">
-        <v>14.9921140670776</v>
+        <v>14.992115020752</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G136" t="n">
-        <v>15.2692155838013</v>
+        <v>15.269214630127</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G139" t="n">
-        <v>16.301176071167</v>
+        <v>16.3011779785156</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G141" t="n">
-        <v>16.2534027099609</v>
+        <v>16.2534008026123</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G142" t="n">
-        <v>16.9795989990234</v>
+        <v>16.9795970916748</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G146" t="n">
-        <v>16.769380569458</v>
+        <v>16.7693824768066</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>16.6100006103516</v>
       </c>
       <c r="G149" t="n">
-        <v>15.8711948394775</v>
+        <v>15.8711938858032</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G151" t="n">
-        <v>16.2056255340576</v>
+        <v>16.205623626709</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G156" t="n">
-        <v>17.6962375640869</v>
+        <v>17.6962394714355</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G158" t="n">
-        <v>17.466911315918</v>
+        <v>17.4669132232666</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G159" t="n">
-        <v>17.3904705047607</v>
+        <v>17.3904724121094</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G160" t="n">
-        <v>17.3904705047607</v>
+        <v>17.3904724121094</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G162" t="n">
-        <v>17.5815734863281</v>
+        <v>17.5815753936768</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G163" t="n">
-        <v>17.2089214324951</v>
+        <v>17.2089233398438</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>17.8204536437988</v>
+        <v>17.8204574584961</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>19.5</v>
       </c>
       <c r="G169" t="n">
-        <v>18.6326484680176</v>
+        <v>18.6326465606689</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G170" t="n">
-        <v>18.9001941680908</v>
+        <v>18.9001922607422</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G171" t="n">
-        <v>18.7664203643799</v>
+        <v>18.7664184570312</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>19.75</v>
       </c>
       <c r="G172" t="n">
-        <v>18.8715267181396</v>
+        <v>18.8715286254883</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>17.7726821899414</v>
+        <v>17.7726802825928</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G177" t="n">
-        <v>18.3077716827393</v>
+        <v>18.3077697753906</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>18.75</v>
       </c>
       <c r="G178" t="n">
-        <v>17.9160060882568</v>
+        <v>17.9160079956055</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G179" t="n">
-        <v>18.8524169921875</v>
+        <v>18.8524150848389</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G180" t="n">
-        <v>18.7664203643799</v>
+        <v>18.7664184570312</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G181" t="n">
-        <v>18.8237533569336</v>
+        <v>18.823751449585</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>18.75</v>
       </c>
       <c r="G182" t="n">
-        <v>17.9160060882568</v>
+        <v>17.9160079956055</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G184" t="n">
-        <v>17.1898136138916</v>
+        <v>17.1898097991943</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>18</v>
       </c>
       <c r="G187" t="n">
-        <v>17.1993675231934</v>
+        <v>17.199369430542</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G188" t="n">
-        <v>17.658016204834</v>
+        <v>17.6580142974854</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G189" t="n">
-        <v>17.658016204834</v>
+        <v>17.6580142974854</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G190" t="n">
-        <v>17.648458480835</v>
+        <v>17.6484603881836</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G192" t="n">
-        <v>16.5305004119873</v>
+        <v>16.5305042266846</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>16.3871746063232</v>
+        <v>16.3871726989746</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G195" t="n">
-        <v>16.301176071167</v>
+        <v>16.3011779785156</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G196" t="n">
-        <v>16.2056255340576</v>
+        <v>16.205623626709</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G198" t="n">
-        <v>16.301176071167</v>
+        <v>16.3011779785156</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G199" t="n">
-        <v>16.6069450378418</v>
+        <v>16.6069431304932</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>16.6260528564453</v>
+        <v>16.6260547637939</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G203" t="n">
-        <v>16.7407169342041</v>
+        <v>16.7407188415527</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G205" t="n">
-        <v>17.0369281768799</v>
+        <v>17.0369262695312</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G206" t="n">
-        <v>17.2375869750977</v>
+        <v>17.2375888824463</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G207" t="n">
-        <v>16.6547222137451</v>
+        <v>16.6547183990479</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G208" t="n">
-        <v>16.9031581878662</v>
+        <v>16.9031562805176</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G209" t="n">
-        <v>16.9222660064697</v>
+        <v>16.9222640991211</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G210" t="n">
-        <v>17.2375869750977</v>
+        <v>17.2375888824463</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G211" t="n">
-        <v>17.3713607788086</v>
+        <v>17.37135887146</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>17.2949180603027</v>
+        <v>17.2949199676514</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G222" t="n">
-        <v>18.5789890289307</v>
+        <v>18.5789909362793</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G223" t="n">
-        <v>18.6559219360352</v>
+        <v>18.6559238433838</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G225" t="n">
-        <v>18.6559219360352</v>
+        <v>18.6559238433838</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G229" t="n">
-        <v>18.8097839355469</v>
+        <v>18.8097877502441</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>19.75</v>
       </c>
       <c r="G233" t="n">
-        <v>18.9924983978271</v>
+        <v>18.9925003051758</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G236" t="n">
-        <v>20.1753215789795</v>
+        <v>20.1753234863281</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>19.3290729522705</v>
+        <v>19.3290748596191</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G240" t="n">
-        <v>19.4637031555176</v>
+        <v>19.4637050628662</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>19.4252414703369</v>
+        <v>19.4252376556396</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G246" t="n">
-        <v>17.8481388092041</v>
+        <v>17.8481407165527</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G248" t="n">
-        <v>18.5789890289307</v>
+        <v>18.5789909362793</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G255" t="n">
-        <v>19.4637031555176</v>
+        <v>19.4637050628662</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G256" t="n">
-        <v>19.4637031555176</v>
+        <v>19.4637050628662</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G258" t="n">
-        <v>20.1368560791016</v>
+        <v>20.1368579864502</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G264" t="n">
-        <v>19.4829387664795</v>
+        <v>19.4829368591309</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>19.8098964691162</v>
+        <v>19.8098983764648</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G272" t="n">
-        <v>17.5019474029541</v>
+        <v>17.5019493103027</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G276" t="n">
-        <v>18.5020580291748</v>
+        <v>18.5020599365234</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G280" t="n">
-        <v>18.6559219360352</v>
+        <v>18.6559238433838</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G282" t="n">
-        <v>17.8866081237793</v>
+        <v>17.8866062164307</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G286" t="n">
-        <v>17.059591293335</v>
+        <v>17.0595932006836</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G289" t="n">
-        <v>16.6460838317871</v>
+        <v>16.6460819244385</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G290" t="n">
-        <v>17.1942195892334</v>
+        <v>17.194221496582</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G291" t="n">
-        <v>17.4923324584961</v>
+        <v>17.4923305511475</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G293" t="n">
-        <v>17.2134532928467</v>
+        <v>17.213451385498</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G295" t="n">
-        <v>17.1749897003174</v>
+        <v>17.1749877929688</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G296" t="n">
-        <v>17.2807674407959</v>
+        <v>17.2807693481445</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G300" t="n">
-        <v>16.6460838317871</v>
+        <v>16.6460819244385</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G301" t="n">
-        <v>16.4441375732422</v>
+        <v>16.4441394805908</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G305" t="n">
-        <v>16.3575916290283</v>
+        <v>16.3575897216797</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>16.75</v>
       </c>
       <c r="G307" t="n">
-        <v>16.1075611114502</v>
+        <v>16.1075630187988</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G309" t="n">
-        <v>15.7132873535156</v>
+        <v>15.7132883071899</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G315" t="n">
-        <v>15.8479175567627</v>
+        <v>15.8479166030884</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>16.2700004577637</v>
       </c>
       <c r="G316" t="n">
-        <v>15.6459722518921</v>
+        <v>15.6459732055664</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G318" t="n">
-        <v>14.4150648117065</v>
+        <v>14.4150657653809</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G320" t="n">
-        <v>14.318902015686</v>
+        <v>14.3189010620117</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G322" t="n">
-        <v>14.5689296722412</v>
+        <v>14.5689287185669</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G328" t="n">
-        <v>14.2227373123169</v>
+        <v>14.2227363586426</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G331" t="n">
-        <v>13.174542427063</v>
+        <v>13.1745433807373</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G334" t="n">
-        <v>12.674488067627</v>
+        <v>12.6744890213013</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G338" t="n">
-        <v>13.9053936004639</v>
+        <v>13.9053945541382</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G339" t="n">
-        <v>13.8284616470337</v>
+        <v>13.828462600708</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>14.0100002288818</v>
       </c>
       <c r="G343" t="n">
-        <v>13.4726533889771</v>
+        <v>13.4726543426514</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G344" t="n">
-        <v>13.0399141311646</v>
+        <v>13.0399131774902</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G345" t="n">
-        <v>13.655366897583</v>
+        <v>13.6553659439087</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G346" t="n">
-        <v>14.5016136169434</v>
+        <v>14.5016145706177</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G348" t="n">
-        <v>14.2227373123169</v>
+        <v>14.2227363586426</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G350" t="n">
-        <v>14.2708187103271</v>
+        <v>14.2708196640015</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G352" t="n">
-        <v>14.2515859603882</v>
+        <v>14.2515869140625</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G354" t="n">
-        <v>14.2996673583984</v>
+        <v>14.2996683120728</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G356" t="n">
-        <v>13.7322978973389</v>
+        <v>13.7322969436646</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G357" t="n">
-        <v>13.7611474990845</v>
+        <v>13.7611465454102</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>14.3900003433228</v>
       </c>
       <c r="G358" t="n">
-        <v>13.8380794525146</v>
+        <v>13.8380784988403</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G363" t="n">
-        <v>13.1841602325439</v>
+        <v>13.1841592788696</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G366" t="n">
-        <v>13.5015020370483</v>
+        <v>13.5015029907227</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G367" t="n">
-        <v>13.5495853424072</v>
+        <v>13.5495862960815</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G369" t="n">
-        <v>14.674711227417</v>
+        <v>14.6747102737427</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G370" t="n">
-        <v>14.9151210784912</v>
+        <v>14.9151220321655</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G371" t="n">
-        <v>15.68443775177</v>
+        <v>15.6844387054443</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G373" t="n">
-        <v>14.9151210784912</v>
+        <v>14.9151220321655</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G375" t="n">
-        <v>14.8381910324097</v>
+        <v>14.8381900787354</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G376" t="n">
-        <v>15.0305185317993</v>
+        <v>15.0305194854736</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G378" t="n">
-        <v>14.9632043838501</v>
+        <v>14.9632034301758</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G379" t="n">
-        <v>14.5016136169434</v>
+        <v>14.5016145706177</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>15.0900001525879</v>
       </c>
       <c r="G380" t="n">
-        <v>14.5112314224243</v>
+        <v>14.51123046875</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G381" t="n">
-        <v>14.8862714767456</v>
+        <v>14.8862724304199</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G382" t="n">
-        <v>14.8958892822266</v>
+        <v>14.8958883285522</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G383" t="n">
-        <v>14.867039680481</v>
+        <v>14.8670387268066</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G385" t="n">
-        <v>14.4439153671265</v>
+        <v>14.4439163208008</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G394" t="n">
-        <v>13.7419147491455</v>
+        <v>13.7419137954712</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G398" t="n">
-        <v>13.3668727874756</v>
+        <v>13.3668718338013</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G399" t="n">
-        <v>14.0592575073242</v>
+        <v>14.0592565536499</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G400" t="n">
-        <v>14.0784902572632</v>
+        <v>14.0784912109375</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G404" t="n">
-        <v>13.3764886856079</v>
+        <v>13.3764896392822</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>13.655366897583</v>
+        <v>13.6553659439087</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G408" t="n">
-        <v>14.1650381088257</v>
+        <v>14.1650371551514</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G410" t="n">
-        <v>14.7901077270508</v>
+        <v>14.7901067733765</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G415" t="n">
-        <v>14.8862714767456</v>
+        <v>14.8862724304199</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G420" t="n">
-        <v>14.9632043838501</v>
+        <v>14.9632034301758</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G421" t="n">
-        <v>14.5016136169434</v>
+        <v>14.5016145706177</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G423" t="n">
-        <v>14.2323532104492</v>
+        <v>14.2323541641235</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G424" t="n">
-        <v>14.0688743591309</v>
+        <v>14.0688734054565</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G428" t="n">
-        <v>13.8188457489014</v>
+        <v>13.8188447952271</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>14.1899995803833</v>
       </c>
       <c r="G431" t="n">
-        <v>13.6457481384277</v>
+        <v>13.6457500457764</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G432" t="n">
-        <v>12.6937198638916</v>
+        <v>12.6937208175659</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G433" t="n">
-        <v>12.645637512207</v>
+        <v>12.6456384658813</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G437" t="n">
-        <v>12.7033376693726</v>
+        <v>12.7033367156982</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G438" t="n">
-        <v>12.645637512207</v>
+        <v>12.6456384658813</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G441" t="n">
-        <v>12.3763780593872</v>
+        <v>12.3763771057129</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G442" t="n">
-        <v>12.9725971221924</v>
+        <v>12.9725980758667</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G444" t="n">
-        <v>12.472541809082</v>
+        <v>12.4725427627563</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G447" t="n">
-        <v>12.7033376693726</v>
+        <v>12.7033367156982</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G449" t="n">
-        <v>12.8091173171997</v>
+        <v>12.809118270874</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G451" t="n">
-        <v>12.9629812240601</v>
+        <v>12.9629802703857</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G452" t="n">
-        <v>12.6937198638916</v>
+        <v>12.6937208175659</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G453" t="n">
-        <v>11.9244041442871</v>
+        <v>11.9244031906128</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G454" t="n">
-        <v>11.6839933395386</v>
+        <v>11.6839923858643</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G455" t="n">
-        <v>11.7513084411621</v>
+        <v>11.7513074874878</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G459" t="n">
-        <v>11.8859386444092</v>
+        <v>11.8859376907349</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G461" t="n">
-        <v>12.1552000045776</v>
+        <v>12.1551990509033</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G462" t="n">
-        <v>12.1455821990967</v>
+        <v>12.145583152771</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G463" t="n">
-        <v>12.0494184494019</v>
+        <v>12.0494165420532</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G468" t="n">
-        <v>12.7706518173218</v>
+        <v>12.7706527709961</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G470" t="n">
-        <v>13.3476390838623</v>
+        <v>13.3476400375366</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G472" t="n">
-        <v>13.1841602325439</v>
+        <v>13.1841592788696</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G474" t="n">
-        <v>12.7782726287842</v>
+        <v>12.7782716751099</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G476" t="n">
-        <v>13.0790510177612</v>
+        <v>13.0790500640869</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G477" t="n">
-        <v>12.9141073226929</v>
+        <v>12.9141082763672</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G478" t="n">
-        <v>12.4871950149536</v>
+        <v>12.4871940612793</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G479" t="n">
-        <v>12.8461885452271</v>
+        <v>12.8461894989014</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G482" t="n">
-        <v>12.8073787689209</v>
+        <v>12.8073797225952</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G494" t="n">
-        <v>11.3519954681396</v>
+        <v>11.3519945144653</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G497" t="n">
-        <v>11.487832069397</v>
+        <v>11.4878311157227</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G501" t="n">
-        <v>11.3519954681396</v>
+        <v>11.3519945144653</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G508" t="n">
-        <v>11.0803232192993</v>
+        <v>11.0803241729736</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G512" t="n">
-        <v>11.0803232192993</v>
+        <v>11.0803241729736</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G516" t="n">
-        <v>10.973596572876</v>
+        <v>10.9735956192017</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G519" t="n">
-        <v>10.9638929367065</v>
+        <v>10.9638938903809</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G524" t="n">
-        <v>10.5854930877686</v>
+        <v>10.5854921340942</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G526" t="n">
-        <v>10.381739616394</v>
+        <v>10.3817386627197</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G542" t="n">
-        <v>9.67830371856689</v>
+        <v>9.67830467224121</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G544" t="n">
-        <v>9.51821136474609</v>
+        <v>9.51821231842041</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G545" t="n">
-        <v>9.54731941223145</v>
+        <v>9.54731845855713</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G550" t="n">
-        <v>9.24654006958008</v>
+        <v>9.24653911590576</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G551" t="n">
-        <v>9.16891956329346</v>
+        <v>9.16891860961914</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>8.91499996185303</v>
       </c>
       <c r="G554" t="n">
-        <v>8.6498327255249</v>
+        <v>8.64983177185059</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G555" t="n">
-        <v>9.0815954208374</v>
+        <v>9.08159637451172</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G556" t="n">
-        <v>9.09129905700684</v>
+        <v>9.09129810333252</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G558" t="n">
-        <v>9.0815954208374</v>
+        <v>9.08159637451172</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G560" t="n">
-        <v>9.24654006958008</v>
+        <v>9.24653911590576</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>9.55500030517578</v>
       </c>
       <c r="G561" t="n">
-        <v>9.27079582214355</v>
+        <v>9.27079677581787</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G566" t="n">
-        <v>9.15921592712402</v>
+        <v>9.15921688079834</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G572" t="n">
-        <v>8.91665267944336</v>
+        <v>8.91665172576904</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>8.90499973297119</v>
       </c>
       <c r="G574" t="n">
-        <v>8.64012908935547</v>
+        <v>8.64013004302979</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G576" t="n">
-        <v>8.66438674926758</v>
+        <v>8.66438579559326</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>8.75</v>
       </c>
       <c r="G579" t="n">
-        <v>8.48973941802979</v>
+        <v>8.4897403717041</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G580" t="n">
-        <v>8.72260189056396</v>
+        <v>8.72260093688965</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.82499980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>8.56250858306885</v>
+        <v>8.56250953674316</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G584" t="n">
-        <v>8.80022239685059</v>
+        <v>8.80022144317627</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.91499996185303</v>
       </c>
       <c r="G585" t="n">
-        <v>8.6498327255249</v>
+        <v>8.64983177185059</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G587" t="n">
-        <v>8.76141166687012</v>
+        <v>8.7614107131958</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G591" t="n">
-        <v>8.38786315917969</v>
+        <v>8.387864112854</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G593" t="n">
-        <v>8.7420072555542</v>
+        <v>8.74200630187988</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>8.56735992431641</v>
+        <v>8.56736087799072</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G598" t="n">
-        <v>8.76141166687012</v>
+        <v>8.7614107131958</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>8.47500038146973</v>
       </c>
       <c r="G601" t="n">
-        <v>8.22292041778564</v>
+        <v>8.22291946411133</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>8.28499984741211</v>
       </c>
       <c r="G602" t="n">
-        <v>8.03857135772705</v>
+        <v>8.03857040405273</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G605" t="n">
-        <v>7.67472457885742</v>
+        <v>7.67472505569458</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G606" t="n">
-        <v>7.46126890182495</v>
+        <v>7.46126842498779</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G609" t="n">
-        <v>7.73779153823853</v>
+        <v>7.73779201507568</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>8.00500011444092</v>
       </c>
       <c r="G611" t="n">
-        <v>7.76689958572388</v>
+        <v>7.76689910888672</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G614" t="n">
-        <v>7.73779153823853</v>
+        <v>7.73779201507568</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>7.9850001335144</v>
       </c>
       <c r="G615" t="n">
-        <v>7.74749422073364</v>
+        <v>7.7474946975708</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G617" t="n">
-        <v>7.95609951019287</v>
+        <v>7.95609855651855</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>8.14500045776367</v>
       </c>
       <c r="G618" t="n">
-        <v>7.90273523330688</v>
+        <v>7.90273571014404</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>8.17500019073486</v>
       </c>
       <c r="G619" t="n">
-        <v>7.93184280395508</v>
+        <v>7.93184328079224</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>7.44671487808228</v>
+        <v>7.44671535491943</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>7.64499998092651</v>
       </c>
       <c r="G624" t="n">
-        <v>7.41760683059692</v>
+        <v>7.41760730743408</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G625" t="n">
-        <v>7.41275596618652</v>
+        <v>7.41275548934937</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>7.31087923049927</v>
+        <v>7.31087875366211</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G631" t="n">
-        <v>7.53888940811157</v>
+        <v>7.53888893127441</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G632" t="n">
-        <v>7.42245864868164</v>
+        <v>7.42245817184448</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>7.77500009536743</v>
       </c>
       <c r="G633" t="n">
-        <v>7.54374027252197</v>
+        <v>7.54374074935913</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>7.875</v>
       </c>
       <c r="G634" t="n">
-        <v>7.64076566696167</v>
+        <v>7.64076614379883</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G637" t="n">
-        <v>7.05861282348633</v>
+        <v>7.05861234664917</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>6.84515571594238</v>
+        <v>6.84515619277954</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G641" t="n">
-        <v>6.98099231719971</v>
+        <v>6.98099184036255</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>7.17989444732666</v>
+        <v>7.17989492416382</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G652" t="n">
-        <v>6.96643829345703</v>
+        <v>6.96643781661987</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G653" t="n">
-        <v>6.786940574646</v>
+        <v>6.78694105148315</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G658" t="n">
-        <v>6.786940574646</v>
+        <v>6.78694105148315</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G663" t="n">
-        <v>6.67536163330078</v>
+        <v>6.67536115646362</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>8.65499973297119</v>
       </c>
       <c r="G665" t="n">
-        <v>8.3975658416748</v>
+        <v>8.39756488800049</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G666" t="n">
-        <v>8.19866275787354</v>
+        <v>8.19866371154785</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G667" t="n">
-        <v>8.52855014801025</v>
+        <v>8.52855110168457</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>9.07499980926514</v>
       </c>
       <c r="G671" t="n">
-        <v>8.80507373809814</v>
+        <v>8.80507278442383</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G673" t="n">
-        <v>8.7420072555542</v>
+        <v>8.74200630187988</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>9.04763698577881</v>
+        <v>9.04763793945312</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G678" t="n">
-        <v>9.04763698577881</v>
+        <v>9.04763793945312</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G679" t="n">
-        <v>8.94090843200684</v>
+        <v>8.94090938568115</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G686" t="n">
-        <v>6.82575082778931</v>
+        <v>6.82575130462646</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G688" t="n">
-        <v>6.44249963760376</v>
+        <v>6.44250011444092</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G689" t="n">
-        <v>6.66080713272095</v>
+        <v>6.66080760955811</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>6.64499998092651</v>
       </c>
       <c r="G690" t="n">
-        <v>6.44735145568848</v>
+        <v>6.44735097885132</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G691" t="n">
-        <v>6.46190452575684</v>
+        <v>6.46190500259399</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>6.32606887817383</v>
+        <v>6.32606935501099</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G696" t="n">
-        <v>6.09805917739868</v>
+        <v>6.09805870056152</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G697" t="n">
-        <v>5.84094142913818</v>
+        <v>5.84094095230103</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G699" t="n">
-        <v>6.01073598861694</v>
+        <v>6.0107364654541</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>6.35500001907349</v>
       </c>
       <c r="G702" t="n">
-        <v>6.16597652435303</v>
+        <v>6.16597700119019</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G703" t="n">
-        <v>6.07380247116089</v>
+        <v>6.07380294799805</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G705" t="n">
-        <v>5.97677659988403</v>
+        <v>5.97677707672119</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>6.125</v>
       </c>
       <c r="G709" t="n">
-        <v>5.94281768798828</v>
+        <v>5.94281816482544</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G715" t="n">
-        <v>6.4327974319458</v>
+        <v>6.43279790878296</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G716" t="n">
-        <v>6.2775559425354</v>
+        <v>6.27755641937256</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G719" t="n">
-        <v>6.5007152557373</v>
+        <v>6.50071477890015</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G724" t="n">
-        <v>6.67536163330078</v>
+        <v>6.67536115646362</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -28244,6 +28244,32 @@
         <v>5.90999984741211</v>
       </c>
       <c r="H1072" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1073" t="n">
+        <v>519219</v>
+      </c>
+      <c r="C1073" t="n">
+        <v>6.08500003814697</v>
+      </c>
+      <c r="D1073" t="n">
+        <v>5.90500020980835</v>
+      </c>
+      <c r="E1073" t="n">
+        <v>5.98999977111816</v>
+      </c>
+      <c r="F1073" t="n">
+        <v>6.01999998092651</v>
+      </c>
+      <c r="G1073" t="n">
+        <v>6.01999998092651</v>
+      </c>
+      <c r="H1073" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DNR.MI.xlsx
+++ b/data/DNR.MI.xlsx
@@ -25113,8 +25113,31 @@
       <c r="E1076" t="n">
         <v>5.91499996185303</v>
       </c>
-      <c r="F1076"/>
+      <c r="F1076" t="n">
+        <v>5.94000005722046</v>
+      </c>
       <c r="G1076" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1077" t="n">
+        <v>610734</v>
+      </c>
+      <c r="C1077" t="n">
+        <v>6.17500019073486</v>
+      </c>
+      <c r="D1077" t="n">
+        <v>5.94999980926514</v>
+      </c>
+      <c r="E1077" t="n">
+        <v>5.96000003814697</v>
+      </c>
+      <c r="F1077"/>
+      <c r="G1077" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DNR.MI.xlsx
+++ b/data/DNR.MI.xlsx
@@ -25136,8 +25136,31 @@
       <c r="E1077" t="n">
         <v>5.96000003814697</v>
       </c>
-      <c r="F1077"/>
+      <c r="F1077" t="n">
+        <v>6.11999988555908</v>
+      </c>
       <c r="G1077" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1078" t="n">
+        <v>430685</v>
+      </c>
+      <c r="C1078" t="n">
+        <v>6.15500020980835</v>
+      </c>
+      <c r="D1078" t="n">
+        <v>5.84999990463257</v>
+      </c>
+      <c r="E1078" t="n">
+        <v>6.15500020980835</v>
+      </c>
+      <c r="F1078"/>
+      <c r="G1078" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DNR.MI.xlsx
+++ b/data/DNR.MI.xlsx
@@ -25159,8 +25159,31 @@
       <c r="E1078" t="n">
         <v>6.15500020980835</v>
       </c>
-      <c r="F1078"/>
+      <c r="F1078" t="n">
+        <v>5.875</v>
+      </c>
       <c r="G1078" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1079" t="n">
+        <v>509615</v>
+      </c>
+      <c r="C1079" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="D1079" t="n">
+        <v>5.73999977111816</v>
+      </c>
+      <c r="E1079" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="F1079"/>
+      <c r="G1079" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DNR.MI.xlsx
+++ b/data/DNR.MI.xlsx
@@ -25182,8 +25182,31 @@
       <c r="E1079" t="n">
         <v>5.90000009536743</v>
       </c>
-      <c r="F1079"/>
+      <c r="F1079" t="n">
+        <v>5.73999977111816</v>
+      </c>
       <c r="G1079" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1080" t="n">
+        <v>408869</v>
+      </c>
+      <c r="C1080" t="n">
+        <v>5.90500020980835</v>
+      </c>
+      <c r="D1080" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="E1080" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="F1080"/>
+      <c r="G1080" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DNR.MI.xlsx
+++ b/data/DNR.MI.xlsx
@@ -25212,6 +25212,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1081">
+      <c r="A1081" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1081" t="n">
+        <v>399853</v>
+      </c>
+      <c r="C1081" t="n">
+        <v>5.84499979019165</v>
+      </c>
+      <c r="D1081" t="n">
+        <v>5.71000003814697</v>
+      </c>
+      <c r="E1081" t="n">
+        <v>5.78499984741211</v>
+      </c>
+      <c r="F1081" t="n">
+        <v>5.76000022888184</v>
+      </c>
+      <c r="G1081" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DNR.MI.xlsx
+++ b/data/DNR.MI.xlsx
@@ -525,7 +525,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>12.4122095108032</v>
+        <v>12.4122104644775</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G9" t="n">
-        <v>12.3548784255981</v>
+        <v>12.3548793792725</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G18" t="n">
-        <v>13.1575155258179</v>
+        <v>13.1575164794922</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G25" t="n">
-        <v>13.9410429000854</v>
+        <v>13.9410419464111</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G26" t="n">
-        <v>14.1608123779297</v>
+        <v>14.1608114242554</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G27" t="n">
-        <v>14.199031829834</v>
+        <v>14.1990327835083</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G29" t="n">
-        <v>13.8263807296753</v>
+        <v>13.826379776001</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G35" t="n">
-        <v>13.5397233963013</v>
+        <v>13.5397243499756</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G38" t="n">
-        <v>13.4250621795654</v>
+        <v>13.4250612258911</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G40" t="n">
-        <v>13.8454904556274</v>
+        <v>13.8454895019531</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G48" t="n">
-        <v>16.0909633636475</v>
+        <v>16.0909652709961</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>15.8900003433228</v>
       </c>
       <c r="G51" t="n">
-        <v>15.1832189559937</v>
+        <v>15.183219909668</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>14.7627897262573</v>
+        <v>14.7627906799316</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G54" t="n">
-        <v>14.0079288482666</v>
+        <v>14.0079298019409</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G56" t="n">
-        <v>15.1163320541382</v>
+        <v>15.1163311004639</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G57" t="n">
-        <v>14.7436800003052</v>
+        <v>14.7436809539795</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>15.75</v>
       </c>
       <c r="G59" t="n">
-        <v>15.0494451522827</v>
+        <v>15.049446105957</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G61" t="n">
-        <v>15.5558710098267</v>
+        <v>15.555871963501</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G63" t="n">
-        <v>15.1736631393433</v>
+        <v>15.1736640930176</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G64" t="n">
-        <v>14.9634485244751</v>
+        <v>14.9634494781494</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G68" t="n">
-        <v>15.517650604248</v>
+        <v>15.5176496505737</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G72" t="n">
-        <v>14.6003513336182</v>
+        <v>14.6003503799438</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G79" t="n">
-        <v>13.8646001815796</v>
+        <v>13.8646011352539</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="n">
-        <v>14.3328056335449</v>
+        <v>14.3328065872192</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G85" t="n">
-        <v>12.9377450942993</v>
+        <v>12.9377460479736</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G87" t="n">
-        <v>13.6448316574097</v>
+        <v>13.6448307037354</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G88" t="n">
-        <v>14.6003513336182</v>
+        <v>14.6003503799438</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G94" t="n">
-        <v>14.6003513336182</v>
+        <v>14.6003503799438</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G95" t="n">
-        <v>14.199031829834</v>
+        <v>14.1990327835083</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>14.6194620132446</v>
+        <v>14.6194629669189</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G99" t="n">
-        <v>14.9347829818726</v>
+        <v>14.9347839355469</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G100" t="n">
-        <v>14.9347829818726</v>
+        <v>14.9347839355469</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G102" t="n">
-        <v>15.3456573486328</v>
+        <v>15.3456563949585</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G103" t="n">
-        <v>15.3074369430542</v>
+        <v>15.3074378967285</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G105" t="n">
-        <v>14.5907974243164</v>
+        <v>14.5907964706421</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G107" t="n">
-        <v>14.6576843261719</v>
+        <v>14.6576833724976</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G108" t="n">
-        <v>14.7627897262573</v>
+        <v>14.7627906799316</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G110" t="n">
-        <v>15.0876665115356</v>
+        <v>15.0876655578613</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G112" t="n">
-        <v>14.6481275558472</v>
+        <v>14.6481266021729</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G114" t="n">
-        <v>14.7819013595581</v>
+        <v>14.7818994522095</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G116" t="n">
-        <v>14.4570236206055</v>
+        <v>14.4570226669312</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G117" t="n">
-        <v>14.4474687576294</v>
+        <v>14.4474678039551</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G125" t="n">
-        <v>14.4952430725098</v>
+        <v>14.4952440261841</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G127" t="n">
-        <v>14.9634485244751</v>
+        <v>14.9634494781494</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G129" t="n">
-        <v>15.1641092300415</v>
+        <v>15.1641082763672</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G131" t="n">
-        <v>15.0876665115356</v>
+        <v>15.0876655578613</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G132" t="n">
-        <v>15.1258869171143</v>
+        <v>15.1258878707886</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>15.75</v>
       </c>
       <c r="G133" t="n">
-        <v>15.0494451522827</v>
+        <v>15.049446105957</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>14.9538946151733</v>
+        <v>14.953893661499</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G136" t="n">
-        <v>15.269214630127</v>
+        <v>15.2692155838013</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G137" t="n">
-        <v>15.1736631393433</v>
+        <v>15.1736640930176</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G142" t="n">
-        <v>16.9795970916748</v>
+        <v>16.9795989990234</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>17.8700008392334</v>
       </c>
       <c r="G143" t="n">
-        <v>17.0751514434814</v>
+        <v>17.0751495361328</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G146" t="n">
-        <v>16.769380569458</v>
+        <v>16.7693824768066</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G147" t="n">
-        <v>16.1769599914551</v>
+        <v>16.1769618988037</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G148" t="n">
-        <v>15.8425264358521</v>
+        <v>15.8425283432007</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>18.25</v>
       </c>
       <c r="G155" t="n">
-        <v>17.4382457733154</v>
+        <v>17.4382476806641</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G158" t="n">
-        <v>17.4669132232666</v>
+        <v>17.466911315918</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G159" t="n">
-        <v>17.3904705047607</v>
+        <v>17.3904685974121</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G160" t="n">
-        <v>17.3904705047607</v>
+        <v>17.3904685974121</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G164" t="n">
-        <v>17.5529117584229</v>
+        <v>17.5529098510742</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G165" t="n">
-        <v>17.9542293548584</v>
+        <v>17.9542274475098</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>17.8204555511475</v>
+        <v>17.8204536437988</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G167" t="n">
-        <v>18.2313289642334</v>
+        <v>18.2313270568848</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>19.5</v>
       </c>
       <c r="G169" t="n">
-        <v>18.6326465606689</v>
+        <v>18.6326503753662</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G170" t="n">
-        <v>18.9001922607422</v>
+        <v>18.9001941680908</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>18.4415416717529</v>
+        <v>18.4415435791016</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>17.7726783752441</v>
+        <v>17.7726821899414</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>18.75</v>
       </c>
       <c r="G178" t="n">
-        <v>17.9160079956055</v>
+        <v>17.9160060882568</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G179" t="n">
-        <v>18.8524188995361</v>
+        <v>18.8524169921875</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>18.75</v>
       </c>
       <c r="G182" t="n">
-        <v>17.9160079956055</v>
+        <v>17.9160060882568</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G183" t="n">
-        <v>17.7249031066895</v>
+        <v>17.7249011993408</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>18</v>
       </c>
       <c r="G187" t="n">
-        <v>17.1993675231934</v>
+        <v>17.1993656158447</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G188" t="n">
-        <v>17.658016204834</v>
+        <v>17.6580142974854</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G189" t="n">
-        <v>17.658016204834</v>
+        <v>17.6580142974854</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>17.75</v>
       </c>
       <c r="G191" t="n">
-        <v>16.9604892730713</v>
+        <v>16.9604873657227</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G192" t="n">
-        <v>16.5305023193359</v>
+        <v>16.5305004119873</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G193" t="n">
-        <v>16.4540615081787</v>
+        <v>16.4540596008301</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>16.3871746063232</v>
+        <v>16.3871765136719</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>16.6260547637939</v>
+        <v>16.6260528564453</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G205" t="n">
-        <v>17.0369281768799</v>
+        <v>17.0369300842285</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G211" t="n">
-        <v>17.37135887146</v>
+        <v>17.3713607788086</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G212" t="n">
-        <v>17.2184791564941</v>
+        <v>17.2184772491455</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>17.2949199676514</v>
+        <v>17.2949180603027</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G214" t="n">
-        <v>16.6642742156982</v>
+        <v>16.6642761230469</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G217" t="n">
-        <v>18.2313289642334</v>
+        <v>18.2313270568848</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G218" t="n">
-        <v>18.4415416717529</v>
+        <v>18.4415435791016</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G219" t="n">
-        <v>18.4415416717529</v>
+        <v>18.4415435791016</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G222" t="n">
-        <v>18.5789909362793</v>
+        <v>18.5789890289307</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G229" t="n">
-        <v>18.8097858428955</v>
+        <v>18.8097839355469</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>18.3674278259277</v>
+        <v>18.3674297332764</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>19.3290748596191</v>
+        <v>19.3290729522705</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G240" t="n">
-        <v>19.4637050628662</v>
+        <v>19.4637031555176</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>19.4252395629883</v>
+        <v>19.4252414703369</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G248" t="n">
-        <v>18.5789909362793</v>
+        <v>18.5789890289307</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G249" t="n">
-        <v>18.4924411773682</v>
+        <v>18.4924430847168</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G250" t="n">
-        <v>18.4924411773682</v>
+        <v>18.4924430847168</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G255" t="n">
-        <v>19.4637050628662</v>
+        <v>19.4637031555176</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G256" t="n">
-        <v>19.4637050628662</v>
+        <v>19.4637031555176</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>19.8098983764648</v>
+        <v>19.8098964691162</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G268" t="n">
-        <v>18.9828834533691</v>
+        <v>18.9828815460205</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>20</v>
       </c>
       <c r="G269" t="n">
-        <v>19.23291015625</v>
+        <v>19.2329082489014</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>20.1399993896484</v>
       </c>
       <c r="G270" t="n">
-        <v>19.3675384521484</v>
+        <v>19.3675403594971</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>18.7700004577637</v>
       </c>
       <c r="G271" t="n">
-        <v>18.0500869750977</v>
+        <v>18.050085067749</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G282" t="n">
-        <v>17.8866062164307</v>
+        <v>17.8866081237793</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G288" t="n">
-        <v>16.7999477386475</v>
+        <v>16.7999458312988</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G290" t="n">
-        <v>17.194221496582</v>
+        <v>17.1942195892334</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G291" t="n">
-        <v>17.4923305511475</v>
+        <v>17.4923324584961</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G293" t="n">
-        <v>17.213451385498</v>
+        <v>17.2134532928467</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G305" t="n">
-        <v>16.3575897216797</v>
+        <v>16.3575916290283</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G308" t="n">
-        <v>15.7902183532715</v>
+        <v>15.7902193069458</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G309" t="n">
-        <v>15.7132883071899</v>
+        <v>15.7132873535156</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G310" t="n">
-        <v>15.5401906967163</v>
+        <v>15.5401916503906</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>16.2700004577637</v>
       </c>
       <c r="G316" t="n">
-        <v>15.6459732055664</v>
+        <v>15.6459722518921</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G318" t="n">
-        <v>14.4150657653809</v>
+        <v>14.4150648117065</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>15.0299997329712</v>
       </c>
       <c r="G319" t="n">
-        <v>14.4535303115845</v>
+        <v>14.4535312652588</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G320" t="n">
-        <v>14.3189010620117</v>
+        <v>14.318902015686</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G323" t="n">
-        <v>14.7612581253052</v>
+        <v>14.7612590789795</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G328" t="n">
-        <v>14.2227363586426</v>
+        <v>14.2227373123169</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G331" t="n">
-        <v>13.1745433807373</v>
+        <v>13.174542427063</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>14.0100002288818</v>
       </c>
       <c r="G343" t="n">
-        <v>13.4726543426514</v>
+        <v>13.4726533889771</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G345" t="n">
-        <v>13.6553659439087</v>
+        <v>13.655366897583</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G346" t="n">
-        <v>14.5016145706177</v>
+        <v>14.5016136169434</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G347" t="n">
-        <v>14.6362438201904</v>
+        <v>14.6362447738647</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G348" t="n">
-        <v>14.2227363586426</v>
+        <v>14.2227373123169</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G352" t="n">
-        <v>14.2515869140625</v>
+        <v>14.2515859603882</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G354" t="n">
-        <v>14.2996683120728</v>
+        <v>14.2996673583984</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G363" t="n">
-        <v>13.1841592788696</v>
+        <v>13.1841602325439</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>14.1099996566772</v>
       </c>
       <c r="G365" t="n">
-        <v>13.5688171386719</v>
+        <v>13.5688180923462</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G367" t="n">
-        <v>13.5495862960815</v>
+        <v>13.5495853424072</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G368" t="n">
-        <v>14.7131767272949</v>
+        <v>14.7131757736206</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G370" t="n">
-        <v>14.9151220321655</v>
+        <v>14.9151210784912</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G371" t="n">
-        <v>15.6844387054443</v>
+        <v>15.68443775177</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G373" t="n">
-        <v>14.9151220321655</v>
+        <v>14.9151210784912</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G375" t="n">
-        <v>14.8381900787354</v>
+        <v>14.8381910324097</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>15.6899995803833</v>
       </c>
       <c r="G377" t="n">
-        <v>15.0882167816162</v>
+        <v>15.0882177352905</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G378" t="n">
-        <v>14.9632034301758</v>
+        <v>14.9632043838501</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G379" t="n">
-        <v>14.5016145706177</v>
+        <v>14.5016136169434</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>15.0900001525879</v>
       </c>
       <c r="G380" t="n">
-        <v>14.51123046875</v>
+        <v>14.5112314224243</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G381" t="n">
-        <v>14.8862724304199</v>
+        <v>14.8862714767456</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G382" t="n">
-        <v>14.8958883285522</v>
+        <v>14.8958892822266</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G398" t="n">
-        <v>13.3668718338013</v>
+        <v>13.3668727874756</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G401" t="n">
-        <v>13.7996139526367</v>
+        <v>13.7996129989624</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>13.6553659439087</v>
+        <v>13.655366897583</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G412" t="n">
-        <v>14.7612581253052</v>
+        <v>14.7612590789795</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G413" t="n">
-        <v>14.6170120239258</v>
+        <v>14.6170110702515</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G415" t="n">
-        <v>14.8862724304199</v>
+        <v>14.8862714767456</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G416" t="n">
-        <v>14.7516431808472</v>
+        <v>14.7516422271729</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G417" t="n">
-        <v>14.7612581253052</v>
+        <v>14.7612590789795</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G420" t="n">
-        <v>14.9632034301758</v>
+        <v>14.9632043838501</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G421" t="n">
-        <v>14.5016145706177</v>
+        <v>14.5016136169434</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G424" t="n">
-        <v>14.0688734054565</v>
+        <v>14.0688743591309</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G425" t="n">
-        <v>14.155421257019</v>
+        <v>14.1554222106934</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G426" t="n">
-        <v>13.809229850769</v>
+        <v>13.8092288970947</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G428" t="n">
-        <v>13.8188447952271</v>
+        <v>13.8188457489014</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>14.1899995803833</v>
       </c>
       <c r="G431" t="n">
-        <v>13.6457490921021</v>
+        <v>13.6457481384277</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G433" t="n">
-        <v>12.6456384658813</v>
+        <v>12.645637512207</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G438" t="n">
-        <v>12.6456384658813</v>
+        <v>12.645637512207</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G442" t="n">
-        <v>12.9725980758667</v>
+        <v>12.9725971221924</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G444" t="n">
-        <v>12.4725427627563</v>
+        <v>12.472541809082</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G445" t="n">
-        <v>12.7802696228027</v>
+        <v>12.7802686691284</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G453" t="n">
-        <v>11.9244031906128</v>
+        <v>11.9244041442871</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G454" t="n">
-        <v>11.6839923858643</v>
+        <v>11.6839933395386</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G459" t="n">
-        <v>11.8859376907349</v>
+        <v>11.8859386444092</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G462" t="n">
-        <v>12.145583152771</v>
+        <v>12.1455821990967</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G463" t="n">
-        <v>12.0494174957275</v>
+        <v>12.0494184494019</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G466" t="n">
-        <v>12.0301856994629</v>
+        <v>12.0301847457886</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G467" t="n">
-        <v>12.7514190673828</v>
+        <v>12.7514200210571</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G470" t="n">
-        <v>13.3476400375366</v>
+        <v>13.3476390838623</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G472" t="n">
-        <v>13.1841592788696</v>
+        <v>13.1841602325439</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -28530,6 +28530,32 @@
         <v>5.65999984741211</v>
       </c>
       <c r="H1083" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1084" t="n">
+        <v>761020</v>
+      </c>
+      <c r="C1084" t="n">
+        <v>5.625</v>
+      </c>
+      <c r="D1084" t="n">
+        <v>5.42500019073486</v>
+      </c>
+      <c r="E1084" t="n">
+        <v>5.6100001335144</v>
+      </c>
+      <c r="F1084" t="n">
+        <v>5.55499982833862</v>
+      </c>
+      <c r="G1084" t="n">
+        <v>5.55499982833862</v>
+      </c>
+      <c r="H1084" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DNR.MI.xlsx
+++ b/data/DNR.MI.xlsx
@@ -421,7 +421,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G2" t="n">
-        <v>12.5555381774902</v>
+        <v>12.5555391311646</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>13.25</v>
       </c>
       <c r="G3" t="n">
-        <v>12.6606454849243</v>
+        <v>12.66064453125</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>12.4122104644775</v>
+        <v>12.4122095108032</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G9" t="n">
-        <v>12.3548793792725</v>
+        <v>12.3548774719238</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G10" t="n">
-        <v>12.5173177719116</v>
+        <v>12.5173168182373</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>12.5173177719116</v>
+        <v>12.5173168182373</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G12" t="n">
-        <v>12.4504308700562</v>
+        <v>12.4504299163818</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G17" t="n">
-        <v>13.7021617889404</v>
+        <v>13.7021627426147</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G21" t="n">
-        <v>14.0748147964478</v>
+        <v>14.0748138427734</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G22" t="n">
-        <v>14.0652599334717</v>
+        <v>14.065260887146</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G26" t="n">
-        <v>14.1608114242554</v>
+        <v>14.1608123779297</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G30" t="n">
-        <v>13.7021617889404</v>
+        <v>13.7021627426147</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G33" t="n">
-        <v>13.740382194519</v>
+        <v>13.7403831481934</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G34" t="n">
-        <v>13.3486204147339</v>
+        <v>13.3486194610596</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G36" t="n">
-        <v>13.3486204147339</v>
+        <v>13.3486194610596</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G37" t="n">
-        <v>13.2912883758545</v>
+        <v>13.2912893295288</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G38" t="n">
-        <v>13.4250612258911</v>
+        <v>13.4250621795654</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>15.1927728652954</v>
+        <v>15.1927738189697</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>15.3838787078857</v>
+        <v>15.3838796615601</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>15.5749807357788</v>
+        <v>15.5749816894531</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>16.0900001525879</v>
       </c>
       <c r="G47" t="n">
-        <v>15.3743228912354</v>
+        <v>15.374321937561</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G48" t="n">
-        <v>16.0909652709961</v>
+        <v>16.0909614562988</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>14.7627906799316</v>
+        <v>14.7627897262573</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G54" t="n">
-        <v>14.0079298019409</v>
+        <v>14.0079288482666</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G55" t="n">
-        <v>14.7341241836548</v>
+        <v>14.7341232299805</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G56" t="n">
-        <v>15.1163311004639</v>
+        <v>15.1163320541382</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G57" t="n">
-        <v>14.7436809539795</v>
+        <v>14.7436800003052</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G60" t="n">
-        <v>15.4889850616455</v>
+        <v>15.4889841079712</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G65" t="n">
-        <v>15.7469758987427</v>
+        <v>15.7469730377197</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>16.2900009155273</v>
       </c>
       <c r="G66" t="n">
-        <v>15.5654268264771</v>
+        <v>15.5654277801514</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G68" t="n">
-        <v>15.5176496505737</v>
+        <v>15.5176515579224</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G69" t="n">
-        <v>15.3552131652832</v>
+        <v>15.3552122116089</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G73" t="n">
-        <v>14.3519163131714</v>
+        <v>14.35191822052</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G75" t="n">
-        <v>14.1894788742065</v>
+        <v>14.1894779205322</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>14.3805818557739</v>
+        <v>14.3805809020996</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>15.5</v>
       </c>
       <c r="G77" t="n">
-        <v>14.8105659484863</v>
+        <v>14.810564994812</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G78" t="n">
-        <v>14.0652599334717</v>
+        <v>14.065260887146</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G79" t="n">
-        <v>13.8646011352539</v>
+        <v>13.8646001815796</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G80" t="n">
-        <v>13.9888181686401</v>
+        <v>13.9888191223145</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="n">
-        <v>14.3328065872192</v>
+        <v>14.3328056335449</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>15.5</v>
       </c>
       <c r="G91" t="n">
-        <v>14.8105659484863</v>
+        <v>14.810564994812</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G92" t="n">
-        <v>14.5621299743652</v>
+        <v>14.5621309280396</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>14.6194629669189</v>
+        <v>14.6194620132446</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G97" t="n">
-        <v>14.8678970336914</v>
+        <v>14.8678979873657</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G98" t="n">
-        <v>14.8678970336914</v>
+        <v>14.8678979873657</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G103" t="n">
-        <v>15.3074378967285</v>
+        <v>15.3074369430542</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G108" t="n">
-        <v>14.7627906799316</v>
+        <v>14.7627897262573</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G109" t="n">
-        <v>14.8487873077393</v>
+        <v>14.8487854003906</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G110" t="n">
-        <v>15.0876655578613</v>
+        <v>15.08766746521</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G111" t="n">
-        <v>14.9443397521973</v>
+        <v>14.9443378448486</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G112" t="n">
-        <v>14.6481266021729</v>
+        <v>14.6481275558472</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G114" t="n">
-        <v>14.7818994522095</v>
+        <v>14.7819004058838</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G116" t="n">
-        <v>14.4570226669312</v>
+        <v>14.4570236206055</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G118" t="n">
-        <v>14.0461492538452</v>
+        <v>14.0461502075195</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G123" t="n">
-        <v>13.7021617889404</v>
+        <v>13.7021627426147</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G126" t="n">
-        <v>14.7150135040283</v>
+        <v>14.715012550354</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G131" t="n">
-        <v>15.0876655578613</v>
+        <v>15.08766746521</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G132" t="n">
-        <v>15.1258878707886</v>
+        <v>15.1258888244629</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>14.953893661499</v>
+        <v>14.9538946151733</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>16.5</v>
       </c>
       <c r="G138" t="n">
-        <v>15.7660856246948</v>
+        <v>15.7660865783691</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G142" t="n">
-        <v>16.9795989990234</v>
+        <v>16.9795970916748</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G146" t="n">
-        <v>16.7693824768066</v>
+        <v>16.769380569458</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G147" t="n">
-        <v>16.1769618988037</v>
+        <v>16.1769599914551</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>16.6100006103516</v>
       </c>
       <c r="G149" t="n">
-        <v>15.8711948394775</v>
+        <v>15.8711938858032</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G156" t="n">
-        <v>17.6962394714355</v>
+        <v>17.6962375640869</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G158" t="n">
-        <v>17.466911315918</v>
+        <v>17.4669132232666</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G159" t="n">
-        <v>17.3904685974121</v>
+        <v>17.3904724121094</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G160" t="n">
-        <v>17.3904685974121</v>
+        <v>17.3904724121094</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G165" t="n">
-        <v>17.9542274475098</v>
+        <v>17.9542293548584</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>17.8204536437988</v>
+        <v>17.8204574584961</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G167" t="n">
-        <v>18.2313270568848</v>
+        <v>18.2313289642334</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>19.5</v>
       </c>
       <c r="G169" t="n">
-        <v>18.6326503753662</v>
+        <v>18.6326465606689</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>19.75</v>
       </c>
       <c r="G172" t="n">
-        <v>18.8715267181396</v>
+        <v>18.8715286254883</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G173" t="n">
-        <v>18.508430480957</v>
+        <v>18.5084285736084</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>18.4415435791016</v>
+        <v>18.4415416717529</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>17.7726821899414</v>
+        <v>17.7726802825928</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>18.75</v>
       </c>
       <c r="G178" t="n">
-        <v>17.9160060882568</v>
+        <v>17.9160079956055</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G179" t="n">
-        <v>18.8524169921875</v>
+        <v>18.8524150848389</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G181" t="n">
-        <v>18.8237533569336</v>
+        <v>18.823751449585</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>18.75</v>
       </c>
       <c r="G182" t="n">
-        <v>17.9160060882568</v>
+        <v>17.9160079956055</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G184" t="n">
-        <v>17.189811706543</v>
+        <v>17.1898097991943</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>18</v>
       </c>
       <c r="G187" t="n">
-        <v>17.1993656158447</v>
+        <v>17.1993675231934</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G188" t="n">
-        <v>17.6580142974854</v>
+        <v>17.658016204834</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G189" t="n">
-        <v>17.6580142974854</v>
+        <v>17.658016204834</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G192" t="n">
-        <v>16.5305004119873</v>
+        <v>16.5305042266846</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G193" t="n">
-        <v>16.4540596008301</v>
+        <v>16.4540615081787</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>16.3871765136719</v>
+        <v>16.3871726989746</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>16.6260528564453</v>
+        <v>16.6260547637939</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G203" t="n">
-        <v>16.7407169342041</v>
+        <v>16.7407188415527</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G204" t="n">
-        <v>16.7884922027588</v>
+        <v>16.7884941101074</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G205" t="n">
-        <v>17.0369300842285</v>
+        <v>17.0369262695312</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G206" t="n">
-        <v>17.2375869750977</v>
+        <v>17.2375888824463</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G207" t="n">
-        <v>16.6547203063965</v>
+        <v>16.6547183990479</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G210" t="n">
-        <v>17.2375869750977</v>
+        <v>17.2375888824463</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G211" t="n">
-        <v>17.3713607788086</v>
+        <v>17.37135887146</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G215" t="n">
-        <v>17.476469039917</v>
+        <v>17.4764709472656</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G217" t="n">
-        <v>18.2313270568848</v>
+        <v>18.2313289642334</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G218" t="n">
-        <v>18.4415435791016</v>
+        <v>18.4415416717529</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G219" t="n">
-        <v>18.4415435791016</v>
+        <v>18.4415416717529</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G220" t="n">
-        <v>18.0020046234131</v>
+        <v>18.0020065307617</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G222" t="n">
-        <v>18.5789890289307</v>
+        <v>18.5789909362793</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G223" t="n">
-        <v>18.6559219360352</v>
+        <v>18.6559238433838</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G225" t="n">
-        <v>18.6559219360352</v>
+        <v>18.6559238433838</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G229" t="n">
-        <v>18.8097839355469</v>
+        <v>18.8097877502441</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>19.75</v>
       </c>
       <c r="G233" t="n">
-        <v>18.9924983978271</v>
+        <v>18.9925003051758</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G236" t="n">
-        <v>20.1753215789795</v>
+        <v>20.1753234863281</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>19.3290729522705</v>
+        <v>19.3290748596191</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G240" t="n">
-        <v>19.4637031555176</v>
+        <v>19.4637050628662</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>19.4252414703369</v>
+        <v>19.4252376556396</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G246" t="n">
-        <v>17.8481388092041</v>
+        <v>17.8481407165527</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G248" t="n">
-        <v>18.5789890289307</v>
+        <v>18.5789909362793</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G255" t="n">
-        <v>19.4637031555176</v>
+        <v>19.4637050628662</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G256" t="n">
-        <v>19.4637031555176</v>
+        <v>19.4637050628662</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G258" t="n">
-        <v>20.1368560791016</v>
+        <v>20.1368579864502</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G264" t="n">
-        <v>19.4829387664795</v>
+        <v>19.4829368591309</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>19.8098964691162</v>
+        <v>19.8098983764648</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G272" t="n">
-        <v>17.5019474029541</v>
+        <v>17.5019493103027</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G276" t="n">
-        <v>18.5020580291748</v>
+        <v>18.5020599365234</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G280" t="n">
-        <v>18.6559219360352</v>
+        <v>18.6559238433838</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G282" t="n">
-        <v>17.8866081237793</v>
+        <v>17.8866062164307</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G286" t="n">
-        <v>17.059591293335</v>
+        <v>17.0595932006836</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G289" t="n">
-        <v>16.6460838317871</v>
+        <v>16.6460819244385</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G290" t="n">
-        <v>17.1942195892334</v>
+        <v>17.194221496582</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G291" t="n">
-        <v>17.4923324584961</v>
+        <v>17.4923305511475</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G293" t="n">
-        <v>17.2134532928467</v>
+        <v>17.213451385498</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G295" t="n">
-        <v>17.1749897003174</v>
+        <v>17.1749877929688</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G296" t="n">
-        <v>17.2807674407959</v>
+        <v>17.2807693481445</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G300" t="n">
-        <v>16.6460838317871</v>
+        <v>16.6460819244385</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G301" t="n">
-        <v>16.4441375732422</v>
+        <v>16.4441394805908</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G305" t="n">
-        <v>16.3575916290283</v>
+        <v>16.3575897216797</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>16.75</v>
       </c>
       <c r="G307" t="n">
-        <v>16.1075611114502</v>
+        <v>16.1075630187988</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G309" t="n">
-        <v>15.7132873535156</v>
+        <v>15.7132883071899</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G315" t="n">
-        <v>15.8479175567627</v>
+        <v>15.8479166030884</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>16.2700004577637</v>
       </c>
       <c r="G316" t="n">
-        <v>15.6459722518921</v>
+        <v>15.6459732055664</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G318" t="n">
-        <v>14.4150648117065</v>
+        <v>14.4150657653809</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G320" t="n">
-        <v>14.318902015686</v>
+        <v>14.3189010620117</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G322" t="n">
-        <v>14.5689296722412</v>
+        <v>14.5689287185669</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G328" t="n">
-        <v>14.2227373123169</v>
+        <v>14.2227363586426</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G331" t="n">
-        <v>13.174542427063</v>
+        <v>13.1745433807373</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G334" t="n">
-        <v>12.674488067627</v>
+        <v>12.6744890213013</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G338" t="n">
-        <v>13.9053936004639</v>
+        <v>13.9053945541382</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G339" t="n">
-        <v>13.8284616470337</v>
+        <v>13.828462600708</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>14.0100002288818</v>
       </c>
       <c r="G343" t="n">
-        <v>13.4726533889771</v>
+        <v>13.4726543426514</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G344" t="n">
-        <v>13.0399141311646</v>
+        <v>13.0399131774902</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G345" t="n">
-        <v>13.655366897583</v>
+        <v>13.6553659439087</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G346" t="n">
-        <v>14.5016136169434</v>
+        <v>14.5016145706177</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G348" t="n">
-        <v>14.2227373123169</v>
+        <v>14.2227363586426</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G350" t="n">
-        <v>14.2708187103271</v>
+        <v>14.2708196640015</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G352" t="n">
-        <v>14.2515859603882</v>
+        <v>14.2515869140625</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G354" t="n">
-        <v>14.2996673583984</v>
+        <v>14.2996683120728</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G356" t="n">
-        <v>13.7322978973389</v>
+        <v>13.7322969436646</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G357" t="n">
-        <v>13.7611474990845</v>
+        <v>13.7611465454102</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>14.3900003433228</v>
       </c>
       <c r="G358" t="n">
-        <v>13.8380794525146</v>
+        <v>13.8380784988403</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G363" t="n">
-        <v>13.1841602325439</v>
+        <v>13.1841592788696</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G366" t="n">
-        <v>13.5015020370483</v>
+        <v>13.5015029907227</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G367" t="n">
-        <v>13.5495853424072</v>
+        <v>13.5495862960815</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G369" t="n">
-        <v>14.674711227417</v>
+        <v>14.6747102737427</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G370" t="n">
-        <v>14.9151210784912</v>
+        <v>14.9151220321655</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G371" t="n">
-        <v>15.68443775177</v>
+        <v>15.6844387054443</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G373" t="n">
-        <v>14.9151210784912</v>
+        <v>14.9151220321655</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G375" t="n">
-        <v>14.8381910324097</v>
+        <v>14.8381900787354</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G376" t="n">
-        <v>15.0305185317993</v>
+        <v>15.0305194854736</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G378" t="n">
-        <v>14.9632043838501</v>
+        <v>14.9632034301758</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G379" t="n">
-        <v>14.5016136169434</v>
+        <v>14.5016145706177</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>15.0900001525879</v>
       </c>
       <c r="G380" t="n">
-        <v>14.5112314224243</v>
+        <v>14.51123046875</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G381" t="n">
-        <v>14.8862714767456</v>
+        <v>14.8862724304199</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G382" t="n">
-        <v>14.8958892822266</v>
+        <v>14.8958883285522</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G383" t="n">
-        <v>14.867039680481</v>
+        <v>14.8670387268066</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G385" t="n">
-        <v>14.4439153671265</v>
+        <v>14.4439163208008</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G394" t="n">
-        <v>13.7419147491455</v>
+        <v>13.7419137954712</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G398" t="n">
-        <v>13.3668727874756</v>
+        <v>13.3668718338013</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G399" t="n">
-        <v>14.0592575073242</v>
+        <v>14.0592565536499</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G400" t="n">
-        <v>14.0784902572632</v>
+        <v>14.0784912109375</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G404" t="n">
-        <v>13.3764886856079</v>
+        <v>13.3764896392822</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>13.655366897583</v>
+        <v>13.6553659439087</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G408" t="n">
-        <v>14.1650381088257</v>
+        <v>14.1650371551514</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G410" t="n">
-        <v>14.7901077270508</v>
+        <v>14.7901067733765</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G415" t="n">
-        <v>14.8862714767456</v>
+        <v>14.8862724304199</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G420" t="n">
-        <v>14.9632043838501</v>
+        <v>14.9632034301758</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G421" t="n">
-        <v>14.5016136169434</v>
+        <v>14.5016145706177</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G423" t="n">
-        <v>14.2323532104492</v>
+        <v>14.2323541641235</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G424" t="n">
-        <v>14.0688743591309</v>
+        <v>14.0688734054565</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G428" t="n">
-        <v>13.8188457489014</v>
+        <v>13.8188447952271</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>14.1899995803833</v>
       </c>
       <c r="G431" t="n">
-        <v>13.6457481384277</v>
+        <v>13.6457500457764</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G432" t="n">
-        <v>12.6937198638916</v>
+        <v>12.6937208175659</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G433" t="n">
-        <v>12.645637512207</v>
+        <v>12.6456384658813</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G437" t="n">
-        <v>12.7033376693726</v>
+        <v>12.7033367156982</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G438" t="n">
-        <v>12.645637512207</v>
+        <v>12.6456384658813</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G441" t="n">
-        <v>12.3763780593872</v>
+        <v>12.3763771057129</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G442" t="n">
-        <v>12.9725971221924</v>
+        <v>12.9725980758667</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G444" t="n">
-        <v>12.472541809082</v>
+        <v>12.4725427627563</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G447" t="n">
-        <v>12.7033376693726</v>
+        <v>12.7033367156982</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G449" t="n">
-        <v>12.8091173171997</v>
+        <v>12.809118270874</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G451" t="n">
-        <v>12.9629812240601</v>
+        <v>12.9629802703857</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G452" t="n">
-        <v>12.6937198638916</v>
+        <v>12.6937208175659</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G453" t="n">
-        <v>11.9244041442871</v>
+        <v>11.9244031906128</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G454" t="n">
-        <v>11.6839933395386</v>
+        <v>11.6839923858643</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G455" t="n">
-        <v>11.7513084411621</v>
+        <v>11.7513074874878</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G459" t="n">
-        <v>11.8859386444092</v>
+        <v>11.8859376907349</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G461" t="n">
-        <v>12.1552000045776</v>
+        <v>12.1551990509033</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G462" t="n">
-        <v>12.1455821990967</v>
+        <v>12.145583152771</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G463" t="n">
-        <v>12.0494184494019</v>
+        <v>12.0494165420532</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G468" t="n">
-        <v>12.7706518173218</v>
+        <v>12.7706527709961</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G470" t="n">
-        <v>13.3476390838623</v>
+        <v>13.3476400375366</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G472" t="n">
-        <v>13.1841602325439</v>
+        <v>13.1841592788696</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G474" t="n">
-        <v>12.7782726287842</v>
+        <v>12.7782716751099</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G476" t="n">
-        <v>13.0790510177612</v>
+        <v>13.0790500640869</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G477" t="n">
-        <v>12.9141073226929</v>
+        <v>12.9141082763672</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G478" t="n">
-        <v>12.4871950149536</v>
+        <v>12.4871940612793</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G479" t="n">
-        <v>12.8461885452271</v>
+        <v>12.8461894989014</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G482" t="n">
-        <v>12.8073787689209</v>
+        <v>12.8073797225952</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G494" t="n">
-        <v>11.3519954681396</v>
+        <v>11.3519945144653</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G497" t="n">
-        <v>11.487832069397</v>
+        <v>11.4878311157227</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G501" t="n">
-        <v>11.3519954681396</v>
+        <v>11.3519945144653</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G508" t="n">
-        <v>11.0803232192993</v>
+        <v>11.0803241729736</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G512" t="n">
-        <v>11.0803232192993</v>
+        <v>11.0803241729736</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G516" t="n">
-        <v>10.973596572876</v>
+        <v>10.9735956192017</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G519" t="n">
-        <v>10.9638929367065</v>
+        <v>10.9638938903809</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G524" t="n">
-        <v>10.5854930877686</v>
+        <v>10.5854921340942</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G526" t="n">
-        <v>10.381739616394</v>
+        <v>10.3817386627197</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G542" t="n">
-        <v>9.67830371856689</v>
+        <v>9.67830467224121</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G544" t="n">
-        <v>9.51821136474609</v>
+        <v>9.51821231842041</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G545" t="n">
-        <v>9.54731941223145</v>
+        <v>9.54731845855713</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G550" t="n">
-        <v>9.24654006958008</v>
+        <v>9.24653911590576</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G551" t="n">
-        <v>9.16891956329346</v>
+        <v>9.16891860961914</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>8.91499996185303</v>
       </c>
       <c r="G554" t="n">
-        <v>8.6498327255249</v>
+        <v>8.64983177185059</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G555" t="n">
-        <v>9.0815954208374</v>
+        <v>9.08159637451172</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G556" t="n">
-        <v>9.09129905700684</v>
+        <v>9.09129810333252</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G558" t="n">
-        <v>9.0815954208374</v>
+        <v>9.08159637451172</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G560" t="n">
-        <v>9.24654006958008</v>
+        <v>9.24653911590576</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>9.55500030517578</v>
       </c>
       <c r="G561" t="n">
-        <v>9.27079582214355</v>
+        <v>9.27079677581787</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G566" t="n">
-        <v>9.15921592712402</v>
+        <v>9.15921688079834</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G572" t="n">
-        <v>8.91665267944336</v>
+        <v>8.91665172576904</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>8.90499973297119</v>
       </c>
       <c r="G574" t="n">
-        <v>8.64012908935547</v>
+        <v>8.64013004302979</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G576" t="n">
-        <v>8.66438674926758</v>
+        <v>8.66438579559326</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>8.75</v>
       </c>
       <c r="G579" t="n">
-        <v>8.48973941802979</v>
+        <v>8.4897403717041</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G580" t="n">
-        <v>8.72260189056396</v>
+        <v>8.72260093688965</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.82499980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>8.56250858306885</v>
+        <v>8.56250953674316</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G584" t="n">
-        <v>8.80022239685059</v>
+        <v>8.80022144317627</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.91499996185303</v>
       </c>
       <c r="G585" t="n">
-        <v>8.6498327255249</v>
+        <v>8.64983177185059</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G587" t="n">
-        <v>8.76141166687012</v>
+        <v>8.7614107131958</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G591" t="n">
-        <v>8.38786315917969</v>
+        <v>8.387864112854</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G593" t="n">
-        <v>8.7420072555542</v>
+        <v>8.74200630187988</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>8.56735992431641</v>
+        <v>8.56736087799072</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G598" t="n">
-        <v>8.76141166687012</v>
+        <v>8.7614107131958</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>8.47500038146973</v>
       </c>
       <c r="G601" t="n">
-        <v>8.22292041778564</v>
+        <v>8.22291946411133</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>8.28499984741211</v>
       </c>
       <c r="G602" t="n">
-        <v>8.03857135772705</v>
+        <v>8.03857040405273</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G605" t="n">
-        <v>7.67472457885742</v>
+        <v>7.67472505569458</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G606" t="n">
-        <v>7.46126890182495</v>
+        <v>7.46126842498779</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G609" t="n">
-        <v>7.73779153823853</v>
+        <v>7.73779201507568</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>8.00500011444092</v>
       </c>
       <c r="G611" t="n">
-        <v>7.76689958572388</v>
+        <v>7.76689910888672</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G614" t="n">
-        <v>7.73779153823853</v>
+        <v>7.73779201507568</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>7.9850001335144</v>
       </c>
       <c r="G615" t="n">
-        <v>7.74749422073364</v>
+        <v>7.7474946975708</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G617" t="n">
-        <v>7.95609951019287</v>
+        <v>7.95609855651855</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>8.14500045776367</v>
       </c>
       <c r="G618" t="n">
-        <v>7.90273523330688</v>
+        <v>7.90273571014404</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>8.17500019073486</v>
       </c>
       <c r="G619" t="n">
-        <v>7.93184280395508</v>
+        <v>7.93184328079224</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>7.44671487808228</v>
+        <v>7.44671535491943</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>7.64499998092651</v>
       </c>
       <c r="G624" t="n">
-        <v>7.41760683059692</v>
+        <v>7.41760730743408</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G625" t="n">
-        <v>7.41275596618652</v>
+        <v>7.41275548934937</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>7.31087923049927</v>
+        <v>7.31087875366211</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G631" t="n">
-        <v>7.53888940811157</v>
+        <v>7.53888893127441</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G632" t="n">
-        <v>7.42245864868164</v>
+        <v>7.42245817184448</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>7.77500009536743</v>
       </c>
       <c r="G633" t="n">
-        <v>7.54374027252197</v>
+        <v>7.54374074935913</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>7.875</v>
       </c>
       <c r="G634" t="n">
-        <v>7.64076566696167</v>
+        <v>7.64076614379883</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G637" t="n">
-        <v>7.05861282348633</v>
+        <v>7.05861234664917</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>6.84515571594238</v>
+        <v>6.84515619277954</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G641" t="n">
-        <v>6.98099231719971</v>
+        <v>6.98099184036255</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>7.17989444732666</v>
+        <v>7.17989492416382</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G652" t="n">
-        <v>6.96643829345703</v>
+        <v>6.96643781661987</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G653" t="n">
-        <v>6.786940574646</v>
+        <v>6.78694105148315</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G658" t="n">
-        <v>6.786940574646</v>
+        <v>6.78694105148315</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G663" t="n">
-        <v>6.67536163330078</v>
+        <v>6.67536115646362</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>8.65499973297119</v>
       </c>
       <c r="G665" t="n">
-        <v>8.3975658416748</v>
+        <v>8.39756488800049</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G666" t="n">
-        <v>8.19866275787354</v>
+        <v>8.19866371154785</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G667" t="n">
-        <v>8.52855014801025</v>
+        <v>8.52855110168457</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>9.07499980926514</v>
       </c>
       <c r="G671" t="n">
-        <v>8.80507373809814</v>
+        <v>8.80507278442383</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G673" t="n">
-        <v>8.7420072555542</v>
+        <v>8.74200630187988</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>9.04763698577881</v>
+        <v>9.04763793945312</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G678" t="n">
-        <v>9.04763698577881</v>
+        <v>9.04763793945312</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G679" t="n">
-        <v>8.94090843200684</v>
+        <v>8.94090938568115</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G686" t="n">
-        <v>6.82575082778931</v>
+        <v>6.82575130462646</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G688" t="n">
-        <v>6.44249963760376</v>
+        <v>6.44250011444092</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G689" t="n">
-        <v>6.66080713272095</v>
+        <v>6.66080760955811</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>6.64499998092651</v>
       </c>
       <c r="G690" t="n">
-        <v>6.44735145568848</v>
+        <v>6.44735097885132</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G691" t="n">
-        <v>6.46190452575684</v>
+        <v>6.46190500259399</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>6.32606887817383</v>
+        <v>6.32606935501099</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G696" t="n">
-        <v>6.09805917739868</v>
+        <v>6.09805870056152</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G697" t="n">
-        <v>5.84094142913818</v>
+        <v>5.84094095230103</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G699" t="n">
-        <v>6.01073598861694</v>
+        <v>6.0107364654541</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>6.35500001907349</v>
       </c>
       <c r="G702" t="n">
-        <v>6.16597652435303</v>
+        <v>6.16597700119019</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G703" t="n">
-        <v>6.07380247116089</v>
+        <v>6.07380294799805</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G705" t="n">
-        <v>5.97677659988403</v>
+        <v>5.97677707672119</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>6.125</v>
       </c>
       <c r="G709" t="n">
-        <v>5.94281768798828</v>
+        <v>5.94281816482544</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G715" t="n">
-        <v>6.4327974319458</v>
+        <v>6.43279790878296</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G716" t="n">
-        <v>6.2775559425354</v>
+        <v>6.27755641937256</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G719" t="n">
-        <v>6.5007152557373</v>
+        <v>6.50071477890015</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G724" t="n">
-        <v>6.67536163330078</v>
+        <v>6.67536115646362</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -28538,7 +28538,7 @@
         <v>46310.2916666667</v>
       </c>
       <c r="B1084" t="n">
-        <v>761020</v>
+        <v>764809</v>
       </c>
       <c r="C1084" t="n">
         <v>5.625</v>
@@ -28556,6 +28556,32 @@
         <v>5.55499982833862</v>
       </c>
       <c r="H1084" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1085" t="n">
+        <v>364079</v>
+      </c>
+      <c r="C1085" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="D1085" t="n">
+        <v>5.57999992370605</v>
+      </c>
+      <c r="E1085" t="n">
+        <v>5.6100001335144</v>
+      </c>
+      <c r="F1085" t="n">
+        <v>5.57999992370605</v>
+      </c>
+      <c r="G1085" t="n">
+        <v>5.57999992370605</v>
+      </c>
+      <c r="H1085" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DNR.MI.xlsx
+++ b/data/DNR.MI.xlsx
@@ -485,7 +485,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>12.6128692626953</v>
+        <v>12.612868309021</v>
       </c>
       <c r="H4" t="n">
         <v>150287</v>
@@ -514,7 +514,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G5" t="n">
-        <v>12.4886503219604</v>
+        <v>12.4886512756348</v>
       </c>
       <c r="H5" t="n">
         <v>167412</v>
@@ -543,7 +543,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>12.4122095108032</v>
+        <v>12.4122104644775</v>
       </c>
       <c r="H6" t="n">
         <v>105330</v>
@@ -572,7 +572,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G7" t="n">
-        <v>12.5077610015869</v>
+        <v>12.5077619552612</v>
       </c>
       <c r="H7" t="n">
         <v>117337</v>
@@ -630,7 +630,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G9" t="n">
-        <v>12.3548784255981</v>
+        <v>12.3548793792725</v>
       </c>
       <c r="H9" t="n">
         <v>150902</v>
@@ -862,7 +862,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G17" t="n">
-        <v>13.7021627426147</v>
+        <v>13.7021617889404</v>
       </c>
       <c r="H17" t="n">
         <v>249086</v>
@@ -891,7 +891,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G18" t="n">
-        <v>13.1575174331665</v>
+        <v>13.1575164794922</v>
       </c>
       <c r="H18" t="n">
         <v>226405</v>
@@ -1007,7 +1007,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G22" t="n">
-        <v>14.065260887146</v>
+        <v>14.0652599334717</v>
       </c>
       <c r="H22" t="n">
         <v>577409</v>
@@ -1094,7 +1094,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G25" t="n">
-        <v>13.9410429000854</v>
+        <v>13.9410419464111</v>
       </c>
       <c r="H25" t="n">
         <v>258800</v>
@@ -1181,7 +1181,7 @@
         <v>14.75</v>
       </c>
       <c r="G28" t="n">
-        <v>14.0939254760742</v>
+        <v>14.0939264297485</v>
       </c>
       <c r="H28" t="n">
         <v>136578</v>
@@ -1210,7 +1210,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G29" t="n">
-        <v>13.8263807296753</v>
+        <v>13.826379776001</v>
       </c>
       <c r="H29" t="n">
         <v>61971</v>
@@ -1239,7 +1239,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G30" t="n">
-        <v>13.7021627426147</v>
+        <v>13.7021617889404</v>
       </c>
       <c r="H30" t="n">
         <v>147708</v>
@@ -1268,7 +1268,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G31" t="n">
-        <v>13.549280166626</v>
+        <v>13.5492792129517</v>
       </c>
       <c r="H31" t="n">
         <v>152273</v>
@@ -1326,7 +1326,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G33" t="n">
-        <v>13.7403831481934</v>
+        <v>13.740382194519</v>
       </c>
       <c r="H33" t="n">
         <v>47665</v>
@@ -1471,7 +1471,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G38" t="n">
-        <v>13.4250621795654</v>
+        <v>13.4250612258911</v>
       </c>
       <c r="H38" t="n">
         <v>146037</v>
@@ -1500,7 +1500,7 @@
         <v>14.3299999237061</v>
       </c>
       <c r="G39" t="n">
-        <v>13.6926078796387</v>
+        <v>13.6926069259644</v>
       </c>
       <c r="H39" t="n">
         <v>213096</v>
@@ -1529,7 +1529,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G40" t="n">
-        <v>13.8454904556274</v>
+        <v>13.8454895019531</v>
       </c>
       <c r="H40" t="n">
         <v>109728</v>
@@ -1587,7 +1587,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>15.1927738189697</v>
+        <v>15.1927728652954</v>
       </c>
       <c r="H42" t="n">
         <v>474029</v>
@@ -1674,7 +1674,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>15.5749826431274</v>
+        <v>15.5749807357788</v>
       </c>
       <c r="H45" t="n">
         <v>405367</v>
@@ -1761,7 +1761,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G48" t="n">
-        <v>16.0909614562988</v>
+        <v>16.0909652709961</v>
       </c>
       <c r="H48" t="n">
         <v>581768</v>
@@ -1790,7 +1790,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G49" t="n">
-        <v>15.6418695449829</v>
+        <v>15.6418685913086</v>
       </c>
       <c r="H49" t="n">
         <v>782970</v>
@@ -1848,7 +1848,7 @@
         <v>15.8900003433228</v>
       </c>
       <c r="G51" t="n">
-        <v>15.1832189559937</v>
+        <v>15.183219909668</v>
       </c>
       <c r="H51" t="n">
         <v>161269</v>
@@ -1877,7 +1877,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>14.7627897262573</v>
+        <v>14.7627906799316</v>
       </c>
       <c r="H52" t="n">
         <v>236091</v>
@@ -1935,7 +1935,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G54" t="n">
-        <v>14.0079288482666</v>
+        <v>14.0079298019409</v>
       </c>
       <c r="H54" t="n">
         <v>147319</v>
@@ -1993,7 +1993,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G56" t="n">
-        <v>15.1163320541382</v>
+        <v>15.1163311004639</v>
       </c>
       <c r="H56" t="n">
         <v>204640</v>
@@ -2022,7 +2022,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G57" t="n">
-        <v>14.7436800003052</v>
+        <v>14.7436809539795</v>
       </c>
       <c r="H57" t="n">
         <v>220752</v>
@@ -2051,7 +2051,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G58" t="n">
-        <v>14.4092483520508</v>
+        <v>14.4092473983765</v>
       </c>
       <c r="H58" t="n">
         <v>182625</v>
@@ -2138,7 +2138,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G61" t="n">
-        <v>15.5558710098267</v>
+        <v>15.555871963501</v>
       </c>
       <c r="H61" t="n">
         <v>217368</v>
@@ -2196,7 +2196,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G63" t="n">
-        <v>15.1736631393433</v>
+        <v>15.1736640930176</v>
       </c>
       <c r="H63" t="n">
         <v>103387</v>
@@ -2254,7 +2254,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G65" t="n">
-        <v>15.746976852417</v>
+        <v>15.7469758987427</v>
       </c>
       <c r="H65" t="n">
         <v>163756</v>
@@ -2283,7 +2283,7 @@
         <v>16.2900009155273</v>
       </c>
       <c r="G66" t="n">
-        <v>15.5654277801514</v>
+        <v>15.5654268264771</v>
       </c>
       <c r="H66" t="n">
         <v>117861</v>
@@ -2341,7 +2341,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G68" t="n">
-        <v>15.517650604248</v>
+        <v>15.5176496505737</v>
       </c>
       <c r="H68" t="n">
         <v>132919</v>
@@ -2370,7 +2370,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G69" t="n">
-        <v>15.3552112579346</v>
+        <v>15.3552131652832</v>
       </c>
       <c r="H69" t="n">
         <v>141327</v>
@@ -2399,7 +2399,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G70" t="n">
-        <v>15.3361015319824</v>
+        <v>15.3361005783081</v>
       </c>
       <c r="H70" t="n">
         <v>85001</v>
@@ -2428,7 +2428,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G71" t="n">
-        <v>15.0972232818604</v>
+        <v>15.097222328186</v>
       </c>
       <c r="H71" t="n">
         <v>210329</v>
@@ -2457,7 +2457,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G72" t="n">
-        <v>14.6003522872925</v>
+        <v>14.6003503799438</v>
       </c>
       <c r="H72" t="n">
         <v>144220</v>
@@ -2602,7 +2602,7 @@
         <v>15.5</v>
       </c>
       <c r="G77" t="n">
-        <v>14.810564994812</v>
+        <v>14.8105659484863</v>
       </c>
       <c r="H77" t="n">
         <v>108895</v>
@@ -2631,7 +2631,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G78" t="n">
-        <v>14.065260887146</v>
+        <v>14.0652599334717</v>
       </c>
       <c r="H78" t="n">
         <v>153369</v>
@@ -2660,7 +2660,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G79" t="n">
-        <v>13.8646001815796</v>
+        <v>13.8646011352539</v>
       </c>
       <c r="H79" t="n">
         <v>226264</v>
@@ -2718,7 +2718,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="n">
-        <v>14.3328056335449</v>
+        <v>14.3328065872192</v>
       </c>
       <c r="H81" t="n">
         <v>137258</v>
@@ -2776,7 +2776,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G83" t="n">
-        <v>13.9505968093872</v>
+        <v>13.9505977630615</v>
       </c>
       <c r="H83" t="n">
         <v>137280</v>
@@ -2892,7 +2892,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G87" t="n">
-        <v>13.6448316574097</v>
+        <v>13.6448307037354</v>
       </c>
       <c r="H87" t="n">
         <v>355963</v>
@@ -2921,7 +2921,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G88" t="n">
-        <v>14.6003522872925</v>
+        <v>14.6003503799438</v>
       </c>
       <c r="H88" t="n">
         <v>499133</v>
@@ -2950,7 +2950,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G89" t="n">
-        <v>15.0303344726562</v>
+        <v>15.0303354263306</v>
       </c>
       <c r="H89" t="n">
         <v>401988</v>
@@ -3008,7 +3008,7 @@
         <v>15.5</v>
       </c>
       <c r="G91" t="n">
-        <v>14.810564994812</v>
+        <v>14.8105659484863</v>
       </c>
       <c r="H91" t="n">
         <v>119552</v>
@@ -3037,7 +3037,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G92" t="n">
-        <v>14.5621309280396</v>
+        <v>14.5621299743652</v>
       </c>
       <c r="H92" t="n">
         <v>143627</v>
@@ -3095,7 +3095,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G94" t="n">
-        <v>14.6003522872925</v>
+        <v>14.6003503799438</v>
       </c>
       <c r="H94" t="n">
         <v>65667</v>
@@ -3182,7 +3182,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G97" t="n">
-        <v>14.8678979873657</v>
+        <v>14.8678970336914</v>
       </c>
       <c r="H97" t="n">
         <v>106899</v>
@@ -3211,7 +3211,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G98" t="n">
-        <v>14.8678979873657</v>
+        <v>14.8678970336914</v>
       </c>
       <c r="H98" t="n">
         <v>69896</v>
@@ -3240,7 +3240,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G99" t="n">
-        <v>14.9347829818726</v>
+        <v>14.9347839355469</v>
       </c>
       <c r="H99" t="n">
         <v>117392</v>
@@ -3269,7 +3269,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G100" t="n">
-        <v>14.9347829818726</v>
+        <v>14.9347839355469</v>
       </c>
       <c r="H100" t="n">
         <v>95381</v>
@@ -3327,7 +3327,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G102" t="n">
-        <v>15.3456573486328</v>
+        <v>15.3456563949585</v>
       </c>
       <c r="H102" t="n">
         <v>1185858</v>
@@ -3356,7 +3356,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G103" t="n">
-        <v>15.3074359893799</v>
+        <v>15.3074378967285</v>
       </c>
       <c r="H103" t="n">
         <v>144419</v>
@@ -3414,7 +3414,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G105" t="n">
-        <v>14.5907974243164</v>
+        <v>14.5907964706421</v>
       </c>
       <c r="H105" t="n">
         <v>112390</v>
@@ -3443,7 +3443,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G106" t="n">
-        <v>14.2754735946655</v>
+        <v>14.2754745483398</v>
       </c>
       <c r="H106" t="n">
         <v>86836</v>
@@ -3472,7 +3472,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G107" t="n">
-        <v>14.6576824188232</v>
+        <v>14.6576833724976</v>
       </c>
       <c r="H107" t="n">
         <v>112801</v>
@@ -3501,7 +3501,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G108" t="n">
-        <v>14.7627897262573</v>
+        <v>14.7627906799316</v>
       </c>
       <c r="H108" t="n">
         <v>44432</v>
@@ -3530,7 +3530,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G109" t="n">
-        <v>14.8487863540649</v>
+        <v>14.8487873077393</v>
       </c>
       <c r="H109" t="n">
         <v>53044</v>
@@ -3559,7 +3559,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G110" t="n">
-        <v>15.08766746521</v>
+        <v>15.0876655578613</v>
       </c>
       <c r="H110" t="n">
         <v>72044</v>
@@ -3588,7 +3588,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G111" t="n">
-        <v>14.9443387985229</v>
+        <v>14.9443397521973</v>
       </c>
       <c r="H111" t="n">
         <v>83241</v>
@@ -3675,7 +3675,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G114" t="n">
-        <v>14.7819013595581</v>
+        <v>14.7818994522095</v>
       </c>
       <c r="H114" t="n">
         <v>173217</v>
@@ -3733,7 +3733,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G116" t="n">
-        <v>14.4570236206055</v>
+        <v>14.4570226669312</v>
       </c>
       <c r="H116" t="n">
         <v>75449</v>
@@ -3820,7 +3820,7 @@
         <v>14.5</v>
       </c>
       <c r="G119" t="n">
-        <v>13.8550453186035</v>
+        <v>13.8550462722778</v>
       </c>
       <c r="H119" t="n">
         <v>88896</v>
@@ -3849,7 +3849,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>13.7594919204712</v>
+        <v>13.7594938278198</v>
       </c>
       <c r="H120" t="n">
         <v>41310</v>
@@ -3936,7 +3936,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G123" t="n">
-        <v>13.7021627426147</v>
+        <v>13.7021617889404</v>
       </c>
       <c r="H123" t="n">
         <v>29257</v>
@@ -3965,7 +3965,7 @@
         <v>14.5</v>
       </c>
       <c r="G124" t="n">
-        <v>13.8550453186035</v>
+        <v>13.8550462722778</v>
       </c>
       <c r="H124" t="n">
         <v>15822</v>
@@ -4139,7 +4139,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G130" t="n">
-        <v>15.0398893356323</v>
+        <v>15.0398902893066</v>
       </c>
       <c r="H130" t="n">
         <v>99245</v>
@@ -4168,7 +4168,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G131" t="n">
-        <v>15.08766746521</v>
+        <v>15.0876655578613</v>
       </c>
       <c r="H131" t="n">
         <v>223782</v>
@@ -4197,7 +4197,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G132" t="n">
-        <v>15.1258869171143</v>
+        <v>15.1258878707886</v>
       </c>
       <c r="H132" t="n">
         <v>58545</v>
@@ -4255,7 +4255,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>14.9538946151733</v>
+        <v>14.953893661499</v>
       </c>
       <c r="H134" t="n">
         <v>62972</v>
@@ -4342,7 +4342,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G137" t="n">
-        <v>15.1736631393433</v>
+        <v>15.1736640930176</v>
       </c>
       <c r="H137" t="n">
         <v>135405</v>
@@ -4371,7 +4371,7 @@
         <v>16.5</v>
       </c>
       <c r="G138" t="n">
-        <v>15.7660865783691</v>
+        <v>15.7660856246948</v>
       </c>
       <c r="H138" t="n">
         <v>318203</v>
@@ -4545,7 +4545,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G144" t="n">
-        <v>16.5687255859375</v>
+        <v>16.5687236785889</v>
       </c>
       <c r="H144" t="n">
         <v>196250</v>
@@ -4574,7 +4574,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G145" t="n">
-        <v>16.2916202545166</v>
+        <v>16.2916221618652</v>
       </c>
       <c r="H145" t="n">
         <v>134728</v>
@@ -4632,7 +4632,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G147" t="n">
-        <v>16.1769599914551</v>
+        <v>16.1769618988037</v>
       </c>
       <c r="H147" t="n">
         <v>432672</v>
@@ -4661,7 +4661,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G148" t="n">
-        <v>15.8425273895264</v>
+        <v>15.8425283432007</v>
       </c>
       <c r="H148" t="n">
         <v>256187</v>
@@ -4690,7 +4690,7 @@
         <v>16.6100006103516</v>
       </c>
       <c r="G149" t="n">
-        <v>15.8711938858032</v>
+        <v>15.8711948394775</v>
       </c>
       <c r="H149" t="n">
         <v>130015</v>
@@ -4719,7 +4719,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G150" t="n">
-        <v>15.6418695449829</v>
+        <v>15.6418685913086</v>
       </c>
       <c r="H150" t="n">
         <v>102652</v>
@@ -4777,7 +4777,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G152" t="n">
-        <v>16.5687255859375</v>
+        <v>16.5687236785889</v>
       </c>
       <c r="H152" t="n">
         <v>119764</v>
@@ -4806,7 +4806,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G153" t="n">
-        <v>16.5878353118896</v>
+        <v>16.587833404541</v>
       </c>
       <c r="H153" t="n">
         <v>137920</v>
@@ -4893,7 +4893,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G156" t="n">
-        <v>17.6962375640869</v>
+        <v>17.6962394714355</v>
       </c>
       <c r="H156" t="n">
         <v>187911</v>
@@ -4951,7 +4951,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G158" t="n">
-        <v>17.4669132232666</v>
+        <v>17.466911315918</v>
       </c>
       <c r="H158" t="n">
         <v>73047</v>
@@ -4980,7 +4980,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G159" t="n">
-        <v>17.3904724121094</v>
+        <v>17.3904685974121</v>
       </c>
       <c r="H159" t="n">
         <v>70593</v>
@@ -5009,7 +5009,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G160" t="n">
-        <v>17.3904724121094</v>
+        <v>17.3904685974121</v>
       </c>
       <c r="H160" t="n">
         <v>78063</v>
@@ -5038,7 +5038,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G161" t="n">
-        <v>17.4477996826172</v>
+        <v>17.4478015899658</v>
       </c>
       <c r="H161" t="n">
         <v>67231</v>
@@ -5096,7 +5096,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G163" t="n">
-        <v>17.2089214324951</v>
+        <v>17.2089233398438</v>
       </c>
       <c r="H163" t="n">
         <v>50813</v>
@@ -5125,7 +5125,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G164" t="n">
-        <v>17.5529117584229</v>
+        <v>17.5529098510742</v>
       </c>
       <c r="H164" t="n">
         <v>38762</v>
@@ -5154,7 +5154,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G165" t="n">
-        <v>17.9542293548584</v>
+        <v>17.9542274475098</v>
       </c>
       <c r="H165" t="n">
         <v>337145</v>
@@ -5270,7 +5270,7 @@
         <v>19.5</v>
       </c>
       <c r="G169" t="n">
-        <v>18.6326484680176</v>
+        <v>18.6326503753662</v>
       </c>
       <c r="H169" t="n">
         <v>161677</v>
@@ -5357,7 +5357,7 @@
         <v>19.75</v>
       </c>
       <c r="G172" t="n">
-        <v>18.8715286254883</v>
+        <v>18.8715267181396</v>
       </c>
       <c r="H172" t="n">
         <v>54348</v>
@@ -5386,7 +5386,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G173" t="n">
-        <v>18.5084323883057</v>
+        <v>18.508430480957</v>
       </c>
       <c r="H173" t="n">
         <v>82218</v>
@@ -5415,7 +5415,7 @@
         <v>18.7700004577637</v>
       </c>
       <c r="G174" t="n">
-        <v>17.9351196289062</v>
+        <v>17.9351177215576</v>
       </c>
       <c r="H174" t="n">
         <v>228634</v>
@@ -5444,7 +5444,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>18.4415416717529</v>
+        <v>18.4415435791016</v>
       </c>
       <c r="H175" t="n">
         <v>73309</v>
@@ -5473,7 +5473,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>17.7726783752441</v>
+        <v>17.7726821899414</v>
       </c>
       <c r="H176" t="n">
         <v>132691</v>
@@ -5502,7 +5502,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G177" t="n">
-        <v>18.3077716827393</v>
+        <v>18.3077697753906</v>
       </c>
       <c r="H177" t="n">
         <v>71355</v>
@@ -5531,7 +5531,7 @@
         <v>18.75</v>
       </c>
       <c r="G178" t="n">
-        <v>17.9160079956055</v>
+        <v>17.9160060882568</v>
       </c>
       <c r="H178" t="n">
         <v>107089</v>
@@ -5647,7 +5647,7 @@
         <v>18.75</v>
       </c>
       <c r="G182" t="n">
-        <v>17.9160079956055</v>
+        <v>17.9160060882568</v>
       </c>
       <c r="H182" t="n">
         <v>737639</v>
@@ -5676,7 +5676,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G183" t="n">
-        <v>17.7249031066895</v>
+        <v>17.7249011993408</v>
       </c>
       <c r="H183" t="n">
         <v>316794</v>
@@ -5705,7 +5705,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G184" t="n">
-        <v>17.1898136138916</v>
+        <v>17.189811706543</v>
       </c>
       <c r="H184" t="n">
         <v>165069</v>
@@ -5821,7 +5821,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G188" t="n">
-        <v>17.658016204834</v>
+        <v>17.6580142974854</v>
       </c>
       <c r="H188" t="n">
         <v>106658</v>
@@ -5850,7 +5850,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G189" t="n">
-        <v>17.658016204834</v>
+        <v>17.6580142974854</v>
       </c>
       <c r="H189" t="n">
         <v>195062</v>
@@ -5937,7 +5937,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G192" t="n">
-        <v>16.5305023193359</v>
+        <v>16.5305004119873</v>
       </c>
       <c r="H192" t="n">
         <v>303536</v>
@@ -5966,7 +5966,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G193" t="n">
-        <v>16.4540576934814</v>
+        <v>16.4540596008301</v>
       </c>
       <c r="H193" t="n">
         <v>194779</v>
@@ -5995,7 +5995,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>16.3871746063232</v>
+        <v>16.3871765136719</v>
       </c>
       <c r="H194" t="n">
         <v>289758</v>
@@ -6082,7 +6082,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G197" t="n">
-        <v>16.3489551544189</v>
+        <v>16.3489532470703</v>
       </c>
       <c r="H197" t="n">
         <v>187727</v>
@@ -6140,7 +6140,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G199" t="n">
-        <v>16.6069450378418</v>
+        <v>16.6069431304932</v>
       </c>
       <c r="H199" t="n">
         <v>89821</v>
@@ -6227,7 +6227,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G202" t="n">
-        <v>16.5878353118896</v>
+        <v>16.587833404541</v>
       </c>
       <c r="H202" t="n">
         <v>70415</v>
@@ -6285,7 +6285,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G204" t="n">
-        <v>16.7884941101074</v>
+        <v>16.7884922027588</v>
       </c>
       <c r="H204" t="n">
         <v>110054</v>
@@ -6314,7 +6314,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G205" t="n">
-        <v>17.0369262695312</v>
+        <v>17.0369300842285</v>
       </c>
       <c r="H205" t="n">
         <v>107074</v>
@@ -6488,7 +6488,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G211" t="n">
-        <v>17.3713626861572</v>
+        <v>17.3713607788086</v>
       </c>
       <c r="H211" t="n">
         <v>87623</v>
@@ -6546,7 +6546,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>17.2949199676514</v>
+        <v>17.2949180603027</v>
       </c>
       <c r="H213" t="n">
         <v>63203</v>
@@ -6633,7 +6633,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G216" t="n">
-        <v>17.6293506622314</v>
+        <v>17.6293525695801</v>
       </c>
       <c r="H216" t="n">
         <v>202637</v>
@@ -6691,7 +6691,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G218" t="n">
-        <v>18.4415416717529</v>
+        <v>18.4415435791016</v>
       </c>
       <c r="H218" t="n">
         <v>241224</v>
@@ -6720,7 +6720,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G219" t="n">
-        <v>18.4415416717529</v>
+        <v>18.4415435791016</v>
       </c>
       <c r="H219" t="n">
         <v>270484</v>
@@ -6778,7 +6778,7 @@
         <v>19.2700004577637</v>
       </c>
       <c r="G221" t="n">
-        <v>18.5309085845947</v>
+        <v>18.5309104919434</v>
       </c>
       <c r="H221" t="n">
         <v>86313</v>
@@ -7010,7 +7010,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G229" t="n">
-        <v>18.8097858428955</v>
+        <v>18.8097839355469</v>
       </c>
       <c r="H229" t="n">
         <v>69687</v>
@@ -7097,7 +7097,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>18.3674278259277</v>
+        <v>18.3674297332764</v>
       </c>
       <c r="H232" t="n">
         <v>66293</v>
@@ -7126,7 +7126,7 @@
         <v>19.75</v>
       </c>
       <c r="G233" t="n">
-        <v>18.9925003051758</v>
+        <v>18.9924983978271</v>
       </c>
       <c r="H233" t="n">
         <v>75996</v>
@@ -7155,7 +7155,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>19.1367473602295</v>
+        <v>19.1367454528809</v>
       </c>
       <c r="H234" t="n">
         <v>176092</v>
@@ -7300,7 +7300,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>19.3290748596191</v>
+        <v>19.3290729522705</v>
       </c>
       <c r="H239" t="n">
         <v>78255</v>
@@ -7329,7 +7329,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G240" t="n">
-        <v>19.4637050628662</v>
+        <v>19.4637031555176</v>
       </c>
       <c r="H240" t="n">
         <v>95964</v>
@@ -7387,7 +7387,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>19.4252395629883</v>
+        <v>19.4252414703369</v>
       </c>
       <c r="H242" t="n">
         <v>219460</v>
@@ -7416,7 +7416,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G243" t="n">
-        <v>19.0405807495117</v>
+        <v>19.0405788421631</v>
       </c>
       <c r="H243" t="n">
         <v>51065</v>
@@ -7590,7 +7590,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G249" t="n">
-        <v>18.4924411773682</v>
+        <v>18.4924430847168</v>
       </c>
       <c r="H249" t="n">
         <v>68327</v>
@@ -7619,7 +7619,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G250" t="n">
-        <v>18.4924411773682</v>
+        <v>18.4924430847168</v>
       </c>
       <c r="H250" t="n">
         <v>136559</v>
@@ -7677,7 +7677,7 @@
         <v>19.5</v>
       </c>
       <c r="G252" t="n">
-        <v>18.7520885467529</v>
+        <v>18.7520866394043</v>
       </c>
       <c r="H252" t="n">
         <v>47907</v>
@@ -7735,7 +7735,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G254" t="n">
-        <v>18.386661529541</v>
+        <v>18.3866634368896</v>
       </c>
       <c r="H254" t="n">
         <v>40747</v>
@@ -7764,7 +7764,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G255" t="n">
-        <v>19.4637050628662</v>
+        <v>19.4637031555176</v>
       </c>
       <c r="H255" t="n">
         <v>154255</v>
@@ -7793,7 +7793,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G256" t="n">
-        <v>19.4637050628662</v>
+        <v>19.4637031555176</v>
       </c>
       <c r="H256" t="n">
         <v>168657</v>
@@ -7822,7 +7822,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G257" t="n">
-        <v>19.6944999694824</v>
+        <v>19.6944980621338</v>
       </c>
       <c r="H257" t="n">
         <v>62964</v>
@@ -7909,7 +7909,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G260" t="n">
-        <v>19.5598678588867</v>
+        <v>19.5598697662354</v>
       </c>
       <c r="H260" t="n">
         <v>165590</v>
@@ -7938,7 +7938,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G261" t="n">
-        <v>19.2713756561279</v>
+        <v>19.2713775634766</v>
       </c>
       <c r="H261" t="n">
         <v>226076</v>
@@ -8054,7 +8054,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>19.8098983764648</v>
+        <v>19.8098964691162</v>
       </c>
       <c r="H265" t="n">
         <v>74881</v>
@@ -8199,7 +8199,7 @@
         <v>20.1399993896484</v>
       </c>
       <c r="G270" t="n">
-        <v>19.3675384521484</v>
+        <v>19.3675403594971</v>
       </c>
       <c r="H270" t="n">
         <v>52442</v>
@@ -8228,7 +8228,7 @@
         <v>18.7700004577637</v>
       </c>
       <c r="G271" t="n">
-        <v>18.0500869750977</v>
+        <v>18.050085067749</v>
       </c>
       <c r="H271" t="n">
         <v>522798</v>
@@ -8315,7 +8315,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G274" t="n">
-        <v>17.5115623474121</v>
+        <v>17.5115642547607</v>
       </c>
       <c r="H274" t="n">
         <v>166261</v>
@@ -8344,7 +8344,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G275" t="n">
-        <v>18.2904987335205</v>
+        <v>18.2904968261719</v>
       </c>
       <c r="H275" t="n">
         <v>226073</v>
@@ -8431,7 +8431,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G278" t="n">
-        <v>18.6270751953125</v>
+        <v>18.6270732879639</v>
       </c>
       <c r="H278" t="n">
         <v>96317</v>
@@ -8547,7 +8547,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G282" t="n">
-        <v>17.8866062164307</v>
+        <v>17.8866081237793</v>
       </c>
       <c r="H282" t="n">
         <v>64258</v>
@@ -8576,7 +8576,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G283" t="n">
-        <v>17.5981101989746</v>
+        <v>17.5981121063232</v>
       </c>
       <c r="H283" t="n">
         <v>79763</v>
@@ -8605,7 +8605,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G284" t="n">
-        <v>17.540412902832</v>
+        <v>17.5404148101807</v>
       </c>
       <c r="H284" t="n">
         <v>101821</v>
@@ -8750,7 +8750,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G289" t="n">
-        <v>16.6460819244385</v>
+        <v>16.6460838317871</v>
       </c>
       <c r="H289" t="n">
         <v>130395</v>
@@ -8779,7 +8779,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G290" t="n">
-        <v>17.194221496582</v>
+        <v>17.1942195892334</v>
       </c>
       <c r="H290" t="n">
         <v>97158</v>
@@ -8808,7 +8808,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G291" t="n">
-        <v>17.4923305511475</v>
+        <v>17.4923324584961</v>
       </c>
       <c r="H291" t="n">
         <v>98792</v>
@@ -8953,7 +8953,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G296" t="n">
-        <v>17.2807712554932</v>
+        <v>17.2807674407959</v>
       </c>
       <c r="H296" t="n">
         <v>59361</v>
@@ -9069,7 +9069,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G300" t="n">
-        <v>16.6460819244385</v>
+        <v>16.6460838317871</v>
       </c>
       <c r="H300" t="n">
         <v>104866</v>
@@ -9127,7 +9127,7 @@
         <v>17</v>
       </c>
       <c r="G302" t="n">
-        <v>16.3479747772217</v>
+        <v>16.347972869873</v>
       </c>
       <c r="H302" t="n">
         <v>123413</v>
@@ -9185,7 +9185,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G304" t="n">
-        <v>16.7230129241943</v>
+        <v>16.723014831543</v>
       </c>
       <c r="H304" t="n">
         <v>322231</v>
@@ -9214,7 +9214,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G305" t="n">
-        <v>16.3575897216797</v>
+        <v>16.3575916290283</v>
       </c>
       <c r="H305" t="n">
         <v>47439</v>
@@ -9272,7 +9272,7 @@
         <v>16.75</v>
       </c>
       <c r="G307" t="n">
-        <v>16.1075630187988</v>
+        <v>16.1075611114502</v>
       </c>
       <c r="H307" t="n">
         <v>64826</v>
@@ -9330,7 +9330,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G309" t="n">
-        <v>15.7132883071899</v>
+        <v>15.7132873535156</v>
       </c>
       <c r="H309" t="n">
         <v>82945</v>
@@ -9359,7 +9359,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G310" t="n">
-        <v>15.5401906967163</v>
+        <v>15.5401916503906</v>
       </c>
       <c r="H310" t="n">
         <v>75719</v>
@@ -9417,7 +9417,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>15.4824924468994</v>
+        <v>15.4824934005737</v>
       </c>
       <c r="H312" t="n">
         <v>47778</v>
@@ -9475,7 +9475,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G314" t="n">
-        <v>15.655590057373</v>
+        <v>15.6555881500244</v>
       </c>
       <c r="H314" t="n">
         <v>70184</v>
@@ -9504,7 +9504,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G315" t="n">
-        <v>15.8479166030884</v>
+        <v>15.8479175567627</v>
       </c>
       <c r="H315" t="n">
         <v>74847</v>
@@ -9591,7 +9591,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G318" t="n">
-        <v>14.4150667190552</v>
+        <v>14.4150648117065</v>
       </c>
       <c r="H318" t="n">
         <v>129315</v>
@@ -9707,7 +9707,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G322" t="n">
-        <v>14.5689287185669</v>
+        <v>14.5689296722412</v>
       </c>
       <c r="H322" t="n">
         <v>40798</v>
@@ -9765,7 +9765,7 @@
         <v>15</v>
       </c>
       <c r="G324" t="n">
-        <v>14.4246835708618</v>
+        <v>14.4246826171875</v>
       </c>
       <c r="H324" t="n">
         <v>91074</v>
@@ -9852,7 +9852,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G327" t="n">
-        <v>14.0881061553955</v>
+        <v>14.0881052017212</v>
       </c>
       <c r="H327" t="n">
         <v>66396</v>
@@ -9968,7 +9968,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G331" t="n">
-        <v>13.1745433807373</v>
+        <v>13.174542427063</v>
       </c>
       <c r="H331" t="n">
         <v>46983</v>
@@ -10026,7 +10026,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G333" t="n">
-        <v>12.8572006225586</v>
+        <v>12.8571996688843</v>
       </c>
       <c r="H333" t="n">
         <v>104403</v>
@@ -10055,7 +10055,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G334" t="n">
-        <v>12.6744890213013</v>
+        <v>12.674488067627</v>
       </c>
       <c r="H334" t="n">
         <v>59858</v>
@@ -10171,7 +10171,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G338" t="n">
-        <v>13.9053945541382</v>
+        <v>13.9053936004639</v>
       </c>
       <c r="H338" t="n">
         <v>230450</v>
@@ -10200,7 +10200,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G339" t="n">
-        <v>13.828462600708</v>
+        <v>13.8284616470337</v>
       </c>
       <c r="H339" t="n">
         <v>150608</v>
@@ -10258,7 +10258,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G341" t="n">
-        <v>13.2803239822388</v>
+        <v>13.2803249359131</v>
       </c>
       <c r="H341" t="n">
         <v>70862</v>
@@ -10374,7 +10374,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G345" t="n">
-        <v>13.6553649902344</v>
+        <v>13.655366897583</v>
       </c>
       <c r="H345" t="n">
         <v>126227</v>
@@ -10403,7 +10403,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G346" t="n">
-        <v>14.5016145706177</v>
+        <v>14.5016136169434</v>
       </c>
       <c r="H346" t="n">
         <v>237267</v>
@@ -10432,7 +10432,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G347" t="n">
-        <v>14.6362438201904</v>
+        <v>14.6362447738647</v>
       </c>
       <c r="H347" t="n">
         <v>215592</v>
@@ -10548,7 +10548,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G351" t="n">
-        <v>14.1073389053345</v>
+        <v>14.1073398590088</v>
       </c>
       <c r="H351" t="n">
         <v>93291</v>
@@ -10606,7 +10606,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G353" t="n">
-        <v>14.3092851638794</v>
+        <v>14.3092861175537</v>
       </c>
       <c r="H353" t="n">
         <v>104165</v>
@@ -10635,7 +10635,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G354" t="n">
-        <v>14.2996683120728</v>
+        <v>14.2996673583984</v>
       </c>
       <c r="H354" t="n">
         <v>87931</v>
@@ -10722,7 +10722,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G357" t="n">
-        <v>13.7611465454102</v>
+        <v>13.7611474990845</v>
       </c>
       <c r="H357" t="n">
         <v>89876</v>
@@ -10780,7 +10780,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G359" t="n">
-        <v>13.664981842041</v>
+        <v>13.6649827957153</v>
       </c>
       <c r="H359" t="n">
         <v>97011</v>
@@ -10809,7 +10809,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G360" t="n">
-        <v>13.2707071304321</v>
+        <v>13.2707080841064</v>
       </c>
       <c r="H360" t="n">
         <v>139158</v>
@@ -10838,7 +10838,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G361" t="n">
-        <v>13.5399694442749</v>
+        <v>13.5399684906006</v>
       </c>
       <c r="H361" t="n">
         <v>102042</v>
@@ -10896,7 +10896,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G363" t="n">
-        <v>13.1841592788696</v>
+        <v>13.1841602325439</v>
       </c>
       <c r="H363" t="n">
         <v>159187</v>
@@ -10983,7 +10983,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G366" t="n">
-        <v>13.5015029907227</v>
+        <v>13.5015020370483</v>
       </c>
       <c r="H366" t="n">
         <v>125716</v>
@@ -11012,7 +11012,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G367" t="n">
-        <v>13.5495862960815</v>
+        <v>13.5495853424072</v>
       </c>
       <c r="H367" t="n">
         <v>174963</v>
@@ -11041,7 +11041,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G368" t="n">
-        <v>14.7131767272949</v>
+        <v>14.7131757736206</v>
       </c>
       <c r="H368" t="n">
         <v>469164</v>
@@ -11070,7 +11070,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G369" t="n">
-        <v>14.6747102737427</v>
+        <v>14.674711227417</v>
       </c>
       <c r="H369" t="n">
         <v>228319</v>
@@ -11099,7 +11099,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G370" t="n">
-        <v>14.9151220321655</v>
+        <v>14.9151210784912</v>
       </c>
       <c r="H370" t="n">
         <v>166793</v>
@@ -11186,7 +11186,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G373" t="n">
-        <v>14.9151220321655</v>
+        <v>14.9151210784912</v>
       </c>
       <c r="H373" t="n">
         <v>162189</v>
@@ -11244,7 +11244,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G375" t="n">
-        <v>14.8381900787354</v>
+        <v>14.8381910324097</v>
       </c>
       <c r="H375" t="n">
         <v>137149</v>
@@ -11360,7 +11360,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G379" t="n">
-        <v>14.5016145706177</v>
+        <v>14.5016136169434</v>
       </c>
       <c r="H379" t="n">
         <v>337572</v>
@@ -11418,7 +11418,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G381" t="n">
-        <v>14.8862724304199</v>
+        <v>14.8862714767456</v>
       </c>
       <c r="H381" t="n">
         <v>97752</v>
@@ -11563,7 +11563,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G386" t="n">
-        <v>14.0977220535278</v>
+        <v>14.0977230072021</v>
       </c>
       <c r="H386" t="n">
         <v>236798</v>
@@ -11621,7 +11621,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G388" t="n">
-        <v>13.982325553894</v>
+        <v>13.9823265075684</v>
       </c>
       <c r="H388" t="n">
         <v>99895</v>
@@ -11708,7 +11708,7 @@
         <v>14.2700004577637</v>
       </c>
       <c r="G391" t="n">
-        <v>13.7226819992065</v>
+        <v>13.7226810455322</v>
       </c>
       <c r="H391" t="n">
         <v>186975</v>
@@ -11737,7 +11737,7 @@
         <v>14.5</v>
       </c>
       <c r="G392" t="n">
-        <v>13.9438591003418</v>
+        <v>13.9438600540161</v>
       </c>
       <c r="H392" t="n">
         <v>133628</v>
@@ -11882,7 +11882,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G397" t="n">
-        <v>13.664981842041</v>
+        <v>13.6649827957153</v>
       </c>
       <c r="H397" t="n">
         <v>175445</v>
@@ -11911,7 +11911,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G398" t="n">
-        <v>13.3668718338013</v>
+        <v>13.3668727874756</v>
       </c>
       <c r="H398" t="n">
         <v>212475</v>
@@ -12172,7 +12172,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>13.6553649902344</v>
+        <v>13.655366897583</v>
       </c>
       <c r="H407" t="n">
         <v>163196</v>
@@ -12201,7 +12201,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G408" t="n">
-        <v>14.1650371551514</v>
+        <v>14.1650381088257</v>
       </c>
       <c r="H408" t="n">
         <v>284491</v>
@@ -12404,7 +12404,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G415" t="n">
-        <v>14.8862724304199</v>
+        <v>14.8862714767456</v>
       </c>
       <c r="H415" t="n">
         <v>139801</v>
@@ -12491,7 +12491,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G418" t="n">
-        <v>14.6458597183228</v>
+        <v>14.6458606719971</v>
       </c>
       <c r="H418" t="n">
         <v>94315</v>
@@ -12578,7 +12578,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G421" t="n">
-        <v>14.5016145706177</v>
+        <v>14.5016136169434</v>
       </c>
       <c r="H421" t="n">
         <v>101945</v>
@@ -12607,7 +12607,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G422" t="n">
-        <v>14.3092851638794</v>
+        <v>14.3092861175537</v>
       </c>
       <c r="H422" t="n">
         <v>102639</v>
@@ -12636,7 +12636,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G423" t="n">
-        <v>14.2323541641235</v>
+        <v>14.2323532104492</v>
       </c>
       <c r="H423" t="n">
         <v>63885</v>
@@ -12694,7 +12694,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G425" t="n">
-        <v>14.155421257019</v>
+        <v>14.1554222106934</v>
       </c>
       <c r="H425" t="n">
         <v>117944</v>
@@ -12752,7 +12752,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G427" t="n">
-        <v>13.664981842041</v>
+        <v>13.6649827957153</v>
       </c>
       <c r="H427" t="n">
         <v>159222</v>
@@ -12868,7 +12868,7 @@
         <v>14.1899995803833</v>
       </c>
       <c r="G431" t="n">
-        <v>13.6457490921021</v>
+        <v>13.6457481384277</v>
       </c>
       <c r="H431" t="n">
         <v>223671</v>
@@ -12897,7 +12897,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G432" t="n">
-        <v>12.6937208175659</v>
+        <v>12.6937198638916</v>
       </c>
       <c r="H432" t="n">
         <v>632996</v>
@@ -12926,7 +12926,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G433" t="n">
-        <v>12.6456384658813</v>
+        <v>12.645637512207</v>
       </c>
       <c r="H433" t="n">
         <v>771950</v>
@@ -12955,7 +12955,7 @@
         <v>13.25</v>
       </c>
       <c r="G434" t="n">
-        <v>12.7418022155762</v>
+        <v>12.7418031692505</v>
       </c>
       <c r="H434" t="n">
         <v>207043</v>
@@ -12984,7 +12984,7 @@
         <v>13.25</v>
       </c>
       <c r="G435" t="n">
-        <v>12.7418022155762</v>
+        <v>12.7418031692505</v>
       </c>
       <c r="H435" t="n">
         <v>214799</v>
@@ -13071,7 +13071,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G438" t="n">
-        <v>12.6456384658813</v>
+        <v>12.645637512207</v>
       </c>
       <c r="H438" t="n">
         <v>150121</v>
@@ -13100,7 +13100,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G439" t="n">
-        <v>12.8572006225586</v>
+        <v>12.8571996688843</v>
       </c>
       <c r="H439" t="n">
         <v>90236</v>
@@ -13158,7 +13158,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G441" t="n">
-        <v>12.3763771057129</v>
+        <v>12.3763780593872</v>
       </c>
       <c r="H441" t="n">
         <v>197033</v>
@@ -13245,7 +13245,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G444" t="n">
-        <v>12.4725427627563</v>
+        <v>12.472541809082</v>
       </c>
       <c r="H444" t="n">
         <v>169735</v>
@@ -13274,7 +13274,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G445" t="n">
-        <v>12.7802677154541</v>
+        <v>12.7802686691284</v>
       </c>
       <c r="H445" t="n">
         <v>146927</v>
@@ -13477,7 +13477,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G452" t="n">
-        <v>12.6937208175659</v>
+        <v>12.6937198638916</v>
       </c>
       <c r="H452" t="n">
         <v>67295</v>
@@ -13506,7 +13506,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G453" t="n">
-        <v>11.9244031906128</v>
+        <v>11.9244041442871</v>
       </c>
       <c r="H453" t="n">
         <v>236491</v>
@@ -13535,7 +13535,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G454" t="n">
-        <v>11.6839923858643</v>
+        <v>11.6839933395386</v>
       </c>
       <c r="H454" t="n">
         <v>219490</v>
@@ -13680,7 +13680,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G459" t="n">
-        <v>11.8859376907349</v>
+        <v>11.8859386444092</v>
       </c>
       <c r="H459" t="n">
         <v>67163</v>
@@ -13709,7 +13709,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G460" t="n">
-        <v>12.1744327545166</v>
+        <v>12.1744318008423</v>
       </c>
       <c r="H460" t="n">
         <v>97426</v>
@@ -13767,7 +13767,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G462" t="n">
-        <v>12.145583152771</v>
+        <v>12.1455821990967</v>
       </c>
       <c r="H462" t="n">
         <v>90492</v>
@@ -13796,7 +13796,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G463" t="n">
-        <v>12.0494174957275</v>
+        <v>12.0494184494019</v>
       </c>
       <c r="H463" t="n">
         <v>59080</v>
@@ -13854,7 +13854,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G465" t="n">
-        <v>12.8668174743652</v>
+        <v>12.8668165206909</v>
       </c>
       <c r="H465" t="n">
         <v>259031</v>
@@ -13912,7 +13912,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G467" t="n">
-        <v>12.7514190673828</v>
+        <v>12.7514200210571</v>
       </c>
       <c r="H467" t="n">
         <v>287755</v>
@@ -13999,7 +13999,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G470" t="n">
-        <v>13.3476400375366</v>
+        <v>13.3476390838623</v>
       </c>
       <c r="H470" t="n">
         <v>152417</v>
@@ -14057,7 +14057,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G472" t="n">
-        <v>13.1841592788696</v>
+        <v>13.1841602325439</v>
       </c>
       <c r="H472" t="n">
         <v>75618</v>
@@ -14115,7 +14115,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G474" t="n">
-        <v>12.7782716751099</v>
+        <v>12.7782726287842</v>
       </c>
       <c r="H474" t="n">
         <v>99354</v>
@@ -14173,7 +14173,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G476" t="n">
-        <v>13.0790500640869</v>
+        <v>13.0790510177612</v>
       </c>
       <c r="H476" t="n">
         <v>88070</v>
@@ -14202,7 +14202,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G477" t="n">
-        <v>12.9141082763672</v>
+        <v>12.9141073226929</v>
       </c>
       <c r="H477" t="n">
         <v>53958</v>
@@ -14231,7 +14231,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G478" t="n">
-        <v>12.4871940612793</v>
+        <v>12.4871950149536</v>
       </c>
       <c r="H478" t="n">
         <v>88793</v>
@@ -14260,7 +14260,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G479" t="n">
-        <v>12.8461894989014</v>
+        <v>12.8461885452271</v>
       </c>
       <c r="H479" t="n">
         <v>56934</v>
@@ -14347,7 +14347,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G482" t="n">
-        <v>12.8073797225952</v>
+        <v>12.8073787689209</v>
       </c>
       <c r="H482" t="n">
         <v>146288</v>
@@ -14695,7 +14695,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G494" t="n">
-        <v>11.3519945144653</v>
+        <v>11.3519954681396</v>
       </c>
       <c r="H494" t="n">
         <v>90980</v>
@@ -14782,7 +14782,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G497" t="n">
-        <v>11.4878311157227</v>
+        <v>11.487832069397</v>
       </c>
       <c r="H497" t="n">
         <v>74033</v>
@@ -14898,7 +14898,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G501" t="n">
-        <v>11.3519945144653</v>
+        <v>11.3519954681396</v>
       </c>
       <c r="H501" t="n">
         <v>72055</v>
@@ -15101,7 +15101,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G508" t="n">
-        <v>11.0803241729736</v>
+        <v>11.0803232192993</v>
       </c>
       <c r="H508" t="n">
         <v>52830</v>
@@ -15217,7 +15217,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G512" t="n">
-        <v>11.0803241729736</v>
+        <v>11.0803232192993</v>
       </c>
       <c r="H512" t="n">
         <v>67037</v>
@@ -15333,7 +15333,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G516" t="n">
-        <v>10.9735956192017</v>
+        <v>10.973596572876</v>
       </c>
       <c r="H516" t="n">
         <v>81818</v>
@@ -15420,7 +15420,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G519" t="n">
-        <v>10.9638938903809</v>
+        <v>10.9638929367065</v>
       </c>
       <c r="H519" t="n">
         <v>97469</v>
@@ -15565,7 +15565,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G524" t="n">
-        <v>10.5854921340942</v>
+        <v>10.5854930877686</v>
       </c>
       <c r="H524" t="n">
         <v>134025</v>
@@ -15623,7 +15623,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G526" t="n">
-        <v>10.3817386627197</v>
+        <v>10.381739616394</v>
       </c>
       <c r="H526" t="n">
         <v>195282</v>
@@ -16087,7 +16087,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G542" t="n">
-        <v>9.67830467224121</v>
+        <v>9.67830371856689</v>
       </c>
       <c r="H542" t="n">
         <v>134678</v>
@@ -16145,7 +16145,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G544" t="n">
-        <v>9.51821231842041</v>
+        <v>9.51821136474609</v>
       </c>
       <c r="H544" t="n">
         <v>80660</v>
@@ -16174,7 +16174,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G545" t="n">
-        <v>9.54731845855713</v>
+        <v>9.54731941223145</v>
       </c>
       <c r="H545" t="n">
         <v>95108</v>
@@ -16319,7 +16319,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G550" t="n">
-        <v>9.24653911590576</v>
+        <v>9.24654006958008</v>
       </c>
       <c r="H550" t="n">
         <v>94988</v>
@@ -16348,7 +16348,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G551" t="n">
-        <v>9.16891860961914</v>
+        <v>9.16891956329346</v>
       </c>
       <c r="H551" t="n">
         <v>135094</v>
@@ -16435,7 +16435,7 @@
         <v>8.91499996185303</v>
       </c>
       <c r="G554" t="n">
-        <v>8.64983177185059</v>
+        <v>8.6498327255249</v>
       </c>
       <c r="H554" t="n">
         <v>131072</v>
@@ -16464,7 +16464,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G555" t="n">
-        <v>9.08159637451172</v>
+        <v>9.0815954208374</v>
       </c>
       <c r="H555" t="n">
         <v>164784</v>
@@ -16493,7 +16493,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G556" t="n">
-        <v>9.09129810333252</v>
+        <v>9.09129905700684</v>
       </c>
       <c r="H556" t="n">
         <v>112117</v>
@@ -16551,7 +16551,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G558" t="n">
-        <v>9.08159637451172</v>
+        <v>9.0815954208374</v>
       </c>
       <c r="H558" t="n">
         <v>76175</v>
@@ -16609,7 +16609,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G560" t="n">
-        <v>9.24653911590576</v>
+        <v>9.24654006958008</v>
       </c>
       <c r="H560" t="n">
         <v>57482</v>
@@ -16638,7 +16638,7 @@
         <v>9.55500030517578</v>
       </c>
       <c r="G561" t="n">
-        <v>9.27079677581787</v>
+        <v>9.27079582214355</v>
       </c>
       <c r="H561" t="n">
         <v>80413</v>
@@ -16783,7 +16783,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G566" t="n">
-        <v>9.15921688079834</v>
+        <v>9.15921592712402</v>
       </c>
       <c r="H566" t="n">
         <v>168859</v>
@@ -16957,7 +16957,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G572" t="n">
-        <v>8.91665172576904</v>
+        <v>8.91665267944336</v>
       </c>
       <c r="H572" t="n">
         <v>55529</v>
@@ -17015,7 +17015,7 @@
         <v>8.90499973297119</v>
       </c>
       <c r="G574" t="n">
-        <v>8.64013004302979</v>
+        <v>8.64012908935547</v>
       </c>
       <c r="H574" t="n">
         <v>288790</v>
@@ -17073,7 +17073,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G576" t="n">
-        <v>8.66438579559326</v>
+        <v>8.66438674926758</v>
       </c>
       <c r="H576" t="n">
         <v>85122</v>
@@ -17160,7 +17160,7 @@
         <v>8.75</v>
       </c>
       <c r="G579" t="n">
-        <v>8.4897403717041</v>
+        <v>8.48973941802979</v>
       </c>
       <c r="H579" t="n">
         <v>77770</v>
@@ -17189,7 +17189,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G580" t="n">
-        <v>8.72260093688965</v>
+        <v>8.72260189056396</v>
       </c>
       <c r="H580" t="n">
         <v>167385</v>
@@ -17276,7 +17276,7 @@
         <v>8.82499980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>8.56250953674316</v>
+        <v>8.56250858306885</v>
       </c>
       <c r="H583" t="n">
         <v>185644</v>
@@ -17305,7 +17305,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G584" t="n">
-        <v>8.80022144317627</v>
+        <v>8.80022239685059</v>
       </c>
       <c r="H584" t="n">
         <v>145712</v>
@@ -17334,7 +17334,7 @@
         <v>8.91499996185303</v>
       </c>
       <c r="G585" t="n">
-        <v>8.64983177185059</v>
+        <v>8.6498327255249</v>
       </c>
       <c r="H585" t="n">
         <v>105376</v>
@@ -17392,7 +17392,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G587" t="n">
-        <v>8.7614107131958</v>
+        <v>8.76141166687012</v>
       </c>
       <c r="H587" t="n">
         <v>110831</v>
@@ -17508,7 +17508,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G591" t="n">
-        <v>8.387864112854</v>
+        <v>8.38786315917969</v>
       </c>
       <c r="H591" t="n">
         <v>209095</v>
@@ -17566,7 +17566,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G593" t="n">
-        <v>8.74200630187988</v>
+        <v>8.7420072555542</v>
       </c>
       <c r="H593" t="n">
         <v>123295</v>
@@ -17624,7 +17624,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>8.56736087799072</v>
+        <v>8.56735992431641</v>
       </c>
       <c r="H595" t="n">
         <v>506056</v>
@@ -17711,7 +17711,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G598" t="n">
-        <v>8.7614107131958</v>
+        <v>8.76141166687012</v>
       </c>
       <c r="H598" t="n">
         <v>275140</v>
@@ -17798,7 +17798,7 @@
         <v>8.47500038146973</v>
       </c>
       <c r="G601" t="n">
-        <v>8.22291946411133</v>
+        <v>8.22292041778564</v>
       </c>
       <c r="H601" t="n">
         <v>238471</v>
@@ -17827,7 +17827,7 @@
         <v>8.28499984741211</v>
       </c>
       <c r="G602" t="n">
-        <v>8.03857040405273</v>
+        <v>8.03857135772705</v>
       </c>
       <c r="H602" t="n">
         <v>639924</v>
@@ -17914,7 +17914,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G605" t="n">
-        <v>7.67472505569458</v>
+        <v>7.67472457885742</v>
       </c>
       <c r="H605" t="n">
         <v>165566</v>
@@ -17943,7 +17943,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G606" t="n">
-        <v>7.46126842498779</v>
+        <v>7.46126890182495</v>
       </c>
       <c r="H606" t="n">
         <v>281631</v>
@@ -18030,7 +18030,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G609" t="n">
-        <v>7.73779201507568</v>
+        <v>7.73779153823853</v>
       </c>
       <c r="H609" t="n">
         <v>85842</v>
@@ -18088,7 +18088,7 @@
         <v>8.00500011444092</v>
       </c>
       <c r="G611" t="n">
-        <v>7.76689910888672</v>
+        <v>7.76689958572388</v>
       </c>
       <c r="H611" t="n">
         <v>68292</v>
@@ -18175,7 +18175,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G614" t="n">
-        <v>7.73779201507568</v>
+        <v>7.73779153823853</v>
       </c>
       <c r="H614" t="n">
         <v>142315</v>
@@ -18204,7 +18204,7 @@
         <v>7.9850001335144</v>
       </c>
       <c r="G615" t="n">
-        <v>7.7474946975708</v>
+        <v>7.74749422073364</v>
       </c>
       <c r="H615" t="n">
         <v>116245</v>
@@ -18262,7 +18262,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G617" t="n">
-        <v>7.95609855651855</v>
+        <v>7.95609951019287</v>
       </c>
       <c r="H617" t="n">
         <v>208602</v>
@@ -18291,7 +18291,7 @@
         <v>8.14500045776367</v>
       </c>
       <c r="G618" t="n">
-        <v>7.90273571014404</v>
+        <v>7.90273523330688</v>
       </c>
       <c r="H618" t="n">
         <v>116291</v>
@@ -18320,7 +18320,7 @@
         <v>8.17500019073486</v>
       </c>
       <c r="G619" t="n">
-        <v>7.93184328079224</v>
+        <v>7.93184280395508</v>
       </c>
       <c r="H619" t="n">
         <v>91476</v>
@@ -18436,7 +18436,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>7.44671535491943</v>
+        <v>7.44671487808228</v>
       </c>
       <c r="H623" t="n">
         <v>226325</v>
@@ -18465,7 +18465,7 @@
         <v>7.64499998092651</v>
       </c>
       <c r="G624" t="n">
-        <v>7.41760730743408</v>
+        <v>7.41760683059692</v>
       </c>
       <c r="H624" t="n">
         <v>275750</v>
@@ -18494,7 +18494,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G625" t="n">
-        <v>7.41275548934937</v>
+        <v>7.41275596618652</v>
       </c>
       <c r="H625" t="n">
         <v>150786</v>
@@ -18581,7 +18581,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>7.31087875366211</v>
+        <v>7.31087923049927</v>
       </c>
       <c r="H628" t="n">
         <v>129823</v>
@@ -18668,7 +18668,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G631" t="n">
-        <v>7.53888893127441</v>
+        <v>7.53888940811157</v>
       </c>
       <c r="H631" t="n">
         <v>91913</v>
@@ -18697,7 +18697,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G632" t="n">
-        <v>7.42245817184448</v>
+        <v>7.42245864868164</v>
       </c>
       <c r="H632" t="n">
         <v>71179</v>
@@ -18726,7 +18726,7 @@
         <v>7.77500009536743</v>
       </c>
       <c r="G633" t="n">
-        <v>7.54374074935913</v>
+        <v>7.54374027252197</v>
       </c>
       <c r="H633" t="n">
         <v>104298</v>
@@ -18755,7 +18755,7 @@
         <v>7.875</v>
       </c>
       <c r="G634" t="n">
-        <v>7.64076614379883</v>
+        <v>7.64076566696167</v>
       </c>
       <c r="H634" t="n">
         <v>86228</v>
@@ -18842,7 +18842,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G637" t="n">
-        <v>7.05861234664917</v>
+        <v>7.05861282348633</v>
       </c>
       <c r="H637" t="n">
         <v>150003</v>
@@ -18900,7 +18900,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>6.84515619277954</v>
+        <v>6.84515571594238</v>
       </c>
       <c r="H639" t="n">
         <v>176664</v>
@@ -18958,7 +18958,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G641" t="n">
-        <v>6.98099184036255</v>
+        <v>6.98099231719971</v>
       </c>
       <c r="H641" t="n">
         <v>147248</v>
@@ -18987,7 +18987,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>7.17989492416382</v>
+        <v>7.17989444732666</v>
       </c>
       <c r="H642" t="n">
         <v>152913</v>
@@ -19277,7 +19277,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G652" t="n">
-        <v>6.96643781661987</v>
+        <v>6.96643829345703</v>
       </c>
       <c r="H652" t="n">
         <v>197817</v>
@@ -19306,7 +19306,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G653" t="n">
-        <v>6.78694105148315</v>
+        <v>6.786940574646</v>
       </c>
       <c r="H653" t="n">
         <v>219932</v>
@@ -19451,7 +19451,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G658" t="n">
-        <v>6.78694105148315</v>
+        <v>6.786940574646</v>
       </c>
       <c r="H658" t="n">
         <v>214637</v>
@@ -19596,7 +19596,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G663" t="n">
-        <v>6.67536115646362</v>
+        <v>6.67536163330078</v>
       </c>
       <c r="H663" t="n">
         <v>163183</v>
@@ -19654,7 +19654,7 @@
         <v>8.65499973297119</v>
       </c>
       <c r="G665" t="n">
-        <v>8.39756488800049</v>
+        <v>8.3975658416748</v>
       </c>
       <c r="H665" t="n">
         <v>1421609</v>
@@ -19683,7 +19683,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G666" t="n">
-        <v>8.19866371154785</v>
+        <v>8.19866275787354</v>
       </c>
       <c r="H666" t="n">
         <v>376186</v>
@@ -19712,7 +19712,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G667" t="n">
-        <v>8.52855110168457</v>
+        <v>8.52855014801025</v>
       </c>
       <c r="H667" t="n">
         <v>499509</v>
@@ -19828,7 +19828,7 @@
         <v>9.07499980926514</v>
       </c>
       <c r="G671" t="n">
-        <v>8.80507278442383</v>
+        <v>8.80507373809814</v>
       </c>
       <c r="H671" t="n">
         <v>162058</v>
@@ -19886,7 +19886,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G673" t="n">
-        <v>8.74200630187988</v>
+        <v>8.7420072555542</v>
       </c>
       <c r="H673" t="n">
         <v>106877</v>
@@ -20002,7 +20002,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>9.04763793945312</v>
+        <v>9.04763698577881</v>
       </c>
       <c r="H677" t="n">
         <v>120993</v>
@@ -20031,7 +20031,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G678" t="n">
-        <v>9.04763793945312</v>
+        <v>9.04763698577881</v>
       </c>
       <c r="H678" t="n">
         <v>114620</v>
@@ -20060,7 +20060,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G679" t="n">
-        <v>8.94090938568115</v>
+        <v>8.94090843200684</v>
       </c>
       <c r="H679" t="n">
         <v>176536</v>
@@ -20263,7 +20263,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G686" t="n">
-        <v>6.82575130462646</v>
+        <v>6.82575082778931</v>
       </c>
       <c r="H686" t="n">
         <v>2010202</v>
@@ -20321,7 +20321,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G688" t="n">
-        <v>6.44250011444092</v>
+        <v>6.44249963760376</v>
       </c>
       <c r="H688" t="n">
         <v>526066</v>
@@ -20350,7 +20350,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G689" t="n">
-        <v>6.66080760955811</v>
+        <v>6.66080713272095</v>
       </c>
       <c r="H689" t="n">
         <v>633433</v>
@@ -20379,7 +20379,7 @@
         <v>6.64499998092651</v>
       </c>
       <c r="G690" t="n">
-        <v>6.44735097885132</v>
+        <v>6.44735145568848</v>
       </c>
       <c r="H690" t="n">
         <v>435937</v>
@@ -20408,7 +20408,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G691" t="n">
-        <v>6.46190500259399</v>
+        <v>6.46190452575684</v>
       </c>
       <c r="H691" t="n">
         <v>314939</v>
@@ -20437,7 +20437,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>6.32606935501099</v>
+        <v>6.32606887817383</v>
       </c>
       <c r="H692" t="n">
         <v>246343</v>
@@ -20553,7 +20553,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G696" t="n">
-        <v>6.09805870056152</v>
+        <v>6.09805917739868</v>
       </c>
       <c r="H696" t="n">
         <v>426023</v>
@@ -20582,7 +20582,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G697" t="n">
-        <v>5.84094095230103</v>
+        <v>5.84094142913818</v>
       </c>
       <c r="H697" t="n">
         <v>433195</v>
@@ -20640,7 +20640,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G699" t="n">
-        <v>6.0107364654541</v>
+        <v>6.01073598861694</v>
       </c>
       <c r="H699" t="n">
         <v>258310</v>
@@ -20727,7 +20727,7 @@
         <v>6.35500001907349</v>
       </c>
       <c r="G702" t="n">
-        <v>6.16597700119019</v>
+        <v>6.16597652435303</v>
       </c>
       <c r="H702" t="n">
         <v>169235</v>
@@ -20756,7 +20756,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G703" t="n">
-        <v>6.07380294799805</v>
+        <v>6.07380247116089</v>
       </c>
       <c r="H703" t="n">
         <v>180300</v>
@@ -20814,7 +20814,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G705" t="n">
-        <v>5.97677707672119</v>
+        <v>5.97677659988403</v>
       </c>
       <c r="H705" t="n">
         <v>155044</v>
@@ -20930,7 +20930,7 @@
         <v>6.125</v>
       </c>
       <c r="G709" t="n">
-        <v>5.94281816482544</v>
+        <v>5.94281768798828</v>
       </c>
       <c r="H709" t="n">
         <v>221764</v>
@@ -21104,7 +21104,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G715" t="n">
-        <v>6.43279790878296</v>
+        <v>6.4327974319458</v>
       </c>
       <c r="H715" t="n">
         <v>116884</v>
@@ -21133,7 +21133,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G716" t="n">
-        <v>6.27755641937256</v>
+        <v>6.2775559425354</v>
       </c>
       <c r="H716" t="n">
         <v>222806</v>
@@ -21220,7 +21220,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G719" t="n">
-        <v>6.50071477890015</v>
+        <v>6.5007152557373</v>
       </c>
       <c r="H719" t="n">
         <v>144135</v>
@@ -21365,7 +21365,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G724" t="n">
-        <v>6.67536115646362</v>
+        <v>6.67536163330078</v>
       </c>
       <c r="H724" t="n">
         <v>775096</v>
@@ -31869,6 +31869,35 @@
         <v>263935</v>
       </c>
       <c r="I1086" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1087" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1087" t="n">
+        <v>5.5149998664856</v>
+      </c>
+      <c r="D1087" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="E1087" t="n">
+        <v>5.375</v>
+      </c>
+      <c r="F1087" t="n">
+        <v>5.67999982833862</v>
+      </c>
+      <c r="G1087" t="n">
+        <v>5.67999982833862</v>
+      </c>
+      <c r="H1087" t="n">
+        <v>646898</v>
+      </c>
+      <c r="I1087" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DNR.MI.xlsx
+++ b/data/DNR.MI.xlsx
@@ -456,7 +456,7 @@
         <v>13.25</v>
       </c>
       <c r="G3" t="n">
-        <v>12.6606454849243</v>
+        <v>12.66064453125</v>
       </c>
       <c r="H3" t="n">
         <v>74987</v>
@@ -485,7 +485,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>12.612868309021</v>
+        <v>12.6128692626953</v>
       </c>
       <c r="H4" t="n">
         <v>150287</v>
@@ -514,7 +514,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G5" t="n">
-        <v>12.4886512756348</v>
+        <v>12.4886503219604</v>
       </c>
       <c r="H5" t="n">
         <v>167412</v>
@@ -543,7 +543,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>12.4122104644775</v>
+        <v>12.4122095108032</v>
       </c>
       <c r="H6" t="n">
         <v>105330</v>
@@ -572,7 +572,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G7" t="n">
-        <v>12.5077619552612</v>
+        <v>12.5077610015869</v>
       </c>
       <c r="H7" t="n">
         <v>117337</v>
@@ -630,7 +630,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G9" t="n">
-        <v>12.3548793792725</v>
+        <v>12.3548784255981</v>
       </c>
       <c r="H9" t="n">
         <v>150902</v>
@@ -659,7 +659,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G10" t="n">
-        <v>12.5173177719116</v>
+        <v>12.5173168182373</v>
       </c>
       <c r="H10" t="n">
         <v>111264</v>
@@ -688,7 +688,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>12.5173177719116</v>
+        <v>12.5173168182373</v>
       </c>
       <c r="H11" t="n">
         <v>104743</v>
@@ -833,7 +833,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G16" t="n">
-        <v>13.4155054092407</v>
+        <v>13.415506362915</v>
       </c>
       <c r="H16" t="n">
         <v>258303</v>
@@ -862,7 +862,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G17" t="n">
-        <v>13.7021617889404</v>
+        <v>13.7021627426147</v>
       </c>
       <c r="H17" t="n">
         <v>249086</v>
@@ -920,7 +920,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G19" t="n">
-        <v>13.5683889389038</v>
+        <v>13.5683879852295</v>
       </c>
       <c r="H19" t="n">
         <v>254487</v>
@@ -949,7 +949,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G20" t="n">
-        <v>13.8072690963745</v>
+        <v>13.8072700500488</v>
       </c>
       <c r="H20" t="n">
         <v>301266</v>
@@ -1036,7 +1036,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>14.1417016983032</v>
+        <v>14.1417026519775</v>
       </c>
       <c r="H23" t="n">
         <v>170138</v>
@@ -1094,7 +1094,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G25" t="n">
-        <v>13.9410419464111</v>
+        <v>13.9410429000854</v>
       </c>
       <c r="H25" t="n">
         <v>258800</v>
@@ -1181,7 +1181,7 @@
         <v>14.75</v>
       </c>
       <c r="G28" t="n">
-        <v>14.0939264297485</v>
+        <v>14.0939254760742</v>
       </c>
       <c r="H28" t="n">
         <v>136578</v>
@@ -1210,7 +1210,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G29" t="n">
-        <v>13.826379776001</v>
+        <v>13.8263807296753</v>
       </c>
       <c r="H29" t="n">
         <v>61971</v>
@@ -1239,7 +1239,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G30" t="n">
-        <v>13.7021617889404</v>
+        <v>13.7021627426147</v>
       </c>
       <c r="H30" t="n">
         <v>147708</v>
@@ -1268,7 +1268,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G31" t="n">
-        <v>13.5492792129517</v>
+        <v>13.549280166626</v>
       </c>
       <c r="H31" t="n">
         <v>152273</v>
@@ -1297,7 +1297,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G32" t="n">
-        <v>13.5683889389038</v>
+        <v>13.5683879852295</v>
       </c>
       <c r="H32" t="n">
         <v>138086</v>
@@ -1326,7 +1326,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G33" t="n">
-        <v>13.740382194519</v>
+        <v>13.7403831481934</v>
       </c>
       <c r="H33" t="n">
         <v>47665</v>
@@ -1529,7 +1529,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G40" t="n">
-        <v>13.8454895019531</v>
+        <v>13.8454904556274</v>
       </c>
       <c r="H40" t="n">
         <v>109728</v>
@@ -1587,7 +1587,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>15.1927728652954</v>
+        <v>15.1927738189697</v>
       </c>
       <c r="H42" t="n">
         <v>474029</v>
@@ -1616,7 +1616,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>15.3838787078857</v>
+        <v>15.3838777542114</v>
       </c>
       <c r="H43" t="n">
         <v>436799</v>
@@ -1645,7 +1645,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G44" t="n">
-        <v>16.1387386322021</v>
+        <v>16.1387405395508</v>
       </c>
       <c r="H44" t="n">
         <v>348418</v>
@@ -1674,7 +1674,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>15.5749807357788</v>
+        <v>15.5749816894531</v>
       </c>
       <c r="H45" t="n">
         <v>405367</v>
@@ -1703,7 +1703,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G46" t="n">
-        <v>15.4507646560669</v>
+        <v>15.4507656097412</v>
       </c>
       <c r="H46" t="n">
         <v>226004</v>
@@ -1761,7 +1761,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G48" t="n">
-        <v>16.0909652709961</v>
+        <v>16.0909633636475</v>
       </c>
       <c r="H48" t="n">
         <v>581768</v>
@@ -1790,7 +1790,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G49" t="n">
-        <v>15.6418685913086</v>
+        <v>15.6418695449829</v>
       </c>
       <c r="H49" t="n">
         <v>782970</v>
@@ -1848,7 +1848,7 @@
         <v>15.8900003433228</v>
       </c>
       <c r="G51" t="n">
-        <v>15.183219909668</v>
+        <v>15.1832189559937</v>
       </c>
       <c r="H51" t="n">
         <v>161269</v>
@@ -1877,7 +1877,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>14.7627906799316</v>
+        <v>14.7627897262573</v>
       </c>
       <c r="H52" t="n">
         <v>236091</v>
@@ -1906,7 +1906,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G53" t="n">
-        <v>14.2372531890869</v>
+        <v>14.2372541427612</v>
       </c>
       <c r="H53" t="n">
         <v>139086</v>
@@ -1935,7 +1935,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G54" t="n">
-        <v>14.0079298019409</v>
+        <v>14.0079278945923</v>
       </c>
       <c r="H54" t="n">
         <v>147319</v>
@@ -1993,7 +1993,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G56" t="n">
-        <v>15.1163311004639</v>
+        <v>15.1163320541382</v>
       </c>
       <c r="H56" t="n">
         <v>204640</v>
@@ -2022,7 +2022,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G57" t="n">
-        <v>14.7436809539795</v>
+        <v>14.7436790466309</v>
       </c>
       <c r="H57" t="n">
         <v>220752</v>
@@ -2080,7 +2080,7 @@
         <v>15.75</v>
       </c>
       <c r="G59" t="n">
-        <v>15.049446105957</v>
+        <v>15.0494451522827</v>
       </c>
       <c r="H59" t="n">
         <v>87541</v>
@@ -2109,7 +2109,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G60" t="n">
-        <v>15.4889850616455</v>
+        <v>15.4889841079712</v>
       </c>
       <c r="H60" t="n">
         <v>176931</v>
@@ -2138,7 +2138,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G61" t="n">
-        <v>15.555871963501</v>
+        <v>15.5558729171753</v>
       </c>
       <c r="H61" t="n">
         <v>217368</v>
@@ -2254,7 +2254,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G65" t="n">
-        <v>15.7469758987427</v>
+        <v>15.746973991394</v>
       </c>
       <c r="H65" t="n">
         <v>163756</v>
@@ -2283,7 +2283,7 @@
         <v>16.2900009155273</v>
       </c>
       <c r="G66" t="n">
-        <v>15.5654268264771</v>
+        <v>15.5654277801514</v>
       </c>
       <c r="H66" t="n">
         <v>117861</v>
@@ -2341,7 +2341,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G68" t="n">
-        <v>15.5176496505737</v>
+        <v>15.5176515579224</v>
       </c>
       <c r="H68" t="n">
         <v>132919</v>
@@ -2370,7 +2370,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G69" t="n">
-        <v>15.3552131652832</v>
+        <v>15.3552122116089</v>
       </c>
       <c r="H69" t="n">
         <v>141327</v>
@@ -2399,7 +2399,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G70" t="n">
-        <v>15.3361005783081</v>
+        <v>15.3361015319824</v>
       </c>
       <c r="H70" t="n">
         <v>85001</v>
@@ -2457,7 +2457,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G72" t="n">
-        <v>14.6003503799438</v>
+        <v>14.6003513336182</v>
       </c>
       <c r="H72" t="n">
         <v>144220</v>
@@ -2486,7 +2486,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G73" t="n">
-        <v>14.3519163131714</v>
+        <v>14.3519153594971</v>
       </c>
       <c r="H73" t="n">
         <v>172203</v>
@@ -2544,7 +2544,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G75" t="n">
-        <v>14.1894788742065</v>
+        <v>14.1894779205322</v>
       </c>
       <c r="H75" t="n">
         <v>121982</v>
@@ -2660,7 +2660,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G79" t="n">
-        <v>13.8646011352539</v>
+        <v>13.8646001815796</v>
       </c>
       <c r="H79" t="n">
         <v>226264</v>
@@ -2689,7 +2689,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G80" t="n">
-        <v>13.9888181686401</v>
+        <v>13.9888191223145</v>
       </c>
       <c r="H80" t="n">
         <v>82515</v>
@@ -2805,7 +2805,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G84" t="n">
-        <v>13.1670703887939</v>
+        <v>13.1670713424683</v>
       </c>
       <c r="H84" t="n">
         <v>628995</v>
@@ -2892,7 +2892,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G87" t="n">
-        <v>13.6448307037354</v>
+        <v>13.6448316574097</v>
       </c>
       <c r="H87" t="n">
         <v>355963</v>
@@ -2921,7 +2921,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G88" t="n">
-        <v>14.6003503799438</v>
+        <v>14.6003513336182</v>
       </c>
       <c r="H88" t="n">
         <v>499133</v>
@@ -3066,7 +3066,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G93" t="n">
-        <v>14.6767921447754</v>
+        <v>14.6767930984497</v>
       </c>
       <c r="H93" t="n">
         <v>110219</v>
@@ -3095,7 +3095,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G94" t="n">
-        <v>14.6003503799438</v>
+        <v>14.6003513336182</v>
       </c>
       <c r="H94" t="n">
         <v>65667</v>
@@ -3298,7 +3298,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G101" t="n">
-        <v>15.3265476226807</v>
+        <v>15.326548576355</v>
       </c>
       <c r="H101" t="n">
         <v>177567</v>
@@ -3327,7 +3327,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G102" t="n">
-        <v>15.3456563949585</v>
+        <v>15.3456573486328</v>
       </c>
       <c r="H102" t="n">
         <v>1185858</v>
@@ -3356,7 +3356,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G103" t="n">
-        <v>15.3074378967285</v>
+        <v>15.3074369430542</v>
       </c>
       <c r="H103" t="n">
         <v>144419</v>
@@ -3414,7 +3414,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G105" t="n">
-        <v>14.5907964706421</v>
+        <v>14.5907974243164</v>
       </c>
       <c r="H105" t="n">
         <v>112390</v>
@@ -3443,7 +3443,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G106" t="n">
-        <v>14.2754745483398</v>
+        <v>14.2754735946655</v>
       </c>
       <c r="H106" t="n">
         <v>86836</v>
@@ -3472,7 +3472,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G107" t="n">
-        <v>14.6576833724976</v>
+        <v>14.6576824188232</v>
       </c>
       <c r="H107" t="n">
         <v>112801</v>
@@ -3501,7 +3501,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G108" t="n">
-        <v>14.7627906799316</v>
+        <v>14.7627897262573</v>
       </c>
       <c r="H108" t="n">
         <v>44432</v>
@@ -3530,7 +3530,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G109" t="n">
-        <v>14.8487873077393</v>
+        <v>14.8487863540649</v>
       </c>
       <c r="H109" t="n">
         <v>53044</v>
@@ -3559,7 +3559,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G110" t="n">
-        <v>15.0876655578613</v>
+        <v>15.0876665115356</v>
       </c>
       <c r="H110" t="n">
         <v>72044</v>
@@ -3588,7 +3588,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G111" t="n">
-        <v>14.9443397521973</v>
+        <v>14.9443387985229</v>
       </c>
       <c r="H111" t="n">
         <v>83241</v>
@@ -3675,7 +3675,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G114" t="n">
-        <v>14.7818994522095</v>
+        <v>14.7819013595581</v>
       </c>
       <c r="H114" t="n">
         <v>173217</v>
@@ -3791,7 +3791,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G118" t="n">
-        <v>14.0461492538452</v>
+        <v>14.0461502075195</v>
       </c>
       <c r="H118" t="n">
         <v>88132</v>
@@ -3820,7 +3820,7 @@
         <v>14.5</v>
       </c>
       <c r="G119" t="n">
-        <v>13.8550462722778</v>
+        <v>13.8550453186035</v>
       </c>
       <c r="H119" t="n">
         <v>88896</v>
@@ -3849,7 +3849,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>13.7594938278198</v>
+        <v>13.7594928741455</v>
       </c>
       <c r="H120" t="n">
         <v>41310</v>
@@ -3936,7 +3936,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G123" t="n">
-        <v>13.7021617889404</v>
+        <v>13.7021627426147</v>
       </c>
       <c r="H123" t="n">
         <v>29257</v>
@@ -3965,7 +3965,7 @@
         <v>14.5</v>
       </c>
       <c r="G124" t="n">
-        <v>13.8550462722778</v>
+        <v>13.8550453186035</v>
       </c>
       <c r="H124" t="n">
         <v>15822</v>
@@ -3994,7 +3994,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G125" t="n">
-        <v>14.4952440261841</v>
+        <v>14.4952449798584</v>
       </c>
       <c r="H125" t="n">
         <v>221654</v>
@@ -4110,7 +4110,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G129" t="n">
-        <v>15.1641082763672</v>
+        <v>15.1641092300415</v>
       </c>
       <c r="H129" t="n">
         <v>73585</v>
@@ -4139,7 +4139,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G130" t="n">
-        <v>15.0398902893066</v>
+        <v>15.0398893356323</v>
       </c>
       <c r="H130" t="n">
         <v>99245</v>
@@ -4168,7 +4168,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G131" t="n">
-        <v>15.0876655578613</v>
+        <v>15.0876665115356</v>
       </c>
       <c r="H131" t="n">
         <v>223782</v>
@@ -4226,7 +4226,7 @@
         <v>15.75</v>
       </c>
       <c r="G133" t="n">
-        <v>15.049446105957</v>
+        <v>15.0494451522827</v>
       </c>
       <c r="H133" t="n">
         <v>54662</v>
@@ -4371,7 +4371,7 @@
         <v>16.5</v>
       </c>
       <c r="G138" t="n">
-        <v>15.7660856246948</v>
+        <v>15.7660846710205</v>
       </c>
       <c r="H138" t="n">
         <v>318203</v>
@@ -4400,7 +4400,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G139" t="n">
-        <v>16.3011779785156</v>
+        <v>16.3011798858643</v>
       </c>
       <c r="H139" t="n">
         <v>212600</v>
@@ -4487,7 +4487,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G142" t="n">
-        <v>16.9795989990234</v>
+        <v>16.9795970916748</v>
       </c>
       <c r="H142" t="n">
         <v>321463</v>
@@ -4574,7 +4574,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G145" t="n">
-        <v>16.2916221618652</v>
+        <v>16.2916202545166</v>
       </c>
       <c r="H145" t="n">
         <v>134728</v>
@@ -4603,7 +4603,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G146" t="n">
-        <v>16.7693824768066</v>
+        <v>16.7693843841553</v>
       </c>
       <c r="H146" t="n">
         <v>112560</v>
@@ -4632,7 +4632,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G147" t="n">
-        <v>16.1769618988037</v>
+        <v>16.1769599914551</v>
       </c>
       <c r="H147" t="n">
         <v>432672</v>
@@ -4661,7 +4661,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G148" t="n">
-        <v>15.8425283432007</v>
+        <v>15.842529296875</v>
       </c>
       <c r="H148" t="n">
         <v>256187</v>
@@ -4690,7 +4690,7 @@
         <v>16.6100006103516</v>
       </c>
       <c r="G149" t="n">
-        <v>15.8711948394775</v>
+        <v>15.8711938858032</v>
       </c>
       <c r="H149" t="n">
         <v>130015</v>
@@ -4719,7 +4719,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G150" t="n">
-        <v>15.6418685913086</v>
+        <v>15.6418695449829</v>
       </c>
       <c r="H150" t="n">
         <v>102652</v>
@@ -4806,7 +4806,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G153" t="n">
-        <v>16.587833404541</v>
+        <v>16.5878353118896</v>
       </c>
       <c r="H153" t="n">
         <v>137920</v>
@@ -4893,7 +4893,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G156" t="n">
-        <v>17.6962394714355</v>
+        <v>17.6962375640869</v>
       </c>
       <c r="H156" t="n">
         <v>187911</v>
@@ -4951,7 +4951,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G158" t="n">
-        <v>17.466911315918</v>
+        <v>17.4669132232666</v>
       </c>
       <c r="H158" t="n">
         <v>73047</v>
@@ -4980,7 +4980,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G159" t="n">
-        <v>17.3904685974121</v>
+        <v>17.3904724121094</v>
       </c>
       <c r="H159" t="n">
         <v>70593</v>
@@ -5009,7 +5009,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G160" t="n">
-        <v>17.3904685974121</v>
+        <v>17.3904724121094</v>
       </c>
       <c r="H160" t="n">
         <v>78063</v>
@@ -5096,7 +5096,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G163" t="n">
-        <v>17.2089233398438</v>
+        <v>17.2089214324951</v>
       </c>
       <c r="H163" t="n">
         <v>50813</v>
@@ -5125,7 +5125,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G164" t="n">
-        <v>17.5529098510742</v>
+        <v>17.5529117584229</v>
       </c>
       <c r="H164" t="n">
         <v>38762</v>
@@ -5183,7 +5183,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>17.8204536437988</v>
+        <v>17.8204555511475</v>
       </c>
       <c r="H166" t="n">
         <v>70506</v>
@@ -5212,7 +5212,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G167" t="n">
-        <v>18.2313270568848</v>
+        <v>18.2313289642334</v>
       </c>
       <c r="H167" t="n">
         <v>148047</v>
@@ -5270,7 +5270,7 @@
         <v>19.5</v>
       </c>
       <c r="G169" t="n">
-        <v>18.6326503753662</v>
+        <v>18.6326484680176</v>
       </c>
       <c r="H169" t="n">
         <v>161677</v>
@@ -5299,7 +5299,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G170" t="n">
-        <v>18.9001941680908</v>
+        <v>18.9001922607422</v>
       </c>
       <c r="H170" t="n">
         <v>196771</v>
@@ -5328,7 +5328,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G171" t="n">
-        <v>18.7664184570312</v>
+        <v>18.7664203643799</v>
       </c>
       <c r="H171" t="n">
         <v>104982</v>
@@ -5357,7 +5357,7 @@
         <v>19.75</v>
       </c>
       <c r="G172" t="n">
-        <v>18.8715267181396</v>
+        <v>18.8715286254883</v>
       </c>
       <c r="H172" t="n">
         <v>54348</v>
@@ -5386,7 +5386,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G173" t="n">
-        <v>18.508430480957</v>
+        <v>18.5084323883057</v>
       </c>
       <c r="H173" t="n">
         <v>82218</v>
@@ -5415,7 +5415,7 @@
         <v>18.7700004577637</v>
       </c>
       <c r="G174" t="n">
-        <v>17.9351177215576</v>
+        <v>17.9351196289062</v>
       </c>
       <c r="H174" t="n">
         <v>228634</v>
@@ -5473,7 +5473,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>17.7726821899414</v>
+        <v>17.7726783752441</v>
       </c>
       <c r="H176" t="n">
         <v>132691</v>
@@ -5531,7 +5531,7 @@
         <v>18.75</v>
       </c>
       <c r="G178" t="n">
-        <v>17.9160060882568</v>
+        <v>17.9160079956055</v>
       </c>
       <c r="H178" t="n">
         <v>107089</v>
@@ -5589,7 +5589,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G180" t="n">
-        <v>18.7664184570312</v>
+        <v>18.7664203643799</v>
       </c>
       <c r="H180" t="n">
         <v>186766</v>
@@ -5647,7 +5647,7 @@
         <v>18.75</v>
       </c>
       <c r="G182" t="n">
-        <v>17.9160060882568</v>
+        <v>17.9160079956055</v>
       </c>
       <c r="H182" t="n">
         <v>737639</v>
@@ -5676,7 +5676,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G183" t="n">
-        <v>17.7249011993408</v>
+        <v>17.7249031066895</v>
       </c>
       <c r="H183" t="n">
         <v>316794</v>
@@ -5705,7 +5705,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G184" t="n">
-        <v>17.189811706543</v>
+        <v>17.1898097991943</v>
       </c>
       <c r="H184" t="n">
         <v>165069</v>
@@ -5734,7 +5734,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G185" t="n">
-        <v>16.3967304229736</v>
+        <v>16.396728515625</v>
       </c>
       <c r="H185" t="n">
         <v>282326</v>
@@ -5792,7 +5792,7 @@
         <v>18</v>
       </c>
       <c r="G187" t="n">
-        <v>17.1993656158447</v>
+        <v>17.1993675231934</v>
       </c>
       <c r="H187" t="n">
         <v>168778</v>
@@ -5821,7 +5821,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G188" t="n">
-        <v>17.6580142974854</v>
+        <v>17.6580181121826</v>
       </c>
       <c r="H188" t="n">
         <v>106658</v>
@@ -5850,7 +5850,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G189" t="n">
-        <v>17.6580142974854</v>
+        <v>17.6580181121826</v>
       </c>
       <c r="H189" t="n">
         <v>195062</v>
@@ -5937,7 +5937,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G192" t="n">
-        <v>16.5305004119873</v>
+        <v>16.5305023193359</v>
       </c>
       <c r="H192" t="n">
         <v>303536</v>
@@ -5995,7 +5995,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>16.3871765136719</v>
+        <v>16.3871746063232</v>
       </c>
       <c r="H194" t="n">
         <v>289758</v>
@@ -6024,7 +6024,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G195" t="n">
-        <v>16.3011779785156</v>
+        <v>16.3011798858643</v>
       </c>
       <c r="H195" t="n">
         <v>519554</v>
@@ -6082,7 +6082,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G197" t="n">
-        <v>16.3489532470703</v>
+        <v>16.3489551544189</v>
       </c>
       <c r="H197" t="n">
         <v>187727</v>
@@ -6111,7 +6111,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G198" t="n">
-        <v>16.3011779785156</v>
+        <v>16.3011798858643</v>
       </c>
       <c r="H198" t="n">
         <v>103373</v>
@@ -6140,7 +6140,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G199" t="n">
-        <v>16.6069431304932</v>
+        <v>16.6069450378418</v>
       </c>
       <c r="H199" t="n">
         <v>89821</v>
@@ -6198,7 +6198,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>16.6260528564453</v>
+        <v>16.6260566711426</v>
       </c>
       <c r="H201" t="n">
         <v>108711</v>
@@ -6227,7 +6227,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G202" t="n">
-        <v>16.587833404541</v>
+        <v>16.5878353118896</v>
       </c>
       <c r="H202" t="n">
         <v>70415</v>
@@ -6256,7 +6256,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G203" t="n">
-        <v>16.7407169342041</v>
+        <v>16.7407150268555</v>
       </c>
       <c r="H203" t="n">
         <v>93120</v>
@@ -6285,7 +6285,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G204" t="n">
-        <v>16.7884922027588</v>
+        <v>16.7884941101074</v>
       </c>
       <c r="H204" t="n">
         <v>110054</v>
@@ -6314,7 +6314,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G205" t="n">
-        <v>17.0369300842285</v>
+        <v>17.0369281768799</v>
       </c>
       <c r="H205" t="n">
         <v>107074</v>
@@ -6343,7 +6343,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G206" t="n">
-        <v>17.2375869750977</v>
+        <v>17.2375888824463</v>
       </c>
       <c r="H206" t="n">
         <v>108799</v>
@@ -6401,7 +6401,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G208" t="n">
-        <v>16.9031562805176</v>
+        <v>16.9031543731689</v>
       </c>
       <c r="H208" t="n">
         <v>80044</v>
@@ -6459,7 +6459,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G210" t="n">
-        <v>17.2375869750977</v>
+        <v>17.2375888824463</v>
       </c>
       <c r="H210" t="n">
         <v>68530</v>
@@ -6546,7 +6546,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>17.2949180603027</v>
+        <v>17.2949199676514</v>
       </c>
       <c r="H213" t="n">
         <v>63203</v>
@@ -6633,7 +6633,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G216" t="n">
-        <v>17.6293525695801</v>
+        <v>17.6293506622314</v>
       </c>
       <c r="H216" t="n">
         <v>202637</v>
@@ -6662,7 +6662,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G217" t="n">
-        <v>18.2313270568848</v>
+        <v>18.2313289642334</v>
       </c>
       <c r="H217" t="n">
         <v>171919</v>
@@ -6749,7 +6749,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G220" t="n">
-        <v>18.0020046234131</v>
+        <v>18.0020065307617</v>
       </c>
       <c r="H220" t="n">
         <v>388714</v>
@@ -6778,7 +6778,7 @@
         <v>19.2700004577637</v>
       </c>
       <c r="G221" t="n">
-        <v>18.5309104919434</v>
+        <v>18.5309085845947</v>
       </c>
       <c r="H221" t="n">
         <v>86313</v>
@@ -7010,7 +7010,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G229" t="n">
-        <v>18.8097839355469</v>
+        <v>18.8097858428955</v>
       </c>
       <c r="H229" t="n">
         <v>69687</v>
@@ -7097,7 +7097,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>18.3674297332764</v>
+        <v>18.3674278259277</v>
       </c>
       <c r="H232" t="n">
         <v>66293</v>
@@ -7126,7 +7126,7 @@
         <v>19.75</v>
       </c>
       <c r="G233" t="n">
-        <v>18.9924983978271</v>
+        <v>18.9925003051758</v>
       </c>
       <c r="H233" t="n">
         <v>75996</v>
@@ -7155,7 +7155,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>19.1367454528809</v>
+        <v>19.1367473602295</v>
       </c>
       <c r="H234" t="n">
         <v>176092</v>
@@ -7300,7 +7300,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>19.3290729522705</v>
+        <v>19.3290748596191</v>
       </c>
       <c r="H239" t="n">
         <v>78255</v>
@@ -7329,7 +7329,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G240" t="n">
-        <v>19.4637031555176</v>
+        <v>19.4637050628662</v>
       </c>
       <c r="H240" t="n">
         <v>95964</v>
@@ -7387,7 +7387,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>19.4252414703369</v>
+        <v>19.4252395629883</v>
       </c>
       <c r="H242" t="n">
         <v>219460</v>
@@ -7416,7 +7416,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G243" t="n">
-        <v>19.0405788421631</v>
+        <v>19.0405807495117</v>
       </c>
       <c r="H243" t="n">
         <v>51065</v>
@@ -7590,7 +7590,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G249" t="n">
-        <v>18.4924430847168</v>
+        <v>18.4924411773682</v>
       </c>
       <c r="H249" t="n">
         <v>68327</v>
@@ -7619,7 +7619,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G250" t="n">
-        <v>18.4924430847168</v>
+        <v>18.4924411773682</v>
       </c>
       <c r="H250" t="n">
         <v>136559</v>
@@ -7677,7 +7677,7 @@
         <v>19.5</v>
       </c>
       <c r="G252" t="n">
-        <v>18.7520866394043</v>
+        <v>18.7520885467529</v>
       </c>
       <c r="H252" t="n">
         <v>47907</v>
@@ -7735,7 +7735,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G254" t="n">
-        <v>18.3866634368896</v>
+        <v>18.386661529541</v>
       </c>
       <c r="H254" t="n">
         <v>40747</v>
@@ -7764,7 +7764,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G255" t="n">
-        <v>19.4637031555176</v>
+        <v>19.4637050628662</v>
       </c>
       <c r="H255" t="n">
         <v>154255</v>
@@ -7793,7 +7793,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G256" t="n">
-        <v>19.4637031555176</v>
+        <v>19.4637050628662</v>
       </c>
       <c r="H256" t="n">
         <v>168657</v>
@@ -7822,7 +7822,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G257" t="n">
-        <v>19.6944980621338</v>
+        <v>19.6944999694824</v>
       </c>
       <c r="H257" t="n">
         <v>62964</v>
@@ -7909,7 +7909,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G260" t="n">
-        <v>19.5598697662354</v>
+        <v>19.5598678588867</v>
       </c>
       <c r="H260" t="n">
         <v>165590</v>
@@ -7938,7 +7938,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G261" t="n">
-        <v>19.2713775634766</v>
+        <v>19.2713756561279</v>
       </c>
       <c r="H261" t="n">
         <v>226076</v>
@@ -8054,7 +8054,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>19.8098964691162</v>
+        <v>19.8098983764648</v>
       </c>
       <c r="H265" t="n">
         <v>74881</v>
@@ -8199,7 +8199,7 @@
         <v>20.1399993896484</v>
       </c>
       <c r="G270" t="n">
-        <v>19.3675403594971</v>
+        <v>19.3675384521484</v>
       </c>
       <c r="H270" t="n">
         <v>52442</v>
@@ -8228,7 +8228,7 @@
         <v>18.7700004577637</v>
       </c>
       <c r="G271" t="n">
-        <v>18.050085067749</v>
+        <v>18.0500869750977</v>
       </c>
       <c r="H271" t="n">
         <v>522798</v>
@@ -8315,7 +8315,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G274" t="n">
-        <v>17.5115642547607</v>
+        <v>17.5115623474121</v>
       </c>
       <c r="H274" t="n">
         <v>166261</v>
@@ -8344,7 +8344,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G275" t="n">
-        <v>18.2904968261719</v>
+        <v>18.2904987335205</v>
       </c>
       <c r="H275" t="n">
         <v>226073</v>
@@ -8431,7 +8431,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G278" t="n">
-        <v>18.6270732879639</v>
+        <v>18.6270751953125</v>
       </c>
       <c r="H278" t="n">
         <v>96317</v>
@@ -8547,7 +8547,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G282" t="n">
-        <v>17.8866081237793</v>
+        <v>17.8866062164307</v>
       </c>
       <c r="H282" t="n">
         <v>64258</v>
@@ -8576,7 +8576,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G283" t="n">
-        <v>17.5981121063232</v>
+        <v>17.5981101989746</v>
       </c>
       <c r="H283" t="n">
         <v>79763</v>
@@ -8605,7 +8605,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G284" t="n">
-        <v>17.5404148101807</v>
+        <v>17.540412902832</v>
       </c>
       <c r="H284" t="n">
         <v>101821</v>
@@ -8750,7 +8750,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G289" t="n">
-        <v>16.6460838317871</v>
+        <v>16.6460819244385</v>
       </c>
       <c r="H289" t="n">
         <v>130395</v>
@@ -8779,7 +8779,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G290" t="n">
-        <v>17.1942195892334</v>
+        <v>17.194221496582</v>
       </c>
       <c r="H290" t="n">
         <v>97158</v>
@@ -8808,7 +8808,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G291" t="n">
-        <v>17.4923324584961</v>
+        <v>17.4923305511475</v>
       </c>
       <c r="H291" t="n">
         <v>98792</v>
@@ -8953,7 +8953,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G296" t="n">
-        <v>17.2807674407959</v>
+        <v>17.2807712554932</v>
       </c>
       <c r="H296" t="n">
         <v>59361</v>
@@ -9069,7 +9069,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G300" t="n">
-        <v>16.6460838317871</v>
+        <v>16.6460819244385</v>
       </c>
       <c r="H300" t="n">
         <v>104866</v>
@@ -9127,7 +9127,7 @@
         <v>17</v>
       </c>
       <c r="G302" t="n">
-        <v>16.347972869873</v>
+        <v>16.3479747772217</v>
       </c>
       <c r="H302" t="n">
         <v>123413</v>
@@ -9185,7 +9185,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G304" t="n">
-        <v>16.723014831543</v>
+        <v>16.7230129241943</v>
       </c>
       <c r="H304" t="n">
         <v>322231</v>
@@ -9214,7 +9214,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G305" t="n">
-        <v>16.3575916290283</v>
+        <v>16.3575897216797</v>
       </c>
       <c r="H305" t="n">
         <v>47439</v>
@@ -9272,7 +9272,7 @@
         <v>16.75</v>
       </c>
       <c r="G307" t="n">
-        <v>16.1075611114502</v>
+        <v>16.1075630187988</v>
       </c>
       <c r="H307" t="n">
         <v>64826</v>
@@ -9330,7 +9330,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G309" t="n">
-        <v>15.7132873535156</v>
+        <v>15.7132883071899</v>
       </c>
       <c r="H309" t="n">
         <v>82945</v>
@@ -9359,7 +9359,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G310" t="n">
-        <v>15.5401916503906</v>
+        <v>15.5401906967163</v>
       </c>
       <c r="H310" t="n">
         <v>75719</v>
@@ -9417,7 +9417,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>15.4824934005737</v>
+        <v>15.4824924468994</v>
       </c>
       <c r="H312" t="n">
         <v>47778</v>
@@ -9475,7 +9475,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G314" t="n">
-        <v>15.6555881500244</v>
+        <v>15.655590057373</v>
       </c>
       <c r="H314" t="n">
         <v>70184</v>
@@ -9504,7 +9504,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G315" t="n">
-        <v>15.8479175567627</v>
+        <v>15.8479166030884</v>
       </c>
       <c r="H315" t="n">
         <v>74847</v>
@@ -9591,7 +9591,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G318" t="n">
-        <v>14.4150648117065</v>
+        <v>14.4150667190552</v>
       </c>
       <c r="H318" t="n">
         <v>129315</v>
@@ -9707,7 +9707,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G322" t="n">
-        <v>14.5689296722412</v>
+        <v>14.5689287185669</v>
       </c>
       <c r="H322" t="n">
         <v>40798</v>
@@ -9765,7 +9765,7 @@
         <v>15</v>
       </c>
       <c r="G324" t="n">
-        <v>14.4246826171875</v>
+        <v>14.4246835708618</v>
       </c>
       <c r="H324" t="n">
         <v>91074</v>
@@ -9852,7 +9852,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G327" t="n">
-        <v>14.0881052017212</v>
+        <v>14.0881061553955</v>
       </c>
       <c r="H327" t="n">
         <v>66396</v>
@@ -9968,7 +9968,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G331" t="n">
-        <v>13.174542427063</v>
+        <v>13.1745433807373</v>
       </c>
       <c r="H331" t="n">
         <v>46983</v>
@@ -10026,7 +10026,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G333" t="n">
-        <v>12.8571996688843</v>
+        <v>12.8572006225586</v>
       </c>
       <c r="H333" t="n">
         <v>104403</v>
@@ -10055,7 +10055,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G334" t="n">
-        <v>12.674488067627</v>
+        <v>12.6744890213013</v>
       </c>
       <c r="H334" t="n">
         <v>59858</v>
@@ -10171,7 +10171,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G338" t="n">
-        <v>13.9053936004639</v>
+        <v>13.9053945541382</v>
       </c>
       <c r="H338" t="n">
         <v>230450</v>
@@ -10200,7 +10200,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G339" t="n">
-        <v>13.8284616470337</v>
+        <v>13.828462600708</v>
       </c>
       <c r="H339" t="n">
         <v>150608</v>
@@ -10258,7 +10258,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G341" t="n">
-        <v>13.2803249359131</v>
+        <v>13.2803239822388</v>
       </c>
       <c r="H341" t="n">
         <v>70862</v>
@@ -10374,7 +10374,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G345" t="n">
-        <v>13.655366897583</v>
+        <v>13.6553649902344</v>
       </c>
       <c r="H345" t="n">
         <v>126227</v>
@@ -10403,7 +10403,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G346" t="n">
-        <v>14.5016136169434</v>
+        <v>14.5016145706177</v>
       </c>
       <c r="H346" t="n">
         <v>237267</v>
@@ -10432,7 +10432,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G347" t="n">
-        <v>14.6362447738647</v>
+        <v>14.6362438201904</v>
       </c>
       <c r="H347" t="n">
         <v>215592</v>
@@ -10548,7 +10548,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G351" t="n">
-        <v>14.1073398590088</v>
+        <v>14.1073389053345</v>
       </c>
       <c r="H351" t="n">
         <v>93291</v>
@@ -10606,7 +10606,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G353" t="n">
-        <v>14.3092861175537</v>
+        <v>14.3092851638794</v>
       </c>
       <c r="H353" t="n">
         <v>104165</v>
@@ -10635,7 +10635,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G354" t="n">
-        <v>14.2996673583984</v>
+        <v>14.2996683120728</v>
       </c>
       <c r="H354" t="n">
         <v>87931</v>
@@ -10722,7 +10722,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G357" t="n">
-        <v>13.7611474990845</v>
+        <v>13.7611465454102</v>
       </c>
       <c r="H357" t="n">
         <v>89876</v>
@@ -10780,7 +10780,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G359" t="n">
-        <v>13.6649827957153</v>
+        <v>13.664981842041</v>
       </c>
       <c r="H359" t="n">
         <v>97011</v>
@@ -10809,7 +10809,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G360" t="n">
-        <v>13.2707080841064</v>
+        <v>13.2707071304321</v>
       </c>
       <c r="H360" t="n">
         <v>139158</v>
@@ -10838,7 +10838,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G361" t="n">
-        <v>13.5399684906006</v>
+        <v>13.5399694442749</v>
       </c>
       <c r="H361" t="n">
         <v>102042</v>
@@ -10896,7 +10896,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G363" t="n">
-        <v>13.1841602325439</v>
+        <v>13.1841592788696</v>
       </c>
       <c r="H363" t="n">
         <v>159187</v>
@@ -10983,7 +10983,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G366" t="n">
-        <v>13.5015020370483</v>
+        <v>13.5015029907227</v>
       </c>
       <c r="H366" t="n">
         <v>125716</v>
@@ -11012,7 +11012,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G367" t="n">
-        <v>13.5495853424072</v>
+        <v>13.5495862960815</v>
       </c>
       <c r="H367" t="n">
         <v>174963</v>
@@ -11041,7 +11041,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G368" t="n">
-        <v>14.7131757736206</v>
+        <v>14.7131767272949</v>
       </c>
       <c r="H368" t="n">
         <v>469164</v>
@@ -11070,7 +11070,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G369" t="n">
-        <v>14.674711227417</v>
+        <v>14.6747102737427</v>
       </c>
       <c r="H369" t="n">
         <v>228319</v>
@@ -11099,7 +11099,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G370" t="n">
-        <v>14.9151210784912</v>
+        <v>14.9151220321655</v>
       </c>
       <c r="H370" t="n">
         <v>166793</v>
@@ -11186,7 +11186,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G373" t="n">
-        <v>14.9151210784912</v>
+        <v>14.9151220321655</v>
       </c>
       <c r="H373" t="n">
         <v>162189</v>
@@ -11244,7 +11244,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G375" t="n">
-        <v>14.8381910324097</v>
+        <v>14.8381900787354</v>
       </c>
       <c r="H375" t="n">
         <v>137149</v>
@@ -11360,7 +11360,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G379" t="n">
-        <v>14.5016136169434</v>
+        <v>14.5016145706177</v>
       </c>
       <c r="H379" t="n">
         <v>337572</v>
@@ -11418,7 +11418,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G381" t="n">
-        <v>14.8862714767456</v>
+        <v>14.8862724304199</v>
       </c>
       <c r="H381" t="n">
         <v>97752</v>
@@ -11563,7 +11563,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G386" t="n">
-        <v>14.0977230072021</v>
+        <v>14.0977220535278</v>
       </c>
       <c r="H386" t="n">
         <v>236798</v>
@@ -11621,7 +11621,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G388" t="n">
-        <v>13.9823265075684</v>
+        <v>13.982325553894</v>
       </c>
       <c r="H388" t="n">
         <v>99895</v>
@@ -11708,7 +11708,7 @@
         <v>14.2700004577637</v>
       </c>
       <c r="G391" t="n">
-        <v>13.7226810455322</v>
+        <v>13.7226819992065</v>
       </c>
       <c r="H391" t="n">
         <v>186975</v>
@@ -11737,7 +11737,7 @@
         <v>14.5</v>
       </c>
       <c r="G392" t="n">
-        <v>13.9438600540161</v>
+        <v>13.9438591003418</v>
       </c>
       <c r="H392" t="n">
         <v>133628</v>
@@ -11882,7 +11882,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G397" t="n">
-        <v>13.6649827957153</v>
+        <v>13.664981842041</v>
       </c>
       <c r="H397" t="n">
         <v>175445</v>
@@ -11911,7 +11911,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G398" t="n">
-        <v>13.3668727874756</v>
+        <v>13.3668718338013</v>
       </c>
       <c r="H398" t="n">
         <v>212475</v>
@@ -12172,7 +12172,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>13.655366897583</v>
+        <v>13.6553649902344</v>
       </c>
       <c r="H407" t="n">
         <v>163196</v>
@@ -12201,7 +12201,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G408" t="n">
-        <v>14.1650381088257</v>
+        <v>14.1650371551514</v>
       </c>
       <c r="H408" t="n">
         <v>284491</v>
@@ -12404,7 +12404,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G415" t="n">
-        <v>14.8862714767456</v>
+        <v>14.8862724304199</v>
       </c>
       <c r="H415" t="n">
         <v>139801</v>
@@ -12491,7 +12491,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G418" t="n">
-        <v>14.6458606719971</v>
+        <v>14.6458597183228</v>
       </c>
       <c r="H418" t="n">
         <v>94315</v>
@@ -12578,7 +12578,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G421" t="n">
-        <v>14.5016136169434</v>
+        <v>14.5016145706177</v>
       </c>
       <c r="H421" t="n">
         <v>101945</v>
@@ -12607,7 +12607,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G422" t="n">
-        <v>14.3092861175537</v>
+        <v>14.3092851638794</v>
       </c>
       <c r="H422" t="n">
         <v>102639</v>
@@ -12636,7 +12636,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G423" t="n">
-        <v>14.2323532104492</v>
+        <v>14.2323541641235</v>
       </c>
       <c r="H423" t="n">
         <v>63885</v>
@@ -12694,7 +12694,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G425" t="n">
-        <v>14.1554222106934</v>
+        <v>14.155421257019</v>
       </c>
       <c r="H425" t="n">
         <v>117944</v>
@@ -12752,7 +12752,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G427" t="n">
-        <v>13.6649827957153</v>
+        <v>13.664981842041</v>
       </c>
       <c r="H427" t="n">
         <v>159222</v>
@@ -12868,7 +12868,7 @@
         <v>14.1899995803833</v>
       </c>
       <c r="G431" t="n">
-        <v>13.6457481384277</v>
+        <v>13.6457490921021</v>
       </c>
       <c r="H431" t="n">
         <v>223671</v>
@@ -12897,7 +12897,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G432" t="n">
-        <v>12.6937198638916</v>
+        <v>12.6937208175659</v>
       </c>
       <c r="H432" t="n">
         <v>632996</v>
@@ -12926,7 +12926,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G433" t="n">
-        <v>12.645637512207</v>
+        <v>12.6456384658813</v>
       </c>
       <c r="H433" t="n">
         <v>771950</v>
@@ -12955,7 +12955,7 @@
         <v>13.25</v>
       </c>
       <c r="G434" t="n">
-        <v>12.7418031692505</v>
+        <v>12.7418022155762</v>
       </c>
       <c r="H434" t="n">
         <v>207043</v>
@@ -12984,7 +12984,7 @@
         <v>13.25</v>
       </c>
       <c r="G435" t="n">
-        <v>12.7418031692505</v>
+        <v>12.7418022155762</v>
       </c>
       <c r="H435" t="n">
         <v>214799</v>
@@ -13071,7 +13071,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G438" t="n">
-        <v>12.645637512207</v>
+        <v>12.6456384658813</v>
       </c>
       <c r="H438" t="n">
         <v>150121</v>
@@ -13100,7 +13100,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G439" t="n">
-        <v>12.8571996688843</v>
+        <v>12.8572006225586</v>
       </c>
       <c r="H439" t="n">
         <v>90236</v>
@@ -13158,7 +13158,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G441" t="n">
-        <v>12.3763780593872</v>
+        <v>12.3763771057129</v>
       </c>
       <c r="H441" t="n">
         <v>197033</v>
@@ -13245,7 +13245,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G444" t="n">
-        <v>12.472541809082</v>
+        <v>12.4725427627563</v>
       </c>
       <c r="H444" t="n">
         <v>169735</v>
@@ -13274,7 +13274,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G445" t="n">
-        <v>12.7802686691284</v>
+        <v>12.7802677154541</v>
       </c>
       <c r="H445" t="n">
         <v>146927</v>
@@ -13477,7 +13477,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G452" t="n">
-        <v>12.6937198638916</v>
+        <v>12.6937208175659</v>
       </c>
       <c r="H452" t="n">
         <v>67295</v>
@@ -13506,7 +13506,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G453" t="n">
-        <v>11.9244041442871</v>
+        <v>11.9244031906128</v>
       </c>
       <c r="H453" t="n">
         <v>236491</v>
@@ -13535,7 +13535,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G454" t="n">
-        <v>11.6839933395386</v>
+        <v>11.6839923858643</v>
       </c>
       <c r="H454" t="n">
         <v>219490</v>
@@ -13680,7 +13680,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G459" t="n">
-        <v>11.8859386444092</v>
+        <v>11.8859376907349</v>
       </c>
       <c r="H459" t="n">
         <v>67163</v>
@@ -13709,7 +13709,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G460" t="n">
-        <v>12.1744318008423</v>
+        <v>12.1744327545166</v>
       </c>
       <c r="H460" t="n">
         <v>97426</v>
@@ -13767,7 +13767,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G462" t="n">
-        <v>12.1455821990967</v>
+        <v>12.145583152771</v>
       </c>
       <c r="H462" t="n">
         <v>90492</v>
@@ -13796,7 +13796,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G463" t="n">
-        <v>12.0494184494019</v>
+        <v>12.0494174957275</v>
       </c>
       <c r="H463" t="n">
         <v>59080</v>
@@ -13854,7 +13854,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G465" t="n">
-        <v>12.8668165206909</v>
+        <v>12.8668174743652</v>
       </c>
       <c r="H465" t="n">
         <v>259031</v>
@@ -13912,7 +13912,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G467" t="n">
-        <v>12.7514200210571</v>
+        <v>12.7514190673828</v>
       </c>
       <c r="H467" t="n">
         <v>287755</v>
@@ -13999,7 +13999,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G470" t="n">
-        <v>13.3476390838623</v>
+        <v>13.3476400375366</v>
       </c>
       <c r="H470" t="n">
         <v>152417</v>
@@ -14057,7 +14057,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G472" t="n">
-        <v>13.1841602325439</v>
+        <v>13.1841592788696</v>
       </c>
       <c r="H472" t="n">
         <v>75618</v>
@@ -14115,7 +14115,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G474" t="n">
-        <v>12.7782726287842</v>
+        <v>12.7782716751099</v>
       </c>
       <c r="H474" t="n">
         <v>99354</v>
@@ -14173,7 +14173,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G476" t="n">
-        <v>13.0790510177612</v>
+        <v>13.0790500640869</v>
       </c>
       <c r="H476" t="n">
         <v>88070</v>
@@ -14202,7 +14202,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G477" t="n">
-        <v>12.9141073226929</v>
+        <v>12.9141082763672</v>
       </c>
       <c r="H477" t="n">
         <v>53958</v>
@@ -14231,7 +14231,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G478" t="n">
-        <v>12.4871950149536</v>
+        <v>12.4871940612793</v>
       </c>
       <c r="H478" t="n">
         <v>88793</v>
@@ -14260,7 +14260,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G479" t="n">
-        <v>12.8461885452271</v>
+        <v>12.8461894989014</v>
       </c>
       <c r="H479" t="n">
         <v>56934</v>
@@ -14347,7 +14347,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G482" t="n">
-        <v>12.8073787689209</v>
+        <v>12.8073797225952</v>
       </c>
       <c r="H482" t="n">
         <v>146288</v>
@@ -14695,7 +14695,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G494" t="n">
-        <v>11.3519954681396</v>
+        <v>11.3519945144653</v>
       </c>
       <c r="H494" t="n">
         <v>90980</v>
@@ -14782,7 +14782,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G497" t="n">
-        <v>11.487832069397</v>
+        <v>11.4878311157227</v>
       </c>
       <c r="H497" t="n">
         <v>74033</v>
@@ -14898,7 +14898,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G501" t="n">
-        <v>11.3519954681396</v>
+        <v>11.3519945144653</v>
       </c>
       <c r="H501" t="n">
         <v>72055</v>
@@ -15101,7 +15101,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G508" t="n">
-        <v>11.0803232192993</v>
+        <v>11.0803241729736</v>
       </c>
       <c r="H508" t="n">
         <v>52830</v>
@@ -15217,7 +15217,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G512" t="n">
-        <v>11.0803232192993</v>
+        <v>11.0803241729736</v>
       </c>
       <c r="H512" t="n">
         <v>67037</v>
@@ -15333,7 +15333,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G516" t="n">
-        <v>10.973596572876</v>
+        <v>10.9735956192017</v>
       </c>
       <c r="H516" t="n">
         <v>81818</v>
@@ -15420,7 +15420,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G519" t="n">
-        <v>10.9638929367065</v>
+        <v>10.9638938903809</v>
       </c>
       <c r="H519" t="n">
         <v>97469</v>
@@ -15565,7 +15565,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G524" t="n">
-        <v>10.5854930877686</v>
+        <v>10.5854921340942</v>
       </c>
       <c r="H524" t="n">
         <v>134025</v>
@@ -15623,7 +15623,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G526" t="n">
-        <v>10.381739616394</v>
+        <v>10.3817386627197</v>
       </c>
       <c r="H526" t="n">
         <v>195282</v>
@@ -16087,7 +16087,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G542" t="n">
-        <v>9.67830371856689</v>
+        <v>9.67830467224121</v>
       </c>
       <c r="H542" t="n">
         <v>134678</v>
@@ -16145,7 +16145,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G544" t="n">
-        <v>9.51821136474609</v>
+        <v>9.51821231842041</v>
       </c>
       <c r="H544" t="n">
         <v>80660</v>
@@ -16174,7 +16174,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G545" t="n">
-        <v>9.54731941223145</v>
+        <v>9.54731845855713</v>
       </c>
       <c r="H545" t="n">
         <v>95108</v>
@@ -16319,7 +16319,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G550" t="n">
-        <v>9.24654006958008</v>
+        <v>9.24653911590576</v>
       </c>
       <c r="H550" t="n">
         <v>94988</v>
@@ -16348,7 +16348,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G551" t="n">
-        <v>9.16891956329346</v>
+        <v>9.16891860961914</v>
       </c>
       <c r="H551" t="n">
         <v>135094</v>
@@ -16435,7 +16435,7 @@
         <v>8.91499996185303</v>
       </c>
       <c r="G554" t="n">
-        <v>8.6498327255249</v>
+        <v>8.64983177185059</v>
       </c>
       <c r="H554" t="n">
         <v>131072</v>
@@ -16464,7 +16464,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G555" t="n">
-        <v>9.0815954208374</v>
+        <v>9.08159637451172</v>
       </c>
       <c r="H555" t="n">
         <v>164784</v>
@@ -16493,7 +16493,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G556" t="n">
-        <v>9.09129905700684</v>
+        <v>9.09129810333252</v>
       </c>
       <c r="H556" t="n">
         <v>112117</v>
@@ -16551,7 +16551,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G558" t="n">
-        <v>9.0815954208374</v>
+        <v>9.08159637451172</v>
       </c>
       <c r="H558" t="n">
         <v>76175</v>
@@ -16609,7 +16609,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G560" t="n">
-        <v>9.24654006958008</v>
+        <v>9.24653911590576</v>
       </c>
       <c r="H560" t="n">
         <v>57482</v>
@@ -16638,7 +16638,7 @@
         <v>9.55500030517578</v>
       </c>
       <c r="G561" t="n">
-        <v>9.27079582214355</v>
+        <v>9.27079677581787</v>
       </c>
       <c r="H561" t="n">
         <v>80413</v>
@@ -16783,7 +16783,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G566" t="n">
-        <v>9.15921592712402</v>
+        <v>9.15921688079834</v>
       </c>
       <c r="H566" t="n">
         <v>168859</v>
@@ -16957,7 +16957,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G572" t="n">
-        <v>8.91665267944336</v>
+        <v>8.91665172576904</v>
       </c>
       <c r="H572" t="n">
         <v>55529</v>
@@ -17015,7 +17015,7 @@
         <v>8.90499973297119</v>
       </c>
       <c r="G574" t="n">
-        <v>8.64012908935547</v>
+        <v>8.64013004302979</v>
       </c>
       <c r="H574" t="n">
         <v>288790</v>
@@ -17073,7 +17073,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G576" t="n">
-        <v>8.66438674926758</v>
+        <v>8.66438579559326</v>
       </c>
       <c r="H576" t="n">
         <v>85122</v>
@@ -17160,7 +17160,7 @@
         <v>8.75</v>
       </c>
       <c r="G579" t="n">
-        <v>8.48973941802979</v>
+        <v>8.4897403717041</v>
       </c>
       <c r="H579" t="n">
         <v>77770</v>
@@ -17189,7 +17189,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G580" t="n">
-        <v>8.72260189056396</v>
+        <v>8.72260093688965</v>
       </c>
       <c r="H580" t="n">
         <v>167385</v>
@@ -17276,7 +17276,7 @@
         <v>8.82499980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>8.56250858306885</v>
+        <v>8.56250953674316</v>
       </c>
       <c r="H583" t="n">
         <v>185644</v>
@@ -17305,7 +17305,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G584" t="n">
-        <v>8.80022239685059</v>
+        <v>8.80022144317627</v>
       </c>
       <c r="H584" t="n">
         <v>145712</v>
@@ -17334,7 +17334,7 @@
         <v>8.91499996185303</v>
       </c>
       <c r="G585" t="n">
-        <v>8.6498327255249</v>
+        <v>8.64983177185059</v>
       </c>
       <c r="H585" t="n">
         <v>105376</v>
@@ -17392,7 +17392,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G587" t="n">
-        <v>8.76141166687012</v>
+        <v>8.7614107131958</v>
       </c>
       <c r="H587" t="n">
         <v>110831</v>
@@ -17508,7 +17508,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G591" t="n">
-        <v>8.38786315917969</v>
+        <v>8.387864112854</v>
       </c>
       <c r="H591" t="n">
         <v>209095</v>
@@ -17566,7 +17566,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G593" t="n">
-        <v>8.7420072555542</v>
+        <v>8.74200630187988</v>
       </c>
       <c r="H593" t="n">
         <v>123295</v>
@@ -17624,7 +17624,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>8.56735992431641</v>
+        <v>8.56736087799072</v>
       </c>
       <c r="H595" t="n">
         <v>506056</v>
@@ -17711,7 +17711,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G598" t="n">
-        <v>8.76141166687012</v>
+        <v>8.7614107131958</v>
       </c>
       <c r="H598" t="n">
         <v>275140</v>
@@ -17798,7 +17798,7 @@
         <v>8.47500038146973</v>
       </c>
       <c r="G601" t="n">
-        <v>8.22292041778564</v>
+        <v>8.22291946411133</v>
       </c>
       <c r="H601" t="n">
         <v>238471</v>
@@ -17827,7 +17827,7 @@
         <v>8.28499984741211</v>
       </c>
       <c r="G602" t="n">
-        <v>8.03857135772705</v>
+        <v>8.03857040405273</v>
       </c>
       <c r="H602" t="n">
         <v>639924</v>
@@ -17914,7 +17914,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G605" t="n">
-        <v>7.67472457885742</v>
+        <v>7.67472505569458</v>
       </c>
       <c r="H605" t="n">
         <v>165566</v>
@@ -17943,7 +17943,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G606" t="n">
-        <v>7.46126890182495</v>
+        <v>7.46126842498779</v>
       </c>
       <c r="H606" t="n">
         <v>281631</v>
@@ -18030,7 +18030,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G609" t="n">
-        <v>7.73779153823853</v>
+        <v>7.73779201507568</v>
       </c>
       <c r="H609" t="n">
         <v>85842</v>
@@ -18088,7 +18088,7 @@
         <v>8.00500011444092</v>
       </c>
       <c r="G611" t="n">
-        <v>7.76689958572388</v>
+        <v>7.76689910888672</v>
       </c>
       <c r="H611" t="n">
         <v>68292</v>
@@ -18175,7 +18175,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G614" t="n">
-        <v>7.73779153823853</v>
+        <v>7.73779201507568</v>
       </c>
       <c r="H614" t="n">
         <v>142315</v>
@@ -18204,7 +18204,7 @@
         <v>7.9850001335144</v>
       </c>
       <c r="G615" t="n">
-        <v>7.74749422073364</v>
+        <v>7.7474946975708</v>
       </c>
       <c r="H615" t="n">
         <v>116245</v>
@@ -18262,7 +18262,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G617" t="n">
-        <v>7.95609951019287</v>
+        <v>7.95609855651855</v>
       </c>
       <c r="H617" t="n">
         <v>208602</v>
@@ -18291,7 +18291,7 @@
         <v>8.14500045776367</v>
       </c>
       <c r="G618" t="n">
-        <v>7.90273523330688</v>
+        <v>7.90273571014404</v>
       </c>
       <c r="H618" t="n">
         <v>116291</v>
@@ -18320,7 +18320,7 @@
         <v>8.17500019073486</v>
       </c>
       <c r="G619" t="n">
-        <v>7.93184280395508</v>
+        <v>7.93184328079224</v>
       </c>
       <c r="H619" t="n">
         <v>91476</v>
@@ -18436,7 +18436,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>7.44671487808228</v>
+        <v>7.44671535491943</v>
       </c>
       <c r="H623" t="n">
         <v>226325</v>
@@ -18465,7 +18465,7 @@
         <v>7.64499998092651</v>
       </c>
       <c r="G624" t="n">
-        <v>7.41760683059692</v>
+        <v>7.41760730743408</v>
       </c>
       <c r="H624" t="n">
         <v>275750</v>
@@ -18494,7 +18494,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G625" t="n">
-        <v>7.41275596618652</v>
+        <v>7.41275548934937</v>
       </c>
       <c r="H625" t="n">
         <v>150786</v>
@@ -18581,7 +18581,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>7.31087923049927</v>
+        <v>7.31087875366211</v>
       </c>
       <c r="H628" t="n">
         <v>129823</v>
@@ -18668,7 +18668,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G631" t="n">
-        <v>7.53888940811157</v>
+        <v>7.53888893127441</v>
       </c>
       <c r="H631" t="n">
         <v>91913</v>
@@ -18697,7 +18697,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G632" t="n">
-        <v>7.42245864868164</v>
+        <v>7.42245817184448</v>
       </c>
       <c r="H632" t="n">
         <v>71179</v>
@@ -18726,7 +18726,7 @@
         <v>7.77500009536743</v>
       </c>
       <c r="G633" t="n">
-        <v>7.54374027252197</v>
+        <v>7.54374074935913</v>
       </c>
       <c r="H633" t="n">
         <v>104298</v>
@@ -18755,7 +18755,7 @@
         <v>7.875</v>
       </c>
       <c r="G634" t="n">
-        <v>7.64076566696167</v>
+        <v>7.64076614379883</v>
       </c>
       <c r="H634" t="n">
         <v>86228</v>
@@ -18842,7 +18842,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G637" t="n">
-        <v>7.05861282348633</v>
+        <v>7.05861234664917</v>
       </c>
       <c r="H637" t="n">
         <v>150003</v>
@@ -18900,7 +18900,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>6.84515571594238</v>
+        <v>6.84515619277954</v>
       </c>
       <c r="H639" t="n">
         <v>176664</v>
@@ -18958,7 +18958,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G641" t="n">
-        <v>6.98099231719971</v>
+        <v>6.98099184036255</v>
       </c>
       <c r="H641" t="n">
         <v>147248</v>
@@ -18987,7 +18987,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>7.17989444732666</v>
+        <v>7.17989492416382</v>
       </c>
       <c r="H642" t="n">
         <v>152913</v>
@@ -19277,7 +19277,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G652" t="n">
-        <v>6.96643829345703</v>
+        <v>6.96643781661987</v>
       </c>
       <c r="H652" t="n">
         <v>197817</v>
@@ -19306,7 +19306,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G653" t="n">
-        <v>6.786940574646</v>
+        <v>6.78694105148315</v>
       </c>
       <c r="H653" t="n">
         <v>219932</v>
@@ -19451,7 +19451,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G658" t="n">
-        <v>6.786940574646</v>
+        <v>6.78694105148315</v>
       </c>
       <c r="H658" t="n">
         <v>214637</v>
@@ -19596,7 +19596,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G663" t="n">
-        <v>6.67536163330078</v>
+        <v>6.67536115646362</v>
       </c>
       <c r="H663" t="n">
         <v>163183</v>
@@ -19654,7 +19654,7 @@
         <v>8.65499973297119</v>
       </c>
       <c r="G665" t="n">
-        <v>8.3975658416748</v>
+        <v>8.39756488800049</v>
       </c>
       <c r="H665" t="n">
         <v>1421609</v>
@@ -19683,7 +19683,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G666" t="n">
-        <v>8.19866275787354</v>
+        <v>8.19866371154785</v>
       </c>
       <c r="H666" t="n">
         <v>376186</v>
@@ -19712,7 +19712,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G667" t="n">
-        <v>8.52855014801025</v>
+        <v>8.52855110168457</v>
       </c>
       <c r="H667" t="n">
         <v>499509</v>
@@ -19828,7 +19828,7 @@
         <v>9.07499980926514</v>
       </c>
       <c r="G671" t="n">
-        <v>8.80507373809814</v>
+        <v>8.80507278442383</v>
       </c>
       <c r="H671" t="n">
         <v>162058</v>
@@ -19886,7 +19886,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G673" t="n">
-        <v>8.7420072555542</v>
+        <v>8.74200630187988</v>
       </c>
       <c r="H673" t="n">
         <v>106877</v>
@@ -20002,7 +20002,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>9.04763698577881</v>
+        <v>9.04763793945312</v>
       </c>
       <c r="H677" t="n">
         <v>120993</v>
@@ -20031,7 +20031,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G678" t="n">
-        <v>9.04763698577881</v>
+        <v>9.04763793945312</v>
       </c>
       <c r="H678" t="n">
         <v>114620</v>
@@ -20060,7 +20060,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G679" t="n">
-        <v>8.94090843200684</v>
+        <v>8.94090938568115</v>
       </c>
       <c r="H679" t="n">
         <v>176536</v>
@@ -20263,7 +20263,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G686" t="n">
-        <v>6.82575082778931</v>
+        <v>6.82575130462646</v>
       </c>
       <c r="H686" t="n">
         <v>2010202</v>
@@ -20321,7 +20321,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G688" t="n">
-        <v>6.44249963760376</v>
+        <v>6.44250011444092</v>
       </c>
       <c r="H688" t="n">
         <v>526066</v>
@@ -20350,7 +20350,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G689" t="n">
-        <v>6.66080713272095</v>
+        <v>6.66080760955811</v>
       </c>
       <c r="H689" t="n">
         <v>633433</v>
@@ -20379,7 +20379,7 @@
         <v>6.64499998092651</v>
       </c>
       <c r="G690" t="n">
-        <v>6.44735145568848</v>
+        <v>6.44735097885132</v>
       </c>
       <c r="H690" t="n">
         <v>435937</v>
@@ -20408,7 +20408,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G691" t="n">
-        <v>6.46190452575684</v>
+        <v>6.46190500259399</v>
       </c>
       <c r="H691" t="n">
         <v>314939</v>
@@ -20437,7 +20437,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>6.32606887817383</v>
+        <v>6.32606935501099</v>
       </c>
       <c r="H692" t="n">
         <v>246343</v>
@@ -20553,7 +20553,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G696" t="n">
-        <v>6.09805917739868</v>
+        <v>6.09805870056152</v>
       </c>
       <c r="H696" t="n">
         <v>426023</v>
@@ -20582,7 +20582,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G697" t="n">
-        <v>5.84094142913818</v>
+        <v>5.84094095230103</v>
       </c>
       <c r="H697" t="n">
         <v>433195</v>
@@ -20640,7 +20640,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G699" t="n">
-        <v>6.01073598861694</v>
+        <v>6.0107364654541</v>
       </c>
       <c r="H699" t="n">
         <v>258310</v>
@@ -20727,7 +20727,7 @@
         <v>6.35500001907349</v>
       </c>
       <c r="G702" t="n">
-        <v>6.16597652435303</v>
+        <v>6.16597700119019</v>
       </c>
       <c r="H702" t="n">
         <v>169235</v>
@@ -20756,7 +20756,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G703" t="n">
-        <v>6.07380247116089</v>
+        <v>6.07380294799805</v>
       </c>
       <c r="H703" t="n">
         <v>180300</v>
@@ -20814,7 +20814,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G705" t="n">
-        <v>5.97677659988403</v>
+        <v>5.97677707672119</v>
       </c>
       <c r="H705" t="n">
         <v>155044</v>
@@ -20930,7 +20930,7 @@
         <v>6.125</v>
       </c>
       <c r="G709" t="n">
-        <v>5.94281768798828</v>
+        <v>5.94281816482544</v>
       </c>
       <c r="H709" t="n">
         <v>221764</v>
@@ -21104,7 +21104,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G715" t="n">
-        <v>6.4327974319458</v>
+        <v>6.43279790878296</v>
       </c>
       <c r="H715" t="n">
         <v>116884</v>
@@ -21133,7 +21133,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G716" t="n">
-        <v>6.2775559425354</v>
+        <v>6.27755641937256</v>
       </c>
       <c r="H716" t="n">
         <v>222806</v>
@@ -21220,7 +21220,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G719" t="n">
-        <v>6.5007152557373</v>
+        <v>6.50071477890015</v>
       </c>
       <c r="H719" t="n">
         <v>144135</v>
@@ -21365,7 +21365,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G724" t="n">
-        <v>6.67536163330078</v>
+        <v>6.67536115646362</v>
       </c>
       <c r="H724" t="n">
         <v>775096</v>
@@ -31883,7 +31883,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="D1087" t="n">
-        <v>5.65000009536743</v>
+        <v>5.67999982833862</v>
       </c>
       <c r="E1087" t="n">
         <v>5.375</v>
@@ -31898,6 +31898,35 @@
         <v>646898</v>
       </c>
       <c r="I1087" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1088" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1088" t="n">
+        <v>5.61499977111816</v>
+      </c>
+      <c r="D1088" t="n">
+        <v>5.69500017166138</v>
+      </c>
+      <c r="E1088" t="n">
+        <v>5.55999994277954</v>
+      </c>
+      <c r="F1088" t="n">
+        <v>5.63000011444092</v>
+      </c>
+      <c r="G1088" t="n">
+        <v>5.63000011444092</v>
+      </c>
+      <c r="H1088" t="n">
+        <v>267624</v>
+      </c>
+      <c r="I1088" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DNR.MI.xlsx
+++ b/data/DNR.MI.xlsx
@@ -572,7 +572,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G7" t="n">
-        <v>12.5077610015869</v>
+        <v>12.5077619552612</v>
       </c>
       <c r="H7" t="n">
         <v>117337</v>
@@ -659,7 +659,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G10" t="n">
-        <v>12.5173168182373</v>
+        <v>12.5173177719116</v>
       </c>
       <c r="H10" t="n">
         <v>111264</v>
@@ -688,7 +688,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>12.5173168182373</v>
+        <v>12.5173177719116</v>
       </c>
       <c r="H11" t="n">
         <v>104743</v>
@@ -833,7 +833,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G16" t="n">
-        <v>13.415506362915</v>
+        <v>13.4155054092407</v>
       </c>
       <c r="H16" t="n">
         <v>258303</v>
@@ -949,7 +949,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G20" t="n">
-        <v>13.8072700500488</v>
+        <v>13.8072690963745</v>
       </c>
       <c r="H20" t="n">
         <v>301266</v>
@@ -1007,7 +1007,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G22" t="n">
-        <v>14.0652599334717</v>
+        <v>14.065260887146</v>
       </c>
       <c r="H22" t="n">
         <v>577409</v>
@@ -1036,7 +1036,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>14.1417026519775</v>
+        <v>14.1417016983032</v>
       </c>
       <c r="H23" t="n">
         <v>170138</v>
@@ -1094,7 +1094,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G25" t="n">
-        <v>13.9410429000854</v>
+        <v>13.9410419464111</v>
       </c>
       <c r="H25" t="n">
         <v>258800</v>
@@ -1210,7 +1210,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G29" t="n">
-        <v>13.8263807296753</v>
+        <v>13.826379776001</v>
       </c>
       <c r="H29" t="n">
         <v>61971</v>
@@ -1326,7 +1326,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G33" t="n">
-        <v>13.7403831481934</v>
+        <v>13.740382194519</v>
       </c>
       <c r="H33" t="n">
         <v>47665</v>
@@ -1384,7 +1384,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G35" t="n">
-        <v>13.5397243499756</v>
+        <v>13.5397253036499</v>
       </c>
       <c r="H35" t="n">
         <v>88256</v>
@@ -1529,7 +1529,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G40" t="n">
-        <v>13.8454904556274</v>
+        <v>13.8454895019531</v>
       </c>
       <c r="H40" t="n">
         <v>109728</v>
@@ -1558,7 +1558,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G41" t="n">
-        <v>14.8870077133179</v>
+        <v>14.8870067596436</v>
       </c>
       <c r="H41" t="n">
         <v>505585</v>
@@ -1587,7 +1587,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>15.1927738189697</v>
+        <v>15.1927728652954</v>
       </c>
       <c r="H42" t="n">
         <v>474029</v>
@@ -1616,7 +1616,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>15.3838777542114</v>
+        <v>15.3838787078857</v>
       </c>
       <c r="H43" t="n">
         <v>436799</v>
@@ -1645,7 +1645,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G44" t="n">
-        <v>16.1387405395508</v>
+        <v>16.1387386322021</v>
       </c>
       <c r="H44" t="n">
         <v>348418</v>
@@ -1703,7 +1703,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G46" t="n">
-        <v>15.4507656097412</v>
+        <v>15.4507646560669</v>
       </c>
       <c r="H46" t="n">
         <v>226004</v>
@@ -1732,7 +1732,7 @@
         <v>16.0900001525879</v>
       </c>
       <c r="G47" t="n">
-        <v>15.3743228912354</v>
+        <v>15.374321937561</v>
       </c>
       <c r="H47" t="n">
         <v>347713</v>
@@ -1761,7 +1761,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G48" t="n">
-        <v>16.0909633636475</v>
+        <v>16.0909614562988</v>
       </c>
       <c r="H48" t="n">
         <v>581768</v>
@@ -1790,7 +1790,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G49" t="n">
-        <v>15.6418695449829</v>
+        <v>15.6418685913086</v>
       </c>
       <c r="H49" t="n">
         <v>782970</v>
@@ -1935,7 +1935,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G54" t="n">
-        <v>14.0079278945923</v>
+        <v>14.0079288482666</v>
       </c>
       <c r="H54" t="n">
         <v>147319</v>
@@ -1964,7 +1964,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G55" t="n">
-        <v>14.7341241836548</v>
+        <v>14.7341232299805</v>
       </c>
       <c r="H55" t="n">
         <v>155751</v>
@@ -2022,7 +2022,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G57" t="n">
-        <v>14.7436790466309</v>
+        <v>14.7436800003052</v>
       </c>
       <c r="H57" t="n">
         <v>220752</v>
@@ -2051,7 +2051,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G58" t="n">
-        <v>14.4092473983765</v>
+        <v>14.4092483520508</v>
       </c>
       <c r="H58" t="n">
         <v>182625</v>
@@ -2080,7 +2080,7 @@
         <v>15.75</v>
       </c>
       <c r="G59" t="n">
-        <v>15.0494451522827</v>
+        <v>15.049446105957</v>
       </c>
       <c r="H59" t="n">
         <v>87541</v>
@@ -2138,7 +2138,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G61" t="n">
-        <v>15.5558729171753</v>
+        <v>15.555871963501</v>
       </c>
       <c r="H61" t="n">
         <v>217368</v>
@@ -2196,7 +2196,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G63" t="n">
-        <v>15.1736640930176</v>
+        <v>15.1736631393433</v>
       </c>
       <c r="H63" t="n">
         <v>103387</v>
@@ -2370,7 +2370,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G69" t="n">
-        <v>15.3552122116089</v>
+        <v>15.3552112579346</v>
       </c>
       <c r="H69" t="n">
         <v>141327</v>
@@ -2399,7 +2399,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G70" t="n">
-        <v>15.3361015319824</v>
+        <v>15.3361005783081</v>
       </c>
       <c r="H70" t="n">
         <v>85001</v>
@@ -2457,7 +2457,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G72" t="n">
-        <v>14.6003513336182</v>
+        <v>14.6003503799438</v>
       </c>
       <c r="H72" t="n">
         <v>144220</v>
@@ -2486,7 +2486,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G73" t="n">
-        <v>14.3519153594971</v>
+        <v>14.3519172668457</v>
       </c>
       <c r="H73" t="n">
         <v>172203</v>
@@ -2602,7 +2602,7 @@
         <v>15.5</v>
       </c>
       <c r="G77" t="n">
-        <v>14.8105659484863</v>
+        <v>14.810564994812</v>
       </c>
       <c r="H77" t="n">
         <v>108895</v>
@@ -2631,7 +2631,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G78" t="n">
-        <v>14.0652599334717</v>
+        <v>14.065260887146</v>
       </c>
       <c r="H78" t="n">
         <v>153369</v>
@@ -2718,7 +2718,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="n">
-        <v>14.3328065872192</v>
+        <v>14.3328056335449</v>
       </c>
       <c r="H81" t="n">
         <v>137258</v>
@@ -2747,7 +2747,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G82" t="n">
-        <v>14.2659196853638</v>
+        <v>14.2659206390381</v>
       </c>
       <c r="H82" t="n">
         <v>101770</v>
@@ -2805,7 +2805,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G84" t="n">
-        <v>13.1670713424683</v>
+        <v>13.1670703887939</v>
       </c>
       <c r="H84" t="n">
         <v>628995</v>
@@ -2892,7 +2892,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G87" t="n">
-        <v>13.6448316574097</v>
+        <v>13.6448307037354</v>
       </c>
       <c r="H87" t="n">
         <v>355963</v>
@@ -2921,7 +2921,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G88" t="n">
-        <v>14.6003513336182</v>
+        <v>14.6003503799438</v>
       </c>
       <c r="H88" t="n">
         <v>499133</v>
@@ -2950,7 +2950,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G89" t="n">
-        <v>15.0303354263306</v>
+        <v>15.0303344726562</v>
       </c>
       <c r="H89" t="n">
         <v>401988</v>
@@ -3008,7 +3008,7 @@
         <v>15.5</v>
       </c>
       <c r="G91" t="n">
-        <v>14.8105659484863</v>
+        <v>14.810564994812</v>
       </c>
       <c r="H91" t="n">
         <v>119552</v>
@@ -3037,7 +3037,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G92" t="n">
-        <v>14.5621299743652</v>
+        <v>14.5621309280396</v>
       </c>
       <c r="H92" t="n">
         <v>143627</v>
@@ -3066,7 +3066,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G93" t="n">
-        <v>14.6767930984497</v>
+        <v>14.6767921447754</v>
       </c>
       <c r="H93" t="n">
         <v>110219</v>
@@ -3095,7 +3095,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G94" t="n">
-        <v>14.6003513336182</v>
+        <v>14.6003503799438</v>
       </c>
       <c r="H94" t="n">
         <v>65667</v>
@@ -3153,7 +3153,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>14.6194629669189</v>
+        <v>14.6194620132446</v>
       </c>
       <c r="H96" t="n">
         <v>186490</v>
@@ -3182,7 +3182,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G97" t="n">
-        <v>14.8678970336914</v>
+        <v>14.8678979873657</v>
       </c>
       <c r="H97" t="n">
         <v>106899</v>
@@ -3211,7 +3211,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G98" t="n">
-        <v>14.8678970336914</v>
+        <v>14.8678979873657</v>
       </c>
       <c r="H98" t="n">
         <v>69896</v>
@@ -3298,7 +3298,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G101" t="n">
-        <v>15.326548576355</v>
+        <v>15.3265476226807</v>
       </c>
       <c r="H101" t="n">
         <v>177567</v>
@@ -3356,7 +3356,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G103" t="n">
-        <v>15.3074369430542</v>
+        <v>15.3074378967285</v>
       </c>
       <c r="H103" t="n">
         <v>144419</v>
@@ -3385,7 +3385,7 @@
         <v>15.25</v>
       </c>
       <c r="G104" t="n">
-        <v>14.5716857910156</v>
+        <v>14.5716867446899</v>
       </c>
       <c r="H104" t="n">
         <v>190918</v>
@@ -3414,7 +3414,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G105" t="n">
-        <v>14.5907974243164</v>
+        <v>14.5907964706421</v>
       </c>
       <c r="H105" t="n">
         <v>112390</v>
@@ -3443,7 +3443,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G106" t="n">
-        <v>14.2754735946655</v>
+        <v>14.2754745483398</v>
       </c>
       <c r="H106" t="n">
         <v>86836</v>
@@ -3559,7 +3559,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G110" t="n">
-        <v>15.0876665115356</v>
+        <v>15.08766746521</v>
       </c>
       <c r="H110" t="n">
         <v>72044</v>
@@ -3617,7 +3617,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G112" t="n">
-        <v>14.6481266021729</v>
+        <v>14.6481275558472</v>
       </c>
       <c r="H112" t="n">
         <v>60854</v>
@@ -3994,7 +3994,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G125" t="n">
-        <v>14.4952449798584</v>
+        <v>14.4952440261841</v>
       </c>
       <c r="H125" t="n">
         <v>221654</v>
@@ -4081,7 +4081,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G128" t="n">
-        <v>14.8870077133179</v>
+        <v>14.8870067596436</v>
       </c>
       <c r="H128" t="n">
         <v>40404</v>
@@ -4110,7 +4110,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G129" t="n">
-        <v>15.1641092300415</v>
+        <v>15.1641082763672</v>
       </c>
       <c r="H129" t="n">
         <v>73585</v>
@@ -4139,7 +4139,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G130" t="n">
-        <v>15.0398893356323</v>
+        <v>15.0398902893066</v>
       </c>
       <c r="H130" t="n">
         <v>99245</v>
@@ -4168,7 +4168,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G131" t="n">
-        <v>15.0876665115356</v>
+        <v>15.08766746521</v>
       </c>
       <c r="H131" t="n">
         <v>223782</v>
@@ -4197,7 +4197,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G132" t="n">
-        <v>15.1258878707886</v>
+        <v>15.1258888244629</v>
       </c>
       <c r="H132" t="n">
         <v>58545</v>
@@ -4226,7 +4226,7 @@
         <v>15.75</v>
       </c>
       <c r="G133" t="n">
-        <v>15.0494451522827</v>
+        <v>15.049446105957</v>
       </c>
       <c r="H133" t="n">
         <v>54662</v>
@@ -4255,7 +4255,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>14.953893661499</v>
+        <v>14.9538946151733</v>
       </c>
       <c r="H134" t="n">
         <v>62972</v>
@@ -4342,7 +4342,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G137" t="n">
-        <v>15.1736640930176</v>
+        <v>15.1736631393433</v>
       </c>
       <c r="H137" t="n">
         <v>135405</v>
@@ -4371,7 +4371,7 @@
         <v>16.5</v>
       </c>
       <c r="G138" t="n">
-        <v>15.7660846710205</v>
+        <v>15.7660865783691</v>
       </c>
       <c r="H138" t="n">
         <v>318203</v>
@@ -4400,7 +4400,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G139" t="n">
-        <v>16.3011798858643</v>
+        <v>16.3011779785156</v>
       </c>
       <c r="H139" t="n">
         <v>212600</v>
@@ -4429,7 +4429,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G140" t="n">
-        <v>16.1865158081055</v>
+        <v>16.1865177154541</v>
       </c>
       <c r="H140" t="n">
         <v>143796</v>
@@ -4487,7 +4487,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G142" t="n">
-        <v>16.9795970916748</v>
+        <v>16.9795989990234</v>
       </c>
       <c r="H142" t="n">
         <v>321463</v>
@@ -4574,7 +4574,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G145" t="n">
-        <v>16.2916202545166</v>
+        <v>16.2916221618652</v>
       </c>
       <c r="H145" t="n">
         <v>134728</v>
@@ -4603,7 +4603,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G146" t="n">
-        <v>16.7693843841553</v>
+        <v>16.769380569458</v>
       </c>
       <c r="H146" t="n">
         <v>112560</v>
@@ -4632,7 +4632,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G147" t="n">
-        <v>16.1769599914551</v>
+        <v>16.1769580841064</v>
       </c>
       <c r="H147" t="n">
         <v>432672</v>
@@ -4719,7 +4719,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G150" t="n">
-        <v>15.6418695449829</v>
+        <v>15.6418685913086</v>
       </c>
       <c r="H150" t="n">
         <v>102652</v>
@@ -4806,7 +4806,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G153" t="n">
-        <v>16.5878353118896</v>
+        <v>16.587833404541</v>
       </c>
       <c r="H153" t="n">
         <v>137920</v>
@@ -4835,7 +4835,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>17.3426952362061</v>
+        <v>17.3426933288574</v>
       </c>
       <c r="H154" t="n">
         <v>130344</v>
@@ -4893,7 +4893,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G156" t="n">
-        <v>17.6962375640869</v>
+        <v>17.6962394714355</v>
       </c>
       <c r="H156" t="n">
         <v>187911</v>
@@ -4951,7 +4951,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G158" t="n">
-        <v>17.4669132232666</v>
+        <v>17.466911315918</v>
       </c>
       <c r="H158" t="n">
         <v>73047</v>
@@ -4980,7 +4980,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G159" t="n">
-        <v>17.3904724121094</v>
+        <v>17.390474319458</v>
       </c>
       <c r="H159" t="n">
         <v>70593</v>
@@ -5009,7 +5009,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G160" t="n">
-        <v>17.3904724121094</v>
+        <v>17.390474319458</v>
       </c>
       <c r="H160" t="n">
         <v>78063</v>
@@ -5038,7 +5038,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G161" t="n">
-        <v>17.4478015899658</v>
+        <v>17.4477996826172</v>
       </c>
       <c r="H161" t="n">
         <v>67231</v>
@@ -5096,7 +5096,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G163" t="n">
-        <v>17.2089214324951</v>
+        <v>17.2089233398438</v>
       </c>
       <c r="H163" t="n">
         <v>50813</v>
@@ -5183,7 +5183,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>17.8204555511475</v>
+        <v>17.8204574584961</v>
       </c>
       <c r="H166" t="n">
         <v>70506</v>
@@ -5270,7 +5270,7 @@
         <v>19.5</v>
       </c>
       <c r="G169" t="n">
-        <v>18.6326484680176</v>
+        <v>18.6326465606689</v>
       </c>
       <c r="H169" t="n">
         <v>161677</v>
@@ -5328,7 +5328,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G171" t="n">
-        <v>18.7664203643799</v>
+        <v>18.7664184570312</v>
       </c>
       <c r="H171" t="n">
         <v>104982</v>
@@ -5386,7 +5386,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G173" t="n">
-        <v>18.5084323883057</v>
+        <v>18.5084285736084</v>
       </c>
       <c r="H173" t="n">
         <v>82218</v>
@@ -5415,7 +5415,7 @@
         <v>18.7700004577637</v>
       </c>
       <c r="G174" t="n">
-        <v>17.9351196289062</v>
+        <v>17.9351177215576</v>
       </c>
       <c r="H174" t="n">
         <v>228634</v>
@@ -5502,7 +5502,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G177" t="n">
-        <v>18.3077697753906</v>
+        <v>18.3077716827393</v>
       </c>
       <c r="H177" t="n">
         <v>71355</v>
@@ -5560,7 +5560,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G179" t="n">
-        <v>18.8524169921875</v>
+        <v>18.8524150848389</v>
       </c>
       <c r="H179" t="n">
         <v>160303</v>
@@ -5589,7 +5589,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G180" t="n">
-        <v>18.7664203643799</v>
+        <v>18.7664184570312</v>
       </c>
       <c r="H180" t="n">
         <v>186766</v>
@@ -5676,7 +5676,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G183" t="n">
-        <v>17.7249031066895</v>
+        <v>17.7249011993408</v>
       </c>
       <c r="H183" t="n">
         <v>316794</v>
@@ -5705,7 +5705,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G184" t="n">
-        <v>17.1898097991943</v>
+        <v>17.189811706543</v>
       </c>
       <c r="H184" t="n">
         <v>165069</v>
@@ -5792,7 +5792,7 @@
         <v>18</v>
       </c>
       <c r="G187" t="n">
-        <v>17.1993675231934</v>
+        <v>17.1993656158447</v>
       </c>
       <c r="H187" t="n">
         <v>168778</v>
@@ -5937,7 +5937,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G192" t="n">
-        <v>16.5305023193359</v>
+        <v>16.5305042266846</v>
       </c>
       <c r="H192" t="n">
         <v>303536</v>
@@ -5966,7 +5966,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G193" t="n">
-        <v>16.4540596008301</v>
+        <v>16.4540615081787</v>
       </c>
       <c r="H193" t="n">
         <v>194779</v>
@@ -6024,7 +6024,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G195" t="n">
-        <v>16.3011798858643</v>
+        <v>16.3011779785156</v>
       </c>
       <c r="H195" t="n">
         <v>519554</v>
@@ -6082,7 +6082,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G197" t="n">
-        <v>16.3489551544189</v>
+        <v>16.3489532470703</v>
       </c>
       <c r="H197" t="n">
         <v>187727</v>
@@ -6111,7 +6111,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G198" t="n">
-        <v>16.3011798858643</v>
+        <v>16.3011779785156</v>
       </c>
       <c r="H198" t="n">
         <v>103373</v>
@@ -6140,7 +6140,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G199" t="n">
-        <v>16.6069450378418</v>
+        <v>16.6069431304932</v>
       </c>
       <c r="H199" t="n">
         <v>89821</v>
@@ -6198,7 +6198,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>16.6260566711426</v>
+        <v>16.6260547637939</v>
       </c>
       <c r="H201" t="n">
         <v>108711</v>
@@ -6227,7 +6227,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G202" t="n">
-        <v>16.5878353118896</v>
+        <v>16.587833404541</v>
       </c>
       <c r="H202" t="n">
         <v>70415</v>
@@ -6256,7 +6256,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G203" t="n">
-        <v>16.7407150268555</v>
+        <v>16.7407169342041</v>
       </c>
       <c r="H203" t="n">
         <v>93120</v>
@@ -6314,7 +6314,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G205" t="n">
-        <v>17.0369281768799</v>
+        <v>17.0369262695312</v>
       </c>
       <c r="H205" t="n">
         <v>107074</v>
@@ -6401,7 +6401,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G208" t="n">
-        <v>16.9031543731689</v>
+        <v>16.9031562805176</v>
       </c>
       <c r="H208" t="n">
         <v>80044</v>
@@ -6546,7 +6546,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>17.2949199676514</v>
+        <v>17.2949180603027</v>
       </c>
       <c r="H213" t="n">
         <v>63203</v>
@@ -6604,7 +6604,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G215" t="n">
-        <v>17.476469039917</v>
+        <v>17.4764709472656</v>
       </c>
       <c r="H215" t="n">
         <v>330056</v>
@@ -6807,7 +6807,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G222" t="n">
-        <v>18.5789890289307</v>
+        <v>18.5789909362793</v>
       </c>
       <c r="H222" t="n">
         <v>75028</v>
@@ -7155,7 +7155,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>19.1367473602295</v>
+        <v>19.1367454528809</v>
       </c>
       <c r="H234" t="n">
         <v>176092</v>
@@ -7329,7 +7329,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G240" t="n">
-        <v>19.4637050628662</v>
+        <v>19.4637031555176</v>
       </c>
       <c r="H240" t="n">
         <v>95964</v>
@@ -7474,7 +7474,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G245" t="n">
-        <v>17.6077289581299</v>
+        <v>17.6077270507812</v>
       </c>
       <c r="H245" t="n">
         <v>371087</v>
@@ -7503,7 +7503,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G246" t="n">
-        <v>17.8481388092041</v>
+        <v>17.8481407165527</v>
       </c>
       <c r="H246" t="n">
         <v>191126</v>
@@ -7561,7 +7561,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G248" t="n">
-        <v>18.5789890289307</v>
+        <v>18.5789909362793</v>
       </c>
       <c r="H248" t="n">
         <v>83004</v>
@@ -7590,7 +7590,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G249" t="n">
-        <v>18.4924411773682</v>
+        <v>18.4924430847168</v>
       </c>
       <c r="H249" t="n">
         <v>68327</v>
@@ -7619,7 +7619,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G250" t="n">
-        <v>18.4924411773682</v>
+        <v>18.4924430847168</v>
       </c>
       <c r="H250" t="n">
         <v>136559</v>
@@ -7648,7 +7648,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G251" t="n">
-        <v>18.4347438812256</v>
+        <v>18.434741973877</v>
       </c>
       <c r="H251" t="n">
         <v>105907</v>
@@ -7677,7 +7677,7 @@
         <v>19.5</v>
       </c>
       <c r="G252" t="n">
-        <v>18.7520885467529</v>
+        <v>18.7520866394043</v>
       </c>
       <c r="H252" t="n">
         <v>47907</v>
@@ -7735,7 +7735,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G254" t="n">
-        <v>18.386661529541</v>
+        <v>18.3866634368896</v>
       </c>
       <c r="H254" t="n">
         <v>40747</v>
@@ -7764,7 +7764,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G255" t="n">
-        <v>19.4637050628662</v>
+        <v>19.4637031555176</v>
       </c>
       <c r="H255" t="n">
         <v>154255</v>
@@ -7793,7 +7793,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G256" t="n">
-        <v>19.4637050628662</v>
+        <v>19.4637031555176</v>
       </c>
       <c r="H256" t="n">
         <v>168657</v>
@@ -7822,7 +7822,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G257" t="n">
-        <v>19.6944999694824</v>
+        <v>19.6944980621338</v>
       </c>
       <c r="H257" t="n">
         <v>62964</v>
@@ -7851,7 +7851,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G258" t="n">
-        <v>20.1368560791016</v>
+        <v>20.1368579864502</v>
       </c>
       <c r="H258" t="n">
         <v>123239</v>
@@ -7909,7 +7909,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G260" t="n">
-        <v>19.5598678588867</v>
+        <v>19.5598697662354</v>
       </c>
       <c r="H260" t="n">
         <v>165590</v>
@@ -7967,7 +7967,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G262" t="n">
-        <v>19.3098411560059</v>
+        <v>19.3098392486572</v>
       </c>
       <c r="H262" t="n">
         <v>117839</v>
@@ -8228,7 +8228,7 @@
         <v>18.7700004577637</v>
       </c>
       <c r="G271" t="n">
-        <v>18.0500869750977</v>
+        <v>18.050085067749</v>
       </c>
       <c r="H271" t="n">
         <v>522798</v>
@@ -8315,7 +8315,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G274" t="n">
-        <v>17.5115623474121</v>
+        <v>17.5115642547607</v>
       </c>
       <c r="H274" t="n">
         <v>166261</v>
@@ -8373,7 +8373,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G276" t="n">
-        <v>18.5020580291748</v>
+        <v>18.5020599365234</v>
       </c>
       <c r="H276" t="n">
         <v>314121</v>
@@ -8431,7 +8431,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G278" t="n">
-        <v>18.6270751953125</v>
+        <v>18.6270732879639</v>
       </c>
       <c r="H278" t="n">
         <v>96317</v>
@@ -8924,7 +8924,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G295" t="n">
-        <v>17.1749897003174</v>
+        <v>17.1749877929688</v>
       </c>
       <c r="H295" t="n">
         <v>38905</v>
@@ -8953,7 +8953,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G296" t="n">
-        <v>17.2807712554932</v>
+        <v>17.2807693481445</v>
       </c>
       <c r="H296" t="n">
         <v>59361</v>
@@ -9098,7 +9098,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G301" t="n">
-        <v>16.4441375732422</v>
+        <v>16.4441394805908</v>
       </c>
       <c r="H301" t="n">
         <v>93310</v>
@@ -9127,7 +9127,7 @@
         <v>17</v>
       </c>
       <c r="G302" t="n">
-        <v>16.3479747772217</v>
+        <v>16.347972869873</v>
       </c>
       <c r="H302" t="n">
         <v>123413</v>
@@ -9214,7 +9214,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G305" t="n">
-        <v>16.3575897216797</v>
+        <v>16.3575916290283</v>
       </c>
       <c r="H305" t="n">
         <v>47439</v>
@@ -9475,7 +9475,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G314" t="n">
-        <v>15.655590057373</v>
+        <v>15.6555881500244</v>
       </c>
       <c r="H314" t="n">
         <v>70184</v>
@@ -9533,7 +9533,7 @@
         <v>16.2700004577637</v>
       </c>
       <c r="G316" t="n">
-        <v>15.6459722518921</v>
+        <v>15.6459732055664</v>
       </c>
       <c r="H316" t="n">
         <v>152152</v>
@@ -9591,7 +9591,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G318" t="n">
-        <v>14.4150667190552</v>
+        <v>14.4150657653809</v>
       </c>
       <c r="H318" t="n">
         <v>129315</v>
@@ -9620,7 +9620,7 @@
         <v>15.0299997329712</v>
       </c>
       <c r="G319" t="n">
-        <v>14.4535312652588</v>
+        <v>14.4535322189331</v>
       </c>
       <c r="H319" t="n">
         <v>131804</v>
@@ -9678,7 +9678,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G321" t="n">
-        <v>14.4631481170654</v>
+        <v>14.4631490707397</v>
       </c>
       <c r="H321" t="n">
         <v>76846</v>
@@ -9852,7 +9852,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G327" t="n">
-        <v>14.0881061553955</v>
+        <v>14.0881052017212</v>
       </c>
       <c r="H327" t="n">
         <v>66396</v>
@@ -9881,7 +9881,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G328" t="n">
-        <v>14.2227373123169</v>
+        <v>14.2227363586426</v>
       </c>
       <c r="H328" t="n">
         <v>104116</v>
@@ -10026,7 +10026,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G333" t="n">
-        <v>12.8572006225586</v>
+        <v>12.8571996688843</v>
       </c>
       <c r="H333" t="n">
         <v>104403</v>
@@ -10258,7 +10258,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G341" t="n">
-        <v>13.2803239822388</v>
+        <v>13.2803249359131</v>
       </c>
       <c r="H341" t="n">
         <v>70862</v>
@@ -10316,7 +10316,7 @@
         <v>14.0100002288818</v>
       </c>
       <c r="G343" t="n">
-        <v>13.4726533889771</v>
+        <v>13.4726543426514</v>
       </c>
       <c r="H343" t="n">
         <v>569136</v>
@@ -10345,7 +10345,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G344" t="n">
-        <v>13.0399141311646</v>
+        <v>13.0399131774902</v>
       </c>
       <c r="H344" t="n">
         <v>146201</v>
@@ -10461,7 +10461,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G348" t="n">
-        <v>14.2227373123169</v>
+        <v>14.2227363586426</v>
       </c>
       <c r="H348" t="n">
         <v>121936</v>
@@ -10490,7 +10490,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G349" t="n">
-        <v>14.5785455703735</v>
+        <v>14.5785446166992</v>
       </c>
       <c r="H349" t="n">
         <v>165968</v>
@@ -10519,7 +10519,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G350" t="n">
-        <v>14.2708187103271</v>
+        <v>14.2708196640015</v>
       </c>
       <c r="H350" t="n">
         <v>157799</v>
@@ -10664,7 +10664,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G355" t="n">
-        <v>13.68421459198</v>
+        <v>13.6842155456543</v>
       </c>
       <c r="H355" t="n">
         <v>248368</v>
@@ -10693,7 +10693,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G356" t="n">
-        <v>13.7322978973389</v>
+        <v>13.7322969436646</v>
       </c>
       <c r="H356" t="n">
         <v>217186</v>
@@ -10751,7 +10751,7 @@
         <v>14.3900003433228</v>
       </c>
       <c r="G358" t="n">
-        <v>13.8380794525146</v>
+        <v>13.8380784988403</v>
       </c>
       <c r="H358" t="n">
         <v>106575</v>
@@ -10780,7 +10780,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G359" t="n">
-        <v>13.664981842041</v>
+        <v>13.6649827957153</v>
       </c>
       <c r="H359" t="n">
         <v>97011</v>
@@ -10838,7 +10838,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G361" t="n">
-        <v>13.5399694442749</v>
+        <v>13.5399684906006</v>
       </c>
       <c r="H361" t="n">
         <v>102042</v>
@@ -11041,7 +11041,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G368" t="n">
-        <v>14.7131767272949</v>
+        <v>14.7131757736206</v>
       </c>
       <c r="H368" t="n">
         <v>469164</v>
@@ -11128,7 +11128,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G371" t="n">
-        <v>15.68443775177</v>
+        <v>15.6844387054443</v>
       </c>
       <c r="H371" t="n">
         <v>353221</v>
@@ -11244,7 +11244,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G375" t="n">
-        <v>14.8381900787354</v>
+        <v>14.8381910324097</v>
       </c>
       <c r="H375" t="n">
         <v>137149</v>
@@ -11273,7 +11273,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G376" t="n">
-        <v>15.0305185317993</v>
+        <v>15.0305194854736</v>
       </c>
       <c r="H376" t="n">
         <v>110938</v>
@@ -11418,7 +11418,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G381" t="n">
-        <v>14.8862724304199</v>
+        <v>14.8862714767456</v>
       </c>
       <c r="H381" t="n">
         <v>97752</v>
@@ -11534,7 +11534,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G385" t="n">
-        <v>14.4439153671265</v>
+        <v>14.4439163208008</v>
       </c>
       <c r="H385" t="n">
         <v>156312</v>
@@ -11563,7 +11563,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G386" t="n">
-        <v>14.0977220535278</v>
+        <v>14.0977230072021</v>
       </c>
       <c r="H386" t="n">
         <v>236798</v>
@@ -11650,7 +11650,7 @@
         <v>14.7700004577637</v>
       </c>
       <c r="G389" t="n">
-        <v>14.2035045623779</v>
+        <v>14.2035036087036</v>
       </c>
       <c r="H389" t="n">
         <v>136228</v>
@@ -11679,7 +11679,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G390" t="n">
-        <v>14.4631481170654</v>
+        <v>14.4631490707397</v>
       </c>
       <c r="H390" t="n">
         <v>99312</v>
@@ -11708,7 +11708,7 @@
         <v>14.2700004577637</v>
       </c>
       <c r="G391" t="n">
-        <v>13.7226819992065</v>
+        <v>13.7226810455322</v>
       </c>
       <c r="H391" t="n">
         <v>186975</v>
@@ -11737,7 +11737,7 @@
         <v>14.5</v>
       </c>
       <c r="G392" t="n">
-        <v>13.9438591003418</v>
+        <v>13.9438600540161</v>
       </c>
       <c r="H392" t="n">
         <v>133628</v>
@@ -11795,7 +11795,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G394" t="n">
-        <v>13.7419147491455</v>
+        <v>13.7419137954712</v>
       </c>
       <c r="H394" t="n">
         <v>128563</v>
@@ -11853,7 +11853,7 @@
         <v>14.25</v>
       </c>
       <c r="G396" t="n">
-        <v>13.7034482955933</v>
+        <v>13.7034473419189</v>
       </c>
       <c r="H396" t="n">
         <v>267247</v>
@@ -11882,7 +11882,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G397" t="n">
-        <v>13.664981842041</v>
+        <v>13.6649827957153</v>
       </c>
       <c r="H397" t="n">
         <v>175445</v>
@@ -12114,7 +12114,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G405" t="n">
-        <v>13.5880508422852</v>
+        <v>13.5880517959595</v>
       </c>
       <c r="H405" t="n">
         <v>184485</v>
@@ -12404,7 +12404,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G415" t="n">
-        <v>14.8862724304199</v>
+        <v>14.8862714767456</v>
       </c>
       <c r="H415" t="n">
         <v>139801</v>
@@ -12433,7 +12433,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G416" t="n">
-        <v>14.7516422271729</v>
+        <v>14.7516412734985</v>
       </c>
       <c r="H416" t="n">
         <v>59687</v>
@@ -12491,7 +12491,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G418" t="n">
-        <v>14.6458597183228</v>
+        <v>14.6458606719971</v>
       </c>
       <c r="H418" t="n">
         <v>94315</v>
@@ -12694,7 +12694,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G425" t="n">
-        <v>14.155421257019</v>
+        <v>14.1554222106934</v>
       </c>
       <c r="H425" t="n">
         <v>117944</v>
@@ -12752,7 +12752,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G427" t="n">
-        <v>13.664981842041</v>
+        <v>13.6649827957153</v>
       </c>
       <c r="H427" t="n">
         <v>159222</v>
@@ -12781,7 +12781,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G428" t="n">
-        <v>13.8188457489014</v>
+        <v>13.8188447952271</v>
       </c>
       <c r="H428" t="n">
         <v>206029</v>
@@ -12839,7 +12839,7 @@
         <v>14.25</v>
       </c>
       <c r="G430" t="n">
-        <v>13.7034482955933</v>
+        <v>13.7034473419189</v>
       </c>
       <c r="H430" t="n">
         <v>96228</v>
@@ -13100,7 +13100,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G439" t="n">
-        <v>12.8572006225586</v>
+        <v>12.8571996688843</v>
       </c>
       <c r="H439" t="n">
         <v>90236</v>
@@ -13187,7 +13187,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G442" t="n">
-        <v>12.9725971221924</v>
+        <v>12.9725980758667</v>
       </c>
       <c r="H442" t="n">
         <v>207392</v>
@@ -13245,7 +13245,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G444" t="n">
-        <v>12.4725427627563</v>
+        <v>12.472541809082</v>
       </c>
       <c r="H444" t="n">
         <v>169735</v>
@@ -13274,7 +13274,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G445" t="n">
-        <v>12.7802677154541</v>
+        <v>12.7802686691284</v>
       </c>
       <c r="H445" t="n">
         <v>146927</v>
@@ -13390,7 +13390,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G449" t="n">
-        <v>12.8091173171997</v>
+        <v>12.809118270874</v>
       </c>
       <c r="H449" t="n">
         <v>66508</v>
@@ -13448,7 +13448,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G451" t="n">
-        <v>12.9629812240601</v>
+        <v>12.9629802703857</v>
       </c>
       <c r="H451" t="n">
         <v>102016</v>
@@ -13535,7 +13535,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G454" t="n">
-        <v>11.6839923858643</v>
+        <v>11.6839933395386</v>
       </c>
       <c r="H454" t="n">
         <v>219490</v>
@@ -13622,7 +13622,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G457" t="n">
-        <v>11.9724864959717</v>
+        <v>11.9724855422974</v>
       </c>
       <c r="H457" t="n">
         <v>126601</v>
@@ -13709,7 +13709,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G460" t="n">
-        <v>12.1744327545166</v>
+        <v>12.1744318008423</v>
       </c>
       <c r="H460" t="n">
         <v>97426</v>
@@ -13767,7 +13767,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G462" t="n">
-        <v>12.145583152771</v>
+        <v>12.1455821990967</v>
       </c>
       <c r="H462" t="n">
         <v>90492</v>
@@ -13825,7 +13825,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G464" t="n">
-        <v>11.9724864959717</v>
+        <v>11.9724855422974</v>
       </c>
       <c r="H464" t="n">
         <v>57037</v>
@@ -13854,7 +13854,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G465" t="n">
-        <v>12.8668174743652</v>
+        <v>12.8668165206909</v>
       </c>
       <c r="H465" t="n">
         <v>259031</v>
@@ -13999,7 +13999,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G470" t="n">
-        <v>13.3476400375366</v>
+        <v>13.3476390838623</v>
       </c>
       <c r="H470" t="n">
         <v>152417</v>
@@ -31927,6 +31927,35 @@
         <v>267624</v>
       </c>
       <c r="I1088" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1089" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1089" t="n">
+        <v>5.625</v>
+      </c>
+      <c r="D1089" t="n">
+        <v>5.625</v>
+      </c>
+      <c r="E1089" t="n">
+        <v>5.40999984741211</v>
+      </c>
+      <c r="F1089" t="n">
+        <v>5.38500022888184</v>
+      </c>
+      <c r="G1089" t="n">
+        <v>5.38500022888184</v>
+      </c>
+      <c r="H1089" t="n">
+        <v>313719</v>
+      </c>
+      <c r="I1089" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DNR.MI.xlsx
+++ b/data/DNR.MI.xlsx
@@ -456,7 +456,7 @@
         <v>13.25</v>
       </c>
       <c r="G3" t="n">
-        <v>12.66064453125</v>
+        <v>12.6606454849243</v>
       </c>
       <c r="H3" t="n">
         <v>74987</v>
@@ -485,7 +485,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>12.6128692626953</v>
+        <v>12.612868309021</v>
       </c>
       <c r="H4" t="n">
         <v>150287</v>
@@ -514,7 +514,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G5" t="n">
-        <v>12.4886503219604</v>
+        <v>12.4886512756348</v>
       </c>
       <c r="H5" t="n">
         <v>167412</v>
@@ -543,7 +543,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>12.4122095108032</v>
+        <v>12.4122104644775</v>
       </c>
       <c r="H6" t="n">
         <v>105330</v>
@@ -630,7 +630,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G9" t="n">
-        <v>12.3548784255981</v>
+        <v>12.3548793792725</v>
       </c>
       <c r="H9" t="n">
         <v>150902</v>
@@ -862,7 +862,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G17" t="n">
-        <v>13.7021627426147</v>
+        <v>13.7021617889404</v>
       </c>
       <c r="H17" t="n">
         <v>249086</v>
@@ -920,7 +920,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G19" t="n">
-        <v>13.5683879852295</v>
+        <v>13.5683889389038</v>
       </c>
       <c r="H19" t="n">
         <v>254487</v>
@@ -1007,7 +1007,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G22" t="n">
-        <v>14.065260887146</v>
+        <v>14.0652599334717</v>
       </c>
       <c r="H22" t="n">
         <v>577409</v>
@@ -1181,7 +1181,7 @@
         <v>14.75</v>
       </c>
       <c r="G28" t="n">
-        <v>14.0939254760742</v>
+        <v>14.0939264297485</v>
       </c>
       <c r="H28" t="n">
         <v>136578</v>
@@ -1239,7 +1239,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G30" t="n">
-        <v>13.7021627426147</v>
+        <v>13.7021617889404</v>
       </c>
       <c r="H30" t="n">
         <v>147708</v>
@@ -1268,7 +1268,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G31" t="n">
-        <v>13.549280166626</v>
+        <v>13.5492792129517</v>
       </c>
       <c r="H31" t="n">
         <v>152273</v>
@@ -1297,7 +1297,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G32" t="n">
-        <v>13.5683879852295</v>
+        <v>13.5683889389038</v>
       </c>
       <c r="H32" t="n">
         <v>138086</v>
@@ -1384,7 +1384,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G35" t="n">
-        <v>13.5397253036499</v>
+        <v>13.5397243499756</v>
       </c>
       <c r="H35" t="n">
         <v>88256</v>
@@ -1558,7 +1558,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G41" t="n">
-        <v>14.8870067596436</v>
+        <v>14.8870077133179</v>
       </c>
       <c r="H41" t="n">
         <v>505585</v>
@@ -1674,7 +1674,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>15.5749816894531</v>
+        <v>15.5749807357788</v>
       </c>
       <c r="H45" t="n">
         <v>405367</v>
@@ -1732,7 +1732,7 @@
         <v>16.0900001525879</v>
       </c>
       <c r="G47" t="n">
-        <v>15.374321937561</v>
+        <v>15.3743228912354</v>
       </c>
       <c r="H47" t="n">
         <v>347713</v>
@@ -1761,7 +1761,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G48" t="n">
-        <v>16.0909614562988</v>
+        <v>16.0909652709961</v>
       </c>
       <c r="H48" t="n">
         <v>581768</v>
@@ -1848,7 +1848,7 @@
         <v>15.8900003433228</v>
       </c>
       <c r="G51" t="n">
-        <v>15.1832189559937</v>
+        <v>15.183219909668</v>
       </c>
       <c r="H51" t="n">
         <v>161269</v>
@@ -1877,7 +1877,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>14.7627897262573</v>
+        <v>14.7627906799316</v>
       </c>
       <c r="H52" t="n">
         <v>236091</v>
@@ -1906,7 +1906,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G53" t="n">
-        <v>14.2372541427612</v>
+        <v>14.2372531890869</v>
       </c>
       <c r="H53" t="n">
         <v>139086</v>
@@ -1935,7 +1935,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G54" t="n">
-        <v>14.0079288482666</v>
+        <v>14.0079298019409</v>
       </c>
       <c r="H54" t="n">
         <v>147319</v>
@@ -1964,7 +1964,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G55" t="n">
-        <v>14.7341232299805</v>
+        <v>14.7341241836548</v>
       </c>
       <c r="H55" t="n">
         <v>155751</v>
@@ -1993,7 +1993,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G56" t="n">
-        <v>15.1163320541382</v>
+        <v>15.1163311004639</v>
       </c>
       <c r="H56" t="n">
         <v>204640</v>
@@ -2022,7 +2022,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G57" t="n">
-        <v>14.7436800003052</v>
+        <v>14.7436809539795</v>
       </c>
       <c r="H57" t="n">
         <v>220752</v>
@@ -2051,7 +2051,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G58" t="n">
-        <v>14.4092483520508</v>
+        <v>14.4092473983765</v>
       </c>
       <c r="H58" t="n">
         <v>182625</v>
@@ -2109,7 +2109,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G60" t="n">
-        <v>15.4889841079712</v>
+        <v>15.4889850616455</v>
       </c>
       <c r="H60" t="n">
         <v>176931</v>
@@ -2196,7 +2196,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G63" t="n">
-        <v>15.1736631393433</v>
+        <v>15.1736640930176</v>
       </c>
       <c r="H63" t="n">
         <v>103387</v>
@@ -2254,7 +2254,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G65" t="n">
-        <v>15.746973991394</v>
+        <v>15.7469758987427</v>
       </c>
       <c r="H65" t="n">
         <v>163756</v>
@@ -2283,7 +2283,7 @@
         <v>16.2900009155273</v>
       </c>
       <c r="G66" t="n">
-        <v>15.5654277801514</v>
+        <v>15.5654268264771</v>
       </c>
       <c r="H66" t="n">
         <v>117861</v>
@@ -2341,7 +2341,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G68" t="n">
-        <v>15.5176515579224</v>
+        <v>15.5176496505737</v>
       </c>
       <c r="H68" t="n">
         <v>132919</v>
@@ -2370,7 +2370,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G69" t="n">
-        <v>15.3552112579346</v>
+        <v>15.3552131652832</v>
       </c>
       <c r="H69" t="n">
         <v>141327</v>
@@ -2486,7 +2486,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G73" t="n">
-        <v>14.3519172668457</v>
+        <v>14.3519163131714</v>
       </c>
       <c r="H73" t="n">
         <v>172203</v>
@@ -2544,7 +2544,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G75" t="n">
-        <v>14.1894779205322</v>
+        <v>14.1894788742065</v>
       </c>
       <c r="H75" t="n">
         <v>121982</v>
@@ -2602,7 +2602,7 @@
         <v>15.5</v>
       </c>
       <c r="G77" t="n">
-        <v>14.810564994812</v>
+        <v>14.8105659484863</v>
       </c>
       <c r="H77" t="n">
         <v>108895</v>
@@ -2631,7 +2631,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G78" t="n">
-        <v>14.065260887146</v>
+        <v>14.0652599334717</v>
       </c>
       <c r="H78" t="n">
         <v>153369</v>
@@ -2660,7 +2660,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G79" t="n">
-        <v>13.8646001815796</v>
+        <v>13.8646011352539</v>
       </c>
       <c r="H79" t="n">
         <v>226264</v>
@@ -2689,7 +2689,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G80" t="n">
-        <v>13.9888191223145</v>
+        <v>13.9888181686401</v>
       </c>
       <c r="H80" t="n">
         <v>82515</v>
@@ -2718,7 +2718,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="n">
-        <v>14.3328056335449</v>
+        <v>14.3328065872192</v>
       </c>
       <c r="H81" t="n">
         <v>137258</v>
@@ -2747,7 +2747,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G82" t="n">
-        <v>14.2659206390381</v>
+        <v>14.2659196853638</v>
       </c>
       <c r="H82" t="n">
         <v>101770</v>
@@ -2950,7 +2950,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G89" t="n">
-        <v>15.0303344726562</v>
+        <v>15.0303354263306</v>
       </c>
       <c r="H89" t="n">
         <v>401988</v>
@@ -3008,7 +3008,7 @@
         <v>15.5</v>
       </c>
       <c r="G91" t="n">
-        <v>14.810564994812</v>
+        <v>14.8105659484863</v>
       </c>
       <c r="H91" t="n">
         <v>119552</v>
@@ -3037,7 +3037,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G92" t="n">
-        <v>14.5621309280396</v>
+        <v>14.5621299743652</v>
       </c>
       <c r="H92" t="n">
         <v>143627</v>
@@ -3153,7 +3153,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>14.6194620132446</v>
+        <v>14.6194629669189</v>
       </c>
       <c r="H96" t="n">
         <v>186490</v>
@@ -3182,7 +3182,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G97" t="n">
-        <v>14.8678979873657</v>
+        <v>14.8678970336914</v>
       </c>
       <c r="H97" t="n">
         <v>106899</v>
@@ -3211,7 +3211,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G98" t="n">
-        <v>14.8678979873657</v>
+        <v>14.8678970336914</v>
       </c>
       <c r="H98" t="n">
         <v>69896</v>
@@ -3327,7 +3327,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G102" t="n">
-        <v>15.3456573486328</v>
+        <v>15.3456563949585</v>
       </c>
       <c r="H102" t="n">
         <v>1185858</v>
@@ -3385,7 +3385,7 @@
         <v>15.25</v>
       </c>
       <c r="G104" t="n">
-        <v>14.5716867446899</v>
+        <v>14.5716857910156</v>
       </c>
       <c r="H104" t="n">
         <v>190918</v>
@@ -3472,7 +3472,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G107" t="n">
-        <v>14.6576824188232</v>
+        <v>14.6576833724976</v>
       </c>
       <c r="H107" t="n">
         <v>112801</v>
@@ -3501,7 +3501,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G108" t="n">
-        <v>14.7627897262573</v>
+        <v>14.7627906799316</v>
       </c>
       <c r="H108" t="n">
         <v>44432</v>
@@ -3530,7 +3530,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G109" t="n">
-        <v>14.8487863540649</v>
+        <v>14.8487873077393</v>
       </c>
       <c r="H109" t="n">
         <v>53044</v>
@@ -3559,7 +3559,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G110" t="n">
-        <v>15.08766746521</v>
+        <v>15.0876655578613</v>
       </c>
       <c r="H110" t="n">
         <v>72044</v>
@@ -3588,7 +3588,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G111" t="n">
-        <v>14.9443387985229</v>
+        <v>14.9443397521973</v>
       </c>
       <c r="H111" t="n">
         <v>83241</v>
@@ -3617,7 +3617,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G112" t="n">
-        <v>14.6481275558472</v>
+        <v>14.6481266021729</v>
       </c>
       <c r="H112" t="n">
         <v>60854</v>
@@ -3675,7 +3675,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G114" t="n">
-        <v>14.7819013595581</v>
+        <v>14.7818994522095</v>
       </c>
       <c r="H114" t="n">
         <v>173217</v>
@@ -3791,7 +3791,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G118" t="n">
-        <v>14.0461502075195</v>
+        <v>14.0461492538452</v>
       </c>
       <c r="H118" t="n">
         <v>88132</v>
@@ -3820,7 +3820,7 @@
         <v>14.5</v>
       </c>
       <c r="G119" t="n">
-        <v>13.8550453186035</v>
+        <v>13.8550462722778</v>
       </c>
       <c r="H119" t="n">
         <v>88896</v>
@@ -3849,7 +3849,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>13.7594928741455</v>
+        <v>13.7594938278198</v>
       </c>
       <c r="H120" t="n">
         <v>41310</v>
@@ -3936,7 +3936,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G123" t="n">
-        <v>13.7021627426147</v>
+        <v>13.7021617889404</v>
       </c>
       <c r="H123" t="n">
         <v>29257</v>
@@ -3965,7 +3965,7 @@
         <v>14.5</v>
       </c>
       <c r="G124" t="n">
-        <v>13.8550453186035</v>
+        <v>13.8550462722778</v>
       </c>
       <c r="H124" t="n">
         <v>15822</v>
@@ -4081,7 +4081,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G128" t="n">
-        <v>14.8870067596436</v>
+        <v>14.8870077133179</v>
       </c>
       <c r="H128" t="n">
         <v>40404</v>
@@ -4168,7 +4168,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G131" t="n">
-        <v>15.08766746521</v>
+        <v>15.0876655578613</v>
       </c>
       <c r="H131" t="n">
         <v>223782</v>
@@ -4197,7 +4197,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G132" t="n">
-        <v>15.1258888244629</v>
+        <v>15.1258878707886</v>
       </c>
       <c r="H132" t="n">
         <v>58545</v>
@@ -4255,7 +4255,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>14.9538946151733</v>
+        <v>14.953893661499</v>
       </c>
       <c r="H134" t="n">
         <v>62972</v>
@@ -4342,7 +4342,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G137" t="n">
-        <v>15.1736631393433</v>
+        <v>15.1736640930176</v>
       </c>
       <c r="H137" t="n">
         <v>135405</v>
@@ -4371,7 +4371,7 @@
         <v>16.5</v>
       </c>
       <c r="G138" t="n">
-        <v>15.7660865783691</v>
+        <v>15.7660856246948</v>
       </c>
       <c r="H138" t="n">
         <v>318203</v>
@@ -4429,7 +4429,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G140" t="n">
-        <v>16.1865177154541</v>
+        <v>16.1865158081055</v>
       </c>
       <c r="H140" t="n">
         <v>143796</v>
@@ -4603,7 +4603,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G146" t="n">
-        <v>16.769380569458</v>
+        <v>16.7693824768066</v>
       </c>
       <c r="H146" t="n">
         <v>112560</v>
@@ -4632,7 +4632,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G147" t="n">
-        <v>16.1769580841064</v>
+        <v>16.1769618988037</v>
       </c>
       <c r="H147" t="n">
         <v>432672</v>
@@ -4661,7 +4661,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G148" t="n">
-        <v>15.842529296875</v>
+        <v>15.8425283432007</v>
       </c>
       <c r="H148" t="n">
         <v>256187</v>
@@ -4690,7 +4690,7 @@
         <v>16.6100006103516</v>
       </c>
       <c r="G149" t="n">
-        <v>15.8711938858032</v>
+        <v>15.8711948394775</v>
       </c>
       <c r="H149" t="n">
         <v>130015</v>
@@ -4835,7 +4835,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>17.3426933288574</v>
+        <v>17.3426952362061</v>
       </c>
       <c r="H154" t="n">
         <v>130344</v>
@@ -4980,7 +4980,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G159" t="n">
-        <v>17.390474319458</v>
+        <v>17.3904685974121</v>
       </c>
       <c r="H159" t="n">
         <v>70593</v>
@@ -5009,7 +5009,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G160" t="n">
-        <v>17.390474319458</v>
+        <v>17.3904685974121</v>
       </c>
       <c r="H160" t="n">
         <v>78063</v>
@@ -5038,7 +5038,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G161" t="n">
-        <v>17.4477996826172</v>
+        <v>17.4478015899658</v>
       </c>
       <c r="H161" t="n">
         <v>67231</v>
@@ -5125,7 +5125,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G164" t="n">
-        <v>17.5529117584229</v>
+        <v>17.5529098510742</v>
       </c>
       <c r="H164" t="n">
         <v>38762</v>
@@ -5183,7 +5183,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>17.8204574584961</v>
+        <v>17.8204536437988</v>
       </c>
       <c r="H166" t="n">
         <v>70506</v>
@@ -5212,7 +5212,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G167" t="n">
-        <v>18.2313289642334</v>
+        <v>18.2313270568848</v>
       </c>
       <c r="H167" t="n">
         <v>148047</v>
@@ -5270,7 +5270,7 @@
         <v>19.5</v>
       </c>
       <c r="G169" t="n">
-        <v>18.6326465606689</v>
+        <v>18.6326503753662</v>
       </c>
       <c r="H169" t="n">
         <v>161677</v>
@@ -5299,7 +5299,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G170" t="n">
-        <v>18.9001922607422</v>
+        <v>18.9001941680908</v>
       </c>
       <c r="H170" t="n">
         <v>196771</v>
@@ -5357,7 +5357,7 @@
         <v>19.75</v>
       </c>
       <c r="G172" t="n">
-        <v>18.8715286254883</v>
+        <v>18.8715267181396</v>
       </c>
       <c r="H172" t="n">
         <v>54348</v>
@@ -5386,7 +5386,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G173" t="n">
-        <v>18.5084285736084</v>
+        <v>18.508430480957</v>
       </c>
       <c r="H173" t="n">
         <v>82218</v>
@@ -5473,7 +5473,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>17.7726783752441</v>
+        <v>17.7726821899414</v>
       </c>
       <c r="H176" t="n">
         <v>132691</v>
@@ -5502,7 +5502,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G177" t="n">
-        <v>18.3077716827393</v>
+        <v>18.3077697753906</v>
       </c>
       <c r="H177" t="n">
         <v>71355</v>
@@ -5531,7 +5531,7 @@
         <v>18.75</v>
       </c>
       <c r="G178" t="n">
-        <v>17.9160079956055</v>
+        <v>17.9160060882568</v>
       </c>
       <c r="H178" t="n">
         <v>107089</v>
@@ -5560,7 +5560,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G179" t="n">
-        <v>18.8524150848389</v>
+        <v>18.8524169921875</v>
       </c>
       <c r="H179" t="n">
         <v>160303</v>
@@ -5647,7 +5647,7 @@
         <v>18.75</v>
       </c>
       <c r="G182" t="n">
-        <v>17.9160079956055</v>
+        <v>17.9160060882568</v>
       </c>
       <c r="H182" t="n">
         <v>737639</v>
@@ -5734,7 +5734,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G185" t="n">
-        <v>16.396728515625</v>
+        <v>16.3967304229736</v>
       </c>
       <c r="H185" t="n">
         <v>282326</v>
@@ -5821,7 +5821,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G188" t="n">
-        <v>17.6580181121826</v>
+        <v>17.6580142974854</v>
       </c>
       <c r="H188" t="n">
         <v>106658</v>
@@ -5850,7 +5850,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G189" t="n">
-        <v>17.6580181121826</v>
+        <v>17.6580142974854</v>
       </c>
       <c r="H189" t="n">
         <v>195062</v>
@@ -5937,7 +5937,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G192" t="n">
-        <v>16.5305042266846</v>
+        <v>16.5305004119873</v>
       </c>
       <c r="H192" t="n">
         <v>303536</v>
@@ -5966,7 +5966,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G193" t="n">
-        <v>16.4540615081787</v>
+        <v>16.4540596008301</v>
       </c>
       <c r="H193" t="n">
         <v>194779</v>
@@ -5995,7 +5995,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>16.3871746063232</v>
+        <v>16.3871765136719</v>
       </c>
       <c r="H194" t="n">
         <v>289758</v>
@@ -6198,7 +6198,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>16.6260547637939</v>
+        <v>16.6260528564453</v>
       </c>
       <c r="H201" t="n">
         <v>108711</v>
@@ -6285,7 +6285,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G204" t="n">
-        <v>16.7884941101074</v>
+        <v>16.7884922027588</v>
       </c>
       <c r="H204" t="n">
         <v>110054</v>
@@ -6314,7 +6314,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G205" t="n">
-        <v>17.0369262695312</v>
+        <v>17.0369300842285</v>
       </c>
       <c r="H205" t="n">
         <v>107074</v>
@@ -6343,7 +6343,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G206" t="n">
-        <v>17.2375888824463</v>
+        <v>17.2375869750977</v>
       </c>
       <c r="H206" t="n">
         <v>108799</v>
@@ -6459,7 +6459,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G210" t="n">
-        <v>17.2375888824463</v>
+        <v>17.2375869750977</v>
       </c>
       <c r="H210" t="n">
         <v>68530</v>
@@ -6604,7 +6604,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G215" t="n">
-        <v>17.4764709472656</v>
+        <v>17.476469039917</v>
       </c>
       <c r="H215" t="n">
         <v>330056</v>
@@ -6633,7 +6633,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G216" t="n">
-        <v>17.6293506622314</v>
+        <v>17.6293525695801</v>
       </c>
       <c r="H216" t="n">
         <v>202637</v>
@@ -6662,7 +6662,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G217" t="n">
-        <v>18.2313289642334</v>
+        <v>18.2313270568848</v>
       </c>
       <c r="H217" t="n">
         <v>171919</v>
@@ -6749,7 +6749,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G220" t="n">
-        <v>18.0020065307617</v>
+        <v>18.0020046234131</v>
       </c>
       <c r="H220" t="n">
         <v>388714</v>
@@ -6778,7 +6778,7 @@
         <v>19.2700004577637</v>
       </c>
       <c r="G221" t="n">
-        <v>18.5309085845947</v>
+        <v>18.5309104919434</v>
       </c>
       <c r="H221" t="n">
         <v>86313</v>
@@ -6807,7 +6807,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G222" t="n">
-        <v>18.5789909362793</v>
+        <v>18.5789890289307</v>
       </c>
       <c r="H222" t="n">
         <v>75028</v>
@@ -7010,7 +7010,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G229" t="n">
-        <v>18.8097858428955</v>
+        <v>18.8097839355469</v>
       </c>
       <c r="H229" t="n">
         <v>69687</v>
@@ -7097,7 +7097,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>18.3674278259277</v>
+        <v>18.3674297332764</v>
       </c>
       <c r="H232" t="n">
         <v>66293</v>
@@ -7126,7 +7126,7 @@
         <v>19.75</v>
       </c>
       <c r="G233" t="n">
-        <v>18.9925003051758</v>
+        <v>18.9924983978271</v>
       </c>
       <c r="H233" t="n">
         <v>75996</v>
@@ -7300,7 +7300,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>19.3290748596191</v>
+        <v>19.3290729522705</v>
       </c>
       <c r="H239" t="n">
         <v>78255</v>
@@ -7387,7 +7387,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>19.4252395629883</v>
+        <v>19.4252414703369</v>
       </c>
       <c r="H242" t="n">
         <v>219460</v>
@@ -7416,7 +7416,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G243" t="n">
-        <v>19.0405807495117</v>
+        <v>19.0405788421631</v>
       </c>
       <c r="H243" t="n">
         <v>51065</v>
@@ -7474,7 +7474,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G245" t="n">
-        <v>17.6077270507812</v>
+        <v>17.6077289581299</v>
       </c>
       <c r="H245" t="n">
         <v>371087</v>
@@ -7503,7 +7503,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G246" t="n">
-        <v>17.8481407165527</v>
+        <v>17.8481388092041</v>
       </c>
       <c r="H246" t="n">
         <v>191126</v>
@@ -7561,7 +7561,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G248" t="n">
-        <v>18.5789909362793</v>
+        <v>18.5789890289307</v>
       </c>
       <c r="H248" t="n">
         <v>83004</v>
@@ -7648,7 +7648,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G251" t="n">
-        <v>18.434741973877</v>
+        <v>18.4347438812256</v>
       </c>
       <c r="H251" t="n">
         <v>105907</v>
@@ -7851,7 +7851,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G258" t="n">
-        <v>20.1368579864502</v>
+        <v>20.1368560791016</v>
       </c>
       <c r="H258" t="n">
         <v>123239</v>
@@ -7938,7 +7938,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G261" t="n">
-        <v>19.2713756561279</v>
+        <v>19.2713775634766</v>
       </c>
       <c r="H261" t="n">
         <v>226076</v>
@@ -7967,7 +7967,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G262" t="n">
-        <v>19.3098392486572</v>
+        <v>19.3098411560059</v>
       </c>
       <c r="H262" t="n">
         <v>117839</v>
@@ -8054,7 +8054,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>19.8098983764648</v>
+        <v>19.8098964691162</v>
       </c>
       <c r="H265" t="n">
         <v>74881</v>
@@ -8199,7 +8199,7 @@
         <v>20.1399993896484</v>
       </c>
       <c r="G270" t="n">
-        <v>19.3675384521484</v>
+        <v>19.3675403594971</v>
       </c>
       <c r="H270" t="n">
         <v>52442</v>
@@ -8344,7 +8344,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G275" t="n">
-        <v>18.2904987335205</v>
+        <v>18.2904968261719</v>
       </c>
       <c r="H275" t="n">
         <v>226073</v>
@@ -8373,7 +8373,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G276" t="n">
-        <v>18.5020599365234</v>
+        <v>18.5020580291748</v>
       </c>
       <c r="H276" t="n">
         <v>314121</v>
@@ -8547,7 +8547,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G282" t="n">
-        <v>17.8866062164307</v>
+        <v>17.8866081237793</v>
       </c>
       <c r="H282" t="n">
         <v>64258</v>
@@ -8576,7 +8576,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G283" t="n">
-        <v>17.5981101989746</v>
+        <v>17.5981121063232</v>
       </c>
       <c r="H283" t="n">
         <v>79763</v>
@@ -8605,7 +8605,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G284" t="n">
-        <v>17.540412902832</v>
+        <v>17.5404148101807</v>
       </c>
       <c r="H284" t="n">
         <v>101821</v>
@@ -8750,7 +8750,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G289" t="n">
-        <v>16.6460819244385</v>
+        <v>16.6460838317871</v>
       </c>
       <c r="H289" t="n">
         <v>130395</v>
@@ -8779,7 +8779,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G290" t="n">
-        <v>17.194221496582</v>
+        <v>17.1942195892334</v>
       </c>
       <c r="H290" t="n">
         <v>97158</v>
@@ -8808,7 +8808,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G291" t="n">
-        <v>17.4923305511475</v>
+        <v>17.4923324584961</v>
       </c>
       <c r="H291" t="n">
         <v>98792</v>
@@ -8924,7 +8924,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G295" t="n">
-        <v>17.1749877929688</v>
+        <v>17.1749897003174</v>
       </c>
       <c r="H295" t="n">
         <v>38905</v>
@@ -8953,7 +8953,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G296" t="n">
-        <v>17.2807693481445</v>
+        <v>17.2807674407959</v>
       </c>
       <c r="H296" t="n">
         <v>59361</v>
@@ -9069,7 +9069,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G300" t="n">
-        <v>16.6460819244385</v>
+        <v>16.6460838317871</v>
       </c>
       <c r="H300" t="n">
         <v>104866</v>
@@ -9098,7 +9098,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G301" t="n">
-        <v>16.4441394805908</v>
+        <v>16.4441375732422</v>
       </c>
       <c r="H301" t="n">
         <v>93310</v>
@@ -9185,7 +9185,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G304" t="n">
-        <v>16.7230129241943</v>
+        <v>16.723014831543</v>
       </c>
       <c r="H304" t="n">
         <v>322231</v>
@@ -9272,7 +9272,7 @@
         <v>16.75</v>
       </c>
       <c r="G307" t="n">
-        <v>16.1075630187988</v>
+        <v>16.1075611114502</v>
       </c>
       <c r="H307" t="n">
         <v>64826</v>
@@ -9330,7 +9330,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G309" t="n">
-        <v>15.7132883071899</v>
+        <v>15.7132873535156</v>
       </c>
       <c r="H309" t="n">
         <v>82945</v>
@@ -9359,7 +9359,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G310" t="n">
-        <v>15.5401906967163</v>
+        <v>15.5401916503906</v>
       </c>
       <c r="H310" t="n">
         <v>75719</v>
@@ -9417,7 +9417,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>15.4824924468994</v>
+        <v>15.4824934005737</v>
       </c>
       <c r="H312" t="n">
         <v>47778</v>
@@ -9504,7 +9504,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G315" t="n">
-        <v>15.8479166030884</v>
+        <v>15.8479175567627</v>
       </c>
       <c r="H315" t="n">
         <v>74847</v>
@@ -9533,7 +9533,7 @@
         <v>16.2700004577637</v>
       </c>
       <c r="G316" t="n">
-        <v>15.6459732055664</v>
+        <v>15.6459722518921</v>
       </c>
       <c r="H316" t="n">
         <v>152152</v>
@@ -9591,7 +9591,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G318" t="n">
-        <v>14.4150657653809</v>
+        <v>14.4150648117065</v>
       </c>
       <c r="H318" t="n">
         <v>129315</v>
@@ -9620,7 +9620,7 @@
         <v>15.0299997329712</v>
       </c>
       <c r="G319" t="n">
-        <v>14.4535322189331</v>
+        <v>14.4535312652588</v>
       </c>
       <c r="H319" t="n">
         <v>131804</v>
@@ -9678,7 +9678,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G321" t="n">
-        <v>14.4631490707397</v>
+        <v>14.4631481170654</v>
       </c>
       <c r="H321" t="n">
         <v>76846</v>
@@ -9707,7 +9707,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G322" t="n">
-        <v>14.5689287185669</v>
+        <v>14.5689296722412</v>
       </c>
       <c r="H322" t="n">
         <v>40798</v>
@@ -9765,7 +9765,7 @@
         <v>15</v>
       </c>
       <c r="G324" t="n">
-        <v>14.4246835708618</v>
+        <v>14.4246826171875</v>
       </c>
       <c r="H324" t="n">
         <v>91074</v>
@@ -9881,7 +9881,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G328" t="n">
-        <v>14.2227363586426</v>
+        <v>14.2227373123169</v>
       </c>
       <c r="H328" t="n">
         <v>104116</v>
@@ -9968,7 +9968,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G331" t="n">
-        <v>13.1745433807373</v>
+        <v>13.174542427063</v>
       </c>
       <c r="H331" t="n">
         <v>46983</v>
@@ -10055,7 +10055,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G334" t="n">
-        <v>12.6744890213013</v>
+        <v>12.674488067627</v>
       </c>
       <c r="H334" t="n">
         <v>59858</v>
@@ -10171,7 +10171,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G338" t="n">
-        <v>13.9053945541382</v>
+        <v>13.9053936004639</v>
       </c>
       <c r="H338" t="n">
         <v>230450</v>
@@ -10200,7 +10200,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G339" t="n">
-        <v>13.828462600708</v>
+        <v>13.8284616470337</v>
       </c>
       <c r="H339" t="n">
         <v>150608</v>
@@ -10316,7 +10316,7 @@
         <v>14.0100002288818</v>
       </c>
       <c r="G343" t="n">
-        <v>13.4726543426514</v>
+        <v>13.4726533889771</v>
       </c>
       <c r="H343" t="n">
         <v>569136</v>
@@ -10345,7 +10345,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G344" t="n">
-        <v>13.0399131774902</v>
+        <v>13.0399141311646</v>
       </c>
       <c r="H344" t="n">
         <v>146201</v>
@@ -10374,7 +10374,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G345" t="n">
-        <v>13.6553649902344</v>
+        <v>13.655366897583</v>
       </c>
       <c r="H345" t="n">
         <v>126227</v>
@@ -10403,7 +10403,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G346" t="n">
-        <v>14.5016145706177</v>
+        <v>14.5016136169434</v>
       </c>
       <c r="H346" t="n">
         <v>237267</v>
@@ -10432,7 +10432,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G347" t="n">
-        <v>14.6362438201904</v>
+        <v>14.6362447738647</v>
       </c>
       <c r="H347" t="n">
         <v>215592</v>
@@ -10461,7 +10461,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G348" t="n">
-        <v>14.2227363586426</v>
+        <v>14.2227373123169</v>
       </c>
       <c r="H348" t="n">
         <v>121936</v>
@@ -10490,7 +10490,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G349" t="n">
-        <v>14.5785446166992</v>
+        <v>14.5785455703735</v>
       </c>
       <c r="H349" t="n">
         <v>165968</v>
@@ -10519,7 +10519,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G350" t="n">
-        <v>14.2708196640015</v>
+        <v>14.2708187103271</v>
       </c>
       <c r="H350" t="n">
         <v>157799</v>
@@ -10548,7 +10548,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G351" t="n">
-        <v>14.1073389053345</v>
+        <v>14.1073398590088</v>
       </c>
       <c r="H351" t="n">
         <v>93291</v>
@@ -10606,7 +10606,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G353" t="n">
-        <v>14.3092851638794</v>
+        <v>14.3092861175537</v>
       </c>
       <c r="H353" t="n">
         <v>104165</v>
@@ -10635,7 +10635,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G354" t="n">
-        <v>14.2996683120728</v>
+        <v>14.2996673583984</v>
       </c>
       <c r="H354" t="n">
         <v>87931</v>
@@ -10664,7 +10664,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G355" t="n">
-        <v>13.6842155456543</v>
+        <v>13.68421459198</v>
       </c>
       <c r="H355" t="n">
         <v>248368</v>
@@ -10693,7 +10693,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G356" t="n">
-        <v>13.7322969436646</v>
+        <v>13.7322978973389</v>
       </c>
       <c r="H356" t="n">
         <v>217186</v>
@@ -10722,7 +10722,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G357" t="n">
-        <v>13.7611465454102</v>
+        <v>13.7611474990845</v>
       </c>
       <c r="H357" t="n">
         <v>89876</v>
@@ -10751,7 +10751,7 @@
         <v>14.3900003433228</v>
       </c>
       <c r="G358" t="n">
-        <v>13.8380784988403</v>
+        <v>13.8380794525146</v>
       </c>
       <c r="H358" t="n">
         <v>106575</v>
@@ -10809,7 +10809,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G360" t="n">
-        <v>13.2707071304321</v>
+        <v>13.2707080841064</v>
       </c>
       <c r="H360" t="n">
         <v>139158</v>
@@ -10896,7 +10896,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G363" t="n">
-        <v>13.1841592788696</v>
+        <v>13.1841602325439</v>
       </c>
       <c r="H363" t="n">
         <v>159187</v>
@@ -10983,7 +10983,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G366" t="n">
-        <v>13.5015029907227</v>
+        <v>13.5015020370483</v>
       </c>
       <c r="H366" t="n">
         <v>125716</v>
@@ -11012,7 +11012,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G367" t="n">
-        <v>13.5495862960815</v>
+        <v>13.5495853424072</v>
       </c>
       <c r="H367" t="n">
         <v>174963</v>
@@ -11070,7 +11070,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G369" t="n">
-        <v>14.6747102737427</v>
+        <v>14.674711227417</v>
       </c>
       <c r="H369" t="n">
         <v>228319</v>
@@ -11099,7 +11099,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G370" t="n">
-        <v>14.9151220321655</v>
+        <v>14.9151210784912</v>
       </c>
       <c r="H370" t="n">
         <v>166793</v>
@@ -11128,7 +11128,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G371" t="n">
-        <v>15.6844387054443</v>
+        <v>15.68443775177</v>
       </c>
       <c r="H371" t="n">
         <v>353221</v>
@@ -11186,7 +11186,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G373" t="n">
-        <v>14.9151220321655</v>
+        <v>14.9151210784912</v>
       </c>
       <c r="H373" t="n">
         <v>162189</v>
@@ -11273,7 +11273,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G376" t="n">
-        <v>15.0305194854736</v>
+        <v>15.0305185317993</v>
       </c>
       <c r="H376" t="n">
         <v>110938</v>
@@ -11360,7 +11360,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G379" t="n">
-        <v>14.5016145706177</v>
+        <v>14.5016136169434</v>
       </c>
       <c r="H379" t="n">
         <v>337572</v>
@@ -11534,7 +11534,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G385" t="n">
-        <v>14.4439163208008</v>
+        <v>14.4439153671265</v>
       </c>
       <c r="H385" t="n">
         <v>156312</v>
@@ -11621,7 +11621,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G388" t="n">
-        <v>13.982325553894</v>
+        <v>13.9823265075684</v>
       </c>
       <c r="H388" t="n">
         <v>99895</v>
@@ -11650,7 +11650,7 @@
         <v>14.7700004577637</v>
       </c>
       <c r="G389" t="n">
-        <v>14.2035036087036</v>
+        <v>14.2035045623779</v>
       </c>
       <c r="H389" t="n">
         <v>136228</v>
@@ -11679,7 +11679,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G390" t="n">
-        <v>14.4631490707397</v>
+        <v>14.4631481170654</v>
       </c>
       <c r="H390" t="n">
         <v>99312</v>
@@ -11795,7 +11795,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G394" t="n">
-        <v>13.7419137954712</v>
+        <v>13.7419147491455</v>
       </c>
       <c r="H394" t="n">
         <v>128563</v>
@@ -11853,7 +11853,7 @@
         <v>14.25</v>
       </c>
       <c r="G396" t="n">
-        <v>13.7034473419189</v>
+        <v>13.7034482955933</v>
       </c>
       <c r="H396" t="n">
         <v>267247</v>
@@ -11911,7 +11911,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G398" t="n">
-        <v>13.3668718338013</v>
+        <v>13.3668727874756</v>
       </c>
       <c r="H398" t="n">
         <v>212475</v>
@@ -12114,7 +12114,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G405" t="n">
-        <v>13.5880517959595</v>
+        <v>13.5880508422852</v>
       </c>
       <c r="H405" t="n">
         <v>184485</v>
@@ -12172,7 +12172,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>13.6553649902344</v>
+        <v>13.655366897583</v>
       </c>
       <c r="H407" t="n">
         <v>163196</v>
@@ -12201,7 +12201,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G408" t="n">
-        <v>14.1650371551514</v>
+        <v>14.1650381088257</v>
       </c>
       <c r="H408" t="n">
         <v>284491</v>
@@ -12433,7 +12433,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G416" t="n">
-        <v>14.7516412734985</v>
+        <v>14.7516422271729</v>
       </c>
       <c r="H416" t="n">
         <v>59687</v>
@@ -12578,7 +12578,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G421" t="n">
-        <v>14.5016145706177</v>
+        <v>14.5016136169434</v>
       </c>
       <c r="H421" t="n">
         <v>101945</v>
@@ -12607,7 +12607,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G422" t="n">
-        <v>14.3092851638794</v>
+        <v>14.3092861175537</v>
       </c>
       <c r="H422" t="n">
         <v>102639</v>
@@ -12636,7 +12636,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G423" t="n">
-        <v>14.2323541641235</v>
+        <v>14.2323532104492</v>
       </c>
       <c r="H423" t="n">
         <v>63885</v>
@@ -12781,7 +12781,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G428" t="n">
-        <v>13.8188447952271</v>
+        <v>13.8188457489014</v>
       </c>
       <c r="H428" t="n">
         <v>206029</v>
@@ -12839,7 +12839,7 @@
         <v>14.25</v>
       </c>
       <c r="G430" t="n">
-        <v>13.7034473419189</v>
+        <v>13.7034482955933</v>
       </c>
       <c r="H430" t="n">
         <v>96228</v>
@@ -12868,7 +12868,7 @@
         <v>14.1899995803833</v>
       </c>
       <c r="G431" t="n">
-        <v>13.6457490921021</v>
+        <v>13.6457481384277</v>
       </c>
       <c r="H431" t="n">
         <v>223671</v>
@@ -12897,7 +12897,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G432" t="n">
-        <v>12.6937208175659</v>
+        <v>12.6937198638916</v>
       </c>
       <c r="H432" t="n">
         <v>632996</v>
@@ -12926,7 +12926,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G433" t="n">
-        <v>12.6456384658813</v>
+        <v>12.645637512207</v>
       </c>
       <c r="H433" t="n">
         <v>771950</v>
@@ -12955,7 +12955,7 @@
         <v>13.25</v>
       </c>
       <c r="G434" t="n">
-        <v>12.7418022155762</v>
+        <v>12.7418031692505</v>
       </c>
       <c r="H434" t="n">
         <v>207043</v>
@@ -12984,7 +12984,7 @@
         <v>13.25</v>
       </c>
       <c r="G435" t="n">
-        <v>12.7418022155762</v>
+        <v>12.7418031692505</v>
       </c>
       <c r="H435" t="n">
         <v>214799</v>
@@ -13071,7 +13071,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G438" t="n">
-        <v>12.6456384658813</v>
+        <v>12.645637512207</v>
       </c>
       <c r="H438" t="n">
         <v>150121</v>
@@ -13158,7 +13158,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G441" t="n">
-        <v>12.3763771057129</v>
+        <v>12.3763780593872</v>
       </c>
       <c r="H441" t="n">
         <v>197033</v>
@@ -13187,7 +13187,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G442" t="n">
-        <v>12.9725980758667</v>
+        <v>12.9725971221924</v>
       </c>
       <c r="H442" t="n">
         <v>207392</v>
@@ -13390,7 +13390,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G449" t="n">
-        <v>12.809118270874</v>
+        <v>12.8091173171997</v>
       </c>
       <c r="H449" t="n">
         <v>66508</v>
@@ -13448,7 +13448,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G451" t="n">
-        <v>12.9629802703857</v>
+        <v>12.9629812240601</v>
       </c>
       <c r="H451" t="n">
         <v>102016</v>
@@ -13477,7 +13477,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G452" t="n">
-        <v>12.6937208175659</v>
+        <v>12.6937198638916</v>
       </c>
       <c r="H452" t="n">
         <v>67295</v>
@@ -13506,7 +13506,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G453" t="n">
-        <v>11.9244031906128</v>
+        <v>11.9244041442871</v>
       </c>
       <c r="H453" t="n">
         <v>236491</v>
@@ -13622,7 +13622,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G457" t="n">
-        <v>11.9724855422974</v>
+        <v>11.9724864959717</v>
       </c>
       <c r="H457" t="n">
         <v>126601</v>
@@ -13680,7 +13680,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G459" t="n">
-        <v>11.8859376907349</v>
+        <v>11.8859386444092</v>
       </c>
       <c r="H459" t="n">
         <v>67163</v>
@@ -13796,7 +13796,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G463" t="n">
-        <v>12.0494174957275</v>
+        <v>12.0494184494019</v>
       </c>
       <c r="H463" t="n">
         <v>59080</v>
@@ -13825,7 +13825,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G464" t="n">
-        <v>11.9724855422974</v>
+        <v>11.9724864959717</v>
       </c>
       <c r="H464" t="n">
         <v>57037</v>
@@ -13912,7 +13912,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G467" t="n">
-        <v>12.7514190673828</v>
+        <v>12.7514200210571</v>
       </c>
       <c r="H467" t="n">
         <v>287755</v>
@@ -14057,7 +14057,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G472" t="n">
-        <v>13.1841592788696</v>
+        <v>13.1841602325439</v>
       </c>
       <c r="H472" t="n">
         <v>75618</v>
@@ -14115,7 +14115,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G474" t="n">
-        <v>12.7782716751099</v>
+        <v>12.7782726287842</v>
       </c>
       <c r="H474" t="n">
         <v>99354</v>
@@ -14173,7 +14173,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G476" t="n">
-        <v>13.0790500640869</v>
+        <v>13.0790510177612</v>
       </c>
       <c r="H476" t="n">
         <v>88070</v>
@@ -14202,7 +14202,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G477" t="n">
-        <v>12.9141082763672</v>
+        <v>12.9141073226929</v>
       </c>
       <c r="H477" t="n">
         <v>53958</v>
@@ -14231,7 +14231,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G478" t="n">
-        <v>12.4871940612793</v>
+        <v>12.4871950149536</v>
       </c>
       <c r="H478" t="n">
         <v>88793</v>
@@ -14260,7 +14260,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G479" t="n">
-        <v>12.8461894989014</v>
+        <v>12.8461885452271</v>
       </c>
       <c r="H479" t="n">
         <v>56934</v>
@@ -14347,7 +14347,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G482" t="n">
-        <v>12.8073797225952</v>
+        <v>12.8073787689209</v>
       </c>
       <c r="H482" t="n">
         <v>146288</v>
@@ -14695,7 +14695,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G494" t="n">
-        <v>11.3519945144653</v>
+        <v>11.3519954681396</v>
       </c>
       <c r="H494" t="n">
         <v>90980</v>
@@ -14782,7 +14782,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G497" t="n">
-        <v>11.4878311157227</v>
+        <v>11.487832069397</v>
       </c>
       <c r="H497" t="n">
         <v>74033</v>
@@ -14898,7 +14898,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G501" t="n">
-        <v>11.3519945144653</v>
+        <v>11.3519954681396</v>
       </c>
       <c r="H501" t="n">
         <v>72055</v>
@@ -15101,7 +15101,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G508" t="n">
-        <v>11.0803241729736</v>
+        <v>11.0803232192993</v>
       </c>
       <c r="H508" t="n">
         <v>52830</v>
@@ -15217,7 +15217,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G512" t="n">
-        <v>11.0803241729736</v>
+        <v>11.0803232192993</v>
       </c>
       <c r="H512" t="n">
         <v>67037</v>
@@ -15333,7 +15333,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G516" t="n">
-        <v>10.9735956192017</v>
+        <v>10.973596572876</v>
       </c>
       <c r="H516" t="n">
         <v>81818</v>
@@ -15420,7 +15420,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G519" t="n">
-        <v>10.9638938903809</v>
+        <v>10.9638929367065</v>
       </c>
       <c r="H519" t="n">
         <v>97469</v>
@@ -15565,7 +15565,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G524" t="n">
-        <v>10.5854921340942</v>
+        <v>10.5854930877686</v>
       </c>
       <c r="H524" t="n">
         <v>134025</v>
@@ -15623,7 +15623,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G526" t="n">
-        <v>10.3817386627197</v>
+        <v>10.381739616394</v>
       </c>
       <c r="H526" t="n">
         <v>195282</v>
@@ -16087,7 +16087,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G542" t="n">
-        <v>9.67830467224121</v>
+        <v>9.67830371856689</v>
       </c>
       <c r="H542" t="n">
         <v>134678</v>
@@ -16145,7 +16145,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G544" t="n">
-        <v>9.51821231842041</v>
+        <v>9.51821136474609</v>
       </c>
       <c r="H544" t="n">
         <v>80660</v>
@@ -16174,7 +16174,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G545" t="n">
-        <v>9.54731845855713</v>
+        <v>9.54731941223145</v>
       </c>
       <c r="H545" t="n">
         <v>95108</v>
@@ -16319,7 +16319,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G550" t="n">
-        <v>9.24653911590576</v>
+        <v>9.24654006958008</v>
       </c>
       <c r="H550" t="n">
         <v>94988</v>
@@ -16348,7 +16348,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G551" t="n">
-        <v>9.16891860961914</v>
+        <v>9.16891956329346</v>
       </c>
       <c r="H551" t="n">
         <v>135094</v>
@@ -16435,7 +16435,7 @@
         <v>8.91499996185303</v>
       </c>
       <c r="G554" t="n">
-        <v>8.64983177185059</v>
+        <v>8.6498327255249</v>
       </c>
       <c r="H554" t="n">
         <v>131072</v>
@@ -16464,7 +16464,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G555" t="n">
-        <v>9.08159637451172</v>
+        <v>9.0815954208374</v>
       </c>
       <c r="H555" t="n">
         <v>164784</v>
@@ -16493,7 +16493,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G556" t="n">
-        <v>9.09129810333252</v>
+        <v>9.09129905700684</v>
       </c>
       <c r="H556" t="n">
         <v>112117</v>
@@ -16551,7 +16551,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G558" t="n">
-        <v>9.08159637451172</v>
+        <v>9.0815954208374</v>
       </c>
       <c r="H558" t="n">
         <v>76175</v>
@@ -16609,7 +16609,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G560" t="n">
-        <v>9.24653911590576</v>
+        <v>9.24654006958008</v>
       </c>
       <c r="H560" t="n">
         <v>57482</v>
@@ -16638,7 +16638,7 @@
         <v>9.55500030517578</v>
       </c>
       <c r="G561" t="n">
-        <v>9.27079677581787</v>
+        <v>9.27079582214355</v>
       </c>
       <c r="H561" t="n">
         <v>80413</v>
@@ -16783,7 +16783,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G566" t="n">
-        <v>9.15921688079834</v>
+        <v>9.15921592712402</v>
       </c>
       <c r="H566" t="n">
         <v>168859</v>
@@ -16957,7 +16957,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G572" t="n">
-        <v>8.91665172576904</v>
+        <v>8.91665267944336</v>
       </c>
       <c r="H572" t="n">
         <v>55529</v>
@@ -17015,7 +17015,7 @@
         <v>8.90499973297119</v>
       </c>
       <c r="G574" t="n">
-        <v>8.64013004302979</v>
+        <v>8.64012908935547</v>
       </c>
       <c r="H574" t="n">
         <v>288790</v>
@@ -17073,7 +17073,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G576" t="n">
-        <v>8.66438579559326</v>
+        <v>8.66438674926758</v>
       </c>
       <c r="H576" t="n">
         <v>85122</v>
@@ -17160,7 +17160,7 @@
         <v>8.75</v>
       </c>
       <c r="G579" t="n">
-        <v>8.4897403717041</v>
+        <v>8.48973941802979</v>
       </c>
       <c r="H579" t="n">
         <v>77770</v>
@@ -17189,7 +17189,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G580" t="n">
-        <v>8.72260093688965</v>
+        <v>8.72260189056396</v>
       </c>
       <c r="H580" t="n">
         <v>167385</v>
@@ -17276,7 +17276,7 @@
         <v>8.82499980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>8.56250953674316</v>
+        <v>8.56250858306885</v>
       </c>
       <c r="H583" t="n">
         <v>185644</v>
@@ -17305,7 +17305,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G584" t="n">
-        <v>8.80022144317627</v>
+        <v>8.80022239685059</v>
       </c>
       <c r="H584" t="n">
         <v>145712</v>
@@ -17334,7 +17334,7 @@
         <v>8.91499996185303</v>
       </c>
       <c r="G585" t="n">
-        <v>8.64983177185059</v>
+        <v>8.6498327255249</v>
       </c>
       <c r="H585" t="n">
         <v>105376</v>
@@ -17392,7 +17392,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G587" t="n">
-        <v>8.7614107131958</v>
+        <v>8.76141166687012</v>
       </c>
       <c r="H587" t="n">
         <v>110831</v>
@@ -17508,7 +17508,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G591" t="n">
-        <v>8.387864112854</v>
+        <v>8.38786315917969</v>
       </c>
       <c r="H591" t="n">
         <v>209095</v>
@@ -17566,7 +17566,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G593" t="n">
-        <v>8.74200630187988</v>
+        <v>8.7420072555542</v>
       </c>
       <c r="H593" t="n">
         <v>123295</v>
@@ -17624,7 +17624,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>8.56736087799072</v>
+        <v>8.56735992431641</v>
       </c>
       <c r="H595" t="n">
         <v>506056</v>
@@ -17711,7 +17711,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G598" t="n">
-        <v>8.7614107131958</v>
+        <v>8.76141166687012</v>
       </c>
       <c r="H598" t="n">
         <v>275140</v>
@@ -17798,7 +17798,7 @@
         <v>8.47500038146973</v>
       </c>
       <c r="G601" t="n">
-        <v>8.22291946411133</v>
+        <v>8.22292041778564</v>
       </c>
       <c r="H601" t="n">
         <v>238471</v>
@@ -17827,7 +17827,7 @@
         <v>8.28499984741211</v>
       </c>
       <c r="G602" t="n">
-        <v>8.03857040405273</v>
+        <v>8.03857135772705</v>
       </c>
       <c r="H602" t="n">
         <v>639924</v>
@@ -17914,7 +17914,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G605" t="n">
-        <v>7.67472505569458</v>
+        <v>7.67472457885742</v>
       </c>
       <c r="H605" t="n">
         <v>165566</v>
@@ -17943,7 +17943,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G606" t="n">
-        <v>7.46126842498779</v>
+        <v>7.46126890182495</v>
       </c>
       <c r="H606" t="n">
         <v>281631</v>
@@ -18030,7 +18030,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G609" t="n">
-        <v>7.73779201507568</v>
+        <v>7.73779153823853</v>
       </c>
       <c r="H609" t="n">
         <v>85842</v>
@@ -18088,7 +18088,7 @@
         <v>8.00500011444092</v>
       </c>
       <c r="G611" t="n">
-        <v>7.76689910888672</v>
+        <v>7.76689958572388</v>
       </c>
       <c r="H611" t="n">
         <v>68292</v>
@@ -18175,7 +18175,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G614" t="n">
-        <v>7.73779201507568</v>
+        <v>7.73779153823853</v>
       </c>
       <c r="H614" t="n">
         <v>142315</v>
@@ -18204,7 +18204,7 @@
         <v>7.9850001335144</v>
       </c>
       <c r="G615" t="n">
-        <v>7.7474946975708</v>
+        <v>7.74749422073364</v>
       </c>
       <c r="H615" t="n">
         <v>116245</v>
@@ -18262,7 +18262,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G617" t="n">
-        <v>7.95609855651855</v>
+        <v>7.95609951019287</v>
       </c>
       <c r="H617" t="n">
         <v>208602</v>
@@ -18291,7 +18291,7 @@
         <v>8.14500045776367</v>
       </c>
       <c r="G618" t="n">
-        <v>7.90273571014404</v>
+        <v>7.90273523330688</v>
       </c>
       <c r="H618" t="n">
         <v>116291</v>
@@ -18320,7 +18320,7 @@
         <v>8.17500019073486</v>
       </c>
       <c r="G619" t="n">
-        <v>7.93184328079224</v>
+        <v>7.93184280395508</v>
       </c>
       <c r="H619" t="n">
         <v>91476</v>
@@ -18436,7 +18436,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>7.44671535491943</v>
+        <v>7.44671487808228</v>
       </c>
       <c r="H623" t="n">
         <v>226325</v>
@@ -18465,7 +18465,7 @@
         <v>7.64499998092651</v>
       </c>
       <c r="G624" t="n">
-        <v>7.41760730743408</v>
+        <v>7.41760683059692</v>
       </c>
       <c r="H624" t="n">
         <v>275750</v>
@@ -18494,7 +18494,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G625" t="n">
-        <v>7.41275548934937</v>
+        <v>7.41275596618652</v>
       </c>
       <c r="H625" t="n">
         <v>150786</v>
@@ -18581,7 +18581,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>7.31087875366211</v>
+        <v>7.31087923049927</v>
       </c>
       <c r="H628" t="n">
         <v>129823</v>
@@ -18668,7 +18668,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G631" t="n">
-        <v>7.53888893127441</v>
+        <v>7.53888940811157</v>
       </c>
       <c r="H631" t="n">
         <v>91913</v>
@@ -18697,7 +18697,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G632" t="n">
-        <v>7.42245817184448</v>
+        <v>7.42245864868164</v>
       </c>
       <c r="H632" t="n">
         <v>71179</v>
@@ -18726,7 +18726,7 @@
         <v>7.77500009536743</v>
       </c>
       <c r="G633" t="n">
-        <v>7.54374074935913</v>
+        <v>7.54374027252197</v>
       </c>
       <c r="H633" t="n">
         <v>104298</v>
@@ -18755,7 +18755,7 @@
         <v>7.875</v>
       </c>
       <c r="G634" t="n">
-        <v>7.64076614379883</v>
+        <v>7.64076566696167</v>
       </c>
       <c r="H634" t="n">
         <v>86228</v>
@@ -18842,7 +18842,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G637" t="n">
-        <v>7.05861234664917</v>
+        <v>7.05861282348633</v>
       </c>
       <c r="H637" t="n">
         <v>150003</v>
@@ -18900,7 +18900,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>6.84515619277954</v>
+        <v>6.84515571594238</v>
       </c>
       <c r="H639" t="n">
         <v>176664</v>
@@ -18958,7 +18958,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G641" t="n">
-        <v>6.98099184036255</v>
+        <v>6.98099231719971</v>
       </c>
       <c r="H641" t="n">
         <v>147248</v>
@@ -18987,7 +18987,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>7.17989492416382</v>
+        <v>7.17989444732666</v>
       </c>
       <c r="H642" t="n">
         <v>152913</v>
@@ -19277,7 +19277,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G652" t="n">
-        <v>6.96643781661987</v>
+        <v>6.96643829345703</v>
       </c>
       <c r="H652" t="n">
         <v>197817</v>
@@ -19306,7 +19306,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G653" t="n">
-        <v>6.78694105148315</v>
+        <v>6.786940574646</v>
       </c>
       <c r="H653" t="n">
         <v>219932</v>
@@ -19451,7 +19451,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G658" t="n">
-        <v>6.78694105148315</v>
+        <v>6.786940574646</v>
       </c>
       <c r="H658" t="n">
         <v>214637</v>
@@ -19596,7 +19596,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G663" t="n">
-        <v>6.67536115646362</v>
+        <v>6.67536163330078</v>
       </c>
       <c r="H663" t="n">
         <v>163183</v>
@@ -19654,7 +19654,7 @@
         <v>8.65499973297119</v>
       </c>
       <c r="G665" t="n">
-        <v>8.39756488800049</v>
+        <v>8.3975658416748</v>
       </c>
       <c r="H665" t="n">
         <v>1421609</v>
@@ -19683,7 +19683,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G666" t="n">
-        <v>8.19866371154785</v>
+        <v>8.19866275787354</v>
       </c>
       <c r="H666" t="n">
         <v>376186</v>
@@ -19712,7 +19712,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G667" t="n">
-        <v>8.52855110168457</v>
+        <v>8.52855014801025</v>
       </c>
       <c r="H667" t="n">
         <v>499509</v>
@@ -19828,7 +19828,7 @@
         <v>9.07499980926514</v>
       </c>
       <c r="G671" t="n">
-        <v>8.80507278442383</v>
+        <v>8.80507373809814</v>
       </c>
       <c r="H671" t="n">
         <v>162058</v>
@@ -19886,7 +19886,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G673" t="n">
-        <v>8.74200630187988</v>
+        <v>8.7420072555542</v>
       </c>
       <c r="H673" t="n">
         <v>106877</v>
@@ -20002,7 +20002,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>9.04763793945312</v>
+        <v>9.04763698577881</v>
       </c>
       <c r="H677" t="n">
         <v>120993</v>
@@ -20031,7 +20031,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G678" t="n">
-        <v>9.04763793945312</v>
+        <v>9.04763698577881</v>
       </c>
       <c r="H678" t="n">
         <v>114620</v>
@@ -20060,7 +20060,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G679" t="n">
-        <v>8.94090938568115</v>
+        <v>8.94090843200684</v>
       </c>
       <c r="H679" t="n">
         <v>176536</v>
@@ -20263,7 +20263,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G686" t="n">
-        <v>6.82575130462646</v>
+        <v>6.82575082778931</v>
       </c>
       <c r="H686" t="n">
         <v>2010202</v>
@@ -20321,7 +20321,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G688" t="n">
-        <v>6.44250011444092</v>
+        <v>6.44249963760376</v>
       </c>
       <c r="H688" t="n">
         <v>526066</v>
@@ -20350,7 +20350,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G689" t="n">
-        <v>6.66080760955811</v>
+        <v>6.66080713272095</v>
       </c>
       <c r="H689" t="n">
         <v>633433</v>
@@ -20379,7 +20379,7 @@
         <v>6.64499998092651</v>
       </c>
       <c r="G690" t="n">
-        <v>6.44735097885132</v>
+        <v>6.44735145568848</v>
       </c>
       <c r="H690" t="n">
         <v>435937</v>
@@ -20408,7 +20408,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G691" t="n">
-        <v>6.46190500259399</v>
+        <v>6.46190452575684</v>
       </c>
       <c r="H691" t="n">
         <v>314939</v>
@@ -20437,7 +20437,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>6.32606935501099</v>
+        <v>6.32606887817383</v>
       </c>
       <c r="H692" t="n">
         <v>246343</v>
@@ -20553,7 +20553,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G696" t="n">
-        <v>6.09805870056152</v>
+        <v>6.09805917739868</v>
       </c>
       <c r="H696" t="n">
         <v>426023</v>
@@ -20582,7 +20582,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G697" t="n">
-        <v>5.84094095230103</v>
+        <v>5.84094142913818</v>
       </c>
       <c r="H697" t="n">
         <v>433195</v>
@@ -20640,7 +20640,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G699" t="n">
-        <v>6.0107364654541</v>
+        <v>6.01073598861694</v>
       </c>
       <c r="H699" t="n">
         <v>258310</v>
@@ -20727,7 +20727,7 @@
         <v>6.35500001907349</v>
       </c>
       <c r="G702" t="n">
-        <v>6.16597700119019</v>
+        <v>6.16597652435303</v>
       </c>
       <c r="H702" t="n">
         <v>169235</v>
@@ -20756,7 +20756,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G703" t="n">
-        <v>6.07380294799805</v>
+        <v>6.07380247116089</v>
       </c>
       <c r="H703" t="n">
         <v>180300</v>
@@ -20814,7 +20814,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G705" t="n">
-        <v>5.97677707672119</v>
+        <v>5.97677659988403</v>
       </c>
       <c r="H705" t="n">
         <v>155044</v>
@@ -20930,7 +20930,7 @@
         <v>6.125</v>
       </c>
       <c r="G709" t="n">
-        <v>5.94281816482544</v>
+        <v>5.94281768798828</v>
       </c>
       <c r="H709" t="n">
         <v>221764</v>
@@ -21104,7 +21104,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G715" t="n">
-        <v>6.43279790878296</v>
+        <v>6.4327974319458</v>
       </c>
       <c r="H715" t="n">
         <v>116884</v>
@@ -21133,7 +21133,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G716" t="n">
-        <v>6.27755641937256</v>
+        <v>6.2775559425354</v>
       </c>
       <c r="H716" t="n">
         <v>222806</v>
@@ -21220,7 +21220,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G719" t="n">
-        <v>6.50071477890015</v>
+        <v>6.5007152557373</v>
       </c>
       <c r="H719" t="n">
         <v>144135</v>
@@ -21365,7 +21365,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G724" t="n">
-        <v>6.67536115646362</v>
+        <v>6.67536163330078</v>
       </c>
       <c r="H724" t="n">
         <v>775096</v>
@@ -31944,7 +31944,7 @@
         <v>5.625</v>
       </c>
       <c r="E1089" t="n">
-        <v>5.40999984741211</v>
+        <v>5.38500022888184</v>
       </c>
       <c r="F1089" t="n">
         <v>5.38500022888184</v>
@@ -31956,6 +31956,35 @@
         <v>313719</v>
       </c>
       <c r="I1089" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1090" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1090" t="n">
+        <v>5.45499992370605</v>
+      </c>
+      <c r="D1090" t="n">
+        <v>5.45499992370605</v>
+      </c>
+      <c r="E1090" t="n">
+        <v>5.30999994277954</v>
+      </c>
+      <c r="F1090" t="n">
+        <v>5.30999994277954</v>
+      </c>
+      <c r="G1090" t="n">
+        <v>5.30999994277954</v>
+      </c>
+      <c r="H1090" t="n">
+        <v>419733</v>
+      </c>
+      <c r="I1090" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DNR.MI.xlsx
+++ b/data/DNR.MI.xlsx
@@ -456,7 +456,7 @@
         <v>13.25</v>
       </c>
       <c r="G3" t="n">
-        <v>12.6606454849243</v>
+        <v>12.66064453125</v>
       </c>
       <c r="H3" t="n">
         <v>74987</v>
@@ -485,7 +485,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>12.612868309021</v>
+        <v>12.6128692626953</v>
       </c>
       <c r="H4" t="n">
         <v>150287</v>
@@ -514,7 +514,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G5" t="n">
-        <v>12.4886512756348</v>
+        <v>12.4886503219604</v>
       </c>
       <c r="H5" t="n">
         <v>167412</v>
@@ -543,7 +543,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>12.4122104644775</v>
+        <v>12.4122095108032</v>
       </c>
       <c r="H6" t="n">
         <v>105330</v>
@@ -572,7 +572,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G7" t="n">
-        <v>12.5077619552612</v>
+        <v>12.5077629089355</v>
       </c>
       <c r="H7" t="n">
         <v>117337</v>
@@ -630,7 +630,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G9" t="n">
-        <v>12.3548793792725</v>
+        <v>12.3548784255981</v>
       </c>
       <c r="H9" t="n">
         <v>150902</v>
@@ -659,7 +659,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G10" t="n">
-        <v>12.5173177719116</v>
+        <v>12.5173168182373</v>
       </c>
       <c r="H10" t="n">
         <v>111264</v>
@@ -688,7 +688,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>12.5173177719116</v>
+        <v>12.5173168182373</v>
       </c>
       <c r="H11" t="n">
         <v>104743</v>
@@ -746,7 +746,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G13" t="n">
-        <v>12.5459823608398</v>
+        <v>12.5459833145142</v>
       </c>
       <c r="H13" t="n">
         <v>74915</v>
@@ -833,7 +833,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G16" t="n">
-        <v>13.4155054092407</v>
+        <v>13.415506362915</v>
       </c>
       <c r="H16" t="n">
         <v>258303</v>
@@ -891,7 +891,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G18" t="n">
-        <v>13.1575164794922</v>
+        <v>13.1575155258179</v>
       </c>
       <c r="H18" t="n">
         <v>226405</v>
@@ -949,7 +949,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G20" t="n">
-        <v>13.8072690963745</v>
+        <v>13.8072700500488</v>
       </c>
       <c r="H20" t="n">
         <v>301266</v>
@@ -978,7 +978,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G21" t="n">
-        <v>14.0748147964478</v>
+        <v>14.0748138427734</v>
       </c>
       <c r="H21" t="n">
         <v>546294</v>
@@ -1007,7 +1007,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G22" t="n">
-        <v>14.0652599334717</v>
+        <v>14.065260887146</v>
       </c>
       <c r="H22" t="n">
         <v>577409</v>
@@ -1036,7 +1036,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>14.1417016983032</v>
+        <v>14.1417026519775</v>
       </c>
       <c r="H23" t="n">
         <v>170138</v>
@@ -1094,7 +1094,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G25" t="n">
-        <v>13.9410419464111</v>
+        <v>13.9410429000854</v>
       </c>
       <c r="H25" t="n">
         <v>258800</v>
@@ -1152,7 +1152,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G27" t="n">
-        <v>14.1990327835083</v>
+        <v>14.199031829834</v>
       </c>
       <c r="H27" t="n">
         <v>63326</v>
@@ -1210,7 +1210,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G29" t="n">
-        <v>13.826379776001</v>
+        <v>13.8263807296753</v>
       </c>
       <c r="H29" t="n">
         <v>61971</v>
@@ -1326,7 +1326,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G33" t="n">
-        <v>13.740382194519</v>
+        <v>13.7403831481934</v>
       </c>
       <c r="H33" t="n">
         <v>47665</v>
@@ -1355,7 +1355,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G34" t="n">
-        <v>13.3486204147339</v>
+        <v>13.3486194610596</v>
       </c>
       <c r="H34" t="n">
         <v>107934</v>
@@ -1384,7 +1384,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G35" t="n">
-        <v>13.5397243499756</v>
+        <v>13.5397233963013</v>
       </c>
       <c r="H35" t="n">
         <v>88256</v>
@@ -1413,7 +1413,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G36" t="n">
-        <v>13.3486204147339</v>
+        <v>13.3486194610596</v>
       </c>
       <c r="H36" t="n">
         <v>80762</v>
@@ -1471,7 +1471,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G38" t="n">
-        <v>13.4250612258911</v>
+        <v>13.4250621795654</v>
       </c>
       <c r="H38" t="n">
         <v>146037</v>
@@ -1529,7 +1529,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G40" t="n">
-        <v>13.8454895019531</v>
+        <v>13.8454904556274</v>
       </c>
       <c r="H40" t="n">
         <v>109728</v>
@@ -1558,7 +1558,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G41" t="n">
-        <v>14.8870077133179</v>
+        <v>14.8870067596436</v>
       </c>
       <c r="H41" t="n">
         <v>505585</v>
@@ -1587,7 +1587,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>15.1927728652954</v>
+        <v>15.192774772644</v>
       </c>
       <c r="H42" t="n">
         <v>474029</v>
@@ -1616,7 +1616,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>15.3838787078857</v>
+        <v>15.3838777542114</v>
       </c>
       <c r="H43" t="n">
         <v>436799</v>
@@ -1674,7 +1674,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>15.5749807357788</v>
+        <v>15.5749826431274</v>
       </c>
       <c r="H45" t="n">
         <v>405367</v>
@@ -1703,7 +1703,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G46" t="n">
-        <v>15.4507646560669</v>
+        <v>15.4507656097412</v>
       </c>
       <c r="H46" t="n">
         <v>226004</v>
@@ -1761,7 +1761,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G48" t="n">
-        <v>16.0909652709961</v>
+        <v>16.0909614562988</v>
       </c>
       <c r="H48" t="n">
         <v>581768</v>
@@ -1790,7 +1790,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G49" t="n">
-        <v>15.6418685913086</v>
+        <v>15.6418695449829</v>
       </c>
       <c r="H49" t="n">
         <v>782970</v>
@@ -1819,7 +1819,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G50" t="n">
-        <v>15.2309942245483</v>
+        <v>15.230993270874</v>
       </c>
       <c r="H50" t="n">
         <v>267987</v>
@@ -1848,7 +1848,7 @@
         <v>15.8900003433228</v>
       </c>
       <c r="G51" t="n">
-        <v>15.183219909668</v>
+        <v>15.1832189559937</v>
       </c>
       <c r="H51" t="n">
         <v>161269</v>
@@ -1877,7 +1877,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>14.7627906799316</v>
+        <v>14.7627897262573</v>
       </c>
       <c r="H52" t="n">
         <v>236091</v>
@@ -1935,7 +1935,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G54" t="n">
-        <v>14.0079298019409</v>
+        <v>14.0079278945923</v>
       </c>
       <c r="H54" t="n">
         <v>147319</v>
@@ -1993,7 +1993,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G56" t="n">
-        <v>15.1163311004639</v>
+        <v>15.1163330078125</v>
       </c>
       <c r="H56" t="n">
         <v>204640</v>
@@ -2051,7 +2051,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G58" t="n">
-        <v>14.4092473983765</v>
+        <v>14.4092464447021</v>
       </c>
       <c r="H58" t="n">
         <v>182625</v>
@@ -2080,7 +2080,7 @@
         <v>15.75</v>
       </c>
       <c r="G59" t="n">
-        <v>15.049446105957</v>
+        <v>15.0494451522827</v>
       </c>
       <c r="H59" t="n">
         <v>87541</v>
@@ -2109,7 +2109,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G60" t="n">
-        <v>15.4889850616455</v>
+        <v>15.4889841079712</v>
       </c>
       <c r="H60" t="n">
         <v>176931</v>
@@ -2167,7 +2167,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G62" t="n">
-        <v>15.2309942245483</v>
+        <v>15.230993270874</v>
       </c>
       <c r="H62" t="n">
         <v>177423</v>
@@ -2225,7 +2225,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G64" t="n">
-        <v>14.9634494781494</v>
+        <v>14.9634485244751</v>
       </c>
       <c r="H64" t="n">
         <v>72487</v>
@@ -2283,7 +2283,7 @@
         <v>16.2900009155273</v>
       </c>
       <c r="G66" t="n">
-        <v>15.5654268264771</v>
+        <v>15.5654277801514</v>
       </c>
       <c r="H66" t="n">
         <v>117861</v>
@@ -2312,7 +2312,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G67" t="n">
-        <v>15.2309942245483</v>
+        <v>15.230993270874</v>
       </c>
       <c r="H67" t="n">
         <v>105026</v>
@@ -2341,7 +2341,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G68" t="n">
-        <v>15.5176496505737</v>
+        <v>15.517650604248</v>
       </c>
       <c r="H68" t="n">
         <v>132919</v>
@@ -2399,7 +2399,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G70" t="n">
-        <v>15.3361005783081</v>
+        <v>15.3361015319824</v>
       </c>
       <c r="H70" t="n">
         <v>85001</v>
@@ -2428,7 +2428,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G71" t="n">
-        <v>15.097222328186</v>
+        <v>15.0972213745117</v>
       </c>
       <c r="H71" t="n">
         <v>210329</v>
@@ -2457,7 +2457,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G72" t="n">
-        <v>14.6003503799438</v>
+        <v>14.6003513336182</v>
       </c>
       <c r="H72" t="n">
         <v>144220</v>
@@ -2515,7 +2515,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G74" t="n">
-        <v>14.3136949539185</v>
+        <v>14.3136959075928</v>
       </c>
       <c r="H74" t="n">
         <v>173782</v>
@@ -2544,7 +2544,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G75" t="n">
-        <v>14.1894788742065</v>
+        <v>14.1894779205322</v>
       </c>
       <c r="H75" t="n">
         <v>121982</v>
@@ -2631,7 +2631,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G78" t="n">
-        <v>14.0652599334717</v>
+        <v>14.065260887146</v>
       </c>
       <c r="H78" t="n">
         <v>153369</v>
@@ -2660,7 +2660,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G79" t="n">
-        <v>13.8646011352539</v>
+        <v>13.8646001815796</v>
       </c>
       <c r="H79" t="n">
         <v>226264</v>
@@ -2689,7 +2689,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G80" t="n">
-        <v>13.9888181686401</v>
+        <v>13.9888191223145</v>
       </c>
       <c r="H80" t="n">
         <v>82515</v>
@@ -2718,7 +2718,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="n">
-        <v>14.3328065872192</v>
+        <v>14.3328056335449</v>
       </c>
       <c r="H81" t="n">
         <v>137258</v>
@@ -2892,7 +2892,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G87" t="n">
-        <v>13.6448307037354</v>
+        <v>13.6448316574097</v>
       </c>
       <c r="H87" t="n">
         <v>355963</v>
@@ -2921,7 +2921,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G88" t="n">
-        <v>14.6003503799438</v>
+        <v>14.6003513336182</v>
       </c>
       <c r="H88" t="n">
         <v>499133</v>
@@ -2950,7 +2950,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G89" t="n">
-        <v>15.0303354263306</v>
+        <v>15.0303363800049</v>
       </c>
       <c r="H89" t="n">
         <v>401988</v>
@@ -3066,7 +3066,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G93" t="n">
-        <v>14.6767921447754</v>
+        <v>14.6767930984497</v>
       </c>
       <c r="H93" t="n">
         <v>110219</v>
@@ -3095,7 +3095,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G94" t="n">
-        <v>14.6003503799438</v>
+        <v>14.6003513336182</v>
       </c>
       <c r="H94" t="n">
         <v>65667</v>
@@ -3124,7 +3124,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G95" t="n">
-        <v>14.1990327835083</v>
+        <v>14.199031829834</v>
       </c>
       <c r="H95" t="n">
         <v>59537</v>
@@ -3153,7 +3153,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>14.6194629669189</v>
+        <v>14.6194610595703</v>
       </c>
       <c r="H96" t="n">
         <v>186490</v>
@@ -3182,7 +3182,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G97" t="n">
-        <v>14.8678970336914</v>
+        <v>14.8678979873657</v>
       </c>
       <c r="H97" t="n">
         <v>106899</v>
@@ -3211,7 +3211,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G98" t="n">
-        <v>14.8678970336914</v>
+        <v>14.8678979873657</v>
       </c>
       <c r="H98" t="n">
         <v>69896</v>
@@ -3240,7 +3240,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G99" t="n">
-        <v>14.9347839355469</v>
+        <v>14.9347829818726</v>
       </c>
       <c r="H99" t="n">
         <v>117392</v>
@@ -3269,7 +3269,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G100" t="n">
-        <v>14.9347839355469</v>
+        <v>14.9347829818726</v>
       </c>
       <c r="H100" t="n">
         <v>95381</v>
@@ -3298,7 +3298,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G101" t="n">
-        <v>15.3265476226807</v>
+        <v>15.326548576355</v>
       </c>
       <c r="H101" t="n">
         <v>177567</v>
@@ -3356,7 +3356,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G103" t="n">
-        <v>15.3074378967285</v>
+        <v>15.3074369430542</v>
       </c>
       <c r="H103" t="n">
         <v>144419</v>
@@ -3501,7 +3501,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G108" t="n">
-        <v>14.7627906799316</v>
+        <v>14.7627897262573</v>
       </c>
       <c r="H108" t="n">
         <v>44432</v>
@@ -3559,7 +3559,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G110" t="n">
-        <v>15.0876655578613</v>
+        <v>15.0876665115356</v>
       </c>
       <c r="H110" t="n">
         <v>72044</v>
@@ -3588,7 +3588,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G111" t="n">
-        <v>14.9443397521973</v>
+        <v>14.9443387985229</v>
       </c>
       <c r="H111" t="n">
         <v>83241</v>
@@ -3617,7 +3617,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G112" t="n">
-        <v>14.6481266021729</v>
+        <v>14.6481275558472</v>
       </c>
       <c r="H112" t="n">
         <v>60854</v>
@@ -3675,7 +3675,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G114" t="n">
-        <v>14.7818994522095</v>
+        <v>14.7819004058838</v>
       </c>
       <c r="H114" t="n">
         <v>173217</v>
@@ -3762,7 +3762,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G117" t="n">
-        <v>14.4474678039551</v>
+        <v>14.4474687576294</v>
       </c>
       <c r="H117" t="n">
         <v>75827</v>
@@ -3791,7 +3791,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G118" t="n">
-        <v>14.0461492538452</v>
+        <v>14.0461483001709</v>
       </c>
       <c r="H118" t="n">
         <v>88132</v>
@@ -3849,7 +3849,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>13.7594938278198</v>
+        <v>13.7594928741455</v>
       </c>
       <c r="H120" t="n">
         <v>41310</v>
@@ -3907,7 +3907,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G122" t="n">
-        <v>13.9314870834351</v>
+        <v>13.9314880371094</v>
       </c>
       <c r="H122" t="n">
         <v>58966</v>
@@ -4052,7 +4052,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G127" t="n">
-        <v>14.9634494781494</v>
+        <v>14.9634485244751</v>
       </c>
       <c r="H127" t="n">
         <v>166475</v>
@@ -4081,7 +4081,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G128" t="n">
-        <v>14.8870077133179</v>
+        <v>14.8870067596436</v>
       </c>
       <c r="H128" t="n">
         <v>40404</v>
@@ -4110,7 +4110,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G129" t="n">
-        <v>15.1641082763672</v>
+        <v>15.1641092300415</v>
       </c>
       <c r="H129" t="n">
         <v>73585</v>
@@ -4168,7 +4168,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G131" t="n">
-        <v>15.0876655578613</v>
+        <v>15.0876665115356</v>
       </c>
       <c r="H131" t="n">
         <v>223782</v>
@@ -4197,7 +4197,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G132" t="n">
-        <v>15.1258878707886</v>
+        <v>15.1258869171143</v>
       </c>
       <c r="H132" t="n">
         <v>58545</v>
@@ -4226,7 +4226,7 @@
         <v>15.75</v>
       </c>
       <c r="G133" t="n">
-        <v>15.049446105957</v>
+        <v>15.0494451522827</v>
       </c>
       <c r="H133" t="n">
         <v>54662</v>
@@ -4255,7 +4255,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>14.953893661499</v>
+        <v>14.9538946151733</v>
       </c>
       <c r="H134" t="n">
         <v>62972</v>
@@ -4284,7 +4284,7 @@
         <v>15.6899995803833</v>
       </c>
       <c r="G135" t="n">
-        <v>14.9921140670776</v>
+        <v>14.992115020752</v>
       </c>
       <c r="H135" t="n">
         <v>123072</v>
@@ -4313,7 +4313,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G136" t="n">
-        <v>15.2692155838013</v>
+        <v>15.269214630127</v>
       </c>
       <c r="H136" t="n">
         <v>116552</v>
@@ -4429,7 +4429,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G140" t="n">
-        <v>16.1865158081055</v>
+        <v>16.1865139007568</v>
       </c>
       <c r="H140" t="n">
         <v>143796</v>
@@ -4516,7 +4516,7 @@
         <v>17.8700008392334</v>
       </c>
       <c r="G143" t="n">
-        <v>17.0751495361328</v>
+        <v>17.0751514434814</v>
       </c>
       <c r="H143" t="n">
         <v>118766</v>
@@ -4632,7 +4632,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G147" t="n">
-        <v>16.1769618988037</v>
+        <v>16.1769599914551</v>
       </c>
       <c r="H147" t="n">
         <v>432672</v>
@@ -4661,7 +4661,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G148" t="n">
-        <v>15.8425283432007</v>
+        <v>15.8425273895264</v>
       </c>
       <c r="H148" t="n">
         <v>256187</v>
@@ -4690,7 +4690,7 @@
         <v>16.6100006103516</v>
       </c>
       <c r="G149" t="n">
-        <v>15.8711948394775</v>
+        <v>15.8711929321289</v>
       </c>
       <c r="H149" t="n">
         <v>130015</v>
@@ -4719,7 +4719,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G150" t="n">
-        <v>15.6418685913086</v>
+        <v>15.6418695449829</v>
       </c>
       <c r="H150" t="n">
         <v>102652</v>
@@ -4835,7 +4835,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>17.3426952362061</v>
+        <v>17.3426933288574</v>
       </c>
       <c r="H154" t="n">
         <v>130344</v>
@@ -4864,7 +4864,7 @@
         <v>18.25</v>
       </c>
       <c r="G155" t="n">
-        <v>17.4382476806641</v>
+        <v>17.4382457733154</v>
       </c>
       <c r="H155" t="n">
         <v>175492</v>
@@ -4893,7 +4893,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G156" t="n">
-        <v>17.6962394714355</v>
+        <v>17.6962356567383</v>
       </c>
       <c r="H156" t="n">
         <v>187911</v>
@@ -4951,7 +4951,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G158" t="n">
-        <v>17.466911315918</v>
+        <v>17.4669132232666</v>
       </c>
       <c r="H158" t="n">
         <v>73047</v>
@@ -4980,7 +4980,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G159" t="n">
-        <v>17.3904685974121</v>
+        <v>17.3904705047607</v>
       </c>
       <c r="H159" t="n">
         <v>70593</v>
@@ -5009,7 +5009,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G160" t="n">
-        <v>17.3904685974121</v>
+        <v>17.3904705047607</v>
       </c>
       <c r="H160" t="n">
         <v>78063</v>
@@ -5067,7 +5067,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G162" t="n">
-        <v>17.5815753936768</v>
+        <v>17.5815773010254</v>
       </c>
       <c r="H162" t="n">
         <v>61690</v>
@@ -5096,7 +5096,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G163" t="n">
-        <v>17.2089233398438</v>
+        <v>17.2089214324951</v>
       </c>
       <c r="H163" t="n">
         <v>50813</v>
@@ -5154,7 +5154,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G165" t="n">
-        <v>17.9542274475098</v>
+        <v>17.9542293548584</v>
       </c>
       <c r="H165" t="n">
         <v>337145</v>
@@ -5183,7 +5183,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>17.8204536437988</v>
+        <v>17.8204555511475</v>
       </c>
       <c r="H166" t="n">
         <v>70506</v>
@@ -5212,7 +5212,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G167" t="n">
-        <v>18.2313270568848</v>
+        <v>18.231330871582</v>
       </c>
       <c r="H167" t="n">
         <v>148047</v>
@@ -5270,7 +5270,7 @@
         <v>19.5</v>
       </c>
       <c r="G169" t="n">
-        <v>18.6326503753662</v>
+        <v>18.6326465606689</v>
       </c>
       <c r="H169" t="n">
         <v>161677</v>
@@ -5328,7 +5328,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G171" t="n">
-        <v>18.7664184570312</v>
+        <v>18.7664203643799</v>
       </c>
       <c r="H171" t="n">
         <v>104982</v>
@@ -5357,7 +5357,7 @@
         <v>19.75</v>
       </c>
       <c r="G172" t="n">
-        <v>18.8715267181396</v>
+        <v>18.8715286254883</v>
       </c>
       <c r="H172" t="n">
         <v>54348</v>
@@ -5415,7 +5415,7 @@
         <v>18.7700004577637</v>
       </c>
       <c r="G174" t="n">
-        <v>17.9351177215576</v>
+        <v>17.935115814209</v>
       </c>
       <c r="H174" t="n">
         <v>228634</v>
@@ -5444,7 +5444,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>18.4415435791016</v>
+        <v>18.4415416717529</v>
       </c>
       <c r="H175" t="n">
         <v>73309</v>
@@ -5473,7 +5473,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>17.7726821899414</v>
+        <v>17.7726783752441</v>
       </c>
       <c r="H176" t="n">
         <v>132691</v>
@@ -5560,7 +5560,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G179" t="n">
-        <v>18.8524169921875</v>
+        <v>18.8524188995361</v>
       </c>
       <c r="H179" t="n">
         <v>160303</v>
@@ -5589,7 +5589,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G180" t="n">
-        <v>18.7664184570312</v>
+        <v>18.7664203643799</v>
       </c>
       <c r="H180" t="n">
         <v>186766</v>
@@ -5676,7 +5676,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G183" t="n">
-        <v>17.7249011993408</v>
+        <v>17.7249031066895</v>
       </c>
       <c r="H183" t="n">
         <v>316794</v>
@@ -5705,7 +5705,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G184" t="n">
-        <v>17.189811706543</v>
+        <v>17.1898097991943</v>
       </c>
       <c r="H184" t="n">
         <v>165069</v>
@@ -5763,7 +5763,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G186" t="n">
-        <v>16.683385848999</v>
+        <v>16.6833839416504</v>
       </c>
       <c r="H186" t="n">
         <v>219917</v>
@@ -5792,7 +5792,7 @@
         <v>18</v>
       </c>
       <c r="G187" t="n">
-        <v>17.1993656158447</v>
+        <v>17.1993675231934</v>
       </c>
       <c r="H187" t="n">
         <v>168778</v>
@@ -5821,7 +5821,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G188" t="n">
-        <v>17.6580142974854</v>
+        <v>17.658016204834</v>
       </c>
       <c r="H188" t="n">
         <v>106658</v>
@@ -5850,7 +5850,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G189" t="n">
-        <v>17.6580142974854</v>
+        <v>17.658016204834</v>
       </c>
       <c r="H189" t="n">
         <v>195062</v>
@@ -5908,7 +5908,7 @@
         <v>17.75</v>
       </c>
       <c r="G191" t="n">
-        <v>16.9604873657227</v>
+        <v>16.960485458374</v>
       </c>
       <c r="H191" t="n">
         <v>902705</v>
@@ -5937,7 +5937,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G192" t="n">
-        <v>16.5305004119873</v>
+        <v>16.5305023193359</v>
       </c>
       <c r="H192" t="n">
         <v>303536</v>
@@ -5966,7 +5966,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G193" t="n">
-        <v>16.4540596008301</v>
+        <v>16.4540615081787</v>
       </c>
       <c r="H193" t="n">
         <v>194779</v>
@@ -5995,7 +5995,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>16.3871765136719</v>
+        <v>16.3871746063232</v>
       </c>
       <c r="H194" t="n">
         <v>289758</v>
@@ -6140,7 +6140,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G199" t="n">
-        <v>16.6069431304932</v>
+        <v>16.6069450378418</v>
       </c>
       <c r="H199" t="n">
         <v>89821</v>
@@ -6169,7 +6169,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G200" t="n">
-        <v>16.683385848999</v>
+        <v>16.6833839416504</v>
       </c>
       <c r="H200" t="n">
         <v>78475</v>
@@ -6198,7 +6198,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>16.6260528564453</v>
+        <v>16.6260547637939</v>
       </c>
       <c r="H201" t="n">
         <v>108711</v>
@@ -6314,7 +6314,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G205" t="n">
-        <v>17.0369300842285</v>
+        <v>17.0369281768799</v>
       </c>
       <c r="H205" t="n">
         <v>107074</v>
@@ -6343,7 +6343,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G206" t="n">
-        <v>17.2375869750977</v>
+        <v>17.2375888824463</v>
       </c>
       <c r="H206" t="n">
         <v>108799</v>
@@ -6372,7 +6372,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G207" t="n">
-        <v>16.6547203063965</v>
+        <v>16.6547222137451</v>
       </c>
       <c r="H207" t="n">
         <v>154640</v>
@@ -6459,7 +6459,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G210" t="n">
-        <v>17.2375869750977</v>
+        <v>17.2375888824463</v>
       </c>
       <c r="H210" t="n">
         <v>68530</v>
@@ -6488,7 +6488,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G211" t="n">
-        <v>17.3713607788086</v>
+        <v>17.37135887146</v>
       </c>
       <c r="H211" t="n">
         <v>87623</v>
@@ -6546,7 +6546,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>17.2949180603027</v>
+        <v>17.2949199676514</v>
       </c>
       <c r="H213" t="n">
         <v>63203</v>
@@ -6575,7 +6575,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G214" t="n">
-        <v>16.6642761230469</v>
+        <v>16.6642742156982</v>
       </c>
       <c r="H214" t="n">
         <v>584108</v>
@@ -6604,7 +6604,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G215" t="n">
-        <v>17.476469039917</v>
+        <v>17.4764709472656</v>
       </c>
       <c r="H215" t="n">
         <v>330056</v>
@@ -6662,7 +6662,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G217" t="n">
-        <v>18.2313270568848</v>
+        <v>18.231330871582</v>
       </c>
       <c r="H217" t="n">
         <v>171919</v>
@@ -6691,7 +6691,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G218" t="n">
-        <v>18.4415435791016</v>
+        <v>18.4415416717529</v>
       </c>
       <c r="H218" t="n">
         <v>241224</v>
@@ -6720,7 +6720,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G219" t="n">
-        <v>18.4415435791016</v>
+        <v>18.4415416717529</v>
       </c>
       <c r="H219" t="n">
         <v>270484</v>
@@ -6749,7 +6749,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G220" t="n">
-        <v>18.0020046234131</v>
+        <v>18.0020065307617</v>
       </c>
       <c r="H220" t="n">
         <v>388714</v>
@@ -6778,7 +6778,7 @@
         <v>19.2700004577637</v>
       </c>
       <c r="G221" t="n">
-        <v>18.5309104919434</v>
+        <v>18.5309085845947</v>
       </c>
       <c r="H221" t="n">
         <v>86313</v>
@@ -6865,7 +6865,7 @@
         <v>19.25</v>
       </c>
       <c r="G224" t="n">
-        <v>18.5116748809814</v>
+        <v>18.5116767883301</v>
       </c>
       <c r="H224" t="n">
         <v>52689</v>
@@ -7010,7 +7010,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G229" t="n">
-        <v>18.8097839355469</v>
+        <v>18.8097858428955</v>
       </c>
       <c r="H229" t="n">
         <v>69687</v>
@@ -7126,7 +7126,7 @@
         <v>19.75</v>
       </c>
       <c r="G233" t="n">
-        <v>18.9924983978271</v>
+        <v>18.9925003051758</v>
       </c>
       <c r="H233" t="n">
         <v>75996</v>
@@ -7213,7 +7213,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G236" t="n">
-        <v>20.1753215789795</v>
+        <v>20.1753234863281</v>
       </c>
       <c r="H236" t="n">
         <v>286301</v>
@@ -7242,7 +7242,7 @@
         <v>20.5</v>
       </c>
       <c r="G237" t="n">
-        <v>19.7137336730957</v>
+        <v>19.7137317657471</v>
       </c>
       <c r="H237" t="n">
         <v>224683</v>
@@ -7329,7 +7329,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G240" t="n">
-        <v>19.4637031555176</v>
+        <v>19.4637050628662</v>
       </c>
       <c r="H240" t="n">
         <v>95964</v>
@@ -7416,7 +7416,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G243" t="n">
-        <v>19.0405788421631</v>
+        <v>19.0405807495117</v>
       </c>
       <c r="H243" t="n">
         <v>51065</v>
@@ -7706,7 +7706,7 @@
         <v>19.4099998474121</v>
       </c>
       <c r="G253" t="n">
-        <v>18.6655387878418</v>
+        <v>18.6655406951904</v>
       </c>
       <c r="H253" t="n">
         <v>58888</v>
@@ -7764,7 +7764,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G255" t="n">
-        <v>19.4637031555176</v>
+        <v>19.4637050628662</v>
       </c>
       <c r="H255" t="n">
         <v>154255</v>
@@ -7793,7 +7793,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G256" t="n">
-        <v>19.4637031555176</v>
+        <v>19.4637050628662</v>
       </c>
       <c r="H256" t="n">
         <v>168657</v>
@@ -7822,7 +7822,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G257" t="n">
-        <v>19.6944980621338</v>
+        <v>19.6944999694824</v>
       </c>
       <c r="H257" t="n">
         <v>62964</v>
@@ -7851,7 +7851,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G258" t="n">
-        <v>20.1368560791016</v>
+        <v>20.1368579864502</v>
       </c>
       <c r="H258" t="n">
         <v>123239</v>
@@ -7909,7 +7909,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G260" t="n">
-        <v>19.5598697662354</v>
+        <v>19.5598678588867</v>
       </c>
       <c r="H260" t="n">
         <v>165590</v>
@@ -7938,7 +7938,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G261" t="n">
-        <v>19.2713775634766</v>
+        <v>19.2713756561279</v>
       </c>
       <c r="H261" t="n">
         <v>226076</v>
@@ -7996,7 +7996,7 @@
         <v>20.5</v>
       </c>
       <c r="G263" t="n">
-        <v>19.7137336730957</v>
+        <v>19.7137317657471</v>
       </c>
       <c r="H263" t="n">
         <v>91506</v>
@@ -8054,7 +8054,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>19.8098964691162</v>
+        <v>19.8098983764648</v>
       </c>
       <c r="H265" t="n">
         <v>74881</v>
@@ -8083,7 +8083,7 @@
         <v>20.5</v>
       </c>
       <c r="G266" t="n">
-        <v>19.7137336730957</v>
+        <v>19.7137317657471</v>
       </c>
       <c r="H266" t="n">
         <v>56249</v>
@@ -8112,7 +8112,7 @@
         <v>20.5</v>
       </c>
       <c r="G267" t="n">
-        <v>19.7137336730957</v>
+        <v>19.7137317657471</v>
       </c>
       <c r="H267" t="n">
         <v>68211</v>
@@ -8286,7 +8286,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G273" t="n">
-        <v>17.569263458252</v>
+        <v>17.5692653656006</v>
       </c>
       <c r="H273" t="n">
         <v>162056</v>
@@ -8344,7 +8344,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G275" t="n">
-        <v>18.2904968261719</v>
+        <v>18.2904987335205</v>
       </c>
       <c r="H275" t="n">
         <v>226073</v>
@@ -8460,7 +8460,7 @@
         <v>19.4099998474121</v>
       </c>
       <c r="G279" t="n">
-        <v>18.6655387878418</v>
+        <v>18.6655406951904</v>
       </c>
       <c r="H279" t="n">
         <v>51561</v>
@@ -8547,7 +8547,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G282" t="n">
-        <v>17.8866081237793</v>
+        <v>17.8866062164307</v>
       </c>
       <c r="H282" t="n">
         <v>64258</v>
@@ -8576,7 +8576,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G283" t="n">
-        <v>17.5981121063232</v>
+        <v>17.5981101989746</v>
       </c>
       <c r="H283" t="n">
         <v>79763</v>
@@ -8605,7 +8605,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G284" t="n">
-        <v>17.5404148101807</v>
+        <v>17.540412902832</v>
       </c>
       <c r="H284" t="n">
         <v>101821</v>
@@ -8750,7 +8750,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G289" t="n">
-        <v>16.6460838317871</v>
+        <v>16.6460819244385</v>
       </c>
       <c r="H289" t="n">
         <v>130395</v>
@@ -8837,7 +8837,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G292" t="n">
-        <v>17.569263458252</v>
+        <v>17.5692653656006</v>
       </c>
       <c r="H292" t="n">
         <v>70023</v>
@@ -8924,7 +8924,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G295" t="n">
-        <v>17.1749897003174</v>
+        <v>17.1749877929688</v>
       </c>
       <c r="H295" t="n">
         <v>38905</v>
@@ -8953,7 +8953,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G296" t="n">
-        <v>17.2807674407959</v>
+        <v>17.2807693481445</v>
       </c>
       <c r="H296" t="n">
         <v>59361</v>
@@ -9069,7 +9069,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G300" t="n">
-        <v>16.6460838317871</v>
+        <v>16.6460819244385</v>
       </c>
       <c r="H300" t="n">
         <v>104866</v>
@@ -9214,7 +9214,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G305" t="n">
-        <v>16.3575916290283</v>
+        <v>16.3575897216797</v>
       </c>
       <c r="H305" t="n">
         <v>47439</v>
@@ -9272,7 +9272,7 @@
         <v>16.75</v>
       </c>
       <c r="G307" t="n">
-        <v>16.1075611114502</v>
+        <v>16.1075630187988</v>
       </c>
       <c r="H307" t="n">
         <v>64826</v>
@@ -9330,7 +9330,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G309" t="n">
-        <v>15.7132873535156</v>
+        <v>15.7132883071899</v>
       </c>
       <c r="H309" t="n">
         <v>82945</v>
@@ -9417,7 +9417,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>15.4824934005737</v>
+        <v>15.4824924468994</v>
       </c>
       <c r="H312" t="n">
         <v>47778</v>
@@ -9475,7 +9475,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G314" t="n">
-        <v>15.6555881500244</v>
+        <v>15.6555891036987</v>
       </c>
       <c r="H314" t="n">
         <v>70184</v>
@@ -9591,7 +9591,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G318" t="n">
-        <v>14.4150648117065</v>
+        <v>14.4150657653809</v>
       </c>
       <c r="H318" t="n">
         <v>129315</v>
@@ -9678,7 +9678,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G321" t="n">
-        <v>14.4631481170654</v>
+        <v>14.4631471633911</v>
       </c>
       <c r="H321" t="n">
         <v>76846</v>
@@ -9707,7 +9707,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G322" t="n">
-        <v>14.5689296722412</v>
+        <v>14.5689287185669</v>
       </c>
       <c r="H322" t="n">
         <v>40798</v>
@@ -9823,7 +9823,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>14.1361885070801</v>
+        <v>14.1361875534058</v>
       </c>
       <c r="H326" t="n">
         <v>132397</v>
@@ -9852,7 +9852,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G327" t="n">
-        <v>14.0881052017212</v>
+        <v>14.0881061553955</v>
       </c>
       <c r="H327" t="n">
         <v>66396</v>
@@ -9968,7 +9968,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G331" t="n">
-        <v>13.174542427063</v>
+        <v>13.1745433807373</v>
       </c>
       <c r="H331" t="n">
         <v>46983</v>
@@ -10026,7 +10026,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G333" t="n">
-        <v>12.8571996688843</v>
+        <v>12.8572006225586</v>
       </c>
       <c r="H333" t="n">
         <v>104403</v>
@@ -10171,7 +10171,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G338" t="n">
-        <v>13.9053936004639</v>
+        <v>13.9053945541382</v>
       </c>
       <c r="H338" t="n">
         <v>230450</v>
@@ -10200,7 +10200,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G339" t="n">
-        <v>13.8284616470337</v>
+        <v>13.828462600708</v>
       </c>
       <c r="H339" t="n">
         <v>150608</v>
@@ -10374,7 +10374,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G345" t="n">
-        <v>13.655366897583</v>
+        <v>13.6553659439087</v>
       </c>
       <c r="H345" t="n">
         <v>126227</v>
@@ -10606,7 +10606,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G353" t="n">
-        <v>14.3092861175537</v>
+        <v>14.3092851638794</v>
       </c>
       <c r="H353" t="n">
         <v>104165</v>
@@ -10722,7 +10722,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G357" t="n">
-        <v>13.7611474990845</v>
+        <v>13.7611465454102</v>
       </c>
       <c r="H357" t="n">
         <v>89876</v>
@@ -10751,7 +10751,7 @@
         <v>14.3900003433228</v>
       </c>
       <c r="G358" t="n">
-        <v>13.8380794525146</v>
+        <v>13.8380784988403</v>
       </c>
       <c r="H358" t="n">
         <v>106575</v>
@@ -10809,7 +10809,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G360" t="n">
-        <v>13.2707080841064</v>
+        <v>13.2707071304321</v>
       </c>
       <c r="H360" t="n">
         <v>139158</v>
@@ -10925,7 +10925,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G364" t="n">
-        <v>13.4341878890991</v>
+        <v>13.4341869354248</v>
       </c>
       <c r="H364" t="n">
         <v>99374</v>
@@ -10983,7 +10983,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G366" t="n">
-        <v>13.5015020370483</v>
+        <v>13.5015029907227</v>
       </c>
       <c r="H366" t="n">
         <v>125716</v>
@@ -11099,7 +11099,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G370" t="n">
-        <v>14.9151210784912</v>
+        <v>14.9151220321655</v>
       </c>
       <c r="H370" t="n">
         <v>166793</v>
@@ -11128,7 +11128,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G371" t="n">
-        <v>15.68443775177</v>
+        <v>15.6844367980957</v>
       </c>
       <c r="H371" t="n">
         <v>353221</v>
@@ -11186,7 +11186,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G373" t="n">
-        <v>14.9151210784912</v>
+        <v>14.9151220321655</v>
       </c>
       <c r="H373" t="n">
         <v>162189</v>
@@ -11418,7 +11418,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G381" t="n">
-        <v>14.8862714767456</v>
+        <v>14.8862724304199</v>
       </c>
       <c r="H381" t="n">
         <v>97752</v>
@@ -11447,7 +11447,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G382" t="n">
-        <v>14.8958892822266</v>
+        <v>14.8958883285522</v>
       </c>
       <c r="H382" t="n">
         <v>111609</v>
@@ -11476,7 +11476,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G383" t="n">
-        <v>14.867039680481</v>
+        <v>14.8670387268066</v>
       </c>
       <c r="H383" t="n">
         <v>127709</v>
@@ -11563,7 +11563,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G386" t="n">
-        <v>14.0977230072021</v>
+        <v>14.0977220535278</v>
       </c>
       <c r="H386" t="n">
         <v>236798</v>
@@ -11592,7 +11592,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G387" t="n">
-        <v>14.1361885070801</v>
+        <v>14.1361875534058</v>
       </c>
       <c r="H387" t="n">
         <v>123369</v>
@@ -11621,7 +11621,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G388" t="n">
-        <v>13.9823265075684</v>
+        <v>13.982325553894</v>
       </c>
       <c r="H388" t="n">
         <v>99895</v>
@@ -11679,7 +11679,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G390" t="n">
-        <v>14.4631481170654</v>
+        <v>14.4631471633911</v>
       </c>
       <c r="H390" t="n">
         <v>99312</v>
@@ -11708,7 +11708,7 @@
         <v>14.2700004577637</v>
       </c>
       <c r="G391" t="n">
-        <v>13.7226810455322</v>
+        <v>13.7226819992065</v>
       </c>
       <c r="H391" t="n">
         <v>186975</v>
@@ -11969,7 +11969,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G400" t="n">
-        <v>14.0784902572632</v>
+        <v>14.0784912109375</v>
       </c>
       <c r="H400" t="n">
         <v>204846</v>
@@ -12172,7 +12172,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>13.655366897583</v>
+        <v>13.6553659439087</v>
       </c>
       <c r="H407" t="n">
         <v>163196</v>
@@ -12201,7 +12201,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G408" t="n">
-        <v>14.1650381088257</v>
+        <v>14.1650371551514</v>
       </c>
       <c r="H408" t="n">
         <v>284491</v>
@@ -12259,7 +12259,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G410" t="n">
-        <v>14.7901077270508</v>
+        <v>14.7901067733765</v>
       </c>
       <c r="H410" t="n">
         <v>220807</v>
@@ -12404,7 +12404,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G415" t="n">
-        <v>14.8862714767456</v>
+        <v>14.8862724304199</v>
       </c>
       <c r="H415" t="n">
         <v>139801</v>
@@ -12607,7 +12607,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G422" t="n">
-        <v>14.3092861175537</v>
+        <v>14.3092851638794</v>
       </c>
       <c r="H422" t="n">
         <v>102639</v>
@@ -12636,7 +12636,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G423" t="n">
-        <v>14.2323532104492</v>
+        <v>14.2323541641235</v>
       </c>
       <c r="H423" t="n">
         <v>63885</v>
@@ -12868,7 +12868,7 @@
         <v>14.1899995803833</v>
       </c>
       <c r="G431" t="n">
-        <v>13.6457481384277</v>
+        <v>13.6457490921021</v>
       </c>
       <c r="H431" t="n">
         <v>223671</v>
@@ -12897,7 +12897,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G432" t="n">
-        <v>12.6937198638916</v>
+        <v>12.6937208175659</v>
       </c>
       <c r="H432" t="n">
         <v>632996</v>
@@ -12955,7 +12955,7 @@
         <v>13.25</v>
       </c>
       <c r="G434" t="n">
-        <v>12.7418031692505</v>
+        <v>12.7418022155762</v>
       </c>
       <c r="H434" t="n">
         <v>207043</v>
@@ -12984,7 +12984,7 @@
         <v>13.25</v>
       </c>
       <c r="G435" t="n">
-        <v>12.7418031692505</v>
+        <v>12.7418022155762</v>
       </c>
       <c r="H435" t="n">
         <v>214799</v>
@@ -13100,7 +13100,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G439" t="n">
-        <v>12.8571996688843</v>
+        <v>12.8572006225586</v>
       </c>
       <c r="H439" t="n">
         <v>90236</v>
@@ -13158,7 +13158,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G441" t="n">
-        <v>12.3763780593872</v>
+        <v>12.3763771057129</v>
       </c>
       <c r="H441" t="n">
         <v>197033</v>
@@ -13245,7 +13245,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G444" t="n">
-        <v>12.472541809082</v>
+        <v>12.4725427627563</v>
       </c>
       <c r="H444" t="n">
         <v>169735</v>
@@ -13274,7 +13274,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G445" t="n">
-        <v>12.7802686691284</v>
+        <v>12.7802677154541</v>
       </c>
       <c r="H445" t="n">
         <v>146927</v>
@@ -13477,7 +13477,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G452" t="n">
-        <v>12.6937198638916</v>
+        <v>12.6937208175659</v>
       </c>
       <c r="H452" t="n">
         <v>67295</v>
@@ -13535,7 +13535,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G454" t="n">
-        <v>11.6839933395386</v>
+        <v>11.6839923858643</v>
       </c>
       <c r="H454" t="n">
         <v>219490</v>
@@ -13564,7 +13564,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G455" t="n">
-        <v>11.7513084411621</v>
+        <v>11.7513074874878</v>
       </c>
       <c r="H455" t="n">
         <v>152747</v>
@@ -13680,7 +13680,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G459" t="n">
-        <v>11.8859386444092</v>
+        <v>11.8859376907349</v>
       </c>
       <c r="H459" t="n">
         <v>67163</v>
@@ -13709,7 +13709,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G460" t="n">
-        <v>12.1744318008423</v>
+        <v>12.1744327545166</v>
       </c>
       <c r="H460" t="n">
         <v>97426</v>
@@ -13767,7 +13767,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G462" t="n">
-        <v>12.1455821990967</v>
+        <v>12.145583152771</v>
       </c>
       <c r="H462" t="n">
         <v>90492</v>
@@ -13796,7 +13796,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G463" t="n">
-        <v>12.0494184494019</v>
+        <v>12.0494174957275</v>
       </c>
       <c r="H463" t="n">
         <v>59080</v>
@@ -13999,7 +13999,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G470" t="n">
-        <v>13.3476390838623</v>
+        <v>13.3476400375366</v>
       </c>
       <c r="H470" t="n">
         <v>152417</v>
@@ -31985,6 +31985,35 @@
         <v>419733</v>
       </c>
       <c r="I1090" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1091" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1091" t="n">
+        <v>5.30999994277954</v>
+      </c>
+      <c r="D1091" t="n">
+        <v>5.46999979019165</v>
+      </c>
+      <c r="E1091" t="n">
+        <v>5.30999994277954</v>
+      </c>
+      <c r="F1091" t="n">
+        <v>5.40500020980835</v>
+      </c>
+      <c r="G1091" t="n">
+        <v>5.40500020980835</v>
+      </c>
+      <c r="H1091" t="n">
+        <v>432825</v>
+      </c>
+      <c r="I1091" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DNR.MI.xlsx
+++ b/data/DNR.MI.xlsx
@@ -427,7 +427,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G2" t="n">
-        <v>12.5555381774902</v>
+        <v>12.5555391311646</v>
       </c>
       <c r="H2" t="n">
         <v>264770</v>
@@ -456,7 +456,7 @@
         <v>13.25</v>
       </c>
       <c r="G3" t="n">
-        <v>12.66064453125</v>
+        <v>12.6606454849243</v>
       </c>
       <c r="H3" t="n">
         <v>74987</v>
@@ -514,7 +514,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G5" t="n">
-        <v>12.4886503219604</v>
+        <v>12.4886512756348</v>
       </c>
       <c r="H5" t="n">
         <v>167412</v>
@@ -572,7 +572,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G7" t="n">
-        <v>12.5077629089355</v>
+        <v>12.5077619552612</v>
       </c>
       <c r="H7" t="n">
         <v>117337</v>
@@ -659,7 +659,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G10" t="n">
-        <v>12.5173168182373</v>
+        <v>12.5173177719116</v>
       </c>
       <c r="H10" t="n">
         <v>111264</v>
@@ -688,7 +688,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>12.5173168182373</v>
+        <v>12.5173177719116</v>
       </c>
       <c r="H11" t="n">
         <v>104743</v>
@@ -717,7 +717,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G12" t="n">
-        <v>12.4504308700562</v>
+        <v>12.4504299163818</v>
       </c>
       <c r="H12" t="n">
         <v>94003</v>
@@ -746,7 +746,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G13" t="n">
-        <v>12.5459833145142</v>
+        <v>12.5459823608398</v>
       </c>
       <c r="H13" t="n">
         <v>74915</v>
@@ -862,7 +862,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G17" t="n">
-        <v>13.7021617889404</v>
+        <v>13.7021627426147</v>
       </c>
       <c r="H17" t="n">
         <v>249086</v>
@@ -891,7 +891,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G18" t="n">
-        <v>13.1575155258179</v>
+        <v>13.1575164794922</v>
       </c>
       <c r="H18" t="n">
         <v>226405</v>
@@ -920,7 +920,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G19" t="n">
-        <v>13.5683889389038</v>
+        <v>13.5683898925781</v>
       </c>
       <c r="H19" t="n">
         <v>254487</v>
@@ -949,7 +949,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G20" t="n">
-        <v>13.8072700500488</v>
+        <v>13.8072690963745</v>
       </c>
       <c r="H20" t="n">
         <v>301266</v>
@@ -1094,7 +1094,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G25" t="n">
-        <v>13.9410429000854</v>
+        <v>13.9410419464111</v>
       </c>
       <c r="H25" t="n">
         <v>258800</v>
@@ -1123,7 +1123,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G26" t="n">
-        <v>14.1608114242554</v>
+        <v>14.1608123779297</v>
       </c>
       <c r="H26" t="n">
         <v>270595</v>
@@ -1152,7 +1152,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G27" t="n">
-        <v>14.199031829834</v>
+        <v>14.1990327835083</v>
       </c>
       <c r="H27" t="n">
         <v>63326</v>
@@ -1210,7 +1210,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G29" t="n">
-        <v>13.8263807296753</v>
+        <v>13.826379776001</v>
       </c>
       <c r="H29" t="n">
         <v>61971</v>
@@ -1239,7 +1239,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G30" t="n">
-        <v>13.7021617889404</v>
+        <v>13.7021627426147</v>
       </c>
       <c r="H30" t="n">
         <v>147708</v>
@@ -1268,7 +1268,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G31" t="n">
-        <v>13.5492792129517</v>
+        <v>13.5492782592773</v>
       </c>
       <c r="H31" t="n">
         <v>152273</v>
@@ -1297,7 +1297,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G32" t="n">
-        <v>13.5683889389038</v>
+        <v>13.5683898925781</v>
       </c>
       <c r="H32" t="n">
         <v>138086</v>
@@ -1384,7 +1384,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G35" t="n">
-        <v>13.5397233963013</v>
+        <v>13.5397243499756</v>
       </c>
       <c r="H35" t="n">
         <v>88256</v>
@@ -1442,7 +1442,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G37" t="n">
-        <v>13.2912883758545</v>
+        <v>13.2912893295288</v>
       </c>
       <c r="H37" t="n">
         <v>64058</v>
@@ -1529,7 +1529,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G40" t="n">
-        <v>13.8454904556274</v>
+        <v>13.8454895019531</v>
       </c>
       <c r="H40" t="n">
         <v>109728</v>
@@ -1558,7 +1558,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G41" t="n">
-        <v>14.8870067596436</v>
+        <v>14.8870077133179</v>
       </c>
       <c r="H41" t="n">
         <v>505585</v>
@@ -1587,7 +1587,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>15.192774772644</v>
+        <v>15.1927728652954</v>
       </c>
       <c r="H42" t="n">
         <v>474029</v>
@@ -1616,7 +1616,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>15.3838777542114</v>
+        <v>15.3838787078857</v>
       </c>
       <c r="H43" t="n">
         <v>436799</v>
@@ -1674,7 +1674,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>15.5749826431274</v>
+        <v>15.5749807357788</v>
       </c>
       <c r="H45" t="n">
         <v>405367</v>
@@ -1703,7 +1703,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G46" t="n">
-        <v>15.4507656097412</v>
+        <v>15.4507646560669</v>
       </c>
       <c r="H46" t="n">
         <v>226004</v>
@@ -1732,7 +1732,7 @@
         <v>16.0900001525879</v>
       </c>
       <c r="G47" t="n">
-        <v>15.3743228912354</v>
+        <v>15.374321937561</v>
       </c>
       <c r="H47" t="n">
         <v>347713</v>
@@ -1761,7 +1761,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G48" t="n">
-        <v>16.0909614562988</v>
+        <v>16.0909633636475</v>
       </c>
       <c r="H48" t="n">
         <v>581768</v>
@@ -1790,7 +1790,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G49" t="n">
-        <v>15.6418695449829</v>
+        <v>15.6418685913086</v>
       </c>
       <c r="H49" t="n">
         <v>782970</v>
@@ -1819,7 +1819,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G50" t="n">
-        <v>15.230993270874</v>
+        <v>15.2309942245483</v>
       </c>
       <c r="H50" t="n">
         <v>267987</v>
@@ -1848,7 +1848,7 @@
         <v>15.8900003433228</v>
       </c>
       <c r="G51" t="n">
-        <v>15.1832189559937</v>
+        <v>15.183219909668</v>
       </c>
       <c r="H51" t="n">
         <v>161269</v>
@@ -1877,7 +1877,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>14.7627897262573</v>
+        <v>14.7627906799316</v>
       </c>
       <c r="H52" t="n">
         <v>236091</v>
@@ -1906,7 +1906,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G53" t="n">
-        <v>14.2372531890869</v>
+        <v>14.2372541427612</v>
       </c>
       <c r="H53" t="n">
         <v>139086</v>
@@ -1935,7 +1935,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G54" t="n">
-        <v>14.0079278945923</v>
+        <v>14.0079288482666</v>
       </c>
       <c r="H54" t="n">
         <v>147319</v>
@@ -2022,7 +2022,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G57" t="n">
-        <v>14.7436809539795</v>
+        <v>14.7436790466309</v>
       </c>
       <c r="H57" t="n">
         <v>220752</v>
@@ -2051,7 +2051,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G58" t="n">
-        <v>14.4092464447021</v>
+        <v>14.4092473983765</v>
       </c>
       <c r="H58" t="n">
         <v>182625</v>
@@ -2080,7 +2080,7 @@
         <v>15.75</v>
       </c>
       <c r="G59" t="n">
-        <v>15.0494451522827</v>
+        <v>15.049446105957</v>
       </c>
       <c r="H59" t="n">
         <v>87541</v>
@@ -2109,7 +2109,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G60" t="n">
-        <v>15.4889841079712</v>
+        <v>15.4889850616455</v>
       </c>
       <c r="H60" t="n">
         <v>176931</v>
@@ -2167,7 +2167,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G62" t="n">
-        <v>15.230993270874</v>
+        <v>15.2309942245483</v>
       </c>
       <c r="H62" t="n">
         <v>177423</v>
@@ -2196,7 +2196,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G63" t="n">
-        <v>15.1736640930176</v>
+        <v>15.1736631393433</v>
       </c>
       <c r="H63" t="n">
         <v>103387</v>
@@ -2225,7 +2225,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G64" t="n">
-        <v>14.9634485244751</v>
+        <v>14.9634494781494</v>
       </c>
       <c r="H64" t="n">
         <v>72487</v>
@@ -2254,7 +2254,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G65" t="n">
-        <v>15.7469758987427</v>
+        <v>15.746973991394</v>
       </c>
       <c r="H65" t="n">
         <v>163756</v>
@@ -2312,7 +2312,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G67" t="n">
-        <v>15.230993270874</v>
+        <v>15.2309942245483</v>
       </c>
       <c r="H67" t="n">
         <v>105026</v>
@@ -2370,7 +2370,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G69" t="n">
-        <v>15.3552131652832</v>
+        <v>15.3552122116089</v>
       </c>
       <c r="H69" t="n">
         <v>141327</v>
@@ -2399,7 +2399,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G70" t="n">
-        <v>15.3361015319824</v>
+        <v>15.3361005783081</v>
       </c>
       <c r="H70" t="n">
         <v>85001</v>
@@ -2428,7 +2428,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G71" t="n">
-        <v>15.0972213745117</v>
+        <v>15.097222328186</v>
       </c>
       <c r="H71" t="n">
         <v>210329</v>
@@ -2457,7 +2457,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G72" t="n">
-        <v>14.6003513336182</v>
+        <v>14.6003503799438</v>
       </c>
       <c r="H72" t="n">
         <v>144220</v>
@@ -2486,7 +2486,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G73" t="n">
-        <v>14.3519163131714</v>
+        <v>14.3519172668457</v>
       </c>
       <c r="H73" t="n">
         <v>172203</v>
@@ -2515,7 +2515,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G74" t="n">
-        <v>14.3136959075928</v>
+        <v>14.3136949539185</v>
       </c>
       <c r="H74" t="n">
         <v>173782</v>
@@ -2544,7 +2544,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G75" t="n">
-        <v>14.1894779205322</v>
+        <v>14.1894788742065</v>
       </c>
       <c r="H75" t="n">
         <v>121982</v>
@@ -2660,7 +2660,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G79" t="n">
-        <v>13.8646001815796</v>
+        <v>13.8646011352539</v>
       </c>
       <c r="H79" t="n">
         <v>226264</v>
@@ -2718,7 +2718,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="n">
-        <v>14.3328056335449</v>
+        <v>14.3328065872192</v>
       </c>
       <c r="H81" t="n">
         <v>137258</v>
@@ -2892,7 +2892,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G87" t="n">
-        <v>13.6448316574097</v>
+        <v>13.644829750061</v>
       </c>
       <c r="H87" t="n">
         <v>355963</v>
@@ -2921,7 +2921,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G88" t="n">
-        <v>14.6003513336182</v>
+        <v>14.6003503799438</v>
       </c>
       <c r="H88" t="n">
         <v>499133</v>
@@ -2950,7 +2950,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G89" t="n">
-        <v>15.0303363800049</v>
+        <v>15.0303354263306</v>
       </c>
       <c r="H89" t="n">
         <v>401988</v>
@@ -3066,7 +3066,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G93" t="n">
-        <v>14.6767930984497</v>
+        <v>14.6767921447754</v>
       </c>
       <c r="H93" t="n">
         <v>110219</v>
@@ -3095,7 +3095,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G94" t="n">
-        <v>14.6003513336182</v>
+        <v>14.6003503799438</v>
       </c>
       <c r="H94" t="n">
         <v>65667</v>
@@ -3124,7 +3124,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G95" t="n">
-        <v>14.199031829834</v>
+        <v>14.1990327835083</v>
       </c>
       <c r="H95" t="n">
         <v>59537</v>
@@ -3153,7 +3153,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>14.6194610595703</v>
+        <v>14.6194620132446</v>
       </c>
       <c r="H96" t="n">
         <v>186490</v>
@@ -3182,7 +3182,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G97" t="n">
-        <v>14.8678979873657</v>
+        <v>14.8678970336914</v>
       </c>
       <c r="H97" t="n">
         <v>106899</v>
@@ -3211,7 +3211,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G98" t="n">
-        <v>14.8678979873657</v>
+        <v>14.8678970336914</v>
       </c>
       <c r="H98" t="n">
         <v>69896</v>
@@ -3240,7 +3240,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G99" t="n">
-        <v>14.9347829818726</v>
+        <v>14.9347839355469</v>
       </c>
       <c r="H99" t="n">
         <v>117392</v>
@@ -3269,7 +3269,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G100" t="n">
-        <v>14.9347829818726</v>
+        <v>14.9347839355469</v>
       </c>
       <c r="H100" t="n">
         <v>95381</v>
@@ -3298,7 +3298,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G101" t="n">
-        <v>15.326548576355</v>
+        <v>15.3265476226807</v>
       </c>
       <c r="H101" t="n">
         <v>177567</v>
@@ -3414,7 +3414,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G105" t="n">
-        <v>14.5907964706421</v>
+        <v>14.5907974243164</v>
       </c>
       <c r="H105" t="n">
         <v>112390</v>
@@ -3443,7 +3443,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G106" t="n">
-        <v>14.2754745483398</v>
+        <v>14.2754735946655</v>
       </c>
       <c r="H106" t="n">
         <v>86836</v>
@@ -3472,7 +3472,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G107" t="n">
-        <v>14.6576833724976</v>
+        <v>14.6576824188232</v>
       </c>
       <c r="H107" t="n">
         <v>112801</v>
@@ -3501,7 +3501,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G108" t="n">
-        <v>14.7627897262573</v>
+        <v>14.7627906799316</v>
       </c>
       <c r="H108" t="n">
         <v>44432</v>
@@ -3530,7 +3530,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G109" t="n">
-        <v>14.8487873077393</v>
+        <v>14.8487854003906</v>
       </c>
       <c r="H109" t="n">
         <v>53044</v>
@@ -3559,7 +3559,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G110" t="n">
-        <v>15.0876665115356</v>
+        <v>15.08766746521</v>
       </c>
       <c r="H110" t="n">
         <v>72044</v>
@@ -3588,7 +3588,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G111" t="n">
-        <v>14.9443387985229</v>
+        <v>14.9443378448486</v>
       </c>
       <c r="H111" t="n">
         <v>83241</v>
@@ -3617,7 +3617,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G112" t="n">
-        <v>14.6481275558472</v>
+        <v>14.6481266021729</v>
       </c>
       <c r="H112" t="n">
         <v>60854</v>
@@ -3733,7 +3733,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G116" t="n">
-        <v>14.4570226669312</v>
+        <v>14.4570236206055</v>
       </c>
       <c r="H116" t="n">
         <v>75449</v>
@@ -3762,7 +3762,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G117" t="n">
-        <v>14.4474687576294</v>
+        <v>14.4474668502808</v>
       </c>
       <c r="H117" t="n">
         <v>75827</v>
@@ -3791,7 +3791,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G118" t="n">
-        <v>14.0461483001709</v>
+        <v>14.0461492538452</v>
       </c>
       <c r="H118" t="n">
         <v>88132</v>
@@ -3849,7 +3849,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>13.7594928741455</v>
+        <v>13.7594938278198</v>
       </c>
       <c r="H120" t="n">
         <v>41310</v>
@@ -3907,7 +3907,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G122" t="n">
-        <v>13.9314880371094</v>
+        <v>13.9314870834351</v>
       </c>
       <c r="H122" t="n">
         <v>58966</v>
@@ -3936,7 +3936,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G123" t="n">
-        <v>13.7021617889404</v>
+        <v>13.7021627426147</v>
       </c>
       <c r="H123" t="n">
         <v>29257</v>
@@ -4052,7 +4052,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G127" t="n">
-        <v>14.9634485244751</v>
+        <v>14.9634494781494</v>
       </c>
       <c r="H127" t="n">
         <v>166475</v>
@@ -4081,7 +4081,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G128" t="n">
-        <v>14.8870067596436</v>
+        <v>14.8870077133179</v>
       </c>
       <c r="H128" t="n">
         <v>40404</v>
@@ -4168,7 +4168,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G131" t="n">
-        <v>15.0876665115356</v>
+        <v>15.08766746521</v>
       </c>
       <c r="H131" t="n">
         <v>223782</v>
@@ -4197,7 +4197,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G132" t="n">
-        <v>15.1258869171143</v>
+        <v>15.1258878707886</v>
       </c>
       <c r="H132" t="n">
         <v>58545</v>
@@ -4226,7 +4226,7 @@
         <v>15.75</v>
       </c>
       <c r="G133" t="n">
-        <v>15.0494451522827</v>
+        <v>15.049446105957</v>
       </c>
       <c r="H133" t="n">
         <v>54662</v>
@@ -4342,7 +4342,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G137" t="n">
-        <v>15.1736640930176</v>
+        <v>15.1736631393433</v>
       </c>
       <c r="H137" t="n">
         <v>135405</v>
@@ -4429,7 +4429,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G140" t="n">
-        <v>16.1865139007568</v>
+        <v>16.1865158081055</v>
       </c>
       <c r="H140" t="n">
         <v>143796</v>
@@ -4487,7 +4487,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G142" t="n">
-        <v>16.9795989990234</v>
+        <v>16.9795970916748</v>
       </c>
       <c r="H142" t="n">
         <v>321463</v>
@@ -4661,7 +4661,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G148" t="n">
-        <v>15.8425273895264</v>
+        <v>15.8425283432007</v>
       </c>
       <c r="H148" t="n">
         <v>256187</v>
@@ -4690,7 +4690,7 @@
         <v>16.6100006103516</v>
       </c>
       <c r="G149" t="n">
-        <v>15.8711929321289</v>
+        <v>15.8711938858032</v>
       </c>
       <c r="H149" t="n">
         <v>130015</v>
@@ -4719,7 +4719,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G150" t="n">
-        <v>15.6418695449829</v>
+        <v>15.6418685913086</v>
       </c>
       <c r="H150" t="n">
         <v>102652</v>
@@ -4748,7 +4748,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G151" t="n">
-        <v>16.2056255340576</v>
+        <v>16.205623626709</v>
       </c>
       <c r="H151" t="n">
         <v>92236</v>
@@ -4835,7 +4835,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>17.3426933288574</v>
+        <v>17.3426952362061</v>
       </c>
       <c r="H154" t="n">
         <v>130344</v>
@@ -4864,7 +4864,7 @@
         <v>18.25</v>
       </c>
       <c r="G155" t="n">
-        <v>17.4382457733154</v>
+        <v>17.4382476806641</v>
       </c>
       <c r="H155" t="n">
         <v>175492</v>
@@ -4893,7 +4893,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G156" t="n">
-        <v>17.6962356567383</v>
+        <v>17.6962394714355</v>
       </c>
       <c r="H156" t="n">
         <v>187911</v>
@@ -4980,7 +4980,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G159" t="n">
-        <v>17.3904705047607</v>
+        <v>17.3904724121094</v>
       </c>
       <c r="H159" t="n">
         <v>70593</v>
@@ -5009,7 +5009,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G160" t="n">
-        <v>17.3904705047607</v>
+        <v>17.3904724121094</v>
       </c>
       <c r="H160" t="n">
         <v>78063</v>
@@ -5067,7 +5067,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G162" t="n">
-        <v>17.5815773010254</v>
+        <v>17.5815753936768</v>
       </c>
       <c r="H162" t="n">
         <v>61690</v>
@@ -5096,7 +5096,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G163" t="n">
-        <v>17.2089214324951</v>
+        <v>17.2089233398438</v>
       </c>
       <c r="H163" t="n">
         <v>50813</v>
@@ -5125,7 +5125,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G164" t="n">
-        <v>17.5529098510742</v>
+        <v>17.5529117584229</v>
       </c>
       <c r="H164" t="n">
         <v>38762</v>
@@ -5183,7 +5183,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>17.8204555511475</v>
+        <v>17.8204574584961</v>
       </c>
       <c r="H166" t="n">
         <v>70506</v>
@@ -5212,7 +5212,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G167" t="n">
-        <v>18.231330871582</v>
+        <v>18.2313289642334</v>
       </c>
       <c r="H167" t="n">
         <v>148047</v>
@@ -5299,7 +5299,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G170" t="n">
-        <v>18.9001941680908</v>
+        <v>18.9001922607422</v>
       </c>
       <c r="H170" t="n">
         <v>196771</v>
@@ -5328,7 +5328,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G171" t="n">
-        <v>18.7664203643799</v>
+        <v>18.7664184570312</v>
       </c>
       <c r="H171" t="n">
         <v>104982</v>
@@ -5415,7 +5415,7 @@
         <v>18.7700004577637</v>
       </c>
       <c r="G174" t="n">
-        <v>17.935115814209</v>
+        <v>17.9351177215576</v>
       </c>
       <c r="H174" t="n">
         <v>228634</v>
@@ -5473,7 +5473,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>17.7726783752441</v>
+        <v>17.7726802825928</v>
       </c>
       <c r="H176" t="n">
         <v>132691</v>
@@ -5531,7 +5531,7 @@
         <v>18.75</v>
       </c>
       <c r="G178" t="n">
-        <v>17.9160060882568</v>
+        <v>17.9160079956055</v>
       </c>
       <c r="H178" t="n">
         <v>107089</v>
@@ -5560,7 +5560,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G179" t="n">
-        <v>18.8524188995361</v>
+        <v>18.8524150848389</v>
       </c>
       <c r="H179" t="n">
         <v>160303</v>
@@ -5589,7 +5589,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G180" t="n">
-        <v>18.7664203643799</v>
+        <v>18.7664184570312</v>
       </c>
       <c r="H180" t="n">
         <v>186766</v>
@@ -5618,7 +5618,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G181" t="n">
-        <v>18.8237533569336</v>
+        <v>18.823751449585</v>
       </c>
       <c r="H181" t="n">
         <v>95801</v>
@@ -5647,7 +5647,7 @@
         <v>18.75</v>
       </c>
       <c r="G182" t="n">
-        <v>17.9160060882568</v>
+        <v>17.9160079956055</v>
       </c>
       <c r="H182" t="n">
         <v>737639</v>
@@ -5763,7 +5763,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G186" t="n">
-        <v>16.6833839416504</v>
+        <v>16.683385848999</v>
       </c>
       <c r="H186" t="n">
         <v>219917</v>
@@ -5792,7 +5792,7 @@
         <v>18</v>
       </c>
       <c r="G187" t="n">
-        <v>17.1993675231934</v>
+        <v>17.199369430542</v>
       </c>
       <c r="H187" t="n">
         <v>168778</v>
@@ -5821,7 +5821,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G188" t="n">
-        <v>17.658016204834</v>
+        <v>17.6580142974854</v>
       </c>
       <c r="H188" t="n">
         <v>106658</v>
@@ -5850,7 +5850,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G189" t="n">
-        <v>17.658016204834</v>
+        <v>17.6580142974854</v>
       </c>
       <c r="H189" t="n">
         <v>195062</v>
@@ -5908,7 +5908,7 @@
         <v>17.75</v>
       </c>
       <c r="G191" t="n">
-        <v>16.960485458374</v>
+        <v>16.9604873657227</v>
       </c>
       <c r="H191" t="n">
         <v>902705</v>
@@ -5937,7 +5937,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G192" t="n">
-        <v>16.5305023193359</v>
+        <v>16.5305042266846</v>
       </c>
       <c r="H192" t="n">
         <v>303536</v>
@@ -5966,7 +5966,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G193" t="n">
-        <v>16.4540615081787</v>
+        <v>16.4540596008301</v>
       </c>
       <c r="H193" t="n">
         <v>194779</v>
@@ -5995,7 +5995,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>16.3871746063232</v>
+        <v>16.3871726989746</v>
       </c>
       <c r="H194" t="n">
         <v>289758</v>
@@ -6053,7 +6053,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G196" t="n">
-        <v>16.2056255340576</v>
+        <v>16.205623626709</v>
       </c>
       <c r="H196" t="n">
         <v>122290</v>
@@ -6140,7 +6140,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G199" t="n">
-        <v>16.6069450378418</v>
+        <v>16.6069431304932</v>
       </c>
       <c r="H199" t="n">
         <v>89821</v>
@@ -6169,7 +6169,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G200" t="n">
-        <v>16.6833839416504</v>
+        <v>16.683385848999</v>
       </c>
       <c r="H200" t="n">
         <v>78475</v>
@@ -6256,7 +6256,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G203" t="n">
-        <v>16.7407169342041</v>
+        <v>16.7407188415527</v>
       </c>
       <c r="H203" t="n">
         <v>93120</v>
@@ -6314,7 +6314,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G205" t="n">
-        <v>17.0369281768799</v>
+        <v>17.0369262695312</v>
       </c>
       <c r="H205" t="n">
         <v>107074</v>
@@ -6372,7 +6372,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G207" t="n">
-        <v>16.6547222137451</v>
+        <v>16.6547183990479</v>
       </c>
       <c r="H207" t="n">
         <v>154640</v>
@@ -6575,7 +6575,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G214" t="n">
-        <v>16.6642742156982</v>
+        <v>16.6642761230469</v>
       </c>
       <c r="H214" t="n">
         <v>584108</v>
@@ -6604,7 +6604,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G215" t="n">
-        <v>17.4764709472656</v>
+        <v>17.476469039917</v>
       </c>
       <c r="H215" t="n">
         <v>330056</v>
@@ -6662,7 +6662,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G217" t="n">
-        <v>18.231330871582</v>
+        <v>18.2313289642334</v>
       </c>
       <c r="H217" t="n">
         <v>171919</v>
@@ -6749,7 +6749,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G220" t="n">
-        <v>18.0020065307617</v>
+        <v>18.0020046234131</v>
       </c>
       <c r="H220" t="n">
         <v>388714</v>
@@ -6778,7 +6778,7 @@
         <v>19.2700004577637</v>
       </c>
       <c r="G221" t="n">
-        <v>18.5309085845947</v>
+        <v>18.5309104919434</v>
       </c>
       <c r="H221" t="n">
         <v>86313</v>
@@ -6807,7 +6807,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G222" t="n">
-        <v>18.5789890289307</v>
+        <v>18.5789909362793</v>
       </c>
       <c r="H222" t="n">
         <v>75028</v>
@@ -6836,7 +6836,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G223" t="n">
-        <v>18.6559219360352</v>
+        <v>18.6559238433838</v>
       </c>
       <c r="H223" t="n">
         <v>117863</v>
@@ -6865,7 +6865,7 @@
         <v>19.25</v>
       </c>
       <c r="G224" t="n">
-        <v>18.5116767883301</v>
+        <v>18.5116748809814</v>
       </c>
       <c r="H224" t="n">
         <v>52689</v>
@@ -6894,7 +6894,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G225" t="n">
-        <v>18.6559219360352</v>
+        <v>18.6559238433838</v>
       </c>
       <c r="H225" t="n">
         <v>62425</v>
@@ -7010,7 +7010,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G229" t="n">
-        <v>18.8097858428955</v>
+        <v>18.8097877502441</v>
       </c>
       <c r="H229" t="n">
         <v>69687</v>
@@ -7242,7 +7242,7 @@
         <v>20.5</v>
       </c>
       <c r="G237" t="n">
-        <v>19.7137317657471</v>
+        <v>19.7137336730957</v>
       </c>
       <c r="H237" t="n">
         <v>224683</v>
@@ -7300,7 +7300,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>19.3290729522705</v>
+        <v>19.3290748596191</v>
       </c>
       <c r="H239" t="n">
         <v>78255</v>
@@ -7387,7 +7387,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>19.4252414703369</v>
+        <v>19.4252376556396</v>
       </c>
       <c r="H242" t="n">
         <v>219460</v>
@@ -7416,7 +7416,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G243" t="n">
-        <v>19.0405807495117</v>
+        <v>19.0405788421631</v>
       </c>
       <c r="H243" t="n">
         <v>51065</v>
@@ -7503,7 +7503,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G246" t="n">
-        <v>17.8481388092041</v>
+        <v>17.8481407165527</v>
       </c>
       <c r="H246" t="n">
         <v>191126</v>
@@ -7561,7 +7561,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G248" t="n">
-        <v>18.5789890289307</v>
+        <v>18.5789909362793</v>
       </c>
       <c r="H248" t="n">
         <v>83004</v>
@@ -7706,7 +7706,7 @@
         <v>19.4099998474121</v>
       </c>
       <c r="G253" t="n">
-        <v>18.6655406951904</v>
+        <v>18.6655387878418</v>
       </c>
       <c r="H253" t="n">
         <v>58888</v>
@@ -7822,7 +7822,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G257" t="n">
-        <v>19.6944999694824</v>
+        <v>19.6944980621338</v>
       </c>
       <c r="H257" t="n">
         <v>62964</v>
@@ -7909,7 +7909,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G260" t="n">
-        <v>19.5598678588867</v>
+        <v>19.5598697662354</v>
       </c>
       <c r="H260" t="n">
         <v>165590</v>
@@ -7938,7 +7938,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G261" t="n">
-        <v>19.2713756561279</v>
+        <v>19.2713775634766</v>
       </c>
       <c r="H261" t="n">
         <v>226076</v>
@@ -7996,7 +7996,7 @@
         <v>20.5</v>
       </c>
       <c r="G263" t="n">
-        <v>19.7137317657471</v>
+        <v>19.7137336730957</v>
       </c>
       <c r="H263" t="n">
         <v>91506</v>
@@ -8025,7 +8025,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G264" t="n">
-        <v>19.4829387664795</v>
+        <v>19.4829368591309</v>
       </c>
       <c r="H264" t="n">
         <v>113210</v>
@@ -8083,7 +8083,7 @@
         <v>20.5</v>
       </c>
       <c r="G266" t="n">
-        <v>19.7137317657471</v>
+        <v>19.7137336730957</v>
       </c>
       <c r="H266" t="n">
         <v>56249</v>
@@ -8112,7 +8112,7 @@
         <v>20.5</v>
       </c>
       <c r="G267" t="n">
-        <v>19.7137317657471</v>
+        <v>19.7137336730957</v>
       </c>
       <c r="H267" t="n">
         <v>68211</v>
@@ -8257,7 +8257,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G272" t="n">
-        <v>17.5019474029541</v>
+        <v>17.5019493103027</v>
       </c>
       <c r="H272" t="n">
         <v>364369</v>
@@ -8286,7 +8286,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G273" t="n">
-        <v>17.5692653656006</v>
+        <v>17.569263458252</v>
       </c>
       <c r="H273" t="n">
         <v>162056</v>
@@ -8344,7 +8344,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G275" t="n">
-        <v>18.2904987335205</v>
+        <v>18.2904968261719</v>
       </c>
       <c r="H275" t="n">
         <v>226073</v>
@@ -8373,7 +8373,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G276" t="n">
-        <v>18.5020580291748</v>
+        <v>18.5020599365234</v>
       </c>
       <c r="H276" t="n">
         <v>314121</v>
@@ -8460,7 +8460,7 @@
         <v>19.4099998474121</v>
       </c>
       <c r="G279" t="n">
-        <v>18.6655406951904</v>
+        <v>18.6655387878418</v>
       </c>
       <c r="H279" t="n">
         <v>51561</v>
@@ -8489,7 +8489,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G280" t="n">
-        <v>18.6559219360352</v>
+        <v>18.6559238433838</v>
       </c>
       <c r="H280" t="n">
         <v>71432</v>
@@ -8576,7 +8576,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G283" t="n">
-        <v>17.5981101989746</v>
+        <v>17.5981121063232</v>
       </c>
       <c r="H283" t="n">
         <v>79763</v>
@@ -8605,7 +8605,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G284" t="n">
-        <v>17.540412902832</v>
+        <v>17.5404148101807</v>
       </c>
       <c r="H284" t="n">
         <v>101821</v>
@@ -8663,7 +8663,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G286" t="n">
-        <v>17.059591293335</v>
+        <v>17.0595932006836</v>
       </c>
       <c r="H286" t="n">
         <v>83846</v>
@@ -8779,7 +8779,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G290" t="n">
-        <v>17.1942195892334</v>
+        <v>17.194221496582</v>
       </c>
       <c r="H290" t="n">
         <v>97158</v>
@@ -8808,7 +8808,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G291" t="n">
-        <v>17.4923324584961</v>
+        <v>17.4923305511475</v>
       </c>
       <c r="H291" t="n">
         <v>98792</v>
@@ -8837,7 +8837,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G292" t="n">
-        <v>17.5692653656006</v>
+        <v>17.569263458252</v>
       </c>
       <c r="H292" t="n">
         <v>70023</v>
@@ -8866,7 +8866,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G293" t="n">
-        <v>17.2134532928467</v>
+        <v>17.213451385498</v>
       </c>
       <c r="H293" t="n">
         <v>97852</v>
@@ -9098,7 +9098,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G301" t="n">
-        <v>16.4441375732422</v>
+        <v>16.4441394805908</v>
       </c>
       <c r="H301" t="n">
         <v>93310</v>
@@ -9417,7 +9417,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>15.4824924468994</v>
+        <v>15.4824934005737</v>
       </c>
       <c r="H312" t="n">
         <v>47778</v>
@@ -9475,7 +9475,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G314" t="n">
-        <v>15.6555891036987</v>
+        <v>15.6555881500244</v>
       </c>
       <c r="H314" t="n">
         <v>70184</v>
@@ -9504,7 +9504,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G315" t="n">
-        <v>15.8479175567627</v>
+        <v>15.8479166030884</v>
       </c>
       <c r="H315" t="n">
         <v>74847</v>
@@ -9533,7 +9533,7 @@
         <v>16.2700004577637</v>
       </c>
       <c r="G316" t="n">
-        <v>15.6459722518921</v>
+        <v>15.6459732055664</v>
       </c>
       <c r="H316" t="n">
         <v>152152</v>
@@ -9649,7 +9649,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G320" t="n">
-        <v>14.318902015686</v>
+        <v>14.3189010620117</v>
       </c>
       <c r="H320" t="n">
         <v>84956</v>
@@ -9678,7 +9678,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G321" t="n">
-        <v>14.4631471633911</v>
+        <v>14.4631481170654</v>
       </c>
       <c r="H321" t="n">
         <v>76846</v>
@@ -9823,7 +9823,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>14.1361875534058</v>
+        <v>14.1361885070801</v>
       </c>
       <c r="H326" t="n">
         <v>132397</v>
@@ -9852,7 +9852,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G327" t="n">
-        <v>14.0881061553955</v>
+        <v>14.0881052017212</v>
       </c>
       <c r="H327" t="n">
         <v>66396</v>
@@ -9881,7 +9881,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G328" t="n">
-        <v>14.2227373123169</v>
+        <v>14.2227363586426</v>
       </c>
       <c r="H328" t="n">
         <v>104116</v>
@@ -10026,7 +10026,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G333" t="n">
-        <v>12.8572006225586</v>
+        <v>12.8571996688843</v>
       </c>
       <c r="H333" t="n">
         <v>104403</v>
@@ -10055,7 +10055,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G334" t="n">
-        <v>12.674488067627</v>
+        <v>12.6744890213013</v>
       </c>
       <c r="H334" t="n">
         <v>59858</v>
@@ -10316,7 +10316,7 @@
         <v>14.0100002288818</v>
       </c>
       <c r="G343" t="n">
-        <v>13.4726533889771</v>
+        <v>13.4726543426514</v>
       </c>
       <c r="H343" t="n">
         <v>569136</v>
@@ -10345,7 +10345,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G344" t="n">
-        <v>13.0399141311646</v>
+        <v>13.0399131774902</v>
       </c>
       <c r="H344" t="n">
         <v>146201</v>
@@ -10403,7 +10403,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G346" t="n">
-        <v>14.5016136169434</v>
+        <v>14.5016145706177</v>
       </c>
       <c r="H346" t="n">
         <v>237267</v>
@@ -10461,7 +10461,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G348" t="n">
-        <v>14.2227373123169</v>
+        <v>14.2227363586426</v>
       </c>
       <c r="H348" t="n">
         <v>121936</v>
@@ -10519,7 +10519,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G350" t="n">
-        <v>14.2708187103271</v>
+        <v>14.2708196640015</v>
       </c>
       <c r="H350" t="n">
         <v>157799</v>
@@ -10577,7 +10577,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G352" t="n">
-        <v>14.2515859603882</v>
+        <v>14.2515869140625</v>
       </c>
       <c r="H352" t="n">
         <v>74240</v>
@@ -10606,7 +10606,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G353" t="n">
-        <v>14.3092851638794</v>
+        <v>14.3092861175537</v>
       </c>
       <c r="H353" t="n">
         <v>104165</v>
@@ -10635,7 +10635,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G354" t="n">
-        <v>14.2996673583984</v>
+        <v>14.2996683120728</v>
       </c>
       <c r="H354" t="n">
         <v>87931</v>
@@ -10693,7 +10693,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G356" t="n">
-        <v>13.7322978973389</v>
+        <v>13.7322969436646</v>
       </c>
       <c r="H356" t="n">
         <v>217186</v>
@@ -10809,7 +10809,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G360" t="n">
-        <v>13.2707071304321</v>
+        <v>13.2707080841064</v>
       </c>
       <c r="H360" t="n">
         <v>139158</v>
@@ -10896,7 +10896,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G363" t="n">
-        <v>13.1841602325439</v>
+        <v>13.1841592788696</v>
       </c>
       <c r="H363" t="n">
         <v>159187</v>
@@ -10925,7 +10925,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G364" t="n">
-        <v>13.4341869354248</v>
+        <v>13.4341878890991</v>
       </c>
       <c r="H364" t="n">
         <v>99374</v>
@@ -11012,7 +11012,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G367" t="n">
-        <v>13.5495853424072</v>
+        <v>13.5495862960815</v>
       </c>
       <c r="H367" t="n">
         <v>174963</v>
@@ -11070,7 +11070,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G369" t="n">
-        <v>14.674711227417</v>
+        <v>14.6747102737427</v>
       </c>
       <c r="H369" t="n">
         <v>228319</v>
@@ -11128,7 +11128,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G371" t="n">
-        <v>15.6844367980957</v>
+        <v>15.6844387054443</v>
       </c>
       <c r="H371" t="n">
         <v>353221</v>
@@ -11244,7 +11244,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G375" t="n">
-        <v>14.8381910324097</v>
+        <v>14.8381900787354</v>
       </c>
       <c r="H375" t="n">
         <v>137149</v>
@@ -11273,7 +11273,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G376" t="n">
-        <v>15.0305185317993</v>
+        <v>15.0305194854736</v>
       </c>
       <c r="H376" t="n">
         <v>110938</v>
@@ -11331,7 +11331,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G378" t="n">
-        <v>14.9632043838501</v>
+        <v>14.9632034301758</v>
       </c>
       <c r="H378" t="n">
         <v>149811</v>
@@ -11360,7 +11360,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G379" t="n">
-        <v>14.5016136169434</v>
+        <v>14.5016145706177</v>
       </c>
       <c r="H379" t="n">
         <v>337572</v>
@@ -11389,7 +11389,7 @@
         <v>15.0900001525879</v>
       </c>
       <c r="G380" t="n">
-        <v>14.5112314224243</v>
+        <v>14.51123046875</v>
       </c>
       <c r="H380" t="n">
         <v>88556</v>
@@ -11534,7 +11534,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G385" t="n">
-        <v>14.4439153671265</v>
+        <v>14.4439163208008</v>
       </c>
       <c r="H385" t="n">
         <v>156312</v>
@@ -11563,7 +11563,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G386" t="n">
-        <v>14.0977220535278</v>
+        <v>14.0977230072021</v>
       </c>
       <c r="H386" t="n">
         <v>236798</v>
@@ -11592,7 +11592,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G387" t="n">
-        <v>14.1361875534058</v>
+        <v>14.1361885070801</v>
       </c>
       <c r="H387" t="n">
         <v>123369</v>
@@ -11621,7 +11621,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G388" t="n">
-        <v>13.982325553894</v>
+        <v>13.9823265075684</v>
       </c>
       <c r="H388" t="n">
         <v>99895</v>
@@ -11679,7 +11679,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G390" t="n">
-        <v>14.4631471633911</v>
+        <v>14.4631481170654</v>
       </c>
       <c r="H390" t="n">
         <v>99312</v>
@@ -11708,7 +11708,7 @@
         <v>14.2700004577637</v>
       </c>
       <c r="G391" t="n">
-        <v>13.7226819992065</v>
+        <v>13.7226810455322</v>
       </c>
       <c r="H391" t="n">
         <v>186975</v>
@@ -11795,7 +11795,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G394" t="n">
-        <v>13.7419147491455</v>
+        <v>13.7419137954712</v>
       </c>
       <c r="H394" t="n">
         <v>128563</v>
@@ -11911,7 +11911,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G398" t="n">
-        <v>13.3668727874756</v>
+        <v>13.3668718338013</v>
       </c>
       <c r="H398" t="n">
         <v>212475</v>
@@ -11940,7 +11940,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G399" t="n">
-        <v>14.0592575073242</v>
+        <v>14.0592565536499</v>
       </c>
       <c r="H399" t="n">
         <v>307261</v>
@@ -12085,7 +12085,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G404" t="n">
-        <v>13.3764886856079</v>
+        <v>13.3764896392822</v>
       </c>
       <c r="H404" t="n">
         <v>147194</v>
@@ -12549,7 +12549,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G420" t="n">
-        <v>14.9632043838501</v>
+        <v>14.9632034301758</v>
       </c>
       <c r="H420" t="n">
         <v>161886</v>
@@ -12578,7 +12578,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G421" t="n">
-        <v>14.5016136169434</v>
+        <v>14.5016145706177</v>
       </c>
       <c r="H421" t="n">
         <v>101945</v>
@@ -12607,7 +12607,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G422" t="n">
-        <v>14.3092851638794</v>
+        <v>14.3092861175537</v>
       </c>
       <c r="H422" t="n">
         <v>102639</v>
@@ -12665,7 +12665,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G424" t="n">
-        <v>14.0688743591309</v>
+        <v>14.0688734054565</v>
       </c>
       <c r="H424" t="n">
         <v>101301</v>
@@ -12781,7 +12781,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G428" t="n">
-        <v>13.8188457489014</v>
+        <v>13.8188447952271</v>
       </c>
       <c r="H428" t="n">
         <v>206029</v>
@@ -12868,7 +12868,7 @@
         <v>14.1899995803833</v>
       </c>
       <c r="G431" t="n">
-        <v>13.6457490921021</v>
+        <v>13.6457500457764</v>
       </c>
       <c r="H431" t="n">
         <v>223671</v>
@@ -12926,7 +12926,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G433" t="n">
-        <v>12.645637512207</v>
+        <v>12.6456384658813</v>
       </c>
       <c r="H433" t="n">
         <v>771950</v>
@@ -12955,7 +12955,7 @@
         <v>13.25</v>
       </c>
       <c r="G434" t="n">
-        <v>12.7418022155762</v>
+        <v>12.7418031692505</v>
       </c>
       <c r="H434" t="n">
         <v>207043</v>
@@ -12984,7 +12984,7 @@
         <v>13.25</v>
       </c>
       <c r="G435" t="n">
-        <v>12.7418022155762</v>
+        <v>12.7418031692505</v>
       </c>
       <c r="H435" t="n">
         <v>214799</v>
@@ -13042,7 +13042,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G437" t="n">
-        <v>12.7033376693726</v>
+        <v>12.7033367156982</v>
       </c>
       <c r="H437" t="n">
         <v>188482</v>
@@ -13071,7 +13071,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G438" t="n">
-        <v>12.645637512207</v>
+        <v>12.6456384658813</v>
       </c>
       <c r="H438" t="n">
         <v>150121</v>
@@ -13100,7 +13100,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G439" t="n">
-        <v>12.8572006225586</v>
+        <v>12.8571996688843</v>
       </c>
       <c r="H439" t="n">
         <v>90236</v>
@@ -13187,7 +13187,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G442" t="n">
-        <v>12.9725971221924</v>
+        <v>12.9725980758667</v>
       </c>
       <c r="H442" t="n">
         <v>207392</v>
@@ -13274,7 +13274,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G445" t="n">
-        <v>12.7802677154541</v>
+        <v>12.7802686691284</v>
       </c>
       <c r="H445" t="n">
         <v>146927</v>
@@ -13332,7 +13332,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G447" t="n">
-        <v>12.7033376693726</v>
+        <v>12.7033367156982</v>
       </c>
       <c r="H447" t="n">
         <v>82919</v>
@@ -13390,7 +13390,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G449" t="n">
-        <v>12.8091173171997</v>
+        <v>12.809118270874</v>
       </c>
       <c r="H449" t="n">
         <v>66508</v>
@@ -13448,7 +13448,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G451" t="n">
-        <v>12.9629812240601</v>
+        <v>12.9629802703857</v>
       </c>
       <c r="H451" t="n">
         <v>102016</v>
@@ -13506,7 +13506,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G453" t="n">
-        <v>11.9244041442871</v>
+        <v>11.9244031906128</v>
       </c>
       <c r="H453" t="n">
         <v>236491</v>
@@ -13709,7 +13709,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G460" t="n">
-        <v>12.1744327545166</v>
+        <v>12.1744318008423</v>
       </c>
       <c r="H460" t="n">
         <v>97426</v>
@@ -13738,7 +13738,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G461" t="n">
-        <v>12.1552000045776</v>
+        <v>12.1551990509033</v>
       </c>
       <c r="H461" t="n">
         <v>94886</v>
@@ -13796,7 +13796,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G463" t="n">
-        <v>12.0494174957275</v>
+        <v>12.0494165420532</v>
       </c>
       <c r="H463" t="n">
         <v>59080</v>
@@ -13941,7 +13941,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G468" t="n">
-        <v>12.7706518173218</v>
+        <v>12.7706527709961</v>
       </c>
       <c r="H468" t="n">
         <v>76794</v>
@@ -14057,7 +14057,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G472" t="n">
-        <v>13.1841602325439</v>
+        <v>13.1841592788696</v>
       </c>
       <c r="H472" t="n">
         <v>75618</v>
@@ -14115,7 +14115,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G474" t="n">
-        <v>12.7782726287842</v>
+        <v>12.7782716751099</v>
       </c>
       <c r="H474" t="n">
         <v>99354</v>
@@ -14173,7 +14173,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G476" t="n">
-        <v>13.0790510177612</v>
+        <v>13.0790500640869</v>
       </c>
       <c r="H476" t="n">
         <v>88070</v>
@@ -14202,7 +14202,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G477" t="n">
-        <v>12.9141073226929</v>
+        <v>12.9141082763672</v>
       </c>
       <c r="H477" t="n">
         <v>53958</v>
@@ -14231,7 +14231,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G478" t="n">
-        <v>12.4871950149536</v>
+        <v>12.4871940612793</v>
       </c>
       <c r="H478" t="n">
         <v>88793</v>
@@ -14260,7 +14260,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G479" t="n">
-        <v>12.8461885452271</v>
+        <v>12.8461894989014</v>
       </c>
       <c r="H479" t="n">
         <v>56934</v>
@@ -14347,7 +14347,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G482" t="n">
-        <v>12.8073787689209</v>
+        <v>12.8073797225952</v>
       </c>
       <c r="H482" t="n">
         <v>146288</v>
@@ -14695,7 +14695,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G494" t="n">
-        <v>11.3519954681396</v>
+        <v>11.3519945144653</v>
       </c>
       <c r="H494" t="n">
         <v>90980</v>
@@ -14782,7 +14782,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G497" t="n">
-        <v>11.487832069397</v>
+        <v>11.4878311157227</v>
       </c>
       <c r="H497" t="n">
         <v>74033</v>
@@ -14898,7 +14898,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G501" t="n">
-        <v>11.3519954681396</v>
+        <v>11.3519945144653</v>
       </c>
       <c r="H501" t="n">
         <v>72055</v>
@@ -15101,7 +15101,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G508" t="n">
-        <v>11.0803232192993</v>
+        <v>11.0803241729736</v>
       </c>
       <c r="H508" t="n">
         <v>52830</v>
@@ -15217,7 +15217,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G512" t="n">
-        <v>11.0803232192993</v>
+        <v>11.0803241729736</v>
       </c>
       <c r="H512" t="n">
         <v>67037</v>
@@ -15333,7 +15333,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G516" t="n">
-        <v>10.973596572876</v>
+        <v>10.9735956192017</v>
       </c>
       <c r="H516" t="n">
         <v>81818</v>
@@ -15420,7 +15420,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G519" t="n">
-        <v>10.9638929367065</v>
+        <v>10.9638938903809</v>
       </c>
       <c r="H519" t="n">
         <v>97469</v>
@@ -15565,7 +15565,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G524" t="n">
-        <v>10.5854930877686</v>
+        <v>10.5854921340942</v>
       </c>
       <c r="H524" t="n">
         <v>134025</v>
@@ -15623,7 +15623,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G526" t="n">
-        <v>10.381739616394</v>
+        <v>10.3817386627197</v>
       </c>
       <c r="H526" t="n">
         <v>195282</v>
@@ -16087,7 +16087,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G542" t="n">
-        <v>9.67830371856689</v>
+        <v>9.67830467224121</v>
       </c>
       <c r="H542" t="n">
         <v>134678</v>
@@ -16145,7 +16145,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G544" t="n">
-        <v>9.51821136474609</v>
+        <v>9.51821231842041</v>
       </c>
       <c r="H544" t="n">
         <v>80660</v>
@@ -16174,7 +16174,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G545" t="n">
-        <v>9.54731941223145</v>
+        <v>9.54731845855713</v>
       </c>
       <c r="H545" t="n">
         <v>95108</v>
@@ -16319,7 +16319,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G550" t="n">
-        <v>9.24654006958008</v>
+        <v>9.24653911590576</v>
       </c>
       <c r="H550" t="n">
         <v>94988</v>
@@ -16348,7 +16348,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G551" t="n">
-        <v>9.16891956329346</v>
+        <v>9.16891860961914</v>
       </c>
       <c r="H551" t="n">
         <v>135094</v>
@@ -16435,7 +16435,7 @@
         <v>8.91499996185303</v>
       </c>
       <c r="G554" t="n">
-        <v>8.6498327255249</v>
+        <v>8.64983177185059</v>
       </c>
       <c r="H554" t="n">
         <v>131072</v>
@@ -16464,7 +16464,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G555" t="n">
-        <v>9.0815954208374</v>
+        <v>9.08159637451172</v>
       </c>
       <c r="H555" t="n">
         <v>164784</v>
@@ -16493,7 +16493,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G556" t="n">
-        <v>9.09129905700684</v>
+        <v>9.09129810333252</v>
       </c>
       <c r="H556" t="n">
         <v>112117</v>
@@ -16551,7 +16551,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G558" t="n">
-        <v>9.0815954208374</v>
+        <v>9.08159637451172</v>
       </c>
       <c r="H558" t="n">
         <v>76175</v>
@@ -16609,7 +16609,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G560" t="n">
-        <v>9.24654006958008</v>
+        <v>9.24653911590576</v>
       </c>
       <c r="H560" t="n">
         <v>57482</v>
@@ -16638,7 +16638,7 @@
         <v>9.55500030517578</v>
       </c>
       <c r="G561" t="n">
-        <v>9.27079582214355</v>
+        <v>9.27079677581787</v>
       </c>
       <c r="H561" t="n">
         <v>80413</v>
@@ -16783,7 +16783,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G566" t="n">
-        <v>9.15921592712402</v>
+        <v>9.15921688079834</v>
       </c>
       <c r="H566" t="n">
         <v>168859</v>
@@ -16957,7 +16957,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G572" t="n">
-        <v>8.91665267944336</v>
+        <v>8.91665172576904</v>
       </c>
       <c r="H572" t="n">
         <v>55529</v>
@@ -17015,7 +17015,7 @@
         <v>8.90499973297119</v>
       </c>
       <c r="G574" t="n">
-        <v>8.64012908935547</v>
+        <v>8.64013004302979</v>
       </c>
       <c r="H574" t="n">
         <v>288790</v>
@@ -17073,7 +17073,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G576" t="n">
-        <v>8.66438674926758</v>
+        <v>8.66438579559326</v>
       </c>
       <c r="H576" t="n">
         <v>85122</v>
@@ -17160,7 +17160,7 @@
         <v>8.75</v>
       </c>
       <c r="G579" t="n">
-        <v>8.48973941802979</v>
+        <v>8.4897403717041</v>
       </c>
       <c r="H579" t="n">
         <v>77770</v>
@@ -17189,7 +17189,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G580" t="n">
-        <v>8.72260189056396</v>
+        <v>8.72260093688965</v>
       </c>
       <c r="H580" t="n">
         <v>167385</v>
@@ -17276,7 +17276,7 @@
         <v>8.82499980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>8.56250858306885</v>
+        <v>8.56250953674316</v>
       </c>
       <c r="H583" t="n">
         <v>185644</v>
@@ -17305,7 +17305,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G584" t="n">
-        <v>8.80022239685059</v>
+        <v>8.80022144317627</v>
       </c>
       <c r="H584" t="n">
         <v>145712</v>
@@ -17334,7 +17334,7 @@
         <v>8.91499996185303</v>
       </c>
       <c r="G585" t="n">
-        <v>8.6498327255249</v>
+        <v>8.64983177185059</v>
       </c>
       <c r="H585" t="n">
         <v>105376</v>
@@ -17392,7 +17392,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G587" t="n">
-        <v>8.76141166687012</v>
+        <v>8.7614107131958</v>
       </c>
       <c r="H587" t="n">
         <v>110831</v>
@@ -17508,7 +17508,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G591" t="n">
-        <v>8.38786315917969</v>
+        <v>8.387864112854</v>
       </c>
       <c r="H591" t="n">
         <v>209095</v>
@@ -17566,7 +17566,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G593" t="n">
-        <v>8.7420072555542</v>
+        <v>8.74200630187988</v>
       </c>
       <c r="H593" t="n">
         <v>123295</v>
@@ -17624,7 +17624,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>8.56735992431641</v>
+        <v>8.56736087799072</v>
       </c>
       <c r="H595" t="n">
         <v>506056</v>
@@ -17711,7 +17711,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G598" t="n">
-        <v>8.76141166687012</v>
+        <v>8.7614107131958</v>
       </c>
       <c r="H598" t="n">
         <v>275140</v>
@@ -17798,7 +17798,7 @@
         <v>8.47500038146973</v>
       </c>
       <c r="G601" t="n">
-        <v>8.22292041778564</v>
+        <v>8.22291946411133</v>
       </c>
       <c r="H601" t="n">
         <v>238471</v>
@@ -17827,7 +17827,7 @@
         <v>8.28499984741211</v>
       </c>
       <c r="G602" t="n">
-        <v>8.03857135772705</v>
+        <v>8.03857040405273</v>
       </c>
       <c r="H602" t="n">
         <v>639924</v>
@@ -17914,7 +17914,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G605" t="n">
-        <v>7.67472457885742</v>
+        <v>7.67472505569458</v>
       </c>
       <c r="H605" t="n">
         <v>165566</v>
@@ -17943,7 +17943,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G606" t="n">
-        <v>7.46126890182495</v>
+        <v>7.46126842498779</v>
       </c>
       <c r="H606" t="n">
         <v>281631</v>
@@ -18030,7 +18030,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G609" t="n">
-        <v>7.73779153823853</v>
+        <v>7.73779201507568</v>
       </c>
       <c r="H609" t="n">
         <v>85842</v>
@@ -18088,7 +18088,7 @@
         <v>8.00500011444092</v>
       </c>
       <c r="G611" t="n">
-        <v>7.76689958572388</v>
+        <v>7.76689910888672</v>
       </c>
       <c r="H611" t="n">
         <v>68292</v>
@@ -18175,7 +18175,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G614" t="n">
-        <v>7.73779153823853</v>
+        <v>7.73779201507568</v>
       </c>
       <c r="H614" t="n">
         <v>142315</v>
@@ -18204,7 +18204,7 @@
         <v>7.9850001335144</v>
       </c>
       <c r="G615" t="n">
-        <v>7.74749422073364</v>
+        <v>7.7474946975708</v>
       </c>
       <c r="H615" t="n">
         <v>116245</v>
@@ -18262,7 +18262,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G617" t="n">
-        <v>7.95609951019287</v>
+        <v>7.95609855651855</v>
       </c>
       <c r="H617" t="n">
         <v>208602</v>
@@ -18291,7 +18291,7 @@
         <v>8.14500045776367</v>
       </c>
       <c r="G618" t="n">
-        <v>7.90273523330688</v>
+        <v>7.90273571014404</v>
       </c>
       <c r="H618" t="n">
         <v>116291</v>
@@ -18320,7 +18320,7 @@
         <v>8.17500019073486</v>
       </c>
       <c r="G619" t="n">
-        <v>7.93184280395508</v>
+        <v>7.93184328079224</v>
       </c>
       <c r="H619" t="n">
         <v>91476</v>
@@ -18436,7 +18436,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>7.44671487808228</v>
+        <v>7.44671535491943</v>
       </c>
       <c r="H623" t="n">
         <v>226325</v>
@@ -18465,7 +18465,7 @@
         <v>7.64499998092651</v>
       </c>
       <c r="G624" t="n">
-        <v>7.41760683059692</v>
+        <v>7.41760730743408</v>
       </c>
       <c r="H624" t="n">
         <v>275750</v>
@@ -18494,7 +18494,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G625" t="n">
-        <v>7.41275596618652</v>
+        <v>7.41275548934937</v>
       </c>
       <c r="H625" t="n">
         <v>150786</v>
@@ -18581,7 +18581,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>7.31087923049927</v>
+        <v>7.31087875366211</v>
       </c>
       <c r="H628" t="n">
         <v>129823</v>
@@ -18668,7 +18668,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G631" t="n">
-        <v>7.53888940811157</v>
+        <v>7.53888893127441</v>
       </c>
       <c r="H631" t="n">
         <v>91913</v>
@@ -18697,7 +18697,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G632" t="n">
-        <v>7.42245864868164</v>
+        <v>7.42245817184448</v>
       </c>
       <c r="H632" t="n">
         <v>71179</v>
@@ -18726,7 +18726,7 @@
         <v>7.77500009536743</v>
       </c>
       <c r="G633" t="n">
-        <v>7.54374027252197</v>
+        <v>7.54374074935913</v>
       </c>
       <c r="H633" t="n">
         <v>104298</v>
@@ -18755,7 +18755,7 @@
         <v>7.875</v>
       </c>
       <c r="G634" t="n">
-        <v>7.64076566696167</v>
+        <v>7.64076614379883</v>
       </c>
       <c r="H634" t="n">
         <v>86228</v>
@@ -18842,7 +18842,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G637" t="n">
-        <v>7.05861282348633</v>
+        <v>7.05861234664917</v>
       </c>
       <c r="H637" t="n">
         <v>150003</v>
@@ -18900,7 +18900,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>6.84515571594238</v>
+        <v>6.84515619277954</v>
       </c>
       <c r="H639" t="n">
         <v>176664</v>
@@ -18958,7 +18958,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G641" t="n">
-        <v>6.98099231719971</v>
+        <v>6.98099184036255</v>
       </c>
       <c r="H641" t="n">
         <v>147248</v>
@@ -18987,7 +18987,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>7.17989444732666</v>
+        <v>7.17989492416382</v>
       </c>
       <c r="H642" t="n">
         <v>152913</v>
@@ -19277,7 +19277,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G652" t="n">
-        <v>6.96643829345703</v>
+        <v>6.96643781661987</v>
       </c>
       <c r="H652" t="n">
         <v>197817</v>
@@ -19306,7 +19306,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G653" t="n">
-        <v>6.786940574646</v>
+        <v>6.78694105148315</v>
       </c>
       <c r="H653" t="n">
         <v>219932</v>
@@ -19451,7 +19451,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G658" t="n">
-        <v>6.786940574646</v>
+        <v>6.78694105148315</v>
       </c>
       <c r="H658" t="n">
         <v>214637</v>
@@ -19596,7 +19596,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G663" t="n">
-        <v>6.67536163330078</v>
+        <v>6.67536115646362</v>
       </c>
       <c r="H663" t="n">
         <v>163183</v>
@@ -19654,7 +19654,7 @@
         <v>8.65499973297119</v>
       </c>
       <c r="G665" t="n">
-        <v>8.3975658416748</v>
+        <v>8.39756488800049</v>
       </c>
       <c r="H665" t="n">
         <v>1421609</v>
@@ -19683,7 +19683,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G666" t="n">
-        <v>8.19866275787354</v>
+        <v>8.19866371154785</v>
       </c>
       <c r="H666" t="n">
         <v>376186</v>
@@ -19712,7 +19712,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G667" t="n">
-        <v>8.52855014801025</v>
+        <v>8.52855110168457</v>
       </c>
       <c r="H667" t="n">
         <v>499509</v>
@@ -19828,7 +19828,7 @@
         <v>9.07499980926514</v>
       </c>
       <c r="G671" t="n">
-        <v>8.80507373809814</v>
+        <v>8.80507278442383</v>
       </c>
       <c r="H671" t="n">
         <v>162058</v>
@@ -19886,7 +19886,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G673" t="n">
-        <v>8.7420072555542</v>
+        <v>8.74200630187988</v>
       </c>
       <c r="H673" t="n">
         <v>106877</v>
@@ -20002,7 +20002,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>9.04763698577881</v>
+        <v>9.04763793945312</v>
       </c>
       <c r="H677" t="n">
         <v>120993</v>
@@ -20031,7 +20031,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G678" t="n">
-        <v>9.04763698577881</v>
+        <v>9.04763793945312</v>
       </c>
       <c r="H678" t="n">
         <v>114620</v>
@@ -20060,7 +20060,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G679" t="n">
-        <v>8.94090843200684</v>
+        <v>8.94090938568115</v>
       </c>
       <c r="H679" t="n">
         <v>176536</v>
@@ -20263,7 +20263,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G686" t="n">
-        <v>6.82575082778931</v>
+        <v>6.82575130462646</v>
       </c>
       <c r="H686" t="n">
         <v>2010202</v>
@@ -20321,7 +20321,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G688" t="n">
-        <v>6.44249963760376</v>
+        <v>6.44250011444092</v>
       </c>
       <c r="H688" t="n">
         <v>526066</v>
@@ -20350,7 +20350,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G689" t="n">
-        <v>6.66080713272095</v>
+        <v>6.66080760955811</v>
       </c>
       <c r="H689" t="n">
         <v>633433</v>
@@ -20379,7 +20379,7 @@
         <v>6.64499998092651</v>
       </c>
       <c r="G690" t="n">
-        <v>6.44735145568848</v>
+        <v>6.44735097885132</v>
       </c>
       <c r="H690" t="n">
         <v>435937</v>
@@ -20408,7 +20408,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G691" t="n">
-        <v>6.46190452575684</v>
+        <v>6.46190500259399</v>
       </c>
       <c r="H691" t="n">
         <v>314939</v>
@@ -20437,7 +20437,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>6.32606887817383</v>
+        <v>6.32606935501099</v>
       </c>
       <c r="H692" t="n">
         <v>246343</v>
@@ -20553,7 +20553,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G696" t="n">
-        <v>6.09805917739868</v>
+        <v>6.09805870056152</v>
       </c>
       <c r="H696" t="n">
         <v>426023</v>
@@ -20582,7 +20582,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G697" t="n">
-        <v>5.84094142913818</v>
+        <v>5.84094095230103</v>
       </c>
       <c r="H697" t="n">
         <v>433195</v>
@@ -20640,7 +20640,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G699" t="n">
-        <v>6.01073598861694</v>
+        <v>6.0107364654541</v>
       </c>
       <c r="H699" t="n">
         <v>258310</v>
@@ -20727,7 +20727,7 @@
         <v>6.35500001907349</v>
       </c>
       <c r="G702" t="n">
-        <v>6.16597652435303</v>
+        <v>6.16597700119019</v>
       </c>
       <c r="H702" t="n">
         <v>169235</v>
@@ -20756,7 +20756,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G703" t="n">
-        <v>6.07380247116089</v>
+        <v>6.07380294799805</v>
       </c>
       <c r="H703" t="n">
         <v>180300</v>
@@ -20814,7 +20814,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G705" t="n">
-        <v>5.97677659988403</v>
+        <v>5.97677707672119</v>
       </c>
       <c r="H705" t="n">
         <v>155044</v>
@@ -20930,7 +20930,7 @@
         <v>6.125</v>
       </c>
       <c r="G709" t="n">
-        <v>5.94281768798828</v>
+        <v>5.94281816482544</v>
       </c>
       <c r="H709" t="n">
         <v>221764</v>
@@ -21104,7 +21104,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G715" t="n">
-        <v>6.4327974319458</v>
+        <v>6.43279790878296</v>
       </c>
       <c r="H715" t="n">
         <v>116884</v>
@@ -21133,7 +21133,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G716" t="n">
-        <v>6.2775559425354</v>
+        <v>6.27755641937256</v>
       </c>
       <c r="H716" t="n">
         <v>222806</v>
@@ -21220,7 +21220,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G719" t="n">
-        <v>6.5007152557373</v>
+        <v>6.50071477890015</v>
       </c>
       <c r="H719" t="n">
         <v>144135</v>
@@ -21365,7 +21365,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G724" t="n">
-        <v>6.67536163330078</v>
+        <v>6.67536115646362</v>
       </c>
       <c r="H724" t="n">
         <v>775096</v>
@@ -32014,6 +32014,35 @@
         <v>432825</v>
       </c>
       <c r="I1091" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1092" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1092" t="n">
+        <v>5.47499990463257</v>
+      </c>
+      <c r="D1092" t="n">
+        <v>5.61499977111816</v>
+      </c>
+      <c r="E1092" t="n">
+        <v>5.38500022888184</v>
+      </c>
+      <c r="F1092" t="n">
+        <v>5.55999994277954</v>
+      </c>
+      <c r="G1092" t="n">
+        <v>5.55999994277954</v>
+      </c>
+      <c r="H1092" t="n">
+        <v>482085</v>
+      </c>
+      <c r="I1092" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DNR.MI.xlsx
+++ b/data/DNR.MI.xlsx
@@ -427,7 +427,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G2" t="n">
-        <v>12.5555391311646</v>
+        <v>12.5555381774902</v>
       </c>
       <c r="H2" t="n">
         <v>264770</v>
@@ -456,7 +456,7 @@
         <v>13.25</v>
       </c>
       <c r="G3" t="n">
-        <v>12.6606454849243</v>
+        <v>12.66064453125</v>
       </c>
       <c r="H3" t="n">
         <v>74987</v>
@@ -514,7 +514,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G5" t="n">
-        <v>12.4886512756348</v>
+        <v>12.4886503219604</v>
       </c>
       <c r="H5" t="n">
         <v>167412</v>
@@ -572,7 +572,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G7" t="n">
-        <v>12.5077619552612</v>
+        <v>12.5077610015869</v>
       </c>
       <c r="H7" t="n">
         <v>117337</v>
@@ -659,7 +659,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G10" t="n">
-        <v>12.5173177719116</v>
+        <v>12.5173168182373</v>
       </c>
       <c r="H10" t="n">
         <v>111264</v>
@@ -688,7 +688,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>12.5173177719116</v>
+        <v>12.5173168182373</v>
       </c>
       <c r="H11" t="n">
         <v>104743</v>
@@ -717,7 +717,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G12" t="n">
-        <v>12.4504299163818</v>
+        <v>12.4504308700562</v>
       </c>
       <c r="H12" t="n">
         <v>94003</v>
@@ -920,7 +920,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G19" t="n">
-        <v>13.5683898925781</v>
+        <v>13.5683879852295</v>
       </c>
       <c r="H19" t="n">
         <v>254487</v>
@@ -949,7 +949,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G20" t="n">
-        <v>13.8072690963745</v>
+        <v>13.8072700500488</v>
       </c>
       <c r="H20" t="n">
         <v>301266</v>
@@ -978,7 +978,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G21" t="n">
-        <v>14.0748138427734</v>
+        <v>14.0748147964478</v>
       </c>
       <c r="H21" t="n">
         <v>546294</v>
@@ -1007,7 +1007,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G22" t="n">
-        <v>14.065260887146</v>
+        <v>14.0652599334717</v>
       </c>
       <c r="H22" t="n">
         <v>577409</v>
@@ -1094,7 +1094,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G25" t="n">
-        <v>13.9410419464111</v>
+        <v>13.9410429000854</v>
       </c>
       <c r="H25" t="n">
         <v>258800</v>
@@ -1123,7 +1123,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G26" t="n">
-        <v>14.1608123779297</v>
+        <v>14.1608114242554</v>
       </c>
       <c r="H26" t="n">
         <v>270595</v>
@@ -1181,7 +1181,7 @@
         <v>14.75</v>
       </c>
       <c r="G28" t="n">
-        <v>14.0939264297485</v>
+        <v>14.0939254760742</v>
       </c>
       <c r="H28" t="n">
         <v>136578</v>
@@ -1210,7 +1210,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G29" t="n">
-        <v>13.826379776001</v>
+        <v>13.8263807296753</v>
       </c>
       <c r="H29" t="n">
         <v>61971</v>
@@ -1268,7 +1268,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G31" t="n">
-        <v>13.5492782592773</v>
+        <v>13.549280166626</v>
       </c>
       <c r="H31" t="n">
         <v>152273</v>
@@ -1297,7 +1297,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G32" t="n">
-        <v>13.5683898925781</v>
+        <v>13.5683879852295</v>
       </c>
       <c r="H32" t="n">
         <v>138086</v>
@@ -1355,7 +1355,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G34" t="n">
-        <v>13.3486194610596</v>
+        <v>13.3486204147339</v>
       </c>
       <c r="H34" t="n">
         <v>107934</v>
@@ -1413,7 +1413,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G36" t="n">
-        <v>13.3486194610596</v>
+        <v>13.3486204147339</v>
       </c>
       <c r="H36" t="n">
         <v>80762</v>
@@ -1442,7 +1442,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G37" t="n">
-        <v>13.2912893295288</v>
+        <v>13.2912883758545</v>
       </c>
       <c r="H37" t="n">
         <v>64058</v>
@@ -1471,7 +1471,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G38" t="n">
-        <v>13.4250621795654</v>
+        <v>13.4250612258911</v>
       </c>
       <c r="H38" t="n">
         <v>146037</v>
@@ -1529,7 +1529,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G40" t="n">
-        <v>13.8454895019531</v>
+        <v>13.8454904556274</v>
       </c>
       <c r="H40" t="n">
         <v>109728</v>
@@ -1587,7 +1587,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>15.1927728652954</v>
+        <v>15.1927738189697</v>
       </c>
       <c r="H42" t="n">
         <v>474029</v>
@@ -1616,7 +1616,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>15.3838787078857</v>
+        <v>15.3838777542114</v>
       </c>
       <c r="H43" t="n">
         <v>436799</v>
@@ -1645,7 +1645,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G44" t="n">
-        <v>16.1387386322021</v>
+        <v>16.1387405395508</v>
       </c>
       <c r="H44" t="n">
         <v>348418</v>
@@ -1674,7 +1674,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>15.5749807357788</v>
+        <v>15.5749816894531</v>
       </c>
       <c r="H45" t="n">
         <v>405367</v>
@@ -1703,7 +1703,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G46" t="n">
-        <v>15.4507646560669</v>
+        <v>15.4507656097412</v>
       </c>
       <c r="H46" t="n">
         <v>226004</v>
@@ -1732,7 +1732,7 @@
         <v>16.0900001525879</v>
       </c>
       <c r="G47" t="n">
-        <v>15.374321937561</v>
+        <v>15.3743228912354</v>
       </c>
       <c r="H47" t="n">
         <v>347713</v>
@@ -1790,7 +1790,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G49" t="n">
-        <v>15.6418685913086</v>
+        <v>15.6418695449829</v>
       </c>
       <c r="H49" t="n">
         <v>782970</v>
@@ -1848,7 +1848,7 @@
         <v>15.8900003433228</v>
       </c>
       <c r="G51" t="n">
-        <v>15.183219909668</v>
+        <v>15.1832189559937</v>
       </c>
       <c r="H51" t="n">
         <v>161269</v>
@@ -1877,7 +1877,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>14.7627906799316</v>
+        <v>14.7627897262573</v>
       </c>
       <c r="H52" t="n">
         <v>236091</v>
@@ -1935,7 +1935,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G54" t="n">
-        <v>14.0079288482666</v>
+        <v>14.0079278945923</v>
       </c>
       <c r="H54" t="n">
         <v>147319</v>
@@ -1993,7 +1993,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G56" t="n">
-        <v>15.1163330078125</v>
+        <v>15.1163320541382</v>
       </c>
       <c r="H56" t="n">
         <v>204640</v>
@@ -2080,7 +2080,7 @@
         <v>15.75</v>
       </c>
       <c r="G59" t="n">
-        <v>15.049446105957</v>
+        <v>15.0494451522827</v>
       </c>
       <c r="H59" t="n">
         <v>87541</v>
@@ -2109,7 +2109,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G60" t="n">
-        <v>15.4889850616455</v>
+        <v>15.4889841079712</v>
       </c>
       <c r="H60" t="n">
         <v>176931</v>
@@ -2138,7 +2138,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G61" t="n">
-        <v>15.555871963501</v>
+        <v>15.5558729171753</v>
       </c>
       <c r="H61" t="n">
         <v>217368</v>
@@ -2196,7 +2196,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G63" t="n">
-        <v>15.1736631393433</v>
+        <v>15.1736640930176</v>
       </c>
       <c r="H63" t="n">
         <v>103387</v>
@@ -2341,7 +2341,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G68" t="n">
-        <v>15.517650604248</v>
+        <v>15.5176515579224</v>
       </c>
       <c r="H68" t="n">
         <v>132919</v>
@@ -2399,7 +2399,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G70" t="n">
-        <v>15.3361005783081</v>
+        <v>15.3361015319824</v>
       </c>
       <c r="H70" t="n">
         <v>85001</v>
@@ -2457,7 +2457,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G72" t="n">
-        <v>14.6003503799438</v>
+        <v>14.6003513336182</v>
       </c>
       <c r="H72" t="n">
         <v>144220</v>
@@ -2486,7 +2486,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G73" t="n">
-        <v>14.3519172668457</v>
+        <v>14.3519153594971</v>
       </c>
       <c r="H73" t="n">
         <v>172203</v>
@@ -2544,7 +2544,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G75" t="n">
-        <v>14.1894788742065</v>
+        <v>14.1894779205322</v>
       </c>
       <c r="H75" t="n">
         <v>121982</v>
@@ -2631,7 +2631,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G78" t="n">
-        <v>14.065260887146</v>
+        <v>14.0652599334717</v>
       </c>
       <c r="H78" t="n">
         <v>153369</v>
@@ -2660,7 +2660,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G79" t="n">
-        <v>13.8646011352539</v>
+        <v>13.8646001815796</v>
       </c>
       <c r="H79" t="n">
         <v>226264</v>
@@ -2805,7 +2805,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G84" t="n">
-        <v>13.1670703887939</v>
+        <v>13.1670713424683</v>
       </c>
       <c r="H84" t="n">
         <v>628995</v>
@@ -2892,7 +2892,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G87" t="n">
-        <v>13.644829750061</v>
+        <v>13.6448316574097</v>
       </c>
       <c r="H87" t="n">
         <v>355963</v>
@@ -2921,7 +2921,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G88" t="n">
-        <v>14.6003503799438</v>
+        <v>14.6003513336182</v>
       </c>
       <c r="H88" t="n">
         <v>499133</v>
@@ -3066,7 +3066,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G93" t="n">
-        <v>14.6767921447754</v>
+        <v>14.6767930984497</v>
       </c>
       <c r="H93" t="n">
         <v>110219</v>
@@ -3095,7 +3095,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G94" t="n">
-        <v>14.6003503799438</v>
+        <v>14.6003513336182</v>
       </c>
       <c r="H94" t="n">
         <v>65667</v>
@@ -3153,7 +3153,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>14.6194620132446</v>
+        <v>14.6194629669189</v>
       </c>
       <c r="H96" t="n">
         <v>186490</v>
@@ -3298,7 +3298,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G101" t="n">
-        <v>15.3265476226807</v>
+        <v>15.326548576355</v>
       </c>
       <c r="H101" t="n">
         <v>177567</v>
@@ -3327,7 +3327,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G102" t="n">
-        <v>15.3456563949585</v>
+        <v>15.3456573486328</v>
       </c>
       <c r="H102" t="n">
         <v>1185858</v>
@@ -3501,7 +3501,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G108" t="n">
-        <v>14.7627906799316</v>
+        <v>14.7627897262573</v>
       </c>
       <c r="H108" t="n">
         <v>44432</v>
@@ -3530,7 +3530,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G109" t="n">
-        <v>14.8487854003906</v>
+        <v>14.8487863540649</v>
       </c>
       <c r="H109" t="n">
         <v>53044</v>
@@ -3559,7 +3559,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G110" t="n">
-        <v>15.08766746521</v>
+        <v>15.0876665115356</v>
       </c>
       <c r="H110" t="n">
         <v>72044</v>
@@ -3588,7 +3588,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G111" t="n">
-        <v>14.9443378448486</v>
+        <v>14.9443387985229</v>
       </c>
       <c r="H111" t="n">
         <v>83241</v>
@@ -3675,7 +3675,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G114" t="n">
-        <v>14.7819004058838</v>
+        <v>14.7819013595581</v>
       </c>
       <c r="H114" t="n">
         <v>173217</v>
@@ -3733,7 +3733,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G116" t="n">
-        <v>14.4570236206055</v>
+        <v>14.4570226669312</v>
       </c>
       <c r="H116" t="n">
         <v>75449</v>
@@ -3762,7 +3762,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G117" t="n">
-        <v>14.4474668502808</v>
+        <v>14.4474678039551</v>
       </c>
       <c r="H117" t="n">
         <v>75827</v>
@@ -3791,7 +3791,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G118" t="n">
-        <v>14.0461492538452</v>
+        <v>14.0461502075195</v>
       </c>
       <c r="H118" t="n">
         <v>88132</v>
@@ -3820,7 +3820,7 @@
         <v>14.5</v>
       </c>
       <c r="G119" t="n">
-        <v>13.8550462722778</v>
+        <v>13.8550453186035</v>
       </c>
       <c r="H119" t="n">
         <v>88896</v>
@@ -3849,7 +3849,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>13.7594938278198</v>
+        <v>13.7594928741455</v>
       </c>
       <c r="H120" t="n">
         <v>41310</v>
@@ -3965,7 +3965,7 @@
         <v>14.5</v>
       </c>
       <c r="G124" t="n">
-        <v>13.8550462722778</v>
+        <v>13.8550453186035</v>
       </c>
       <c r="H124" t="n">
         <v>15822</v>
@@ -3994,7 +3994,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G125" t="n">
-        <v>14.4952440261841</v>
+        <v>14.4952449798584</v>
       </c>
       <c r="H125" t="n">
         <v>221654</v>
@@ -4139,7 +4139,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G130" t="n">
-        <v>15.0398902893066</v>
+        <v>15.0398893356323</v>
       </c>
       <c r="H130" t="n">
         <v>99245</v>
@@ -4168,7 +4168,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G131" t="n">
-        <v>15.08766746521</v>
+        <v>15.0876665115356</v>
       </c>
       <c r="H131" t="n">
         <v>223782</v>
@@ -4226,7 +4226,7 @@
         <v>15.75</v>
       </c>
       <c r="G133" t="n">
-        <v>15.049446105957</v>
+        <v>15.0494451522827</v>
       </c>
       <c r="H133" t="n">
         <v>54662</v>
@@ -4255,7 +4255,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>14.9538946151733</v>
+        <v>14.953893661499</v>
       </c>
       <c r="H134" t="n">
         <v>62972</v>
@@ -4284,7 +4284,7 @@
         <v>15.6899995803833</v>
       </c>
       <c r="G135" t="n">
-        <v>14.992115020752</v>
+        <v>14.9921140670776</v>
       </c>
       <c r="H135" t="n">
         <v>123072</v>
@@ -4313,7 +4313,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G136" t="n">
-        <v>15.269214630127</v>
+        <v>15.2692155838013</v>
       </c>
       <c r="H136" t="n">
         <v>116552</v>
@@ -4342,7 +4342,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G137" t="n">
-        <v>15.1736631393433</v>
+        <v>15.1736640930176</v>
       </c>
       <c r="H137" t="n">
         <v>135405</v>
@@ -4371,7 +4371,7 @@
         <v>16.5</v>
       </c>
       <c r="G138" t="n">
-        <v>15.7660856246948</v>
+        <v>15.7660846710205</v>
       </c>
       <c r="H138" t="n">
         <v>318203</v>
@@ -4400,7 +4400,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G139" t="n">
-        <v>16.3011779785156</v>
+        <v>16.3011798858643</v>
       </c>
       <c r="H139" t="n">
         <v>212600</v>
@@ -4516,7 +4516,7 @@
         <v>17.8700008392334</v>
       </c>
       <c r="G143" t="n">
-        <v>17.0751514434814</v>
+        <v>17.0751495361328</v>
       </c>
       <c r="H143" t="n">
         <v>118766</v>
@@ -4574,7 +4574,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G145" t="n">
-        <v>16.2916221618652</v>
+        <v>16.2916202545166</v>
       </c>
       <c r="H145" t="n">
         <v>134728</v>
@@ -4603,7 +4603,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G146" t="n">
-        <v>16.7693824768066</v>
+        <v>16.7693843841553</v>
       </c>
       <c r="H146" t="n">
         <v>112560</v>
@@ -4661,7 +4661,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G148" t="n">
-        <v>15.8425283432007</v>
+        <v>15.842529296875</v>
       </c>
       <c r="H148" t="n">
         <v>256187</v>
@@ -4719,7 +4719,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G150" t="n">
-        <v>15.6418685913086</v>
+        <v>15.6418695449829</v>
       </c>
       <c r="H150" t="n">
         <v>102652</v>
@@ -4748,7 +4748,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G151" t="n">
-        <v>16.205623626709</v>
+        <v>16.2056255340576</v>
       </c>
       <c r="H151" t="n">
         <v>92236</v>
@@ -4806,7 +4806,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G153" t="n">
-        <v>16.587833404541</v>
+        <v>16.5878353118896</v>
       </c>
       <c r="H153" t="n">
         <v>137920</v>
@@ -4893,7 +4893,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G156" t="n">
-        <v>17.6962394714355</v>
+        <v>17.6962375640869</v>
       </c>
       <c r="H156" t="n">
         <v>187911</v>
@@ -5096,7 +5096,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G163" t="n">
-        <v>17.2089233398438</v>
+        <v>17.2089214324951</v>
       </c>
       <c r="H163" t="n">
         <v>50813</v>
@@ -5154,7 +5154,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G165" t="n">
-        <v>17.9542293548584</v>
+        <v>17.9542274475098</v>
       </c>
       <c r="H165" t="n">
         <v>337145</v>
@@ -5183,7 +5183,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>17.8204574584961</v>
+        <v>17.8204555511475</v>
       </c>
       <c r="H166" t="n">
         <v>70506</v>
@@ -5270,7 +5270,7 @@
         <v>19.5</v>
       </c>
       <c r="G169" t="n">
-        <v>18.6326465606689</v>
+        <v>18.6326484680176</v>
       </c>
       <c r="H169" t="n">
         <v>161677</v>
@@ -5328,7 +5328,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G171" t="n">
-        <v>18.7664184570312</v>
+        <v>18.7664203643799</v>
       </c>
       <c r="H171" t="n">
         <v>104982</v>
@@ -5386,7 +5386,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G173" t="n">
-        <v>18.508430480957</v>
+        <v>18.5084323883057</v>
       </c>
       <c r="H173" t="n">
         <v>82218</v>
@@ -5415,7 +5415,7 @@
         <v>18.7700004577637</v>
       </c>
       <c r="G174" t="n">
-        <v>17.9351177215576</v>
+        <v>17.9351196289062</v>
       </c>
       <c r="H174" t="n">
         <v>228634</v>
@@ -5444,7 +5444,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>18.4415416717529</v>
+        <v>18.4415435791016</v>
       </c>
       <c r="H175" t="n">
         <v>73309</v>
@@ -5473,7 +5473,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>17.7726802825928</v>
+        <v>17.7726783752441</v>
       </c>
       <c r="H176" t="n">
         <v>132691</v>
@@ -5560,7 +5560,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G179" t="n">
-        <v>18.8524150848389</v>
+        <v>18.8524169921875</v>
       </c>
       <c r="H179" t="n">
         <v>160303</v>
@@ -5589,7 +5589,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G180" t="n">
-        <v>18.7664184570312</v>
+        <v>18.7664203643799</v>
       </c>
       <c r="H180" t="n">
         <v>186766</v>
@@ -5618,7 +5618,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G181" t="n">
-        <v>18.823751449585</v>
+        <v>18.8237533569336</v>
       </c>
       <c r="H181" t="n">
         <v>95801</v>
@@ -5734,7 +5734,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G185" t="n">
-        <v>16.3967304229736</v>
+        <v>16.396728515625</v>
       </c>
       <c r="H185" t="n">
         <v>282326</v>
@@ -5792,7 +5792,7 @@
         <v>18</v>
       </c>
       <c r="G187" t="n">
-        <v>17.199369430542</v>
+        <v>17.1993675231934</v>
       </c>
       <c r="H187" t="n">
         <v>168778</v>
@@ -5821,7 +5821,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G188" t="n">
-        <v>17.6580142974854</v>
+        <v>17.6580181121826</v>
       </c>
       <c r="H188" t="n">
         <v>106658</v>
@@ -5850,7 +5850,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G189" t="n">
-        <v>17.6580142974854</v>
+        <v>17.6580181121826</v>
       </c>
       <c r="H189" t="n">
         <v>195062</v>
@@ -5937,7 +5937,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G192" t="n">
-        <v>16.5305042266846</v>
+        <v>16.5305023193359</v>
       </c>
       <c r="H192" t="n">
         <v>303536</v>
@@ -5995,7 +5995,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>16.3871726989746</v>
+        <v>16.3871746063232</v>
       </c>
       <c r="H194" t="n">
         <v>289758</v>
@@ -6024,7 +6024,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G195" t="n">
-        <v>16.3011779785156</v>
+        <v>16.3011798858643</v>
       </c>
       <c r="H195" t="n">
         <v>519554</v>
@@ -6053,7 +6053,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G196" t="n">
-        <v>16.205623626709</v>
+        <v>16.2056255340576</v>
       </c>
       <c r="H196" t="n">
         <v>122290</v>
@@ -6082,7 +6082,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G197" t="n">
-        <v>16.3489532470703</v>
+        <v>16.3489551544189</v>
       </c>
       <c r="H197" t="n">
         <v>187727</v>
@@ -6111,7 +6111,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G198" t="n">
-        <v>16.3011779785156</v>
+        <v>16.3011798858643</v>
       </c>
       <c r="H198" t="n">
         <v>103373</v>
@@ -6140,7 +6140,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G199" t="n">
-        <v>16.6069431304932</v>
+        <v>16.6069450378418</v>
       </c>
       <c r="H199" t="n">
         <v>89821</v>
@@ -6198,7 +6198,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>16.6260547637939</v>
+        <v>16.6260566711426</v>
       </c>
       <c r="H201" t="n">
         <v>108711</v>
@@ -6227,7 +6227,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G202" t="n">
-        <v>16.587833404541</v>
+        <v>16.5878353118896</v>
       </c>
       <c r="H202" t="n">
         <v>70415</v>
@@ -6256,7 +6256,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G203" t="n">
-        <v>16.7407188415527</v>
+        <v>16.7407150268555</v>
       </c>
       <c r="H203" t="n">
         <v>93120</v>
@@ -6285,7 +6285,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G204" t="n">
-        <v>16.7884922027588</v>
+        <v>16.7884941101074</v>
       </c>
       <c r="H204" t="n">
         <v>110054</v>
@@ -6314,7 +6314,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G205" t="n">
-        <v>17.0369262695312</v>
+        <v>17.0369281768799</v>
       </c>
       <c r="H205" t="n">
         <v>107074</v>
@@ -6372,7 +6372,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G207" t="n">
-        <v>16.6547183990479</v>
+        <v>16.6547203063965</v>
       </c>
       <c r="H207" t="n">
         <v>154640</v>
@@ -6401,7 +6401,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G208" t="n">
-        <v>16.9031562805176</v>
+        <v>16.9031543731689</v>
       </c>
       <c r="H208" t="n">
         <v>80044</v>
@@ -6488,7 +6488,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G211" t="n">
-        <v>17.37135887146</v>
+        <v>17.3713607788086</v>
       </c>
       <c r="H211" t="n">
         <v>87623</v>
@@ -6633,7 +6633,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G216" t="n">
-        <v>17.6293525695801</v>
+        <v>17.6293506622314</v>
       </c>
       <c r="H216" t="n">
         <v>202637</v>
@@ -6691,7 +6691,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G218" t="n">
-        <v>18.4415416717529</v>
+        <v>18.4415435791016</v>
       </c>
       <c r="H218" t="n">
         <v>241224</v>
@@ -6720,7 +6720,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G219" t="n">
-        <v>18.4415416717529</v>
+        <v>18.4415435791016</v>
       </c>
       <c r="H219" t="n">
         <v>270484</v>
@@ -6749,7 +6749,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G220" t="n">
-        <v>18.0020046234131</v>
+        <v>18.0020065307617</v>
       </c>
       <c r="H220" t="n">
         <v>388714</v>
@@ -6778,7 +6778,7 @@
         <v>19.2700004577637</v>
       </c>
       <c r="G221" t="n">
-        <v>18.5309104919434</v>
+        <v>18.5309085845947</v>
       </c>
       <c r="H221" t="n">
         <v>86313</v>
@@ -6807,7 +6807,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G222" t="n">
-        <v>18.5789909362793</v>
+        <v>18.5789890289307</v>
       </c>
       <c r="H222" t="n">
         <v>75028</v>
@@ -6836,7 +6836,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G223" t="n">
-        <v>18.6559238433838</v>
+        <v>18.6559219360352</v>
       </c>
       <c r="H223" t="n">
         <v>117863</v>
@@ -6894,7 +6894,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G225" t="n">
-        <v>18.6559238433838</v>
+        <v>18.6559219360352</v>
       </c>
       <c r="H225" t="n">
         <v>62425</v>
@@ -7010,7 +7010,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G229" t="n">
-        <v>18.8097877502441</v>
+        <v>18.8097858428955</v>
       </c>
       <c r="H229" t="n">
         <v>69687</v>
@@ -7097,7 +7097,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>18.3674297332764</v>
+        <v>18.3674278259277</v>
       </c>
       <c r="H232" t="n">
         <v>66293</v>
@@ -7155,7 +7155,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>19.1367454528809</v>
+        <v>19.1367473602295</v>
       </c>
       <c r="H234" t="n">
         <v>176092</v>
@@ -7213,7 +7213,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G236" t="n">
-        <v>20.1753234863281</v>
+        <v>20.1753215789795</v>
       </c>
       <c r="H236" t="n">
         <v>286301</v>
@@ -7387,7 +7387,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>19.4252376556396</v>
+        <v>19.4252395629883</v>
       </c>
       <c r="H242" t="n">
         <v>219460</v>
@@ -7416,7 +7416,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G243" t="n">
-        <v>19.0405788421631</v>
+        <v>19.0405807495117</v>
       </c>
       <c r="H243" t="n">
         <v>51065</v>
@@ -7503,7 +7503,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G246" t="n">
-        <v>17.8481407165527</v>
+        <v>17.8481388092041</v>
       </c>
       <c r="H246" t="n">
         <v>191126</v>
@@ -7561,7 +7561,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G248" t="n">
-        <v>18.5789909362793</v>
+        <v>18.5789890289307</v>
       </c>
       <c r="H248" t="n">
         <v>83004</v>
@@ -7590,7 +7590,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G249" t="n">
-        <v>18.4924430847168</v>
+        <v>18.4924411773682</v>
       </c>
       <c r="H249" t="n">
         <v>68327</v>
@@ -7619,7 +7619,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G250" t="n">
-        <v>18.4924430847168</v>
+        <v>18.4924411773682</v>
       </c>
       <c r="H250" t="n">
         <v>136559</v>
@@ -7677,7 +7677,7 @@
         <v>19.5</v>
       </c>
       <c r="G252" t="n">
-        <v>18.7520866394043</v>
+        <v>18.7520885467529</v>
       </c>
       <c r="H252" t="n">
         <v>47907</v>
@@ -7735,7 +7735,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G254" t="n">
-        <v>18.3866634368896</v>
+        <v>18.386661529541</v>
       </c>
       <c r="H254" t="n">
         <v>40747</v>
@@ -7822,7 +7822,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G257" t="n">
-        <v>19.6944980621338</v>
+        <v>19.6944999694824</v>
       </c>
       <c r="H257" t="n">
         <v>62964</v>
@@ -7851,7 +7851,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G258" t="n">
-        <v>20.1368579864502</v>
+        <v>20.1368560791016</v>
       </c>
       <c r="H258" t="n">
         <v>123239</v>
@@ -7909,7 +7909,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G260" t="n">
-        <v>19.5598697662354</v>
+        <v>19.5598678588867</v>
       </c>
       <c r="H260" t="n">
         <v>165590</v>
@@ -7938,7 +7938,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G261" t="n">
-        <v>19.2713775634766</v>
+        <v>19.2713756561279</v>
       </c>
       <c r="H261" t="n">
         <v>226076</v>
@@ -8025,7 +8025,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G264" t="n">
-        <v>19.4829368591309</v>
+        <v>19.4829387664795</v>
       </c>
       <c r="H264" t="n">
         <v>113210</v>
@@ -8199,7 +8199,7 @@
         <v>20.1399993896484</v>
       </c>
       <c r="G270" t="n">
-        <v>19.3675403594971</v>
+        <v>19.3675384521484</v>
       </c>
       <c r="H270" t="n">
         <v>52442</v>
@@ -8228,7 +8228,7 @@
         <v>18.7700004577637</v>
       </c>
       <c r="G271" t="n">
-        <v>18.050085067749</v>
+        <v>18.0500869750977</v>
       </c>
       <c r="H271" t="n">
         <v>522798</v>
@@ -8257,7 +8257,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G272" t="n">
-        <v>17.5019493103027</v>
+        <v>17.5019474029541</v>
       </c>
       <c r="H272" t="n">
         <v>364369</v>
@@ -8315,7 +8315,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G274" t="n">
-        <v>17.5115642547607</v>
+        <v>17.5115623474121</v>
       </c>
       <c r="H274" t="n">
         <v>166261</v>
@@ -8344,7 +8344,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G275" t="n">
-        <v>18.2904968261719</v>
+        <v>18.2904987335205</v>
       </c>
       <c r="H275" t="n">
         <v>226073</v>
@@ -8373,7 +8373,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G276" t="n">
-        <v>18.5020599365234</v>
+        <v>18.5020580291748</v>
       </c>
       <c r="H276" t="n">
         <v>314121</v>
@@ -8431,7 +8431,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G278" t="n">
-        <v>18.6270732879639</v>
+        <v>18.6270751953125</v>
       </c>
       <c r="H278" t="n">
         <v>96317</v>
@@ -8489,7 +8489,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G280" t="n">
-        <v>18.6559238433838</v>
+        <v>18.6559219360352</v>
       </c>
       <c r="H280" t="n">
         <v>71432</v>
@@ -8576,7 +8576,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G283" t="n">
-        <v>17.5981121063232</v>
+        <v>17.5981101989746</v>
       </c>
       <c r="H283" t="n">
         <v>79763</v>
@@ -8605,7 +8605,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G284" t="n">
-        <v>17.5404148101807</v>
+        <v>17.540412902832</v>
       </c>
       <c r="H284" t="n">
         <v>101821</v>
@@ -8663,7 +8663,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G286" t="n">
-        <v>17.0595932006836</v>
+        <v>17.059591293335</v>
       </c>
       <c r="H286" t="n">
         <v>83846</v>
@@ -8866,7 +8866,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G293" t="n">
-        <v>17.213451385498</v>
+        <v>17.2134532928467</v>
       </c>
       <c r="H293" t="n">
         <v>97852</v>
@@ -8924,7 +8924,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G295" t="n">
-        <v>17.1749877929688</v>
+        <v>17.1749897003174</v>
       </c>
       <c r="H295" t="n">
         <v>38905</v>
@@ -8953,7 +8953,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G296" t="n">
-        <v>17.2807693481445</v>
+        <v>17.2807712554932</v>
       </c>
       <c r="H296" t="n">
         <v>59361</v>
@@ -9098,7 +9098,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G301" t="n">
-        <v>16.4441394805908</v>
+        <v>16.4441375732422</v>
       </c>
       <c r="H301" t="n">
         <v>93310</v>
@@ -9127,7 +9127,7 @@
         <v>17</v>
       </c>
       <c r="G302" t="n">
-        <v>16.347972869873</v>
+        <v>16.3479747772217</v>
       </c>
       <c r="H302" t="n">
         <v>123413</v>
@@ -9185,7 +9185,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G304" t="n">
-        <v>16.723014831543</v>
+        <v>16.7230129241943</v>
       </c>
       <c r="H304" t="n">
         <v>322231</v>
@@ -9359,7 +9359,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G310" t="n">
-        <v>15.5401916503906</v>
+        <v>15.5401906967163</v>
       </c>
       <c r="H310" t="n">
         <v>75719</v>
@@ -9417,7 +9417,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>15.4824934005737</v>
+        <v>15.4824924468994</v>
       </c>
       <c r="H312" t="n">
         <v>47778</v>
@@ -9475,7 +9475,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G314" t="n">
-        <v>15.6555881500244</v>
+        <v>15.655590057373</v>
       </c>
       <c r="H314" t="n">
         <v>70184</v>
@@ -9533,7 +9533,7 @@
         <v>16.2700004577637</v>
       </c>
       <c r="G316" t="n">
-        <v>15.6459732055664</v>
+        <v>15.6459722518921</v>
       </c>
       <c r="H316" t="n">
         <v>152152</v>
@@ -9591,7 +9591,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G318" t="n">
-        <v>14.4150657653809</v>
+        <v>14.4150667190552</v>
       </c>
       <c r="H318" t="n">
         <v>129315</v>
@@ -9649,7 +9649,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G320" t="n">
-        <v>14.3189010620117</v>
+        <v>14.318902015686</v>
       </c>
       <c r="H320" t="n">
         <v>84956</v>
@@ -9765,7 +9765,7 @@
         <v>15</v>
       </c>
       <c r="G324" t="n">
-        <v>14.4246826171875</v>
+        <v>14.4246835708618</v>
       </c>
       <c r="H324" t="n">
         <v>91074</v>
@@ -9852,7 +9852,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G327" t="n">
-        <v>14.0881052017212</v>
+        <v>14.0881061553955</v>
       </c>
       <c r="H327" t="n">
         <v>66396</v>
@@ -9881,7 +9881,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G328" t="n">
-        <v>14.2227363586426</v>
+        <v>14.2227373123169</v>
       </c>
       <c r="H328" t="n">
         <v>104116</v>
@@ -10026,7 +10026,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G333" t="n">
-        <v>12.8571996688843</v>
+        <v>12.8572006225586</v>
       </c>
       <c r="H333" t="n">
         <v>104403</v>
@@ -10258,7 +10258,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G341" t="n">
-        <v>13.2803249359131</v>
+        <v>13.2803239822388</v>
       </c>
       <c r="H341" t="n">
         <v>70862</v>
@@ -10316,7 +10316,7 @@
         <v>14.0100002288818</v>
       </c>
       <c r="G343" t="n">
-        <v>13.4726543426514</v>
+        <v>13.4726533889771</v>
       </c>
       <c r="H343" t="n">
         <v>569136</v>
@@ -10345,7 +10345,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G344" t="n">
-        <v>13.0399131774902</v>
+        <v>13.0399141311646</v>
       </c>
       <c r="H344" t="n">
         <v>146201</v>
@@ -10374,7 +10374,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G345" t="n">
-        <v>13.6553659439087</v>
+        <v>13.6553649902344</v>
       </c>
       <c r="H345" t="n">
         <v>126227</v>
@@ -10432,7 +10432,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G347" t="n">
-        <v>14.6362447738647</v>
+        <v>14.6362438201904</v>
       </c>
       <c r="H347" t="n">
         <v>215592</v>
@@ -10461,7 +10461,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G348" t="n">
-        <v>14.2227363586426</v>
+        <v>14.2227373123169</v>
       </c>
       <c r="H348" t="n">
         <v>121936</v>
@@ -10519,7 +10519,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G350" t="n">
-        <v>14.2708196640015</v>
+        <v>14.2708187103271</v>
       </c>
       <c r="H350" t="n">
         <v>157799</v>
@@ -10548,7 +10548,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G351" t="n">
-        <v>14.1073398590088</v>
+        <v>14.1073389053345</v>
       </c>
       <c r="H351" t="n">
         <v>93291</v>
@@ -10577,7 +10577,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G352" t="n">
-        <v>14.2515869140625</v>
+        <v>14.2515859603882</v>
       </c>
       <c r="H352" t="n">
         <v>74240</v>
@@ -10606,7 +10606,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G353" t="n">
-        <v>14.3092861175537</v>
+        <v>14.3092851638794</v>
       </c>
       <c r="H353" t="n">
         <v>104165</v>
@@ -10693,7 +10693,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G356" t="n">
-        <v>13.7322969436646</v>
+        <v>13.7322978973389</v>
       </c>
       <c r="H356" t="n">
         <v>217186</v>
@@ -10751,7 +10751,7 @@
         <v>14.3900003433228</v>
       </c>
       <c r="G358" t="n">
-        <v>13.8380784988403</v>
+        <v>13.8380794525146</v>
       </c>
       <c r="H358" t="n">
         <v>106575</v>
@@ -10780,7 +10780,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G359" t="n">
-        <v>13.6649827957153</v>
+        <v>13.664981842041</v>
       </c>
       <c r="H359" t="n">
         <v>97011</v>
@@ -10809,7 +10809,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G360" t="n">
-        <v>13.2707080841064</v>
+        <v>13.2707071304321</v>
       </c>
       <c r="H360" t="n">
         <v>139158</v>
@@ -10838,7 +10838,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G361" t="n">
-        <v>13.5399684906006</v>
+        <v>13.5399694442749</v>
       </c>
       <c r="H361" t="n">
         <v>102042</v>
@@ -11041,7 +11041,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G368" t="n">
-        <v>14.7131757736206</v>
+        <v>14.7131767272949</v>
       </c>
       <c r="H368" t="n">
         <v>469164</v>
@@ -11128,7 +11128,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G371" t="n">
-        <v>15.6844387054443</v>
+        <v>15.68443775177</v>
       </c>
       <c r="H371" t="n">
         <v>353221</v>
@@ -11273,7 +11273,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G376" t="n">
-        <v>15.0305194854736</v>
+        <v>15.0305185317993</v>
       </c>
       <c r="H376" t="n">
         <v>110938</v>
@@ -11331,7 +11331,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G378" t="n">
-        <v>14.9632034301758</v>
+        <v>14.9632043838501</v>
       </c>
       <c r="H378" t="n">
         <v>149811</v>
@@ -11389,7 +11389,7 @@
         <v>15.0900001525879</v>
       </c>
       <c r="G380" t="n">
-        <v>14.51123046875</v>
+        <v>14.5112314224243</v>
       </c>
       <c r="H380" t="n">
         <v>88556</v>
@@ -11447,7 +11447,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G382" t="n">
-        <v>14.8958883285522</v>
+        <v>14.8958892822266</v>
       </c>
       <c r="H382" t="n">
         <v>111609</v>
@@ -11476,7 +11476,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G383" t="n">
-        <v>14.8670387268066</v>
+        <v>14.867039680481</v>
       </c>
       <c r="H383" t="n">
         <v>127709</v>
@@ -11534,7 +11534,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G385" t="n">
-        <v>14.4439163208008</v>
+        <v>14.4439153671265</v>
       </c>
       <c r="H385" t="n">
         <v>156312</v>
@@ -11563,7 +11563,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G386" t="n">
-        <v>14.0977230072021</v>
+        <v>14.0977220535278</v>
       </c>
       <c r="H386" t="n">
         <v>236798</v>
@@ -11621,7 +11621,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G388" t="n">
-        <v>13.9823265075684</v>
+        <v>13.982325553894</v>
       </c>
       <c r="H388" t="n">
         <v>99895</v>
@@ -11708,7 +11708,7 @@
         <v>14.2700004577637</v>
       </c>
       <c r="G391" t="n">
-        <v>13.7226810455322</v>
+        <v>13.7226819992065</v>
       </c>
       <c r="H391" t="n">
         <v>186975</v>
@@ -11737,7 +11737,7 @@
         <v>14.5</v>
       </c>
       <c r="G392" t="n">
-        <v>13.9438600540161</v>
+        <v>13.9438591003418</v>
       </c>
       <c r="H392" t="n">
         <v>133628</v>
@@ -11795,7 +11795,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G394" t="n">
-        <v>13.7419137954712</v>
+        <v>13.7419147491455</v>
       </c>
       <c r="H394" t="n">
         <v>128563</v>
@@ -11882,7 +11882,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G397" t="n">
-        <v>13.6649827957153</v>
+        <v>13.664981842041</v>
       </c>
       <c r="H397" t="n">
         <v>175445</v>
@@ -11940,7 +11940,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G399" t="n">
-        <v>14.0592565536499</v>
+        <v>14.0592575073242</v>
       </c>
       <c r="H399" t="n">
         <v>307261</v>
@@ -11969,7 +11969,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G400" t="n">
-        <v>14.0784912109375</v>
+        <v>14.0784902572632</v>
       </c>
       <c r="H400" t="n">
         <v>204846</v>
@@ -12085,7 +12085,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G404" t="n">
-        <v>13.3764896392822</v>
+        <v>13.3764886856079</v>
       </c>
       <c r="H404" t="n">
         <v>147194</v>
@@ -12172,7 +12172,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>13.6553659439087</v>
+        <v>13.6553649902344</v>
       </c>
       <c r="H407" t="n">
         <v>163196</v>
@@ -12259,7 +12259,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G410" t="n">
-        <v>14.7901067733765</v>
+        <v>14.7901077270508</v>
       </c>
       <c r="H410" t="n">
         <v>220807</v>
@@ -12491,7 +12491,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G418" t="n">
-        <v>14.6458606719971</v>
+        <v>14.6458597183228</v>
       </c>
       <c r="H418" t="n">
         <v>94315</v>
@@ -12549,7 +12549,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G420" t="n">
-        <v>14.9632034301758</v>
+        <v>14.9632043838501</v>
       </c>
       <c r="H420" t="n">
         <v>161886</v>
@@ -12607,7 +12607,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G422" t="n">
-        <v>14.3092861175537</v>
+        <v>14.3092851638794</v>
       </c>
       <c r="H422" t="n">
         <v>102639</v>
@@ -12665,7 +12665,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G424" t="n">
-        <v>14.0688734054565</v>
+        <v>14.0688743591309</v>
       </c>
       <c r="H424" t="n">
         <v>101301</v>
@@ -12694,7 +12694,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G425" t="n">
-        <v>14.1554222106934</v>
+        <v>14.155421257019</v>
       </c>
       <c r="H425" t="n">
         <v>117944</v>
@@ -12752,7 +12752,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G427" t="n">
-        <v>13.6649827957153</v>
+        <v>13.664981842041</v>
       </c>
       <c r="H427" t="n">
         <v>159222</v>
@@ -12781,7 +12781,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G428" t="n">
-        <v>13.8188447952271</v>
+        <v>13.8188457489014</v>
       </c>
       <c r="H428" t="n">
         <v>206029</v>
@@ -12868,7 +12868,7 @@
         <v>14.1899995803833</v>
       </c>
       <c r="G431" t="n">
-        <v>13.6457500457764</v>
+        <v>13.6457490921021</v>
       </c>
       <c r="H431" t="n">
         <v>223671</v>
@@ -12955,7 +12955,7 @@
         <v>13.25</v>
       </c>
       <c r="G434" t="n">
-        <v>12.7418031692505</v>
+        <v>12.7418022155762</v>
       </c>
       <c r="H434" t="n">
         <v>207043</v>
@@ -12984,7 +12984,7 @@
         <v>13.25</v>
       </c>
       <c r="G435" t="n">
-        <v>12.7418031692505</v>
+        <v>12.7418022155762</v>
       </c>
       <c r="H435" t="n">
         <v>214799</v>
@@ -13042,7 +13042,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G437" t="n">
-        <v>12.7033367156982</v>
+        <v>12.7033376693726</v>
       </c>
       <c r="H437" t="n">
         <v>188482</v>
@@ -13100,7 +13100,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G439" t="n">
-        <v>12.8571996688843</v>
+        <v>12.8572006225586</v>
       </c>
       <c r="H439" t="n">
         <v>90236</v>
@@ -13187,7 +13187,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G442" t="n">
-        <v>12.9725980758667</v>
+        <v>12.9725971221924</v>
       </c>
       <c r="H442" t="n">
         <v>207392</v>
@@ -13274,7 +13274,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G445" t="n">
-        <v>12.7802686691284</v>
+        <v>12.7802677154541</v>
       </c>
       <c r="H445" t="n">
         <v>146927</v>
@@ -13332,7 +13332,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G447" t="n">
-        <v>12.7033367156982</v>
+        <v>12.7033376693726</v>
       </c>
       <c r="H447" t="n">
         <v>82919</v>
@@ -13390,7 +13390,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G449" t="n">
-        <v>12.809118270874</v>
+        <v>12.8091173171997</v>
       </c>
       <c r="H449" t="n">
         <v>66508</v>
@@ -13448,7 +13448,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G451" t="n">
-        <v>12.9629802703857</v>
+        <v>12.9629812240601</v>
       </c>
       <c r="H451" t="n">
         <v>102016</v>
@@ -13564,7 +13564,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G455" t="n">
-        <v>11.7513074874878</v>
+        <v>11.7513084411621</v>
       </c>
       <c r="H455" t="n">
         <v>152747</v>
@@ -13709,7 +13709,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G460" t="n">
-        <v>12.1744318008423</v>
+        <v>12.1744327545166</v>
       </c>
       <c r="H460" t="n">
         <v>97426</v>
@@ -13738,7 +13738,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G461" t="n">
-        <v>12.1551990509033</v>
+        <v>12.1552000045776</v>
       </c>
       <c r="H461" t="n">
         <v>94886</v>
@@ -13796,7 +13796,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G463" t="n">
-        <v>12.0494165420532</v>
+        <v>12.0494174957275</v>
       </c>
       <c r="H463" t="n">
         <v>59080</v>
@@ -13854,7 +13854,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G465" t="n">
-        <v>12.8668165206909</v>
+        <v>12.8668174743652</v>
       </c>
       <c r="H465" t="n">
         <v>259031</v>
@@ -13912,7 +13912,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G467" t="n">
-        <v>12.7514200210571</v>
+        <v>12.7514190673828</v>
       </c>
       <c r="H467" t="n">
         <v>287755</v>
@@ -13941,7 +13941,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G468" t="n">
-        <v>12.7706527709961</v>
+        <v>12.7706518173218</v>
       </c>
       <c r="H468" t="n">
         <v>76794</v>
@@ -32040,9 +32040,38 @@
         <v>5.55999994277954</v>
       </c>
       <c r="H1092" t="n">
-        <v>482085</v>
+        <v>490614</v>
       </c>
       <c r="I1092" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1093" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1093" t="n">
+        <v>5.61999988555908</v>
+      </c>
+      <c r="D1093" t="n">
+        <v>5.71000003814697</v>
+      </c>
+      <c r="E1093" t="n">
+        <v>5.55999994277954</v>
+      </c>
+      <c r="F1093" t="n">
+        <v>5.54500007629395</v>
+      </c>
+      <c r="G1093" t="n">
+        <v>5.54500007629395</v>
+      </c>
+      <c r="H1093" t="n">
+        <v>249364</v>
+      </c>
+      <c r="I1093" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DNR.MI.xlsx
+++ b/data/DNR.MI.xlsx
@@ -456,7 +456,7 @@
         <v>13.25</v>
       </c>
       <c r="G3" t="n">
-        <v>12.66064453125</v>
+        <v>12.6606454849243</v>
       </c>
       <c r="H3" t="n">
         <v>74987</v>
@@ -485,7 +485,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>12.6128692626953</v>
+        <v>12.612868309021</v>
       </c>
       <c r="H4" t="n">
         <v>150287</v>
@@ -514,7 +514,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G5" t="n">
-        <v>12.4886503219604</v>
+        <v>12.4886512756348</v>
       </c>
       <c r="H5" t="n">
         <v>167412</v>
@@ -572,7 +572,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G7" t="n">
-        <v>12.5077610015869</v>
+        <v>12.5077619552612</v>
       </c>
       <c r="H7" t="n">
         <v>117337</v>
@@ -717,7 +717,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G12" t="n">
-        <v>12.4504308700562</v>
+        <v>12.4504299163818</v>
       </c>
       <c r="H12" t="n">
         <v>94003</v>
@@ -833,7 +833,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G16" t="n">
-        <v>13.415506362915</v>
+        <v>13.4155054092407</v>
       </c>
       <c r="H16" t="n">
         <v>258303</v>
@@ -920,7 +920,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G19" t="n">
-        <v>13.5683879852295</v>
+        <v>13.5683898925781</v>
       </c>
       <c r="H19" t="n">
         <v>254487</v>
@@ -949,7 +949,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G20" t="n">
-        <v>13.8072700500488</v>
+        <v>13.8072690963745</v>
       </c>
       <c r="H20" t="n">
         <v>301266</v>
@@ -978,7 +978,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G21" t="n">
-        <v>14.0748147964478</v>
+        <v>14.0748138427734</v>
       </c>
       <c r="H21" t="n">
         <v>546294</v>
@@ -1007,7 +1007,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G22" t="n">
-        <v>14.0652599334717</v>
+        <v>14.065260887146</v>
       </c>
       <c r="H22" t="n">
         <v>577409</v>
@@ -1036,7 +1036,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>14.1417026519775</v>
+        <v>14.1417016983032</v>
       </c>
       <c r="H23" t="n">
         <v>170138</v>
@@ -1094,7 +1094,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G25" t="n">
-        <v>13.9410429000854</v>
+        <v>13.9410419464111</v>
       </c>
       <c r="H25" t="n">
         <v>258800</v>
@@ -1123,7 +1123,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G26" t="n">
-        <v>14.1608114242554</v>
+        <v>14.1608123779297</v>
       </c>
       <c r="H26" t="n">
         <v>270595</v>
@@ -1181,7 +1181,7 @@
         <v>14.75</v>
       </c>
       <c r="G28" t="n">
-        <v>14.0939254760742</v>
+        <v>14.0939264297485</v>
       </c>
       <c r="H28" t="n">
         <v>136578</v>
@@ -1268,7 +1268,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G31" t="n">
-        <v>13.549280166626</v>
+        <v>13.5492792129517</v>
       </c>
       <c r="H31" t="n">
         <v>152273</v>
@@ -1297,7 +1297,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G32" t="n">
-        <v>13.5683879852295</v>
+        <v>13.5683898925781</v>
       </c>
       <c r="H32" t="n">
         <v>138086</v>
@@ -1326,7 +1326,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G33" t="n">
-        <v>13.7403831481934</v>
+        <v>13.7403841018677</v>
       </c>
       <c r="H33" t="n">
         <v>47665</v>
@@ -1355,7 +1355,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G34" t="n">
-        <v>13.3486204147339</v>
+        <v>13.3486194610596</v>
       </c>
       <c r="H34" t="n">
         <v>107934</v>
@@ -1384,7 +1384,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G35" t="n">
-        <v>13.5397243499756</v>
+        <v>13.5397233963013</v>
       </c>
       <c r="H35" t="n">
         <v>88256</v>
@@ -1413,7 +1413,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G36" t="n">
-        <v>13.3486204147339</v>
+        <v>13.3486194610596</v>
       </c>
       <c r="H36" t="n">
         <v>80762</v>
@@ -1442,7 +1442,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G37" t="n">
-        <v>13.2912883758545</v>
+        <v>13.2912893295288</v>
       </c>
       <c r="H37" t="n">
         <v>64058</v>
@@ -1471,7 +1471,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G38" t="n">
-        <v>13.4250612258911</v>
+        <v>13.4250621795654</v>
       </c>
       <c r="H38" t="n">
         <v>146037</v>
@@ -1500,7 +1500,7 @@
         <v>14.3299999237061</v>
       </c>
       <c r="G39" t="n">
-        <v>13.6926069259644</v>
+        <v>13.6926078796387</v>
       </c>
       <c r="H39" t="n">
         <v>213096</v>
@@ -1529,7 +1529,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G40" t="n">
-        <v>13.8454904556274</v>
+        <v>13.8454895019531</v>
       </c>
       <c r="H40" t="n">
         <v>109728</v>
@@ -1616,7 +1616,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>15.3838777542114</v>
+        <v>15.3838787078857</v>
       </c>
       <c r="H43" t="n">
         <v>436799</v>
@@ -1645,7 +1645,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G44" t="n">
-        <v>16.1387405395508</v>
+        <v>16.1387386322021</v>
       </c>
       <c r="H44" t="n">
         <v>348418</v>
@@ -1761,7 +1761,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G48" t="n">
-        <v>16.0909633636475</v>
+        <v>16.0909614562988</v>
       </c>
       <c r="H48" t="n">
         <v>581768</v>
@@ -1790,7 +1790,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G49" t="n">
-        <v>15.6418695449829</v>
+        <v>15.6418685913086</v>
       </c>
       <c r="H49" t="n">
         <v>782970</v>
@@ -1848,7 +1848,7 @@
         <v>15.8900003433228</v>
       </c>
       <c r="G51" t="n">
-        <v>15.1832189559937</v>
+        <v>15.183219909668</v>
       </c>
       <c r="H51" t="n">
         <v>161269</v>
@@ -1906,7 +1906,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G53" t="n">
-        <v>14.2372541427612</v>
+        <v>14.2372531890869</v>
       </c>
       <c r="H53" t="n">
         <v>139086</v>
@@ -1935,7 +1935,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G54" t="n">
-        <v>14.0079278945923</v>
+        <v>14.0079288482666</v>
       </c>
       <c r="H54" t="n">
         <v>147319</v>
@@ -2022,7 +2022,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G57" t="n">
-        <v>14.7436790466309</v>
+        <v>14.7436800003052</v>
       </c>
       <c r="H57" t="n">
         <v>220752</v>
@@ -2080,7 +2080,7 @@
         <v>15.75</v>
       </c>
       <c r="G59" t="n">
-        <v>15.0494451522827</v>
+        <v>15.049446105957</v>
       </c>
       <c r="H59" t="n">
         <v>87541</v>
@@ -2138,7 +2138,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G61" t="n">
-        <v>15.5558729171753</v>
+        <v>15.5558710098267</v>
       </c>
       <c r="H61" t="n">
         <v>217368</v>
@@ -2196,7 +2196,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G63" t="n">
-        <v>15.1736640930176</v>
+        <v>15.1736631393433</v>
       </c>
       <c r="H63" t="n">
         <v>103387</v>
@@ -2254,7 +2254,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G65" t="n">
-        <v>15.746973991394</v>
+        <v>15.7469749450684</v>
       </c>
       <c r="H65" t="n">
         <v>163756</v>
@@ -2341,7 +2341,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G68" t="n">
-        <v>15.5176515579224</v>
+        <v>15.517650604248</v>
       </c>
       <c r="H68" t="n">
         <v>132919</v>
@@ -2486,7 +2486,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G73" t="n">
-        <v>14.3519153594971</v>
+        <v>14.3519172668457</v>
       </c>
       <c r="H73" t="n">
         <v>172203</v>
@@ -2515,7 +2515,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G74" t="n">
-        <v>14.3136949539185</v>
+        <v>14.3136940002441</v>
       </c>
       <c r="H74" t="n">
         <v>173782</v>
@@ -2573,7 +2573,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>14.3805818557739</v>
+        <v>14.3805809020996</v>
       </c>
       <c r="H76" t="n">
         <v>129903</v>
@@ -2602,7 +2602,7 @@
         <v>15.5</v>
       </c>
       <c r="G77" t="n">
-        <v>14.8105659484863</v>
+        <v>14.810564994812</v>
       </c>
       <c r="H77" t="n">
         <v>108895</v>
@@ -2631,7 +2631,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G78" t="n">
-        <v>14.0652599334717</v>
+        <v>14.065260887146</v>
       </c>
       <c r="H78" t="n">
         <v>153369</v>
@@ -2718,7 +2718,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="n">
-        <v>14.3328065872192</v>
+        <v>14.3328056335449</v>
       </c>
       <c r="H81" t="n">
         <v>137258</v>
@@ -2747,7 +2747,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G82" t="n">
-        <v>14.2659196853638</v>
+        <v>14.2659187316895</v>
       </c>
       <c r="H82" t="n">
         <v>101770</v>
@@ -2805,7 +2805,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G84" t="n">
-        <v>13.1670713424683</v>
+        <v>13.1670703887939</v>
       </c>
       <c r="H84" t="n">
         <v>628995</v>
@@ -3008,7 +3008,7 @@
         <v>15.5</v>
       </c>
       <c r="G91" t="n">
-        <v>14.8105659484863</v>
+        <v>14.810564994812</v>
       </c>
       <c r="H91" t="n">
         <v>119552</v>
@@ -3037,7 +3037,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G92" t="n">
-        <v>14.5621299743652</v>
+        <v>14.5621309280396</v>
       </c>
       <c r="H92" t="n">
         <v>143627</v>
@@ -3066,7 +3066,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G93" t="n">
-        <v>14.6767930984497</v>
+        <v>14.6767921447754</v>
       </c>
       <c r="H93" t="n">
         <v>110219</v>
@@ -3153,7 +3153,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>14.6194629669189</v>
+        <v>14.6194620132446</v>
       </c>
       <c r="H96" t="n">
         <v>186490</v>
@@ -3182,7 +3182,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G97" t="n">
-        <v>14.8678970336914</v>
+        <v>14.8678979873657</v>
       </c>
       <c r="H97" t="n">
         <v>106899</v>
@@ -3211,7 +3211,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G98" t="n">
-        <v>14.8678970336914</v>
+        <v>14.8678979873657</v>
       </c>
       <c r="H98" t="n">
         <v>69896</v>
@@ -3298,7 +3298,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G101" t="n">
-        <v>15.326548576355</v>
+        <v>15.3265476226807</v>
       </c>
       <c r="H101" t="n">
         <v>177567</v>
@@ -3327,7 +3327,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G102" t="n">
-        <v>15.3456573486328</v>
+        <v>15.3456554412842</v>
       </c>
       <c r="H102" t="n">
         <v>1185858</v>
@@ -3356,7 +3356,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G103" t="n">
-        <v>15.3074369430542</v>
+        <v>15.3074359893799</v>
       </c>
       <c r="H103" t="n">
         <v>144419</v>
@@ -3443,7 +3443,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G106" t="n">
-        <v>14.2754735946655</v>
+        <v>14.2754745483398</v>
       </c>
       <c r="H106" t="n">
         <v>86836</v>
@@ -3472,7 +3472,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G107" t="n">
-        <v>14.6576824188232</v>
+        <v>14.6576833724976</v>
       </c>
       <c r="H107" t="n">
         <v>112801</v>
@@ -3530,7 +3530,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G109" t="n">
-        <v>14.8487863540649</v>
+        <v>14.8487854003906</v>
       </c>
       <c r="H109" t="n">
         <v>53044</v>
@@ -3559,7 +3559,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G110" t="n">
-        <v>15.0876665115356</v>
+        <v>15.08766746521</v>
       </c>
       <c r="H110" t="n">
         <v>72044</v>
@@ -3588,7 +3588,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G111" t="n">
-        <v>14.9443387985229</v>
+        <v>14.9443378448486</v>
       </c>
       <c r="H111" t="n">
         <v>83241</v>
@@ -3617,7 +3617,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G112" t="n">
-        <v>14.6481266021729</v>
+        <v>14.6481275558472</v>
       </c>
       <c r="H112" t="n">
         <v>60854</v>
@@ -3675,7 +3675,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G114" t="n">
-        <v>14.7819013595581</v>
+        <v>14.7819004058838</v>
       </c>
       <c r="H114" t="n">
         <v>173217</v>
@@ -3733,7 +3733,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G116" t="n">
-        <v>14.4570226669312</v>
+        <v>14.4570236206055</v>
       </c>
       <c r="H116" t="n">
         <v>75449</v>
@@ -3791,7 +3791,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G118" t="n">
-        <v>14.0461502075195</v>
+        <v>14.0461492538452</v>
       </c>
       <c r="H118" t="n">
         <v>88132</v>
@@ -3820,7 +3820,7 @@
         <v>14.5</v>
       </c>
       <c r="G119" t="n">
-        <v>13.8550453186035</v>
+        <v>13.8550462722778</v>
       </c>
       <c r="H119" t="n">
         <v>88896</v>
@@ -3849,7 +3849,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>13.7594928741455</v>
+        <v>13.7594938278198</v>
       </c>
       <c r="H120" t="n">
         <v>41310</v>
@@ -3965,7 +3965,7 @@
         <v>14.5</v>
       </c>
       <c r="G124" t="n">
-        <v>13.8550453186035</v>
+        <v>13.8550462722778</v>
       </c>
       <c r="H124" t="n">
         <v>15822</v>
@@ -3994,7 +3994,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G125" t="n">
-        <v>14.4952449798584</v>
+        <v>14.4952440261841</v>
       </c>
       <c r="H125" t="n">
         <v>221654</v>
@@ -4023,7 +4023,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G126" t="n">
-        <v>14.7150135040283</v>
+        <v>14.715012550354</v>
       </c>
       <c r="H126" t="n">
         <v>141731</v>
@@ -4110,7 +4110,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G129" t="n">
-        <v>15.1641092300415</v>
+        <v>15.1641082763672</v>
       </c>
       <c r="H129" t="n">
         <v>73585</v>
@@ -4168,7 +4168,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G131" t="n">
-        <v>15.0876665115356</v>
+        <v>15.08766746521</v>
       </c>
       <c r="H131" t="n">
         <v>223782</v>
@@ -4226,7 +4226,7 @@
         <v>15.75</v>
       </c>
       <c r="G133" t="n">
-        <v>15.0494451522827</v>
+        <v>15.049446105957</v>
       </c>
       <c r="H133" t="n">
         <v>54662</v>
@@ -4255,7 +4255,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>14.953893661499</v>
+        <v>14.9538946151733</v>
       </c>
       <c r="H134" t="n">
         <v>62972</v>
@@ -4342,7 +4342,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G137" t="n">
-        <v>15.1736640930176</v>
+        <v>15.1736631393433</v>
       </c>
       <c r="H137" t="n">
         <v>135405</v>
@@ -4371,7 +4371,7 @@
         <v>16.5</v>
       </c>
       <c r="G138" t="n">
-        <v>15.7660846710205</v>
+        <v>15.7660865783691</v>
       </c>
       <c r="H138" t="n">
         <v>318203</v>
@@ -4400,7 +4400,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G139" t="n">
-        <v>16.3011798858643</v>
+        <v>16.3011779785156</v>
       </c>
       <c r="H139" t="n">
         <v>212600</v>
@@ -4429,7 +4429,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G140" t="n">
-        <v>16.1865158081055</v>
+        <v>16.1865139007568</v>
       </c>
       <c r="H140" t="n">
         <v>143796</v>
@@ -4458,7 +4458,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G141" t="n">
-        <v>16.2534008026123</v>
+        <v>16.2534027099609</v>
       </c>
       <c r="H141" t="n">
         <v>206345</v>
@@ -4574,7 +4574,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G145" t="n">
-        <v>16.2916202545166</v>
+        <v>16.2916221618652</v>
       </c>
       <c r="H145" t="n">
         <v>134728</v>
@@ -4603,7 +4603,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G146" t="n">
-        <v>16.7693843841553</v>
+        <v>16.769380569458</v>
       </c>
       <c r="H146" t="n">
         <v>112560</v>
@@ -4632,7 +4632,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G147" t="n">
-        <v>16.1769599914551</v>
+        <v>16.1769618988037</v>
       </c>
       <c r="H147" t="n">
         <v>432672</v>
@@ -4661,7 +4661,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G148" t="n">
-        <v>15.842529296875</v>
+        <v>15.8425283432007</v>
       </c>
       <c r="H148" t="n">
         <v>256187</v>
@@ -4719,7 +4719,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G150" t="n">
-        <v>15.6418695449829</v>
+        <v>15.6418685913086</v>
       </c>
       <c r="H150" t="n">
         <v>102652</v>
@@ -4806,7 +4806,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G153" t="n">
-        <v>16.5878353118896</v>
+        <v>16.587833404541</v>
       </c>
       <c r="H153" t="n">
         <v>137920</v>
@@ -4951,7 +4951,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G158" t="n">
-        <v>17.4669132232666</v>
+        <v>17.4669151306152</v>
       </c>
       <c r="H158" t="n">
         <v>73047</v>
@@ -5096,7 +5096,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G163" t="n">
-        <v>17.2089214324951</v>
+        <v>17.2089233398438</v>
       </c>
       <c r="H163" t="n">
         <v>50813</v>
@@ -5125,7 +5125,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G164" t="n">
-        <v>17.5529117584229</v>
+        <v>17.5529098510742</v>
       </c>
       <c r="H164" t="n">
         <v>38762</v>
@@ -5154,7 +5154,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G165" t="n">
-        <v>17.9542274475098</v>
+        <v>17.9542293548584</v>
       </c>
       <c r="H165" t="n">
         <v>337145</v>
@@ -5270,7 +5270,7 @@
         <v>19.5</v>
       </c>
       <c r="G169" t="n">
-        <v>18.6326484680176</v>
+        <v>18.6326465606689</v>
       </c>
       <c r="H169" t="n">
         <v>161677</v>
@@ -5299,7 +5299,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G170" t="n">
-        <v>18.9001922607422</v>
+        <v>18.9001941680908</v>
       </c>
       <c r="H170" t="n">
         <v>196771</v>
@@ -5386,7 +5386,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G173" t="n">
-        <v>18.5084323883057</v>
+        <v>18.508430480957</v>
       </c>
       <c r="H173" t="n">
         <v>82218</v>
@@ -5415,7 +5415,7 @@
         <v>18.7700004577637</v>
       </c>
       <c r="G174" t="n">
-        <v>17.9351196289062</v>
+        <v>17.9351177215576</v>
       </c>
       <c r="H174" t="n">
         <v>228634</v>
@@ -5444,7 +5444,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>18.4415435791016</v>
+        <v>18.4415397644043</v>
       </c>
       <c r="H175" t="n">
         <v>73309</v>
@@ -5473,7 +5473,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>17.7726783752441</v>
+        <v>17.7726802825928</v>
       </c>
       <c r="H176" t="n">
         <v>132691</v>
@@ -5531,7 +5531,7 @@
         <v>18.75</v>
       </c>
       <c r="G178" t="n">
-        <v>17.9160079956055</v>
+        <v>17.9160060882568</v>
       </c>
       <c r="H178" t="n">
         <v>107089</v>
@@ -5618,7 +5618,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G181" t="n">
-        <v>18.8237533569336</v>
+        <v>18.823751449585</v>
       </c>
       <c r="H181" t="n">
         <v>95801</v>
@@ -5647,7 +5647,7 @@
         <v>18.75</v>
       </c>
       <c r="G182" t="n">
-        <v>17.9160079956055</v>
+        <v>17.9160060882568</v>
       </c>
       <c r="H182" t="n">
         <v>737639</v>
@@ -5676,7 +5676,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G183" t="n">
-        <v>17.7249031066895</v>
+        <v>17.7249011993408</v>
       </c>
       <c r="H183" t="n">
         <v>316794</v>
@@ -5734,7 +5734,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G185" t="n">
-        <v>16.396728515625</v>
+        <v>16.3967304229736</v>
       </c>
       <c r="H185" t="n">
         <v>282326</v>
@@ -5792,7 +5792,7 @@
         <v>18</v>
       </c>
       <c r="G187" t="n">
-        <v>17.1993675231934</v>
+        <v>17.199369430542</v>
       </c>
       <c r="H187" t="n">
         <v>168778</v>
@@ -5821,7 +5821,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G188" t="n">
-        <v>17.6580181121826</v>
+        <v>17.658016204834</v>
       </c>
       <c r="H188" t="n">
         <v>106658</v>
@@ -5850,7 +5850,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G189" t="n">
-        <v>17.6580181121826</v>
+        <v>17.658016204834</v>
       </c>
       <c r="H189" t="n">
         <v>195062</v>
@@ -5879,7 +5879,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G190" t="n">
-        <v>17.6484603881836</v>
+        <v>17.648458480835</v>
       </c>
       <c r="H190" t="n">
         <v>98265</v>
@@ -5995,7 +5995,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>16.3871746063232</v>
+        <v>16.3871726989746</v>
       </c>
       <c r="H194" t="n">
         <v>289758</v>
@@ -6024,7 +6024,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G195" t="n">
-        <v>16.3011798858643</v>
+        <v>16.3011779785156</v>
       </c>
       <c r="H195" t="n">
         <v>519554</v>
@@ -6111,7 +6111,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G198" t="n">
-        <v>16.3011798858643</v>
+        <v>16.3011779785156</v>
       </c>
       <c r="H198" t="n">
         <v>103373</v>
@@ -6140,7 +6140,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G199" t="n">
-        <v>16.6069450378418</v>
+        <v>16.6069431304932</v>
       </c>
       <c r="H199" t="n">
         <v>89821</v>
@@ -6198,7 +6198,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>16.6260566711426</v>
+        <v>16.6260528564453</v>
       </c>
       <c r="H201" t="n">
         <v>108711</v>
@@ -6227,7 +6227,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G202" t="n">
-        <v>16.5878353118896</v>
+        <v>16.587833404541</v>
       </c>
       <c r="H202" t="n">
         <v>70415</v>
@@ -6256,7 +6256,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G203" t="n">
-        <v>16.7407150268555</v>
+        <v>16.7407188415527</v>
       </c>
       <c r="H203" t="n">
         <v>93120</v>
@@ -6314,7 +6314,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G205" t="n">
-        <v>17.0369281768799</v>
+        <v>17.0369262695312</v>
       </c>
       <c r="H205" t="n">
         <v>107074</v>
@@ -6372,7 +6372,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G207" t="n">
-        <v>16.6547203063965</v>
+        <v>16.6547183990479</v>
       </c>
       <c r="H207" t="n">
         <v>154640</v>
@@ -6401,7 +6401,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G208" t="n">
-        <v>16.9031543731689</v>
+        <v>16.9031562805176</v>
       </c>
       <c r="H208" t="n">
         <v>80044</v>
@@ -6633,7 +6633,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G216" t="n">
-        <v>17.6293506622314</v>
+        <v>17.6293525695801</v>
       </c>
       <c r="H216" t="n">
         <v>202637</v>
@@ -6691,7 +6691,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G218" t="n">
-        <v>18.4415435791016</v>
+        <v>18.4415397644043</v>
       </c>
       <c r="H218" t="n">
         <v>241224</v>
@@ -6720,7 +6720,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G219" t="n">
-        <v>18.4415435791016</v>
+        <v>18.4415397644043</v>
       </c>
       <c r="H219" t="n">
         <v>270484</v>
@@ -6778,7 +6778,7 @@
         <v>19.2700004577637</v>
       </c>
       <c r="G221" t="n">
-        <v>18.5309085845947</v>
+        <v>18.5309104919434</v>
       </c>
       <c r="H221" t="n">
         <v>86313</v>
@@ -6807,7 +6807,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G222" t="n">
-        <v>18.5789890289307</v>
+        <v>18.5789909362793</v>
       </c>
       <c r="H222" t="n">
         <v>75028</v>
@@ -6836,7 +6836,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G223" t="n">
-        <v>18.6559219360352</v>
+        <v>18.6559238433838</v>
       </c>
       <c r="H223" t="n">
         <v>117863</v>
@@ -6894,7 +6894,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G225" t="n">
-        <v>18.6559219360352</v>
+        <v>18.6559238433838</v>
       </c>
       <c r="H225" t="n">
         <v>62425</v>
@@ -7010,7 +7010,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G229" t="n">
-        <v>18.8097858428955</v>
+        <v>18.8097877502441</v>
       </c>
       <c r="H229" t="n">
         <v>69687</v>
@@ -7097,7 +7097,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G232" t="n">
-        <v>18.3674278259277</v>
+        <v>18.3674297332764</v>
       </c>
       <c r="H232" t="n">
         <v>66293</v>
@@ -7155,7 +7155,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>19.1367473602295</v>
+        <v>19.1367454528809</v>
       </c>
       <c r="H234" t="n">
         <v>176092</v>
@@ -7213,7 +7213,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G236" t="n">
-        <v>20.1753215789795</v>
+        <v>20.1753234863281</v>
       </c>
       <c r="H236" t="n">
         <v>286301</v>
@@ -7387,7 +7387,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>19.4252395629883</v>
+        <v>19.4252376556396</v>
       </c>
       <c r="H242" t="n">
         <v>219460</v>
@@ -7416,7 +7416,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G243" t="n">
-        <v>19.0405807495117</v>
+        <v>19.0405788421631</v>
       </c>
       <c r="H243" t="n">
         <v>51065</v>
@@ -7503,7 +7503,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G246" t="n">
-        <v>17.8481388092041</v>
+        <v>17.8481407165527</v>
       </c>
       <c r="H246" t="n">
         <v>191126</v>
@@ -7561,7 +7561,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G248" t="n">
-        <v>18.5789890289307</v>
+        <v>18.5789909362793</v>
       </c>
       <c r="H248" t="n">
         <v>83004</v>
@@ -7590,7 +7590,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G249" t="n">
-        <v>18.4924411773682</v>
+        <v>18.4924430847168</v>
       </c>
       <c r="H249" t="n">
         <v>68327</v>
@@ -7619,7 +7619,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G250" t="n">
-        <v>18.4924411773682</v>
+        <v>18.4924430847168</v>
       </c>
       <c r="H250" t="n">
         <v>136559</v>
@@ -7677,7 +7677,7 @@
         <v>19.5</v>
       </c>
       <c r="G252" t="n">
-        <v>18.7520885467529</v>
+        <v>18.7520866394043</v>
       </c>
       <c r="H252" t="n">
         <v>47907</v>
@@ -7735,7 +7735,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G254" t="n">
-        <v>18.386661529541</v>
+        <v>18.3866634368896</v>
       </c>
       <c r="H254" t="n">
         <v>40747</v>
@@ -7822,7 +7822,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G257" t="n">
-        <v>19.6944999694824</v>
+        <v>19.6944980621338</v>
       </c>
       <c r="H257" t="n">
         <v>62964</v>
@@ -7851,7 +7851,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G258" t="n">
-        <v>20.1368560791016</v>
+        <v>20.1368579864502</v>
       </c>
       <c r="H258" t="n">
         <v>123239</v>
@@ -7909,7 +7909,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G260" t="n">
-        <v>19.5598678588867</v>
+        <v>19.5598697662354</v>
       </c>
       <c r="H260" t="n">
         <v>165590</v>
@@ -7938,7 +7938,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G261" t="n">
-        <v>19.2713756561279</v>
+        <v>19.2713775634766</v>
       </c>
       <c r="H261" t="n">
         <v>226076</v>
@@ -8025,7 +8025,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G264" t="n">
-        <v>19.4829387664795</v>
+        <v>19.4829368591309</v>
       </c>
       <c r="H264" t="n">
         <v>113210</v>
@@ -8199,7 +8199,7 @@
         <v>20.1399993896484</v>
       </c>
       <c r="G270" t="n">
-        <v>19.3675384521484</v>
+        <v>19.3675403594971</v>
       </c>
       <c r="H270" t="n">
         <v>52442</v>
@@ -8228,7 +8228,7 @@
         <v>18.7700004577637</v>
       </c>
       <c r="G271" t="n">
-        <v>18.0500869750977</v>
+        <v>18.050085067749</v>
       </c>
       <c r="H271" t="n">
         <v>522798</v>
@@ -8257,7 +8257,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G272" t="n">
-        <v>17.5019474029541</v>
+        <v>17.5019493103027</v>
       </c>
       <c r="H272" t="n">
         <v>364369</v>
@@ -8315,7 +8315,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G274" t="n">
-        <v>17.5115623474121</v>
+        <v>17.5115642547607</v>
       </c>
       <c r="H274" t="n">
         <v>166261</v>
@@ -8344,7 +8344,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G275" t="n">
-        <v>18.2904987335205</v>
+        <v>18.2904968261719</v>
       </c>
       <c r="H275" t="n">
         <v>226073</v>
@@ -8373,7 +8373,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G276" t="n">
-        <v>18.5020580291748</v>
+        <v>18.5020599365234</v>
       </c>
       <c r="H276" t="n">
         <v>314121</v>
@@ -8431,7 +8431,7 @@
         <v>19.3700008392334</v>
       </c>
       <c r="G278" t="n">
-        <v>18.6270751953125</v>
+        <v>18.6270732879639</v>
       </c>
       <c r="H278" t="n">
         <v>96317</v>
@@ -8489,7 +8489,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G280" t="n">
-        <v>18.6559219360352</v>
+        <v>18.6559238433838</v>
       </c>
       <c r="H280" t="n">
         <v>71432</v>
@@ -8576,7 +8576,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G283" t="n">
-        <v>17.5981101989746</v>
+        <v>17.5981121063232</v>
       </c>
       <c r="H283" t="n">
         <v>79763</v>
@@ -8605,7 +8605,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G284" t="n">
-        <v>17.540412902832</v>
+        <v>17.5404148101807</v>
       </c>
       <c r="H284" t="n">
         <v>101821</v>
@@ -8663,7 +8663,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G286" t="n">
-        <v>17.059591293335</v>
+        <v>17.0595932006836</v>
       </c>
       <c r="H286" t="n">
         <v>83846</v>
@@ -8866,7 +8866,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G293" t="n">
-        <v>17.2134532928467</v>
+        <v>17.213451385498</v>
       </c>
       <c r="H293" t="n">
         <v>97852</v>
@@ -8924,7 +8924,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G295" t="n">
-        <v>17.1749897003174</v>
+        <v>17.1749877929688</v>
       </c>
       <c r="H295" t="n">
         <v>38905</v>
@@ -8953,7 +8953,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G296" t="n">
-        <v>17.2807712554932</v>
+        <v>17.2807693481445</v>
       </c>
       <c r="H296" t="n">
         <v>59361</v>
@@ -9098,7 +9098,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G301" t="n">
-        <v>16.4441375732422</v>
+        <v>16.4441394805908</v>
       </c>
       <c r="H301" t="n">
         <v>93310</v>
@@ -9127,7 +9127,7 @@
         <v>17</v>
       </c>
       <c r="G302" t="n">
-        <v>16.3479747772217</v>
+        <v>16.347972869873</v>
       </c>
       <c r="H302" t="n">
         <v>123413</v>
@@ -9185,7 +9185,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G304" t="n">
-        <v>16.7230129241943</v>
+        <v>16.723014831543</v>
       </c>
       <c r="H304" t="n">
         <v>322231</v>
@@ -9359,7 +9359,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G310" t="n">
-        <v>15.5401906967163</v>
+        <v>15.5401916503906</v>
       </c>
       <c r="H310" t="n">
         <v>75719</v>
@@ -9417,7 +9417,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>15.4824924468994</v>
+        <v>15.4824934005737</v>
       </c>
       <c r="H312" t="n">
         <v>47778</v>
@@ -9475,7 +9475,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G314" t="n">
-        <v>15.655590057373</v>
+        <v>15.6555881500244</v>
       </c>
       <c r="H314" t="n">
         <v>70184</v>
@@ -9533,7 +9533,7 @@
         <v>16.2700004577637</v>
       </c>
       <c r="G316" t="n">
-        <v>15.6459722518921</v>
+        <v>15.6459732055664</v>
       </c>
       <c r="H316" t="n">
         <v>152152</v>
@@ -9591,7 +9591,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G318" t="n">
-        <v>14.4150667190552</v>
+        <v>14.4150657653809</v>
       </c>
       <c r="H318" t="n">
         <v>129315</v>
@@ -9649,7 +9649,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G320" t="n">
-        <v>14.318902015686</v>
+        <v>14.3189010620117</v>
       </c>
       <c r="H320" t="n">
         <v>84956</v>
@@ -9765,7 +9765,7 @@
         <v>15</v>
       </c>
       <c r="G324" t="n">
-        <v>14.4246835708618</v>
+        <v>14.4246826171875</v>
       </c>
       <c r="H324" t="n">
         <v>91074</v>
@@ -9852,7 +9852,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G327" t="n">
-        <v>14.0881061553955</v>
+        <v>14.0881052017212</v>
       </c>
       <c r="H327" t="n">
         <v>66396</v>
@@ -9881,7 +9881,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G328" t="n">
-        <v>14.2227373123169</v>
+        <v>14.2227363586426</v>
       </c>
       <c r="H328" t="n">
         <v>104116</v>
@@ -10026,7 +10026,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G333" t="n">
-        <v>12.8572006225586</v>
+        <v>12.8571996688843</v>
       </c>
       <c r="H333" t="n">
         <v>104403</v>
@@ -10258,7 +10258,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G341" t="n">
-        <v>13.2803239822388</v>
+        <v>13.2803249359131</v>
       </c>
       <c r="H341" t="n">
         <v>70862</v>
@@ -10316,7 +10316,7 @@
         <v>14.0100002288818</v>
       </c>
       <c r="G343" t="n">
-        <v>13.4726533889771</v>
+        <v>13.4726543426514</v>
       </c>
       <c r="H343" t="n">
         <v>569136</v>
@@ -10345,7 +10345,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G344" t="n">
-        <v>13.0399141311646</v>
+        <v>13.0399131774902</v>
       </c>
       <c r="H344" t="n">
         <v>146201</v>
@@ -10374,7 +10374,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G345" t="n">
-        <v>13.6553649902344</v>
+        <v>13.6553659439087</v>
       </c>
       <c r="H345" t="n">
         <v>126227</v>
@@ -10432,7 +10432,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G347" t="n">
-        <v>14.6362438201904</v>
+        <v>14.6362447738647</v>
       </c>
       <c r="H347" t="n">
         <v>215592</v>
@@ -10461,7 +10461,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G348" t="n">
-        <v>14.2227373123169</v>
+        <v>14.2227363586426</v>
       </c>
       <c r="H348" t="n">
         <v>121936</v>
@@ -10519,7 +10519,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G350" t="n">
-        <v>14.2708187103271</v>
+        <v>14.2708196640015</v>
       </c>
       <c r="H350" t="n">
         <v>157799</v>
@@ -10548,7 +10548,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G351" t="n">
-        <v>14.1073389053345</v>
+        <v>14.1073398590088</v>
       </c>
       <c r="H351" t="n">
         <v>93291</v>
@@ -10577,7 +10577,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G352" t="n">
-        <v>14.2515859603882</v>
+        <v>14.2515869140625</v>
       </c>
       <c r="H352" t="n">
         <v>74240</v>
@@ -10606,7 +10606,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G353" t="n">
-        <v>14.3092851638794</v>
+        <v>14.3092861175537</v>
       </c>
       <c r="H353" t="n">
         <v>104165</v>
@@ -10693,7 +10693,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G356" t="n">
-        <v>13.7322978973389</v>
+        <v>13.7322969436646</v>
       </c>
       <c r="H356" t="n">
         <v>217186</v>
@@ -10751,7 +10751,7 @@
         <v>14.3900003433228</v>
       </c>
       <c r="G358" t="n">
-        <v>13.8380794525146</v>
+        <v>13.8380784988403</v>
       </c>
       <c r="H358" t="n">
         <v>106575</v>
@@ -10780,7 +10780,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G359" t="n">
-        <v>13.664981842041</v>
+        <v>13.6649827957153</v>
       </c>
       <c r="H359" t="n">
         <v>97011</v>
@@ -10809,7 +10809,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G360" t="n">
-        <v>13.2707071304321</v>
+        <v>13.2707080841064</v>
       </c>
       <c r="H360" t="n">
         <v>139158</v>
@@ -10838,7 +10838,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G361" t="n">
-        <v>13.5399694442749</v>
+        <v>13.5399684906006</v>
       </c>
       <c r="H361" t="n">
         <v>102042</v>
@@ -11041,7 +11041,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G368" t="n">
-        <v>14.7131767272949</v>
+        <v>14.7131757736206</v>
       </c>
       <c r="H368" t="n">
         <v>469164</v>
@@ -11128,7 +11128,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G371" t="n">
-        <v>15.68443775177</v>
+        <v>15.6844387054443</v>
       </c>
       <c r="H371" t="n">
         <v>353221</v>
@@ -11273,7 +11273,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G376" t="n">
-        <v>15.0305185317993</v>
+        <v>15.0305194854736</v>
       </c>
       <c r="H376" t="n">
         <v>110938</v>
@@ -11331,7 +11331,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G378" t="n">
-        <v>14.9632043838501</v>
+        <v>14.9632034301758</v>
       </c>
       <c r="H378" t="n">
         <v>149811</v>
@@ -11389,7 +11389,7 @@
         <v>15.0900001525879</v>
       </c>
       <c r="G380" t="n">
-        <v>14.5112314224243</v>
+        <v>14.51123046875</v>
       </c>
       <c r="H380" t="n">
         <v>88556</v>
@@ -11447,7 +11447,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G382" t="n">
-        <v>14.8958892822266</v>
+        <v>14.8958883285522</v>
       </c>
       <c r="H382" t="n">
         <v>111609</v>
@@ -11476,7 +11476,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G383" t="n">
-        <v>14.867039680481</v>
+        <v>14.8670387268066</v>
       </c>
       <c r="H383" t="n">
         <v>127709</v>
@@ -11534,7 +11534,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G385" t="n">
-        <v>14.4439153671265</v>
+        <v>14.4439163208008</v>
       </c>
       <c r="H385" t="n">
         <v>156312</v>
@@ -11563,7 +11563,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G386" t="n">
-        <v>14.0977220535278</v>
+        <v>14.0977230072021</v>
       </c>
       <c r="H386" t="n">
         <v>236798</v>
@@ -11621,7 +11621,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G388" t="n">
-        <v>13.982325553894</v>
+        <v>13.9823265075684</v>
       </c>
       <c r="H388" t="n">
         <v>99895</v>
@@ -11708,7 +11708,7 @@
         <v>14.2700004577637</v>
       </c>
       <c r="G391" t="n">
-        <v>13.7226819992065</v>
+        <v>13.7226810455322</v>
       </c>
       <c r="H391" t="n">
         <v>186975</v>
@@ -11737,7 +11737,7 @@
         <v>14.5</v>
       </c>
       <c r="G392" t="n">
-        <v>13.9438591003418</v>
+        <v>13.9438600540161</v>
       </c>
       <c r="H392" t="n">
         <v>133628</v>
@@ -11795,7 +11795,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G394" t="n">
-        <v>13.7419147491455</v>
+        <v>13.7419137954712</v>
       </c>
       <c r="H394" t="n">
         <v>128563</v>
@@ -11882,7 +11882,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G397" t="n">
-        <v>13.664981842041</v>
+        <v>13.6649827957153</v>
       </c>
       <c r="H397" t="n">
         <v>175445</v>
@@ -11940,7 +11940,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G399" t="n">
-        <v>14.0592575073242</v>
+        <v>14.0592565536499</v>
       </c>
       <c r="H399" t="n">
         <v>307261</v>
@@ -11969,7 +11969,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G400" t="n">
-        <v>14.0784902572632</v>
+        <v>14.0784912109375</v>
       </c>
       <c r="H400" t="n">
         <v>204846</v>
@@ -12085,7 +12085,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G404" t="n">
-        <v>13.3764886856079</v>
+        <v>13.3764896392822</v>
       </c>
       <c r="H404" t="n">
         <v>147194</v>
@@ -12172,7 +12172,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>13.6553649902344</v>
+        <v>13.6553659439087</v>
       </c>
       <c r="H407" t="n">
         <v>163196</v>
@@ -12259,7 +12259,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G410" t="n">
-        <v>14.7901077270508</v>
+        <v>14.7901067733765</v>
       </c>
       <c r="H410" t="n">
         <v>220807</v>
@@ -12491,7 +12491,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G418" t="n">
-        <v>14.6458597183228</v>
+        <v>14.6458606719971</v>
       </c>
       <c r="H418" t="n">
         <v>94315</v>
@@ -12549,7 +12549,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G420" t="n">
-        <v>14.9632043838501</v>
+        <v>14.9632034301758</v>
       </c>
       <c r="H420" t="n">
         <v>161886</v>
@@ -12607,7 +12607,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G422" t="n">
-        <v>14.3092851638794</v>
+        <v>14.3092861175537</v>
       </c>
       <c r="H422" t="n">
         <v>102639</v>
@@ -12665,7 +12665,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G424" t="n">
-        <v>14.0688743591309</v>
+        <v>14.0688734054565</v>
       </c>
       <c r="H424" t="n">
         <v>101301</v>
@@ -12694,7 +12694,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G425" t="n">
-        <v>14.155421257019</v>
+        <v>14.1554222106934</v>
       </c>
       <c r="H425" t="n">
         <v>117944</v>
@@ -12752,7 +12752,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G427" t="n">
-        <v>13.664981842041</v>
+        <v>13.6649827957153</v>
       </c>
       <c r="H427" t="n">
         <v>159222</v>
@@ -12781,7 +12781,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G428" t="n">
-        <v>13.8188457489014</v>
+        <v>13.8188447952271</v>
       </c>
       <c r="H428" t="n">
         <v>206029</v>
@@ -12868,7 +12868,7 @@
         <v>14.1899995803833</v>
       </c>
       <c r="G431" t="n">
-        <v>13.6457490921021</v>
+        <v>13.6457500457764</v>
       </c>
       <c r="H431" t="n">
         <v>223671</v>
@@ -12955,7 +12955,7 @@
         <v>13.25</v>
       </c>
       <c r="G434" t="n">
-        <v>12.7418022155762</v>
+        <v>12.7418031692505</v>
       </c>
       <c r="H434" t="n">
         <v>207043</v>
@@ -12984,7 +12984,7 @@
         <v>13.25</v>
       </c>
       <c r="G435" t="n">
-        <v>12.7418022155762</v>
+        <v>12.7418031692505</v>
       </c>
       <c r="H435" t="n">
         <v>214799</v>
@@ -13042,7 +13042,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G437" t="n">
-        <v>12.7033376693726</v>
+        <v>12.7033367156982</v>
       </c>
       <c r="H437" t="n">
         <v>188482</v>
@@ -13100,7 +13100,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G439" t="n">
-        <v>12.8572006225586</v>
+        <v>12.8571996688843</v>
       </c>
       <c r="H439" t="n">
         <v>90236</v>
@@ -13187,7 +13187,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G442" t="n">
-        <v>12.9725971221924</v>
+        <v>12.9725980758667</v>
       </c>
       <c r="H442" t="n">
         <v>207392</v>
@@ -13274,7 +13274,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G445" t="n">
-        <v>12.7802677154541</v>
+        <v>12.7802686691284</v>
       </c>
       <c r="H445" t="n">
         <v>146927</v>
@@ -13332,7 +13332,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G447" t="n">
-        <v>12.7033376693726</v>
+        <v>12.7033367156982</v>
       </c>
       <c r="H447" t="n">
         <v>82919</v>
@@ -13390,7 +13390,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G449" t="n">
-        <v>12.8091173171997</v>
+        <v>12.809118270874</v>
       </c>
       <c r="H449" t="n">
         <v>66508</v>
@@ -13448,7 +13448,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G451" t="n">
-        <v>12.9629812240601</v>
+        <v>12.9629802703857</v>
       </c>
       <c r="H451" t="n">
         <v>102016</v>
@@ -13564,7 +13564,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G455" t="n">
-        <v>11.7513084411621</v>
+        <v>11.7513074874878</v>
       </c>
       <c r="H455" t="n">
         <v>152747</v>
@@ -13709,7 +13709,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G460" t="n">
-        <v>12.1744327545166</v>
+        <v>12.1744318008423</v>
       </c>
       <c r="H460" t="n">
         <v>97426</v>
@@ -13738,7 +13738,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G461" t="n">
-        <v>12.1552000045776</v>
+        <v>12.1551990509033</v>
       </c>
       <c r="H461" t="n">
         <v>94886</v>
@@ -13796,7 +13796,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G463" t="n">
-        <v>12.0494174957275</v>
+        <v>12.0494165420532</v>
       </c>
       <c r="H463" t="n">
         <v>59080</v>
@@ -13854,7 +13854,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G465" t="n">
-        <v>12.8668174743652</v>
+        <v>12.8668165206909</v>
       </c>
       <c r="H465" t="n">
         <v>259031</v>
@@ -13912,7 +13912,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G467" t="n">
-        <v>12.7514190673828</v>
+        <v>12.7514200210571</v>
       </c>
       <c r="H467" t="n">
         <v>287755</v>
@@ -13941,7 +13941,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G468" t="n">
-        <v>12.7706518173218</v>
+        <v>12.7706527709961</v>
       </c>
       <c r="H468" t="n">
         <v>76794</v>
@@ -32060,7 +32060,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="E1093" t="n">
-        <v>5.55999994277954</v>
+        <v>5.54500007629395</v>
       </c>
       <c r="F1093" t="n">
         <v>5.54500007629395</v>
@@ -32069,9 +32069,38 @@
         <v>5.54500007629395</v>
       </c>
       <c r="H1093" t="n">
-        <v>249364</v>
+        <v>253778</v>
       </c>
       <c r="I1093" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1094" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1094" t="n">
+        <v>5.63000011444092</v>
+      </c>
+      <c r="D1094" t="n">
+        <v>5.63500022888184</v>
+      </c>
+      <c r="E1094" t="n">
+        <v>5.55499982833862</v>
+      </c>
+      <c r="F1094" t="n">
+        <v>5.60500001907349</v>
+      </c>
+      <c r="G1094" t="n">
+        <v>5.60500001907349</v>
+      </c>
+      <c r="H1094" t="n">
+        <v>237833</v>
+      </c>
+      <c r="I1094" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DNR.MI.xlsx
+++ b/data/DNR.MI.xlsx
@@ -456,7 +456,7 @@
         <v>13.25</v>
       </c>
       <c r="G3" t="n">
-        <v>12.6606454849243</v>
+        <v>12.66064453125</v>
       </c>
       <c r="H3" t="n">
         <v>74987</v>
@@ -485,7 +485,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G4" t="n">
-        <v>12.612868309021</v>
+        <v>12.6128692626953</v>
       </c>
       <c r="H4" t="n">
         <v>150287</v>
@@ -514,7 +514,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G5" t="n">
-        <v>12.4886512756348</v>
+        <v>12.4886503219604</v>
       </c>
       <c r="H5" t="n">
         <v>167412</v>
@@ -572,7 +572,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G7" t="n">
-        <v>12.5077619552612</v>
+        <v>12.5077629089355</v>
       </c>
       <c r="H7" t="n">
         <v>117337</v>
@@ -717,7 +717,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G12" t="n">
-        <v>12.4504299163818</v>
+        <v>12.4504308700562</v>
       </c>
       <c r="H12" t="n">
         <v>94003</v>
@@ -746,7 +746,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G13" t="n">
-        <v>12.5459823608398</v>
+        <v>12.5459833145142</v>
       </c>
       <c r="H13" t="n">
         <v>74915</v>
@@ -833,7 +833,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G16" t="n">
-        <v>13.4155054092407</v>
+        <v>13.415506362915</v>
       </c>
       <c r="H16" t="n">
         <v>258303</v>
@@ -862,7 +862,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G17" t="n">
-        <v>13.7021627426147</v>
+        <v>13.7021617889404</v>
       </c>
       <c r="H17" t="n">
         <v>249086</v>
@@ -891,7 +891,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G18" t="n">
-        <v>13.1575164794922</v>
+        <v>13.1575155258179</v>
       </c>
       <c r="H18" t="n">
         <v>226405</v>
@@ -920,7 +920,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G19" t="n">
-        <v>13.5683898925781</v>
+        <v>13.5683889389038</v>
       </c>
       <c r="H19" t="n">
         <v>254487</v>
@@ -949,7 +949,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G20" t="n">
-        <v>13.8072690963745</v>
+        <v>13.8072700500488</v>
       </c>
       <c r="H20" t="n">
         <v>301266</v>
@@ -1036,7 +1036,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>14.1417016983032</v>
+        <v>14.1417026519775</v>
       </c>
       <c r="H23" t="n">
         <v>170138</v>
@@ -1094,7 +1094,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G25" t="n">
-        <v>13.9410419464111</v>
+        <v>13.9410429000854</v>
       </c>
       <c r="H25" t="n">
         <v>258800</v>
@@ -1123,7 +1123,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G26" t="n">
-        <v>14.1608123779297</v>
+        <v>14.1608114242554</v>
       </c>
       <c r="H26" t="n">
         <v>270595</v>
@@ -1152,7 +1152,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G27" t="n">
-        <v>14.1990327835083</v>
+        <v>14.199031829834</v>
       </c>
       <c r="H27" t="n">
         <v>63326</v>
@@ -1239,7 +1239,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G30" t="n">
-        <v>13.7021627426147</v>
+        <v>13.7021617889404</v>
       </c>
       <c r="H30" t="n">
         <v>147708</v>
@@ -1297,7 +1297,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G32" t="n">
-        <v>13.5683898925781</v>
+        <v>13.5683889389038</v>
       </c>
       <c r="H32" t="n">
         <v>138086</v>
@@ -1326,7 +1326,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G33" t="n">
-        <v>13.7403841018677</v>
+        <v>13.7403831481934</v>
       </c>
       <c r="H33" t="n">
         <v>47665</v>
@@ -1442,7 +1442,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G37" t="n">
-        <v>13.2912893295288</v>
+        <v>13.2912883758545</v>
       </c>
       <c r="H37" t="n">
         <v>64058</v>
@@ -1500,7 +1500,7 @@
         <v>14.3299999237061</v>
       </c>
       <c r="G39" t="n">
-        <v>13.6926078796387</v>
+        <v>13.6926069259644</v>
       </c>
       <c r="H39" t="n">
         <v>213096</v>
@@ -1529,7 +1529,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G40" t="n">
-        <v>13.8454895019531</v>
+        <v>13.8454904556274</v>
       </c>
       <c r="H40" t="n">
         <v>109728</v>
@@ -1558,7 +1558,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G41" t="n">
-        <v>14.8870077133179</v>
+        <v>14.8870067596436</v>
       </c>
       <c r="H41" t="n">
         <v>505585</v>
@@ -1587,7 +1587,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>15.1927738189697</v>
+        <v>15.192774772644</v>
       </c>
       <c r="H42" t="n">
         <v>474029</v>
@@ -1616,7 +1616,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>15.3838787078857</v>
+        <v>15.3838777542114</v>
       </c>
       <c r="H43" t="n">
         <v>436799</v>
@@ -1674,7 +1674,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>15.5749816894531</v>
+        <v>15.5749826431274</v>
       </c>
       <c r="H45" t="n">
         <v>405367</v>
@@ -1790,7 +1790,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G49" t="n">
-        <v>15.6418685913086</v>
+        <v>15.6418695449829</v>
       </c>
       <c r="H49" t="n">
         <v>782970</v>
@@ -1819,7 +1819,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G50" t="n">
-        <v>15.2309942245483</v>
+        <v>15.230993270874</v>
       </c>
       <c r="H50" t="n">
         <v>267987</v>
@@ -1848,7 +1848,7 @@
         <v>15.8900003433228</v>
       </c>
       <c r="G51" t="n">
-        <v>15.183219909668</v>
+        <v>15.1832189559937</v>
       </c>
       <c r="H51" t="n">
         <v>161269</v>
@@ -1935,7 +1935,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G54" t="n">
-        <v>14.0079288482666</v>
+        <v>14.0079278945923</v>
       </c>
       <c r="H54" t="n">
         <v>147319</v>
@@ -1993,7 +1993,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G56" t="n">
-        <v>15.1163320541382</v>
+        <v>15.1163330078125</v>
       </c>
       <c r="H56" t="n">
         <v>204640</v>
@@ -2022,7 +2022,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G57" t="n">
-        <v>14.7436800003052</v>
+        <v>14.7436809539795</v>
       </c>
       <c r="H57" t="n">
         <v>220752</v>
@@ -2051,7 +2051,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G58" t="n">
-        <v>14.4092473983765</v>
+        <v>14.4092464447021</v>
       </c>
       <c r="H58" t="n">
         <v>182625</v>
@@ -2080,7 +2080,7 @@
         <v>15.75</v>
       </c>
       <c r="G59" t="n">
-        <v>15.049446105957</v>
+        <v>15.0494451522827</v>
       </c>
       <c r="H59" t="n">
         <v>87541</v>
@@ -2138,7 +2138,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G61" t="n">
-        <v>15.5558710098267</v>
+        <v>15.555871963501</v>
       </c>
       <c r="H61" t="n">
         <v>217368</v>
@@ -2167,7 +2167,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G62" t="n">
-        <v>15.2309942245483</v>
+        <v>15.230993270874</v>
       </c>
       <c r="H62" t="n">
         <v>177423</v>
@@ -2196,7 +2196,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G63" t="n">
-        <v>15.1736631393433</v>
+        <v>15.1736640930176</v>
       </c>
       <c r="H63" t="n">
         <v>103387</v>
@@ -2225,7 +2225,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G64" t="n">
-        <v>14.9634494781494</v>
+        <v>14.9634485244751</v>
       </c>
       <c r="H64" t="n">
         <v>72487</v>
@@ -2254,7 +2254,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G65" t="n">
-        <v>15.7469749450684</v>
+        <v>15.7469758987427</v>
       </c>
       <c r="H65" t="n">
         <v>163756</v>
@@ -2312,7 +2312,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G67" t="n">
-        <v>15.2309942245483</v>
+        <v>15.230993270874</v>
       </c>
       <c r="H67" t="n">
         <v>105026</v>
@@ -2370,7 +2370,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G69" t="n">
-        <v>15.3552122116089</v>
+        <v>15.3552131652832</v>
       </c>
       <c r="H69" t="n">
         <v>141327</v>
@@ -2428,7 +2428,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G71" t="n">
-        <v>15.097222328186</v>
+        <v>15.0972213745117</v>
       </c>
       <c r="H71" t="n">
         <v>210329</v>
@@ -2486,7 +2486,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G73" t="n">
-        <v>14.3519172668457</v>
+        <v>14.3519163131714</v>
       </c>
       <c r="H73" t="n">
         <v>172203</v>
@@ -2515,7 +2515,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G74" t="n">
-        <v>14.3136940002441</v>
+        <v>14.3136959075928</v>
       </c>
       <c r="H74" t="n">
         <v>173782</v>
@@ -2573,7 +2573,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>14.3805809020996</v>
+        <v>14.3805818557739</v>
       </c>
       <c r="H76" t="n">
         <v>129903</v>
@@ -2602,7 +2602,7 @@
         <v>15.5</v>
       </c>
       <c r="G77" t="n">
-        <v>14.810564994812</v>
+        <v>14.8105659484863</v>
       </c>
       <c r="H77" t="n">
         <v>108895</v>
@@ -2747,7 +2747,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G82" t="n">
-        <v>14.2659187316895</v>
+        <v>14.2659196853638</v>
       </c>
       <c r="H82" t="n">
         <v>101770</v>
@@ -2950,7 +2950,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G89" t="n">
-        <v>15.0303354263306</v>
+        <v>15.0303363800049</v>
       </c>
       <c r="H89" t="n">
         <v>401988</v>
@@ -3008,7 +3008,7 @@
         <v>15.5</v>
       </c>
       <c r="G91" t="n">
-        <v>14.810564994812</v>
+        <v>14.8105659484863</v>
       </c>
       <c r="H91" t="n">
         <v>119552</v>
@@ -3037,7 +3037,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G92" t="n">
-        <v>14.5621309280396</v>
+        <v>14.5621299743652</v>
       </c>
       <c r="H92" t="n">
         <v>143627</v>
@@ -3066,7 +3066,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G93" t="n">
-        <v>14.6767921447754</v>
+        <v>14.6767930984497</v>
       </c>
       <c r="H93" t="n">
         <v>110219</v>
@@ -3124,7 +3124,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G95" t="n">
-        <v>14.1990327835083</v>
+        <v>14.199031829834</v>
       </c>
       <c r="H95" t="n">
         <v>59537</v>
@@ -3153,7 +3153,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>14.6194620132446</v>
+        <v>14.6194610595703</v>
       </c>
       <c r="H96" t="n">
         <v>186490</v>
@@ -3240,7 +3240,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G99" t="n">
-        <v>14.9347839355469</v>
+        <v>14.9347829818726</v>
       </c>
       <c r="H99" t="n">
         <v>117392</v>
@@ -3269,7 +3269,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G100" t="n">
-        <v>14.9347839355469</v>
+        <v>14.9347829818726</v>
       </c>
       <c r="H100" t="n">
         <v>95381</v>
@@ -3298,7 +3298,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G101" t="n">
-        <v>15.3265476226807</v>
+        <v>15.326548576355</v>
       </c>
       <c r="H101" t="n">
         <v>177567</v>
@@ -3327,7 +3327,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G102" t="n">
-        <v>15.3456554412842</v>
+        <v>15.3456563949585</v>
       </c>
       <c r="H102" t="n">
         <v>1185858</v>
@@ -3356,7 +3356,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G103" t="n">
-        <v>15.3074359893799</v>
+        <v>15.3074369430542</v>
       </c>
       <c r="H103" t="n">
         <v>144419</v>
@@ -3414,7 +3414,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G105" t="n">
-        <v>14.5907974243164</v>
+        <v>14.5907964706421</v>
       </c>
       <c r="H105" t="n">
         <v>112390</v>
@@ -3530,7 +3530,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G109" t="n">
-        <v>14.8487854003906</v>
+        <v>14.8487873077393</v>
       </c>
       <c r="H109" t="n">
         <v>53044</v>
@@ -3559,7 +3559,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G110" t="n">
-        <v>15.08766746521</v>
+        <v>15.0876665115356</v>
       </c>
       <c r="H110" t="n">
         <v>72044</v>
@@ -3588,7 +3588,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G111" t="n">
-        <v>14.9443378448486</v>
+        <v>14.9443387985229</v>
       </c>
       <c r="H111" t="n">
         <v>83241</v>
@@ -3733,7 +3733,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G116" t="n">
-        <v>14.4570236206055</v>
+        <v>14.4570226669312</v>
       </c>
       <c r="H116" t="n">
         <v>75449</v>
@@ -3762,7 +3762,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G117" t="n">
-        <v>14.4474678039551</v>
+        <v>14.4474687576294</v>
       </c>
       <c r="H117" t="n">
         <v>75827</v>
@@ -3791,7 +3791,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G118" t="n">
-        <v>14.0461492538452</v>
+        <v>14.0461483001709</v>
       </c>
       <c r="H118" t="n">
         <v>88132</v>
@@ -3849,7 +3849,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>13.7594938278198</v>
+        <v>13.7594928741455</v>
       </c>
       <c r="H120" t="n">
         <v>41310</v>
@@ -3907,7 +3907,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G122" t="n">
-        <v>13.9314870834351</v>
+        <v>13.9314880371094</v>
       </c>
       <c r="H122" t="n">
         <v>58966</v>
@@ -3936,7 +3936,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G123" t="n">
-        <v>13.7021627426147</v>
+        <v>13.7021617889404</v>
       </c>
       <c r="H123" t="n">
         <v>29257</v>
@@ -4023,7 +4023,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G126" t="n">
-        <v>14.715012550354</v>
+        <v>14.7150135040283</v>
       </c>
       <c r="H126" t="n">
         <v>141731</v>
@@ -4052,7 +4052,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G127" t="n">
-        <v>14.9634494781494</v>
+        <v>14.9634485244751</v>
       </c>
       <c r="H127" t="n">
         <v>166475</v>
@@ -4081,7 +4081,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G128" t="n">
-        <v>14.8870077133179</v>
+        <v>14.8870067596436</v>
       </c>
       <c r="H128" t="n">
         <v>40404</v>
@@ -4110,7 +4110,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G129" t="n">
-        <v>15.1641082763672</v>
+        <v>15.1641092300415</v>
       </c>
       <c r="H129" t="n">
         <v>73585</v>
@@ -4139,7 +4139,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G130" t="n">
-        <v>15.0398893356323</v>
+        <v>15.0398902893066</v>
       </c>
       <c r="H130" t="n">
         <v>99245</v>
@@ -4168,7 +4168,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G131" t="n">
-        <v>15.08766746521</v>
+        <v>15.0876665115356</v>
       </c>
       <c r="H131" t="n">
         <v>223782</v>
@@ -4197,7 +4197,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G132" t="n">
-        <v>15.1258878707886</v>
+        <v>15.1258869171143</v>
       </c>
       <c r="H132" t="n">
         <v>58545</v>
@@ -4226,7 +4226,7 @@
         <v>15.75</v>
       </c>
       <c r="G133" t="n">
-        <v>15.049446105957</v>
+        <v>15.0494451522827</v>
       </c>
       <c r="H133" t="n">
         <v>54662</v>
@@ -4284,7 +4284,7 @@
         <v>15.6899995803833</v>
       </c>
       <c r="G135" t="n">
-        <v>14.9921140670776</v>
+        <v>14.992115020752</v>
       </c>
       <c r="H135" t="n">
         <v>123072</v>
@@ -4313,7 +4313,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G136" t="n">
-        <v>15.2692155838013</v>
+        <v>15.269214630127</v>
       </c>
       <c r="H136" t="n">
         <v>116552</v>
@@ -4342,7 +4342,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G137" t="n">
-        <v>15.1736631393433</v>
+        <v>15.1736640930176</v>
       </c>
       <c r="H137" t="n">
         <v>135405</v>
@@ -4371,7 +4371,7 @@
         <v>16.5</v>
       </c>
       <c r="G138" t="n">
-        <v>15.7660865783691</v>
+        <v>15.7660856246948</v>
       </c>
       <c r="H138" t="n">
         <v>318203</v>
@@ -4458,7 +4458,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G141" t="n">
-        <v>16.2534027099609</v>
+        <v>16.2534008026123</v>
       </c>
       <c r="H141" t="n">
         <v>206345</v>
@@ -4487,7 +4487,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G142" t="n">
-        <v>16.9795970916748</v>
+        <v>16.9795989990234</v>
       </c>
       <c r="H142" t="n">
         <v>321463</v>
@@ -4516,7 +4516,7 @@
         <v>17.8700008392334</v>
       </c>
       <c r="G143" t="n">
-        <v>17.0751495361328</v>
+        <v>17.0751514434814</v>
       </c>
       <c r="H143" t="n">
         <v>118766</v>
@@ -4603,7 +4603,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G146" t="n">
-        <v>16.769380569458</v>
+        <v>16.7693824768066</v>
       </c>
       <c r="H146" t="n">
         <v>112560</v>
@@ -4632,7 +4632,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G147" t="n">
-        <v>16.1769618988037</v>
+        <v>16.1769599914551</v>
       </c>
       <c r="H147" t="n">
         <v>432672</v>
@@ -4661,7 +4661,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G148" t="n">
-        <v>15.8425283432007</v>
+        <v>15.8425273895264</v>
       </c>
       <c r="H148" t="n">
         <v>256187</v>
@@ -4690,7 +4690,7 @@
         <v>16.6100006103516</v>
       </c>
       <c r="G149" t="n">
-        <v>15.8711938858032</v>
+        <v>15.8711929321289</v>
       </c>
       <c r="H149" t="n">
         <v>130015</v>
@@ -4719,7 +4719,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G150" t="n">
-        <v>15.6418685913086</v>
+        <v>15.6418695449829</v>
       </c>
       <c r="H150" t="n">
         <v>102652</v>
@@ -4835,7 +4835,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>17.3426952362061</v>
+        <v>17.3426933288574</v>
       </c>
       <c r="H154" t="n">
         <v>130344</v>
@@ -4864,7 +4864,7 @@
         <v>18.25</v>
       </c>
       <c r="G155" t="n">
-        <v>17.4382476806641</v>
+        <v>17.4382457733154</v>
       </c>
       <c r="H155" t="n">
         <v>175492</v>
@@ -4893,7 +4893,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G156" t="n">
-        <v>17.6962375640869</v>
+        <v>17.6962356567383</v>
       </c>
       <c r="H156" t="n">
         <v>187911</v>
@@ -4951,7 +4951,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G158" t="n">
-        <v>17.4669151306152</v>
+        <v>17.4669132232666</v>
       </c>
       <c r="H158" t="n">
         <v>73047</v>
@@ -4980,7 +4980,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G159" t="n">
-        <v>17.3904724121094</v>
+        <v>17.3904705047607</v>
       </c>
       <c r="H159" t="n">
         <v>70593</v>
@@ -5009,7 +5009,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G160" t="n">
-        <v>17.3904724121094</v>
+        <v>17.3904705047607</v>
       </c>
       <c r="H160" t="n">
         <v>78063</v>
@@ -5067,7 +5067,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G162" t="n">
-        <v>17.5815753936768</v>
+        <v>17.5815773010254</v>
       </c>
       <c r="H162" t="n">
         <v>61690</v>
@@ -5096,7 +5096,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G163" t="n">
-        <v>17.2089233398438</v>
+        <v>17.2089214324951</v>
       </c>
       <c r="H163" t="n">
         <v>50813</v>
@@ -5212,7 +5212,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G167" t="n">
-        <v>18.2313289642334</v>
+        <v>18.231330871582</v>
       </c>
       <c r="H167" t="n">
         <v>148047</v>
@@ -5415,7 +5415,7 @@
         <v>18.7700004577637</v>
       </c>
       <c r="G174" t="n">
-        <v>17.9351177215576</v>
+        <v>17.935115814209</v>
       </c>
       <c r="H174" t="n">
         <v>228634</v>
@@ -5444,7 +5444,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>18.4415397644043</v>
+        <v>18.4415416717529</v>
       </c>
       <c r="H175" t="n">
         <v>73309</v>
@@ -5473,7 +5473,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>17.7726802825928</v>
+        <v>17.7726783752441</v>
       </c>
       <c r="H176" t="n">
         <v>132691</v>
@@ -5560,7 +5560,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G179" t="n">
-        <v>18.8524169921875</v>
+        <v>18.8524188995361</v>
       </c>
       <c r="H179" t="n">
         <v>160303</v>
@@ -5618,7 +5618,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G181" t="n">
-        <v>18.823751449585</v>
+        <v>18.8237533569336</v>
       </c>
       <c r="H181" t="n">
         <v>95801</v>
@@ -5676,7 +5676,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G183" t="n">
-        <v>17.7249011993408</v>
+        <v>17.7249031066895</v>
       </c>
       <c r="H183" t="n">
         <v>316794</v>
@@ -5763,7 +5763,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G186" t="n">
-        <v>16.683385848999</v>
+        <v>16.6833839416504</v>
       </c>
       <c r="H186" t="n">
         <v>219917</v>
@@ -5792,7 +5792,7 @@
         <v>18</v>
       </c>
       <c r="G187" t="n">
-        <v>17.199369430542</v>
+        <v>17.1993675231934</v>
       </c>
       <c r="H187" t="n">
         <v>168778</v>
@@ -5879,7 +5879,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G190" t="n">
-        <v>17.648458480835</v>
+        <v>17.6484603881836</v>
       </c>
       <c r="H190" t="n">
         <v>98265</v>
@@ -5908,7 +5908,7 @@
         <v>17.75</v>
       </c>
       <c r="G191" t="n">
-        <v>16.9604873657227</v>
+        <v>16.960485458374</v>
       </c>
       <c r="H191" t="n">
         <v>902705</v>
@@ -5966,7 +5966,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G193" t="n">
-        <v>16.4540596008301</v>
+        <v>16.4540615081787</v>
       </c>
       <c r="H193" t="n">
         <v>194779</v>
@@ -5995,7 +5995,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G194" t="n">
-        <v>16.3871726989746</v>
+        <v>16.3871746063232</v>
       </c>
       <c r="H194" t="n">
         <v>289758</v>
@@ -6082,7 +6082,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G197" t="n">
-        <v>16.3489551544189</v>
+        <v>16.3489532470703</v>
       </c>
       <c r="H197" t="n">
         <v>187727</v>
@@ -6140,7 +6140,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G199" t="n">
-        <v>16.6069431304932</v>
+        <v>16.6069450378418</v>
       </c>
       <c r="H199" t="n">
         <v>89821</v>
@@ -6169,7 +6169,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G200" t="n">
-        <v>16.683385848999</v>
+        <v>16.6833839416504</v>
       </c>
       <c r="H200" t="n">
         <v>78475</v>
@@ -6198,7 +6198,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>16.6260528564453</v>
+        <v>16.6260547637939</v>
       </c>
       <c r="H201" t="n">
         <v>108711</v>
@@ -6256,7 +6256,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G203" t="n">
-        <v>16.7407188415527</v>
+        <v>16.7407169342041</v>
       </c>
       <c r="H203" t="n">
         <v>93120</v>
@@ -6285,7 +6285,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G204" t="n">
-        <v>16.7884941101074</v>
+        <v>16.7884922027588</v>
       </c>
       <c r="H204" t="n">
         <v>110054</v>
@@ -6314,7 +6314,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G205" t="n">
-        <v>17.0369262695312</v>
+        <v>17.0369281768799</v>
       </c>
       <c r="H205" t="n">
         <v>107074</v>
@@ -6372,7 +6372,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G207" t="n">
-        <v>16.6547183990479</v>
+        <v>16.6547222137451</v>
       </c>
       <c r="H207" t="n">
         <v>154640</v>
@@ -6488,7 +6488,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G211" t="n">
-        <v>17.3713607788086</v>
+        <v>17.37135887146</v>
       </c>
       <c r="H211" t="n">
         <v>87623</v>
@@ -6575,7 +6575,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G214" t="n">
-        <v>16.6642761230469</v>
+        <v>16.6642742156982</v>
       </c>
       <c r="H214" t="n">
         <v>584108</v>
@@ -6604,7 +6604,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G215" t="n">
-        <v>17.476469039917</v>
+        <v>17.4764709472656</v>
       </c>
       <c r="H215" t="n">
         <v>330056</v>
@@ -6662,7 +6662,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G217" t="n">
-        <v>18.2313289642334</v>
+        <v>18.231330871582</v>
       </c>
       <c r="H217" t="n">
         <v>171919</v>
@@ -6691,7 +6691,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G218" t="n">
-        <v>18.4415397644043</v>
+        <v>18.4415416717529</v>
       </c>
       <c r="H218" t="n">
         <v>241224</v>
@@ -6720,7 +6720,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G219" t="n">
-        <v>18.4415397644043</v>
+        <v>18.4415416717529</v>
       </c>
       <c r="H219" t="n">
         <v>270484</v>
@@ -6778,7 +6778,7 @@
         <v>19.2700004577637</v>
       </c>
       <c r="G221" t="n">
-        <v>18.5309104919434</v>
+        <v>18.5309085845947</v>
       </c>
       <c r="H221" t="n">
         <v>86313</v>
@@ -6807,7 +6807,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G222" t="n">
-        <v>18.5789909362793</v>
+        <v>18.5789890289307</v>
       </c>
       <c r="H222" t="n">
         <v>75028</v>
@@ -6836,7 +6836,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G223" t="n">
-        <v>18.6559238433838</v>
+        <v>18.6559219360352</v>
       </c>
       <c r="H223" t="n">
         <v>117863</v>
@@ -6865,7 +6865,7 @@
         <v>19.25</v>
       </c>
       <c r="G224" t="n">
-        <v>18.5116748809814</v>
+        <v>18.5116767883301</v>
       </c>
       <c r="H224" t="n">
         <v>52689</v>
@@ -6894,7 +6894,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G225" t="n">
-        <v>18.6559238433838</v>
+        <v>18.6559219360352</v>
       </c>
       <c r="H225" t="n">
         <v>62425</v>
@@ -7010,7 +7010,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G229" t="n">
-        <v>18.8097877502441</v>
+        <v>18.8097858428955</v>
       </c>
       <c r="H229" t="n">
         <v>69687</v>
@@ -7242,7 +7242,7 @@
         <v>20.5</v>
       </c>
       <c r="G237" t="n">
-        <v>19.7137336730957</v>
+        <v>19.7137317657471</v>
       </c>
       <c r="H237" t="n">
         <v>224683</v>
@@ -7300,7 +7300,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G239" t="n">
-        <v>19.3290748596191</v>
+        <v>19.3290729522705</v>
       </c>
       <c r="H239" t="n">
         <v>78255</v>
@@ -7387,7 +7387,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>19.4252376556396</v>
+        <v>19.4252414703369</v>
       </c>
       <c r="H242" t="n">
         <v>219460</v>
@@ -7416,7 +7416,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G243" t="n">
-        <v>19.0405788421631</v>
+        <v>19.0405807495117</v>
       </c>
       <c r="H243" t="n">
         <v>51065</v>
@@ -7503,7 +7503,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G246" t="n">
-        <v>17.8481407165527</v>
+        <v>17.8481388092041</v>
       </c>
       <c r="H246" t="n">
         <v>191126</v>
@@ -7561,7 +7561,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G248" t="n">
-        <v>18.5789909362793</v>
+        <v>18.5789890289307</v>
       </c>
       <c r="H248" t="n">
         <v>83004</v>
@@ -7706,7 +7706,7 @@
         <v>19.4099998474121</v>
       </c>
       <c r="G253" t="n">
-        <v>18.6655387878418</v>
+        <v>18.6655406951904</v>
       </c>
       <c r="H253" t="n">
         <v>58888</v>
@@ -7822,7 +7822,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G257" t="n">
-        <v>19.6944980621338</v>
+        <v>19.6944999694824</v>
       </c>
       <c r="H257" t="n">
         <v>62964</v>
@@ -7909,7 +7909,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G260" t="n">
-        <v>19.5598697662354</v>
+        <v>19.5598678588867</v>
       </c>
       <c r="H260" t="n">
         <v>165590</v>
@@ -7938,7 +7938,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G261" t="n">
-        <v>19.2713775634766</v>
+        <v>19.2713756561279</v>
       </c>
       <c r="H261" t="n">
         <v>226076</v>
@@ -7996,7 +7996,7 @@
         <v>20.5</v>
       </c>
       <c r="G263" t="n">
-        <v>19.7137336730957</v>
+        <v>19.7137317657471</v>
       </c>
       <c r="H263" t="n">
         <v>91506</v>
@@ -8025,7 +8025,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G264" t="n">
-        <v>19.4829368591309</v>
+        <v>19.4829387664795</v>
       </c>
       <c r="H264" t="n">
         <v>113210</v>
@@ -8083,7 +8083,7 @@
         <v>20.5</v>
       </c>
       <c r="G266" t="n">
-        <v>19.7137336730957</v>
+        <v>19.7137317657471</v>
       </c>
       <c r="H266" t="n">
         <v>56249</v>
@@ -8112,7 +8112,7 @@
         <v>20.5</v>
       </c>
       <c r="G267" t="n">
-        <v>19.7137336730957</v>
+        <v>19.7137317657471</v>
       </c>
       <c r="H267" t="n">
         <v>68211</v>
@@ -8257,7 +8257,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G272" t="n">
-        <v>17.5019493103027</v>
+        <v>17.5019474029541</v>
       </c>
       <c r="H272" t="n">
         <v>364369</v>
@@ -8286,7 +8286,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G273" t="n">
-        <v>17.569263458252</v>
+        <v>17.5692653656006</v>
       </c>
       <c r="H273" t="n">
         <v>162056</v>
@@ -8344,7 +8344,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G275" t="n">
-        <v>18.2904968261719</v>
+        <v>18.2904987335205</v>
       </c>
       <c r="H275" t="n">
         <v>226073</v>
@@ -8373,7 +8373,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G276" t="n">
-        <v>18.5020599365234</v>
+        <v>18.5020580291748</v>
       </c>
       <c r="H276" t="n">
         <v>314121</v>
@@ -8460,7 +8460,7 @@
         <v>19.4099998474121</v>
       </c>
       <c r="G279" t="n">
-        <v>18.6655387878418</v>
+        <v>18.6655406951904</v>
       </c>
       <c r="H279" t="n">
         <v>51561</v>
@@ -8489,7 +8489,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G280" t="n">
-        <v>18.6559238433838</v>
+        <v>18.6559219360352</v>
       </c>
       <c r="H280" t="n">
         <v>71432</v>
@@ -8576,7 +8576,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G283" t="n">
-        <v>17.5981121063232</v>
+        <v>17.5981101989746</v>
       </c>
       <c r="H283" t="n">
         <v>79763</v>
@@ -8605,7 +8605,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G284" t="n">
-        <v>17.5404148101807</v>
+        <v>17.540412902832</v>
       </c>
       <c r="H284" t="n">
         <v>101821</v>
@@ -8663,7 +8663,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G286" t="n">
-        <v>17.0595932006836</v>
+        <v>17.059591293335</v>
       </c>
       <c r="H286" t="n">
         <v>83846</v>
@@ -8779,7 +8779,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G290" t="n">
-        <v>17.194221496582</v>
+        <v>17.1942195892334</v>
       </c>
       <c r="H290" t="n">
         <v>97158</v>
@@ -8808,7 +8808,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G291" t="n">
-        <v>17.4923305511475</v>
+        <v>17.4923324584961</v>
       </c>
       <c r="H291" t="n">
         <v>98792</v>
@@ -8837,7 +8837,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G292" t="n">
-        <v>17.569263458252</v>
+        <v>17.5692653656006</v>
       </c>
       <c r="H292" t="n">
         <v>70023</v>
@@ -8866,7 +8866,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G293" t="n">
-        <v>17.213451385498</v>
+        <v>17.2134532928467</v>
       </c>
       <c r="H293" t="n">
         <v>97852</v>
@@ -9098,7 +9098,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G301" t="n">
-        <v>16.4441394805908</v>
+        <v>16.4441375732422</v>
       </c>
       <c r="H301" t="n">
         <v>93310</v>
@@ -9417,7 +9417,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>15.4824934005737</v>
+        <v>15.4824924468994</v>
       </c>
       <c r="H312" t="n">
         <v>47778</v>
@@ -9475,7 +9475,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G314" t="n">
-        <v>15.6555881500244</v>
+        <v>15.6555891036987</v>
       </c>
       <c r="H314" t="n">
         <v>70184</v>
@@ -9504,7 +9504,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G315" t="n">
-        <v>15.8479166030884</v>
+        <v>15.8479175567627</v>
       </c>
       <c r="H315" t="n">
         <v>74847</v>
@@ -9533,7 +9533,7 @@
         <v>16.2700004577637</v>
       </c>
       <c r="G316" t="n">
-        <v>15.6459732055664</v>
+        <v>15.6459722518921</v>
       </c>
       <c r="H316" t="n">
         <v>152152</v>
@@ -9649,7 +9649,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G320" t="n">
-        <v>14.3189010620117</v>
+        <v>14.318902015686</v>
       </c>
       <c r="H320" t="n">
         <v>84956</v>
@@ -9678,7 +9678,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G321" t="n">
-        <v>14.4631481170654</v>
+        <v>14.4631471633911</v>
       </c>
       <c r="H321" t="n">
         <v>76846</v>
@@ -9823,7 +9823,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>14.1361885070801</v>
+        <v>14.1361875534058</v>
       </c>
       <c r="H326" t="n">
         <v>132397</v>
@@ -9852,7 +9852,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G327" t="n">
-        <v>14.0881052017212</v>
+        <v>14.0881061553955</v>
       </c>
       <c r="H327" t="n">
         <v>66396</v>
@@ -9881,7 +9881,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G328" t="n">
-        <v>14.2227363586426</v>
+        <v>14.2227373123169</v>
       </c>
       <c r="H328" t="n">
         <v>104116</v>
@@ -10026,7 +10026,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G333" t="n">
-        <v>12.8571996688843</v>
+        <v>12.8572006225586</v>
       </c>
       <c r="H333" t="n">
         <v>104403</v>
@@ -10055,7 +10055,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G334" t="n">
-        <v>12.6744890213013</v>
+        <v>12.674488067627</v>
       </c>
       <c r="H334" t="n">
         <v>59858</v>
@@ -10316,7 +10316,7 @@
         <v>14.0100002288818</v>
       </c>
       <c r="G343" t="n">
-        <v>13.4726543426514</v>
+        <v>13.4726533889771</v>
       </c>
       <c r="H343" t="n">
         <v>569136</v>
@@ -10345,7 +10345,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G344" t="n">
-        <v>13.0399131774902</v>
+        <v>13.0399141311646</v>
       </c>
       <c r="H344" t="n">
         <v>146201</v>
@@ -10403,7 +10403,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G346" t="n">
-        <v>14.5016145706177</v>
+        <v>14.5016136169434</v>
       </c>
       <c r="H346" t="n">
         <v>237267</v>
@@ -10461,7 +10461,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G348" t="n">
-        <v>14.2227363586426</v>
+        <v>14.2227373123169</v>
       </c>
       <c r="H348" t="n">
         <v>121936</v>
@@ -10519,7 +10519,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G350" t="n">
-        <v>14.2708196640015</v>
+        <v>14.2708187103271</v>
       </c>
       <c r="H350" t="n">
         <v>157799</v>
@@ -10577,7 +10577,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G352" t="n">
-        <v>14.2515869140625</v>
+        <v>14.2515859603882</v>
       </c>
       <c r="H352" t="n">
         <v>74240</v>
@@ -10606,7 +10606,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G353" t="n">
-        <v>14.3092861175537</v>
+        <v>14.3092851638794</v>
       </c>
       <c r="H353" t="n">
         <v>104165</v>
@@ -10635,7 +10635,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G354" t="n">
-        <v>14.2996683120728</v>
+        <v>14.2996673583984</v>
       </c>
       <c r="H354" t="n">
         <v>87931</v>
@@ -10693,7 +10693,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G356" t="n">
-        <v>13.7322969436646</v>
+        <v>13.7322978973389</v>
       </c>
       <c r="H356" t="n">
         <v>217186</v>
@@ -10809,7 +10809,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G360" t="n">
-        <v>13.2707080841064</v>
+        <v>13.2707071304321</v>
       </c>
       <c r="H360" t="n">
         <v>139158</v>
@@ -10896,7 +10896,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G363" t="n">
-        <v>13.1841592788696</v>
+        <v>13.1841602325439</v>
       </c>
       <c r="H363" t="n">
         <v>159187</v>
@@ -10925,7 +10925,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G364" t="n">
-        <v>13.4341878890991</v>
+        <v>13.4341869354248</v>
       </c>
       <c r="H364" t="n">
         <v>99374</v>
@@ -11012,7 +11012,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G367" t="n">
-        <v>13.5495862960815</v>
+        <v>13.5495853424072</v>
       </c>
       <c r="H367" t="n">
         <v>174963</v>
@@ -11070,7 +11070,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G369" t="n">
-        <v>14.6747102737427</v>
+        <v>14.674711227417</v>
       </c>
       <c r="H369" t="n">
         <v>228319</v>
@@ -11128,7 +11128,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G371" t="n">
-        <v>15.6844387054443</v>
+        <v>15.6844367980957</v>
       </c>
       <c r="H371" t="n">
         <v>353221</v>
@@ -11244,7 +11244,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G375" t="n">
-        <v>14.8381900787354</v>
+        <v>14.8381910324097</v>
       </c>
       <c r="H375" t="n">
         <v>137149</v>
@@ -11273,7 +11273,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G376" t="n">
-        <v>15.0305194854736</v>
+        <v>15.0305185317993</v>
       </c>
       <c r="H376" t="n">
         <v>110938</v>
@@ -11331,7 +11331,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G378" t="n">
-        <v>14.9632034301758</v>
+        <v>14.9632043838501</v>
       </c>
       <c r="H378" t="n">
         <v>149811</v>
@@ -11360,7 +11360,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G379" t="n">
-        <v>14.5016145706177</v>
+        <v>14.5016136169434</v>
       </c>
       <c r="H379" t="n">
         <v>337572</v>
@@ -11389,7 +11389,7 @@
         <v>15.0900001525879</v>
       </c>
       <c r="G380" t="n">
-        <v>14.51123046875</v>
+        <v>14.5112314224243</v>
       </c>
       <c r="H380" t="n">
         <v>88556</v>
@@ -11534,7 +11534,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G385" t="n">
-        <v>14.4439163208008</v>
+        <v>14.4439153671265</v>
       </c>
       <c r="H385" t="n">
         <v>156312</v>
@@ -11563,7 +11563,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G386" t="n">
-        <v>14.0977230072021</v>
+        <v>14.0977220535278</v>
       </c>
       <c r="H386" t="n">
         <v>236798</v>
@@ -11592,7 +11592,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G387" t="n">
-        <v>14.1361885070801</v>
+        <v>14.1361875534058</v>
       </c>
       <c r="H387" t="n">
         <v>123369</v>
@@ -11621,7 +11621,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G388" t="n">
-        <v>13.9823265075684</v>
+        <v>13.982325553894</v>
       </c>
       <c r="H388" t="n">
         <v>99895</v>
@@ -11679,7 +11679,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G390" t="n">
-        <v>14.4631481170654</v>
+        <v>14.4631471633911</v>
       </c>
       <c r="H390" t="n">
         <v>99312</v>
@@ -11708,7 +11708,7 @@
         <v>14.2700004577637</v>
       </c>
       <c r="G391" t="n">
-        <v>13.7226810455322</v>
+        <v>13.7226819992065</v>
       </c>
       <c r="H391" t="n">
         <v>186975</v>
@@ -11795,7 +11795,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G394" t="n">
-        <v>13.7419137954712</v>
+        <v>13.7419147491455</v>
       </c>
       <c r="H394" t="n">
         <v>128563</v>
@@ -11911,7 +11911,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G398" t="n">
-        <v>13.3668718338013</v>
+        <v>13.3668727874756</v>
       </c>
       <c r="H398" t="n">
         <v>212475</v>
@@ -11940,7 +11940,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G399" t="n">
-        <v>14.0592565536499</v>
+        <v>14.0592575073242</v>
       </c>
       <c r="H399" t="n">
         <v>307261</v>
@@ -12085,7 +12085,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G404" t="n">
-        <v>13.3764896392822</v>
+        <v>13.3764886856079</v>
       </c>
       <c r="H404" t="n">
         <v>147194</v>
@@ -12549,7 +12549,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G420" t="n">
-        <v>14.9632034301758</v>
+        <v>14.9632043838501</v>
       </c>
       <c r="H420" t="n">
         <v>161886</v>
@@ -12578,7 +12578,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G421" t="n">
-        <v>14.5016145706177</v>
+        <v>14.5016136169434</v>
       </c>
       <c r="H421" t="n">
         <v>101945</v>
@@ -12607,7 +12607,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G422" t="n">
-        <v>14.3092861175537</v>
+        <v>14.3092851638794</v>
       </c>
       <c r="H422" t="n">
         <v>102639</v>
@@ -12665,7 +12665,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G424" t="n">
-        <v>14.0688734054565</v>
+        <v>14.0688743591309</v>
       </c>
       <c r="H424" t="n">
         <v>101301</v>
@@ -12781,7 +12781,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G428" t="n">
-        <v>13.8188447952271</v>
+        <v>13.8188457489014</v>
       </c>
       <c r="H428" t="n">
         <v>206029</v>
@@ -12868,7 +12868,7 @@
         <v>14.1899995803833</v>
       </c>
       <c r="G431" t="n">
-        <v>13.6457500457764</v>
+        <v>13.6457490921021</v>
       </c>
       <c r="H431" t="n">
         <v>223671</v>
@@ -12926,7 +12926,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G433" t="n">
-        <v>12.6456384658813</v>
+        <v>12.645637512207</v>
       </c>
       <c r="H433" t="n">
         <v>771950</v>
@@ -12955,7 +12955,7 @@
         <v>13.25</v>
       </c>
       <c r="G434" t="n">
-        <v>12.7418031692505</v>
+        <v>12.7418022155762</v>
       </c>
       <c r="H434" t="n">
         <v>207043</v>
@@ -12984,7 +12984,7 @@
         <v>13.25</v>
       </c>
       <c r="G435" t="n">
-        <v>12.7418031692505</v>
+        <v>12.7418022155762</v>
       </c>
       <c r="H435" t="n">
         <v>214799</v>
@@ -13042,7 +13042,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G437" t="n">
-        <v>12.7033367156982</v>
+        <v>12.7033376693726</v>
       </c>
       <c r="H437" t="n">
         <v>188482</v>
@@ -13071,7 +13071,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G438" t="n">
-        <v>12.6456384658813</v>
+        <v>12.645637512207</v>
       </c>
       <c r="H438" t="n">
         <v>150121</v>
@@ -13100,7 +13100,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G439" t="n">
-        <v>12.8571996688843</v>
+        <v>12.8572006225586</v>
       </c>
       <c r="H439" t="n">
         <v>90236</v>
@@ -13187,7 +13187,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G442" t="n">
-        <v>12.9725980758667</v>
+        <v>12.9725971221924</v>
       </c>
       <c r="H442" t="n">
         <v>207392</v>
@@ -13274,7 +13274,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G445" t="n">
-        <v>12.7802686691284</v>
+        <v>12.7802677154541</v>
       </c>
       <c r="H445" t="n">
         <v>146927</v>
@@ -13332,7 +13332,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G447" t="n">
-        <v>12.7033367156982</v>
+        <v>12.7033376693726</v>
       </c>
       <c r="H447" t="n">
         <v>82919</v>
@@ -13390,7 +13390,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G449" t="n">
-        <v>12.809118270874</v>
+        <v>12.8091173171997</v>
       </c>
       <c r="H449" t="n">
         <v>66508</v>
@@ -13448,7 +13448,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G451" t="n">
-        <v>12.9629802703857</v>
+        <v>12.9629812240601</v>
       </c>
       <c r="H451" t="n">
         <v>102016</v>
@@ -13506,7 +13506,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G453" t="n">
-        <v>11.9244031906128</v>
+        <v>11.9244041442871</v>
       </c>
       <c r="H453" t="n">
         <v>236491</v>
@@ -13709,7 +13709,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G460" t="n">
-        <v>12.1744318008423</v>
+        <v>12.1744327545166</v>
       </c>
       <c r="H460" t="n">
         <v>97426</v>
@@ -13738,7 +13738,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G461" t="n">
-        <v>12.1551990509033</v>
+        <v>12.1552000045776</v>
       </c>
       <c r="H461" t="n">
         <v>94886</v>
@@ -13796,7 +13796,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G463" t="n">
-        <v>12.0494165420532</v>
+        <v>12.0494174957275</v>
       </c>
       <c r="H463" t="n">
         <v>59080</v>
@@ -13941,7 +13941,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G468" t="n">
-        <v>12.7706527709961</v>
+        <v>12.7706518173218</v>
       </c>
       <c r="H468" t="n">
         <v>76794</v>
@@ -14057,7 +14057,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G472" t="n">
-        <v>13.1841592788696</v>
+        <v>13.1841602325439</v>
       </c>
       <c r="H472" t="n">
         <v>75618</v>
@@ -14115,7 +14115,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G474" t="n">
-        <v>12.7782716751099</v>
+        <v>12.7782726287842</v>
       </c>
       <c r="H474" t="n">
         <v>99354</v>
@@ -14173,7 +14173,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G476" t="n">
-        <v>13.0790500640869</v>
+        <v>13.0790510177612</v>
       </c>
       <c r="H476" t="n">
         <v>88070</v>
@@ -14202,7 +14202,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G477" t="n">
-        <v>12.9141082763672</v>
+        <v>12.9141073226929</v>
       </c>
       <c r="H477" t="n">
         <v>53958</v>
@@ -14231,7 +14231,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G478" t="n">
-        <v>12.4871940612793</v>
+        <v>12.4871950149536</v>
       </c>
       <c r="H478" t="n">
         <v>88793</v>
@@ -14260,7 +14260,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G479" t="n">
-        <v>12.8461894989014</v>
+        <v>12.8461885452271</v>
       </c>
       <c r="H479" t="n">
         <v>56934</v>
@@ -14347,7 +14347,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G482" t="n">
-        <v>12.8073797225952</v>
+        <v>12.8073787689209</v>
       </c>
       <c r="H482" t="n">
         <v>146288</v>
@@ -14695,7 +14695,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G494" t="n">
-        <v>11.3519945144653</v>
+        <v>11.3519954681396</v>
       </c>
       <c r="H494" t="n">
         <v>90980</v>
@@ -14782,7 +14782,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G497" t="n">
-        <v>11.4878311157227</v>
+        <v>11.487832069397</v>
       </c>
       <c r="H497" t="n">
         <v>74033</v>
@@ -14898,7 +14898,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G501" t="n">
-        <v>11.3519945144653</v>
+        <v>11.3519954681396</v>
       </c>
       <c r="H501" t="n">
         <v>72055</v>
@@ -15101,7 +15101,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G508" t="n">
-        <v>11.0803241729736</v>
+        <v>11.0803232192993</v>
       </c>
       <c r="H508" t="n">
         <v>52830</v>
@@ -15217,7 +15217,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G512" t="n">
-        <v>11.0803241729736</v>
+        <v>11.0803232192993</v>
       </c>
       <c r="H512" t="n">
         <v>67037</v>
@@ -15333,7 +15333,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G516" t="n">
-        <v>10.9735956192017</v>
+        <v>10.973596572876</v>
       </c>
       <c r="H516" t="n">
         <v>81818</v>
@@ -15420,7 +15420,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G519" t="n">
-        <v>10.9638938903809</v>
+        <v>10.9638929367065</v>
       </c>
       <c r="H519" t="n">
         <v>97469</v>
@@ -15565,7 +15565,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G524" t="n">
-        <v>10.5854921340942</v>
+        <v>10.5854930877686</v>
       </c>
       <c r="H524" t="n">
         <v>134025</v>
@@ -15623,7 +15623,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G526" t="n">
-        <v>10.3817386627197</v>
+        <v>10.381739616394</v>
       </c>
       <c r="H526" t="n">
         <v>195282</v>
@@ -16087,7 +16087,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G542" t="n">
-        <v>9.67830467224121</v>
+        <v>9.67830371856689</v>
       </c>
       <c r="H542" t="n">
         <v>134678</v>
@@ -16145,7 +16145,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G544" t="n">
-        <v>9.51821231842041</v>
+        <v>9.51821136474609</v>
       </c>
       <c r="H544" t="n">
         <v>80660</v>
@@ -16174,7 +16174,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G545" t="n">
-        <v>9.54731845855713</v>
+        <v>9.54731941223145</v>
       </c>
       <c r="H545" t="n">
         <v>95108</v>
@@ -16319,7 +16319,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G550" t="n">
-        <v>9.24653911590576</v>
+        <v>9.24654006958008</v>
       </c>
       <c r="H550" t="n">
         <v>94988</v>
@@ -16348,7 +16348,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G551" t="n">
-        <v>9.16891860961914</v>
+        <v>9.16891956329346</v>
       </c>
       <c r="H551" t="n">
         <v>135094</v>
@@ -16435,7 +16435,7 @@
         <v>8.91499996185303</v>
       </c>
       <c r="G554" t="n">
-        <v>8.64983177185059</v>
+        <v>8.6498327255249</v>
       </c>
       <c r="H554" t="n">
         <v>131072</v>
@@ -16464,7 +16464,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G555" t="n">
-        <v>9.08159637451172</v>
+        <v>9.0815954208374</v>
       </c>
       <c r="H555" t="n">
         <v>164784</v>
@@ -16493,7 +16493,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G556" t="n">
-        <v>9.09129810333252</v>
+        <v>9.09129905700684</v>
       </c>
       <c r="H556" t="n">
         <v>112117</v>
@@ -16551,7 +16551,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G558" t="n">
-        <v>9.08159637451172</v>
+        <v>9.0815954208374</v>
       </c>
       <c r="H558" t="n">
         <v>76175</v>
@@ -16609,7 +16609,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G560" t="n">
-        <v>9.24653911590576</v>
+        <v>9.24654006958008</v>
       </c>
       <c r="H560" t="n">
         <v>57482</v>
@@ -16638,7 +16638,7 @@
         <v>9.55500030517578</v>
       </c>
       <c r="G561" t="n">
-        <v>9.27079677581787</v>
+        <v>9.27079582214355</v>
       </c>
       <c r="H561" t="n">
         <v>80413</v>
@@ -16783,7 +16783,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G566" t="n">
-        <v>9.15921688079834</v>
+        <v>9.15921592712402</v>
       </c>
       <c r="H566" t="n">
         <v>168859</v>
@@ -16957,7 +16957,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G572" t="n">
-        <v>8.91665172576904</v>
+        <v>8.91665267944336</v>
       </c>
       <c r="H572" t="n">
         <v>55529</v>
@@ -17015,7 +17015,7 @@
         <v>8.90499973297119</v>
       </c>
       <c r="G574" t="n">
-        <v>8.64013004302979</v>
+        <v>8.64012908935547</v>
       </c>
       <c r="H574" t="n">
         <v>288790</v>
@@ -17073,7 +17073,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G576" t="n">
-        <v>8.66438579559326</v>
+        <v>8.66438674926758</v>
       </c>
       <c r="H576" t="n">
         <v>85122</v>
@@ -17160,7 +17160,7 @@
         <v>8.75</v>
       </c>
       <c r="G579" t="n">
-        <v>8.4897403717041</v>
+        <v>8.48973941802979</v>
       </c>
       <c r="H579" t="n">
         <v>77770</v>
@@ -17189,7 +17189,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G580" t="n">
-        <v>8.72260093688965</v>
+        <v>8.72260189056396</v>
       </c>
       <c r="H580" t="n">
         <v>167385</v>
@@ -17276,7 +17276,7 @@
         <v>8.82499980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>8.56250953674316</v>
+        <v>8.56250858306885</v>
       </c>
       <c r="H583" t="n">
         <v>185644</v>
@@ -17305,7 +17305,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G584" t="n">
-        <v>8.80022144317627</v>
+        <v>8.80022239685059</v>
       </c>
       <c r="H584" t="n">
         <v>145712</v>
@@ -17334,7 +17334,7 @@
         <v>8.91499996185303</v>
       </c>
       <c r="G585" t="n">
-        <v>8.64983177185059</v>
+        <v>8.6498327255249</v>
       </c>
       <c r="H585" t="n">
         <v>105376</v>
@@ -17392,7 +17392,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G587" t="n">
-        <v>8.7614107131958</v>
+        <v>8.76141166687012</v>
       </c>
       <c r="H587" t="n">
         <v>110831</v>
@@ -17508,7 +17508,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G591" t="n">
-        <v>8.387864112854</v>
+        <v>8.38786315917969</v>
       </c>
       <c r="H591" t="n">
         <v>209095</v>
@@ -17566,7 +17566,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G593" t="n">
-        <v>8.74200630187988</v>
+        <v>8.7420072555542</v>
       </c>
       <c r="H593" t="n">
         <v>123295</v>
@@ -17624,7 +17624,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G595" t="n">
-        <v>8.56736087799072</v>
+        <v>8.56735992431641</v>
       </c>
       <c r="H595" t="n">
         <v>506056</v>
@@ -17711,7 +17711,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G598" t="n">
-        <v>8.7614107131958</v>
+        <v>8.76141166687012</v>
       </c>
       <c r="H598" t="n">
         <v>275140</v>
@@ -17798,7 +17798,7 @@
         <v>8.47500038146973</v>
       </c>
       <c r="G601" t="n">
-        <v>8.22291946411133</v>
+        <v>8.22292041778564</v>
       </c>
       <c r="H601" t="n">
         <v>238471</v>
@@ -17827,7 +17827,7 @@
         <v>8.28499984741211</v>
       </c>
       <c r="G602" t="n">
-        <v>8.03857040405273</v>
+        <v>8.03857135772705</v>
       </c>
       <c r="H602" t="n">
         <v>639924</v>
@@ -17914,7 +17914,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G605" t="n">
-        <v>7.67472505569458</v>
+        <v>7.67472457885742</v>
       </c>
       <c r="H605" t="n">
         <v>165566</v>
@@ -17943,7 +17943,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G606" t="n">
-        <v>7.46126842498779</v>
+        <v>7.46126890182495</v>
       </c>
       <c r="H606" t="n">
         <v>281631</v>
@@ -18030,7 +18030,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G609" t="n">
-        <v>7.73779201507568</v>
+        <v>7.73779153823853</v>
       </c>
       <c r="H609" t="n">
         <v>85842</v>
@@ -18088,7 +18088,7 @@
         <v>8.00500011444092</v>
       </c>
       <c r="G611" t="n">
-        <v>7.76689910888672</v>
+        <v>7.76689958572388</v>
       </c>
       <c r="H611" t="n">
         <v>68292</v>
@@ -18175,7 +18175,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G614" t="n">
-        <v>7.73779201507568</v>
+        <v>7.73779153823853</v>
       </c>
       <c r="H614" t="n">
         <v>142315</v>
@@ -18204,7 +18204,7 @@
         <v>7.9850001335144</v>
       </c>
       <c r="G615" t="n">
-        <v>7.7474946975708</v>
+        <v>7.74749422073364</v>
       </c>
       <c r="H615" t="n">
         <v>116245</v>
@@ -18262,7 +18262,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G617" t="n">
-        <v>7.95609855651855</v>
+        <v>7.95609951019287</v>
       </c>
       <c r="H617" t="n">
         <v>208602</v>
@@ -18291,7 +18291,7 @@
         <v>8.14500045776367</v>
       </c>
       <c r="G618" t="n">
-        <v>7.90273571014404</v>
+        <v>7.90273523330688</v>
       </c>
       <c r="H618" t="n">
         <v>116291</v>
@@ -18320,7 +18320,7 @@
         <v>8.17500019073486</v>
       </c>
       <c r="G619" t="n">
-        <v>7.93184328079224</v>
+        <v>7.93184280395508</v>
       </c>
       <c r="H619" t="n">
         <v>91476</v>
@@ -18436,7 +18436,7 @@
         <v>7.67500019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>7.44671535491943</v>
+        <v>7.44671487808228</v>
       </c>
       <c r="H623" t="n">
         <v>226325</v>
@@ -18465,7 +18465,7 @@
         <v>7.64499998092651</v>
       </c>
       <c r="G624" t="n">
-        <v>7.41760730743408</v>
+        <v>7.41760683059692</v>
       </c>
       <c r="H624" t="n">
         <v>275750</v>
@@ -18494,7 +18494,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G625" t="n">
-        <v>7.41275548934937</v>
+        <v>7.41275596618652</v>
       </c>
       <c r="H625" t="n">
         <v>150786</v>
@@ -18581,7 +18581,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>7.31087875366211</v>
+        <v>7.31087923049927</v>
       </c>
       <c r="H628" t="n">
         <v>129823</v>
@@ -18668,7 +18668,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G631" t="n">
-        <v>7.53888893127441</v>
+        <v>7.53888940811157</v>
       </c>
       <c r="H631" t="n">
         <v>91913</v>
@@ -18697,7 +18697,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G632" t="n">
-        <v>7.42245817184448</v>
+        <v>7.42245864868164</v>
       </c>
       <c r="H632" t="n">
         <v>71179</v>
@@ -18726,7 +18726,7 @@
         <v>7.77500009536743</v>
       </c>
       <c r="G633" t="n">
-        <v>7.54374074935913</v>
+        <v>7.54374027252197</v>
       </c>
       <c r="H633" t="n">
         <v>104298</v>
@@ -18755,7 +18755,7 @@
         <v>7.875</v>
       </c>
       <c r="G634" t="n">
-        <v>7.64076614379883</v>
+        <v>7.64076566696167</v>
       </c>
       <c r="H634" t="n">
         <v>86228</v>
@@ -18842,7 +18842,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G637" t="n">
-        <v>7.05861234664917</v>
+        <v>7.05861282348633</v>
       </c>
       <c r="H637" t="n">
         <v>150003</v>
@@ -18900,7 +18900,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G639" t="n">
-        <v>6.84515619277954</v>
+        <v>6.84515571594238</v>
       </c>
       <c r="H639" t="n">
         <v>176664</v>
@@ -18958,7 +18958,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G641" t="n">
-        <v>6.98099184036255</v>
+        <v>6.98099231719971</v>
       </c>
       <c r="H641" t="n">
         <v>147248</v>
@@ -18987,7 +18987,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>7.17989492416382</v>
+        <v>7.17989444732666</v>
       </c>
       <c r="H642" t="n">
         <v>152913</v>
@@ -19277,7 +19277,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G652" t="n">
-        <v>6.96643781661987</v>
+        <v>6.96643829345703</v>
       </c>
       <c r="H652" t="n">
         <v>197817</v>
@@ -19306,7 +19306,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G653" t="n">
-        <v>6.78694105148315</v>
+        <v>6.786940574646</v>
       </c>
       <c r="H653" t="n">
         <v>219932</v>
@@ -19451,7 +19451,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G658" t="n">
-        <v>6.78694105148315</v>
+        <v>6.786940574646</v>
       </c>
       <c r="H658" t="n">
         <v>214637</v>
@@ -19596,7 +19596,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G663" t="n">
-        <v>6.67536115646362</v>
+        <v>6.67536163330078</v>
       </c>
       <c r="H663" t="n">
         <v>163183</v>
@@ -19654,7 +19654,7 @@
         <v>8.65499973297119</v>
       </c>
       <c r="G665" t="n">
-        <v>8.39756488800049</v>
+        <v>8.3975658416748</v>
       </c>
       <c r="H665" t="n">
         <v>1421609</v>
@@ -19683,7 +19683,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G666" t="n">
-        <v>8.19866371154785</v>
+        <v>8.19866275787354</v>
       </c>
       <c r="H666" t="n">
         <v>376186</v>
@@ -19712,7 +19712,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G667" t="n">
-        <v>8.52855110168457</v>
+        <v>8.52855014801025</v>
       </c>
       <c r="H667" t="n">
         <v>499509</v>
@@ -19828,7 +19828,7 @@
         <v>9.07499980926514</v>
       </c>
       <c r="G671" t="n">
-        <v>8.80507278442383</v>
+        <v>8.80507373809814</v>
       </c>
       <c r="H671" t="n">
         <v>162058</v>
@@ -19886,7 +19886,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G673" t="n">
-        <v>8.74200630187988</v>
+        <v>8.7420072555542</v>
       </c>
       <c r="H673" t="n">
         <v>106877</v>
@@ -20002,7 +20002,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>9.04763793945312</v>
+        <v>9.04763698577881</v>
       </c>
       <c r="H677" t="n">
         <v>120993</v>
@@ -20031,7 +20031,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G678" t="n">
-        <v>9.04763793945312</v>
+        <v>9.04763698577881</v>
       </c>
       <c r="H678" t="n">
         <v>114620</v>
@@ -20060,7 +20060,7 @@
         <v>9.21500015258789</v>
       </c>
       <c r="G679" t="n">
-        <v>8.94090938568115</v>
+        <v>8.94090843200684</v>
       </c>
       <c r="H679" t="n">
         <v>176536</v>
@@ -20263,7 +20263,7 @@
         <v>7.03499984741211</v>
       </c>
       <c r="G686" t="n">
-        <v>6.82575130462646</v>
+        <v>6.82575082778931</v>
       </c>
       <c r="H686" t="n">
         <v>2010202</v>
@@ -20321,7 +20321,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G688" t="n">
-        <v>6.44250011444092</v>
+        <v>6.44249963760376</v>
       </c>
       <c r="H688" t="n">
         <v>526066</v>
@@ -20350,7 +20350,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G689" t="n">
-        <v>6.66080760955811</v>
+        <v>6.66080713272095</v>
       </c>
       <c r="H689" t="n">
         <v>633433</v>
@@ -20379,7 +20379,7 @@
         <v>6.64499998092651</v>
       </c>
       <c r="G690" t="n">
-        <v>6.44735097885132</v>
+        <v>6.44735145568848</v>
       </c>
       <c r="H690" t="n">
         <v>435937</v>
@@ -20408,7 +20408,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G691" t="n">
-        <v>6.46190500259399</v>
+        <v>6.46190452575684</v>
       </c>
       <c r="H691" t="n">
         <v>314939</v>
@@ -20437,7 +20437,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>6.32606935501099</v>
+        <v>6.32606887817383</v>
       </c>
       <c r="H692" t="n">
         <v>246343</v>
@@ -20553,7 +20553,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G696" t="n">
-        <v>6.09805870056152</v>
+        <v>6.09805917739868</v>
       </c>
       <c r="H696" t="n">
         <v>426023</v>
@@ -20582,7 +20582,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G697" t="n">
-        <v>5.84094095230103</v>
+        <v>5.84094142913818</v>
       </c>
       <c r="H697" t="n">
         <v>433195</v>
@@ -20640,7 +20640,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G699" t="n">
-        <v>6.0107364654541</v>
+        <v>6.01073598861694</v>
       </c>
       <c r="H699" t="n">
         <v>258310</v>
@@ -20727,7 +20727,7 @@
         <v>6.35500001907349</v>
       </c>
       <c r="G702" t="n">
-        <v>6.16597700119019</v>
+        <v>6.16597652435303</v>
       </c>
       <c r="H702" t="n">
         <v>169235</v>
@@ -20756,7 +20756,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G703" t="n">
-        <v>6.07380294799805</v>
+        <v>6.07380247116089</v>
       </c>
       <c r="H703" t="n">
         <v>180300</v>
@@ -20814,7 +20814,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G705" t="n">
-        <v>5.97677707672119</v>
+        <v>5.97677659988403</v>
       </c>
       <c r="H705" t="n">
         <v>155044</v>
@@ -20930,7 +20930,7 @@
         <v>6.125</v>
       </c>
       <c r="G709" t="n">
-        <v>5.94281816482544</v>
+        <v>5.94281768798828</v>
       </c>
       <c r="H709" t="n">
         <v>221764</v>
@@ -21104,7 +21104,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G715" t="n">
-        <v>6.43279790878296</v>
+        <v>6.4327974319458</v>
       </c>
       <c r="H715" t="n">
         <v>116884</v>
@@ -21133,7 +21133,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G716" t="n">
-        <v>6.27755641937256</v>
+        <v>6.2775559425354</v>
       </c>
       <c r="H716" t="n">
         <v>222806</v>
@@ -21220,7 +21220,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G719" t="n">
-        <v>6.50071477890015</v>
+        <v>6.5007152557373</v>
       </c>
       <c r="H719" t="n">
         <v>144135</v>
@@ -21365,7 +21365,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G724" t="n">
-        <v>6.67536115646362</v>
+        <v>6.67536163330078</v>
       </c>
       <c r="H724" t="n">
         <v>775096</v>
@@ -32098,9 +32098,38 @@
         <v>5.60500001907349</v>
       </c>
       <c r="H1094" t="n">
-        <v>237833</v>
+        <v>243727</v>
       </c>
       <c r="I1094" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1095" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1095" t="n">
+        <v>5.63500022888184</v>
+      </c>
+      <c r="D1095" t="n">
+        <v>5.63500022888184</v>
+      </c>
+      <c r="E1095" t="n">
+        <v>5.40500020980835</v>
+      </c>
+      <c r="F1095" t="n">
+        <v>5.40500020980835</v>
+      </c>
+      <c r="G1095" t="n">
+        <v>5.40500020980835</v>
+      </c>
+      <c r="H1095" t="n">
+        <v>350143</v>
+      </c>
+      <c r="I1095" t="s">
         <v>9</v>
       </c>
     </row>
